--- a/D2B2_기획_문서/003_시스템_기획서/006_미션_시스템/Project_D2B2_시스템기획서_미션_시스템.xlsx
+++ b/D2B2_기획_문서/003_시스템_기획서/006_미션_시스템/Project_D2B2_시스템기획서_미션_시스템.xlsx
@@ -5,18 +5,19 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KGA\Desktop\Project_D2B2\d2b2\d2b2\D2B2_기획_문서\003_시스템_기획서\006_미션_시스템\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KGA\Desktop\Project_D2B2\d2b2\D2B2_기획_문서\003_시스템_기획서\006_미션_시스템\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12165" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12165" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="미션 시스템 기획서" sheetId="2" r:id="rId1"/>
     <sheet name="테이블 예시" sheetId="1" r:id="rId2"/>
     <sheet name="미션 트리거 예시" sheetId="3" r:id="rId3"/>
     <sheet name="튜토리얼 이미지" sheetId="5" r:id="rId4"/>
-    <sheet name="1챕터 미션&amp;트리거" sheetId="4" r:id="rId5"/>
+    <sheet name="튜토리얼 미션&amp;트리거" sheetId="6" r:id="rId5"/>
+    <sheet name="1챕터 미션&amp;트리거" sheetId="4" r:id="rId6"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="237">
   <si>
     <t>챕터</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -861,6 +862,101 @@
   </si>
   <si>
     <t>NPC를 선택하거나 선택 취소 할 수 있도록 유도한다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>작성자 김준성</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>미션 시스템 - 1챕터</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>미션 시스템 - 튜토리얼</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>목차</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>챕터 목표</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>전체 미션 흐름</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>개별 미션 상세</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>챕터 목표</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>VR게임의 조작법과 상호작용에 익숙해지도록 플레이어를 유도함</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>보행 교육에 앞서 이 게임에서 사용될 기본 입력 및 반응 구조에 대한 학습</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>교육 목표 동작 및 상호작용</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>i</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>이동(Arm Swing Locomotion기반 이동)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ii</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>정지(Arm Swing Locomotion기반 이동)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>iii</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>시선 돌리기</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>iv</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>손 들기</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>v</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Controller Ray로 오브젝트 선택/상호작용</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>자신의 신체 조건에 맞는 플레이 환경을 구축</t>
+  </si>
+  <si>
+    <t>챕터에서 사용될 계정을 생성</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>전체 미션 흐름</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1127,6 +1223,12 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1134,15 +1236,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1163,11 +1256,14 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1187,10 +1283,10 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1928,97 +2024,97 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="11" t="s">
         <v>191</v>
       </c>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
-      <c r="K2" s="10"/>
-      <c r="L2" s="10"/>
-      <c r="M2" s="10"/>
-      <c r="N2" s="10"/>
-      <c r="O2" s="10"/>
-      <c r="P2" s="10"/>
-      <c r="Q2" s="10"/>
-      <c r="R2" s="10"/>
-      <c r="S2" s="10"/>
-      <c r="T2" s="10"/>
-      <c r="U2" s="10"/>
-      <c r="V2" s="10"/>
-      <c r="W2" s="10"/>
-      <c r="X2" s="10"/>
-      <c r="Y2" s="10"/>
-      <c r="Z2" s="11"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="12"/>
+      <c r="J2" s="12"/>
+      <c r="K2" s="12"/>
+      <c r="L2" s="12"/>
+      <c r="M2" s="12"/>
+      <c r="N2" s="12"/>
+      <c r="O2" s="12"/>
+      <c r="P2" s="12"/>
+      <c r="Q2" s="12"/>
+      <c r="R2" s="12"/>
+      <c r="S2" s="12"/>
+      <c r="T2" s="12"/>
+      <c r="U2" s="12"/>
+      <c r="V2" s="12"/>
+      <c r="W2" s="12"/>
+      <c r="X2" s="12"/>
+      <c r="Y2" s="12"/>
+      <c r="Z2" s="13"/>
     </row>
     <row r="3" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B3" s="12"/>
-      <c r="C3" s="13"/>
-      <c r="D3" s="13"/>
-      <c r="E3" s="13"/>
-      <c r="F3" s="13"/>
-      <c r="G3" s="13"/>
-      <c r="H3" s="13"/>
-      <c r="I3" s="13"/>
-      <c r="J3" s="13"/>
-      <c r="K3" s="13"/>
-      <c r="L3" s="13"/>
-      <c r="M3" s="13"/>
-      <c r="N3" s="13"/>
-      <c r="O3" s="13"/>
-      <c r="P3" s="13"/>
-      <c r="Q3" s="13"/>
-      <c r="R3" s="13"/>
-      <c r="S3" s="13"/>
-      <c r="T3" s="13"/>
-      <c r="U3" s="13"/>
-      <c r="V3" s="13"/>
-      <c r="W3" s="13"/>
-      <c r="X3" s="13"/>
-      <c r="Y3" s="13"/>
-      <c r="Z3" s="14"/>
+      <c r="B3" s="20"/>
+      <c r="C3" s="21"/>
+      <c r="D3" s="21"/>
+      <c r="E3" s="21"/>
+      <c r="F3" s="21"/>
+      <c r="G3" s="21"/>
+      <c r="H3" s="21"/>
+      <c r="I3" s="21"/>
+      <c r="J3" s="21"/>
+      <c r="K3" s="21"/>
+      <c r="L3" s="21"/>
+      <c r="M3" s="21"/>
+      <c r="N3" s="21"/>
+      <c r="O3" s="21"/>
+      <c r="P3" s="21"/>
+      <c r="Q3" s="21"/>
+      <c r="R3" s="21"/>
+      <c r="S3" s="21"/>
+      <c r="T3" s="21"/>
+      <c r="U3" s="21"/>
+      <c r="V3" s="21"/>
+      <c r="W3" s="21"/>
+      <c r="X3" s="21"/>
+      <c r="Y3" s="21"/>
+      <c r="Z3" s="22"/>
     </row>
     <row r="4" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B4" s="15"/>
-      <c r="C4" s="16"/>
-      <c r="D4" s="16"/>
-      <c r="E4" s="16"/>
-      <c r="F4" s="16"/>
-      <c r="G4" s="16"/>
-      <c r="H4" s="16"/>
-      <c r="I4" s="16"/>
-      <c r="J4" s="16"/>
-      <c r="K4" s="16"/>
-      <c r="L4" s="16"/>
-      <c r="M4" s="16"/>
-      <c r="N4" s="16"/>
-      <c r="O4" s="16"/>
-      <c r="P4" s="16"/>
-      <c r="Q4" s="16"/>
-      <c r="R4" s="16"/>
-      <c r="S4" s="16"/>
-      <c r="T4" s="16"/>
-      <c r="U4" s="16"/>
-      <c r="V4" s="16"/>
-      <c r="W4" s="16"/>
-      <c r="X4" s="16"/>
-      <c r="Y4" s="16"/>
-      <c r="Z4" s="17"/>
+      <c r="B4" s="14"/>
+      <c r="C4" s="15"/>
+      <c r="D4" s="15"/>
+      <c r="E4" s="15"/>
+      <c r="F4" s="15"/>
+      <c r="G4" s="15"/>
+      <c r="H4" s="15"/>
+      <c r="I4" s="15"/>
+      <c r="J4" s="15"/>
+      <c r="K4" s="15"/>
+      <c r="L4" s="15"/>
+      <c r="M4" s="15"/>
+      <c r="N4" s="15"/>
+      <c r="O4" s="15"/>
+      <c r="P4" s="15"/>
+      <c r="Q4" s="15"/>
+      <c r="R4" s="15"/>
+      <c r="S4" s="15"/>
+      <c r="T4" s="15"/>
+      <c r="U4" s="15"/>
+      <c r="V4" s="15"/>
+      <c r="W4" s="15"/>
+      <c r="X4" s="15"/>
+      <c r="Y4" s="15"/>
+      <c r="Z4" s="16"/>
     </row>
     <row r="6" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="U6" s="18" t="s">
+      <c r="U6" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="V6" s="19"/>
-      <c r="W6" s="19"/>
-      <c r="X6" s="19"/>
-      <c r="Y6" s="19"/>
-      <c r="Z6" s="20"/>
+      <c r="V6" s="18"/>
+      <c r="W6" s="18"/>
+      <c r="X6" s="18"/>
+      <c r="Y6" s="18"/>
+      <c r="Z6" s="19"/>
     </row>
     <row r="8" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B8" s="2">
@@ -2069,58 +2165,58 @@
       </c>
     </row>
     <row r="45" spans="3:26" x14ac:dyDescent="0.3">
-      <c r="C45" s="9" t="s">
+      <c r="C45" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="D45" s="10"/>
-      <c r="E45" s="10"/>
-      <c r="F45" s="10"/>
-      <c r="G45" s="10"/>
-      <c r="H45" s="10"/>
-      <c r="I45" s="10"/>
-      <c r="J45" s="10"/>
-      <c r="K45" s="10"/>
-      <c r="L45" s="10"/>
-      <c r="M45" s="10"/>
-      <c r="N45" s="10"/>
-      <c r="O45" s="10"/>
-      <c r="P45" s="10"/>
-      <c r="Q45" s="10"/>
-      <c r="R45" s="10"/>
-      <c r="S45" s="10"/>
-      <c r="T45" s="10"/>
-      <c r="U45" s="10"/>
-      <c r="V45" s="10"/>
-      <c r="W45" s="10"/>
-      <c r="X45" s="10"/>
-      <c r="Y45" s="10"/>
-      <c r="Z45" s="11"/>
+      <c r="D45" s="12"/>
+      <c r="E45" s="12"/>
+      <c r="F45" s="12"/>
+      <c r="G45" s="12"/>
+      <c r="H45" s="12"/>
+      <c r="I45" s="12"/>
+      <c r="J45" s="12"/>
+      <c r="K45" s="12"/>
+      <c r="L45" s="12"/>
+      <c r="M45" s="12"/>
+      <c r="N45" s="12"/>
+      <c r="O45" s="12"/>
+      <c r="P45" s="12"/>
+      <c r="Q45" s="12"/>
+      <c r="R45" s="12"/>
+      <c r="S45" s="12"/>
+      <c r="T45" s="12"/>
+      <c r="U45" s="12"/>
+      <c r="V45" s="12"/>
+      <c r="W45" s="12"/>
+      <c r="X45" s="12"/>
+      <c r="Y45" s="12"/>
+      <c r="Z45" s="13"/>
     </row>
     <row r="46" spans="3:26" x14ac:dyDescent="0.3">
-      <c r="C46" s="15"/>
-      <c r="D46" s="16"/>
-      <c r="E46" s="16"/>
-      <c r="F46" s="16"/>
-      <c r="G46" s="16"/>
-      <c r="H46" s="16"/>
-      <c r="I46" s="16"/>
-      <c r="J46" s="16"/>
-      <c r="K46" s="16"/>
-      <c r="L46" s="16"/>
-      <c r="M46" s="16"/>
-      <c r="N46" s="16"/>
-      <c r="O46" s="16"/>
-      <c r="P46" s="16"/>
-      <c r="Q46" s="16"/>
-      <c r="R46" s="16"/>
-      <c r="S46" s="16"/>
-      <c r="T46" s="16"/>
-      <c r="U46" s="16"/>
-      <c r="V46" s="16"/>
-      <c r="W46" s="16"/>
-      <c r="X46" s="16"/>
-      <c r="Y46" s="16"/>
-      <c r="Z46" s="17"/>
+      <c r="C46" s="14"/>
+      <c r="D46" s="15"/>
+      <c r="E46" s="15"/>
+      <c r="F46" s="15"/>
+      <c r="G46" s="15"/>
+      <c r="H46" s="15"/>
+      <c r="I46" s="15"/>
+      <c r="J46" s="15"/>
+      <c r="K46" s="15"/>
+      <c r="L46" s="15"/>
+      <c r="M46" s="15"/>
+      <c r="N46" s="15"/>
+      <c r="O46" s="15"/>
+      <c r="P46" s="15"/>
+      <c r="Q46" s="15"/>
+      <c r="R46" s="15"/>
+      <c r="S46" s="15"/>
+      <c r="T46" s="15"/>
+      <c r="U46" s="15"/>
+      <c r="V46" s="15"/>
+      <c r="W46" s="15"/>
+      <c r="X46" s="15"/>
+      <c r="Y46" s="15"/>
+      <c r="Z46" s="16"/>
     </row>
     <row r="48" spans="3:26" x14ac:dyDescent="0.3">
       <c r="D48" s="2" t="s">
@@ -2153,58 +2249,58 @@
       </c>
     </row>
     <row r="56" spans="3:26" x14ac:dyDescent="0.3">
-      <c r="C56" s="9" t="s">
+      <c r="C56" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="D56" s="10"/>
-      <c r="E56" s="10"/>
-      <c r="F56" s="10"/>
-      <c r="G56" s="10"/>
-      <c r="H56" s="10"/>
-      <c r="I56" s="10"/>
-      <c r="J56" s="10"/>
-      <c r="K56" s="10"/>
-      <c r="L56" s="10"/>
-      <c r="M56" s="10"/>
-      <c r="N56" s="10"/>
-      <c r="O56" s="10"/>
-      <c r="P56" s="10"/>
-      <c r="Q56" s="10"/>
-      <c r="R56" s="10"/>
-      <c r="S56" s="10"/>
-      <c r="T56" s="10"/>
-      <c r="U56" s="10"/>
-      <c r="V56" s="10"/>
-      <c r="W56" s="10"/>
-      <c r="X56" s="10"/>
-      <c r="Y56" s="10"/>
-      <c r="Z56" s="11"/>
+      <c r="D56" s="12"/>
+      <c r="E56" s="12"/>
+      <c r="F56" s="12"/>
+      <c r="G56" s="12"/>
+      <c r="H56" s="12"/>
+      <c r="I56" s="12"/>
+      <c r="J56" s="12"/>
+      <c r="K56" s="12"/>
+      <c r="L56" s="12"/>
+      <c r="M56" s="12"/>
+      <c r="N56" s="12"/>
+      <c r="O56" s="12"/>
+      <c r="P56" s="12"/>
+      <c r="Q56" s="12"/>
+      <c r="R56" s="12"/>
+      <c r="S56" s="12"/>
+      <c r="T56" s="12"/>
+      <c r="U56" s="12"/>
+      <c r="V56" s="12"/>
+      <c r="W56" s="12"/>
+      <c r="X56" s="12"/>
+      <c r="Y56" s="12"/>
+      <c r="Z56" s="13"/>
     </row>
     <row r="57" spans="3:26" x14ac:dyDescent="0.3">
-      <c r="C57" s="15"/>
-      <c r="D57" s="16"/>
-      <c r="E57" s="16"/>
-      <c r="F57" s="16"/>
-      <c r="G57" s="16"/>
-      <c r="H57" s="16"/>
-      <c r="I57" s="16"/>
-      <c r="J57" s="16"/>
-      <c r="K57" s="16"/>
-      <c r="L57" s="16"/>
-      <c r="M57" s="16"/>
-      <c r="N57" s="16"/>
-      <c r="O57" s="16"/>
-      <c r="P57" s="16"/>
-      <c r="Q57" s="16"/>
-      <c r="R57" s="16"/>
-      <c r="S57" s="16"/>
-      <c r="T57" s="16"/>
-      <c r="U57" s="16"/>
-      <c r="V57" s="16"/>
-      <c r="W57" s="16"/>
-      <c r="X57" s="16"/>
-      <c r="Y57" s="16"/>
-      <c r="Z57" s="17"/>
+      <c r="C57" s="14"/>
+      <c r="D57" s="15"/>
+      <c r="E57" s="15"/>
+      <c r="F57" s="15"/>
+      <c r="G57" s="15"/>
+      <c r="H57" s="15"/>
+      <c r="I57" s="15"/>
+      <c r="J57" s="15"/>
+      <c r="K57" s="15"/>
+      <c r="L57" s="15"/>
+      <c r="M57" s="15"/>
+      <c r="N57" s="15"/>
+      <c r="O57" s="15"/>
+      <c r="P57" s="15"/>
+      <c r="Q57" s="15"/>
+      <c r="R57" s="15"/>
+      <c r="S57" s="15"/>
+      <c r="T57" s="15"/>
+      <c r="U57" s="15"/>
+      <c r="V57" s="15"/>
+      <c r="W57" s="15"/>
+      <c r="X57" s="15"/>
+      <c r="Y57" s="15"/>
+      <c r="Z57" s="16"/>
     </row>
     <row r="59" spans="3:26" x14ac:dyDescent="0.3">
       <c r="D59" s="2" t="s">
@@ -2237,58 +2333,58 @@
       </c>
     </row>
     <row r="68" spans="3:26" x14ac:dyDescent="0.3">
-      <c r="C68" s="9" t="s">
+      <c r="C68" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="D68" s="10"/>
-      <c r="E68" s="10"/>
-      <c r="F68" s="10"/>
-      <c r="G68" s="10"/>
-      <c r="H68" s="10"/>
-      <c r="I68" s="10"/>
-      <c r="J68" s="10"/>
-      <c r="K68" s="10"/>
-      <c r="L68" s="10"/>
-      <c r="M68" s="10"/>
-      <c r="N68" s="10"/>
-      <c r="O68" s="10"/>
-      <c r="P68" s="10"/>
-      <c r="Q68" s="10"/>
-      <c r="R68" s="10"/>
-      <c r="S68" s="10"/>
-      <c r="T68" s="10"/>
-      <c r="U68" s="10"/>
-      <c r="V68" s="10"/>
-      <c r="W68" s="10"/>
-      <c r="X68" s="10"/>
-      <c r="Y68" s="10"/>
-      <c r="Z68" s="11"/>
+      <c r="D68" s="12"/>
+      <c r="E68" s="12"/>
+      <c r="F68" s="12"/>
+      <c r="G68" s="12"/>
+      <c r="H68" s="12"/>
+      <c r="I68" s="12"/>
+      <c r="J68" s="12"/>
+      <c r="K68" s="12"/>
+      <c r="L68" s="12"/>
+      <c r="M68" s="12"/>
+      <c r="N68" s="12"/>
+      <c r="O68" s="12"/>
+      <c r="P68" s="12"/>
+      <c r="Q68" s="12"/>
+      <c r="R68" s="12"/>
+      <c r="S68" s="12"/>
+      <c r="T68" s="12"/>
+      <c r="U68" s="12"/>
+      <c r="V68" s="12"/>
+      <c r="W68" s="12"/>
+      <c r="X68" s="12"/>
+      <c r="Y68" s="12"/>
+      <c r="Z68" s="13"/>
     </row>
     <row r="69" spans="3:26" x14ac:dyDescent="0.3">
-      <c r="C69" s="15"/>
-      <c r="D69" s="16"/>
-      <c r="E69" s="16"/>
-      <c r="F69" s="16"/>
-      <c r="G69" s="16"/>
-      <c r="H69" s="16"/>
-      <c r="I69" s="16"/>
-      <c r="J69" s="16"/>
-      <c r="K69" s="16"/>
-      <c r="L69" s="16"/>
-      <c r="M69" s="16"/>
-      <c r="N69" s="16"/>
-      <c r="O69" s="16"/>
-      <c r="P69" s="16"/>
-      <c r="Q69" s="16"/>
-      <c r="R69" s="16"/>
-      <c r="S69" s="16"/>
-      <c r="T69" s="16"/>
-      <c r="U69" s="16"/>
-      <c r="V69" s="16"/>
-      <c r="W69" s="16"/>
-      <c r="X69" s="16"/>
-      <c r="Y69" s="16"/>
-      <c r="Z69" s="17"/>
+      <c r="C69" s="14"/>
+      <c r="D69" s="15"/>
+      <c r="E69" s="15"/>
+      <c r="F69" s="15"/>
+      <c r="G69" s="15"/>
+      <c r="H69" s="15"/>
+      <c r="I69" s="15"/>
+      <c r="J69" s="15"/>
+      <c r="K69" s="15"/>
+      <c r="L69" s="15"/>
+      <c r="M69" s="15"/>
+      <c r="N69" s="15"/>
+      <c r="O69" s="15"/>
+      <c r="P69" s="15"/>
+      <c r="Q69" s="15"/>
+      <c r="R69" s="15"/>
+      <c r="S69" s="15"/>
+      <c r="T69" s="15"/>
+      <c r="U69" s="15"/>
+      <c r="V69" s="15"/>
+      <c r="W69" s="15"/>
+      <c r="X69" s="15"/>
+      <c r="Y69" s="15"/>
+      <c r="Z69" s="16"/>
     </row>
     <row r="71" spans="3:26" x14ac:dyDescent="0.3">
       <c r="D71" s="2" t="s">
@@ -2526,58 +2622,58 @@
       </c>
     </row>
     <row r="101" spans="3:26" x14ac:dyDescent="0.3">
-      <c r="C101" s="9" t="s">
+      <c r="C101" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="D101" s="10"/>
-      <c r="E101" s="10"/>
-      <c r="F101" s="10"/>
-      <c r="G101" s="10"/>
-      <c r="H101" s="10"/>
-      <c r="I101" s="10"/>
-      <c r="J101" s="10"/>
-      <c r="K101" s="10"/>
-      <c r="L101" s="10"/>
-      <c r="M101" s="10"/>
-      <c r="N101" s="10"/>
-      <c r="O101" s="10"/>
-      <c r="P101" s="10"/>
-      <c r="Q101" s="10"/>
-      <c r="R101" s="10"/>
-      <c r="S101" s="10"/>
-      <c r="T101" s="10"/>
-      <c r="U101" s="10"/>
-      <c r="V101" s="10"/>
-      <c r="W101" s="10"/>
-      <c r="X101" s="10"/>
-      <c r="Y101" s="10"/>
-      <c r="Z101" s="11"/>
+      <c r="D101" s="12"/>
+      <c r="E101" s="12"/>
+      <c r="F101" s="12"/>
+      <c r="G101" s="12"/>
+      <c r="H101" s="12"/>
+      <c r="I101" s="12"/>
+      <c r="J101" s="12"/>
+      <c r="K101" s="12"/>
+      <c r="L101" s="12"/>
+      <c r="M101" s="12"/>
+      <c r="N101" s="12"/>
+      <c r="O101" s="12"/>
+      <c r="P101" s="12"/>
+      <c r="Q101" s="12"/>
+      <c r="R101" s="12"/>
+      <c r="S101" s="12"/>
+      <c r="T101" s="12"/>
+      <c r="U101" s="12"/>
+      <c r="V101" s="12"/>
+      <c r="W101" s="12"/>
+      <c r="X101" s="12"/>
+      <c r="Y101" s="12"/>
+      <c r="Z101" s="13"/>
     </row>
     <row r="102" spans="3:26" x14ac:dyDescent="0.3">
-      <c r="C102" s="15"/>
-      <c r="D102" s="16"/>
-      <c r="E102" s="16"/>
-      <c r="F102" s="16"/>
-      <c r="G102" s="16"/>
-      <c r="H102" s="16"/>
-      <c r="I102" s="16"/>
-      <c r="J102" s="16"/>
-      <c r="K102" s="16"/>
-      <c r="L102" s="16"/>
-      <c r="M102" s="16"/>
-      <c r="N102" s="16"/>
-      <c r="O102" s="16"/>
-      <c r="P102" s="16"/>
-      <c r="Q102" s="16"/>
-      <c r="R102" s="16"/>
-      <c r="S102" s="16"/>
-      <c r="T102" s="16"/>
-      <c r="U102" s="16"/>
-      <c r="V102" s="16"/>
-      <c r="W102" s="16"/>
-      <c r="X102" s="16"/>
-      <c r="Y102" s="16"/>
-      <c r="Z102" s="17"/>
+      <c r="C102" s="14"/>
+      <c r="D102" s="15"/>
+      <c r="E102" s="15"/>
+      <c r="F102" s="15"/>
+      <c r="G102" s="15"/>
+      <c r="H102" s="15"/>
+      <c r="I102" s="15"/>
+      <c r="J102" s="15"/>
+      <c r="K102" s="15"/>
+      <c r="L102" s="15"/>
+      <c r="M102" s="15"/>
+      <c r="N102" s="15"/>
+      <c r="O102" s="15"/>
+      <c r="P102" s="15"/>
+      <c r="Q102" s="15"/>
+      <c r="R102" s="15"/>
+      <c r="S102" s="15"/>
+      <c r="T102" s="15"/>
+      <c r="U102" s="15"/>
+      <c r="V102" s="15"/>
+      <c r="W102" s="15"/>
+      <c r="X102" s="15"/>
+      <c r="Y102" s="15"/>
+      <c r="Z102" s="16"/>
     </row>
     <row r="104" spans="3:26" x14ac:dyDescent="0.3">
       <c r="D104" s="2" t="s">
@@ -2611,212 +2707,212 @@
       <c r="X106" s="8"/>
     </row>
     <row r="107" spans="3:26" x14ac:dyDescent="0.3">
-      <c r="E107" s="21" t="s">
+      <c r="E107" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="F107" s="21"/>
-      <c r="G107" s="21"/>
-      <c r="H107" s="21"/>
-      <c r="I107" s="21"/>
-      <c r="J107" s="21"/>
-      <c r="K107" s="21" t="s">
+      <c r="F107" s="9"/>
+      <c r="G107" s="9"/>
+      <c r="H107" s="9"/>
+      <c r="I107" s="9"/>
+      <c r="J107" s="9"/>
+      <c r="K107" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="L107" s="21"/>
-      <c r="M107" s="21"/>
-      <c r="N107" s="21"/>
-      <c r="O107" s="21"/>
-      <c r="P107" s="21"/>
-      <c r="Q107" s="21"/>
-      <c r="R107" s="21"/>
-      <c r="S107" s="21"/>
-      <c r="T107" s="21"/>
-      <c r="U107" s="21"/>
-      <c r="V107" s="21"/>
-      <c r="W107" s="21"/>
-      <c r="X107" s="21"/>
+      <c r="L107" s="9"/>
+      <c r="M107" s="9"/>
+      <c r="N107" s="9"/>
+      <c r="O107" s="9"/>
+      <c r="P107" s="9"/>
+      <c r="Q107" s="9"/>
+      <c r="R107" s="9"/>
+      <c r="S107" s="9"/>
+      <c r="T107" s="9"/>
+      <c r="U107" s="9"/>
+      <c r="V107" s="9"/>
+      <c r="W107" s="9"/>
+      <c r="X107" s="9"/>
     </row>
     <row r="108" spans="3:26" x14ac:dyDescent="0.3">
-      <c r="E108" s="21" t="s">
+      <c r="E108" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="F108" s="21"/>
-      <c r="G108" s="21"/>
-      <c r="H108" s="21"/>
-      <c r="I108" s="21"/>
-      <c r="J108" s="21"/>
-      <c r="K108" s="21" t="s">
+      <c r="F108" s="9"/>
+      <c r="G108" s="9"/>
+      <c r="H108" s="9"/>
+      <c r="I108" s="9"/>
+      <c r="J108" s="9"/>
+      <c r="K108" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="L108" s="21"/>
-      <c r="M108" s="21"/>
-      <c r="N108" s="21"/>
-      <c r="O108" s="21"/>
-      <c r="P108" s="21"/>
-      <c r="Q108" s="21"/>
-      <c r="R108" s="21"/>
-      <c r="S108" s="21"/>
-      <c r="T108" s="21"/>
-      <c r="U108" s="21"/>
-      <c r="V108" s="21"/>
-      <c r="W108" s="21"/>
-      <c r="X108" s="21"/>
+      <c r="L108" s="9"/>
+      <c r="M108" s="9"/>
+      <c r="N108" s="9"/>
+      <c r="O108" s="9"/>
+      <c r="P108" s="9"/>
+      <c r="Q108" s="9"/>
+      <c r="R108" s="9"/>
+      <c r="S108" s="9"/>
+      <c r="T108" s="9"/>
+      <c r="U108" s="9"/>
+      <c r="V108" s="9"/>
+      <c r="W108" s="9"/>
+      <c r="X108" s="9"/>
     </row>
     <row r="109" spans="3:26" x14ac:dyDescent="0.3">
-      <c r="E109" s="21" t="s">
+      <c r="E109" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="F109" s="21"/>
-      <c r="G109" s="21"/>
-      <c r="H109" s="21"/>
-      <c r="I109" s="21"/>
-      <c r="J109" s="21"/>
-      <c r="K109" s="21" t="s">
+      <c r="F109" s="9"/>
+      <c r="G109" s="9"/>
+      <c r="H109" s="9"/>
+      <c r="I109" s="9"/>
+      <c r="J109" s="9"/>
+      <c r="K109" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="L109" s="21"/>
-      <c r="M109" s="21"/>
-      <c r="N109" s="21"/>
-      <c r="O109" s="21"/>
-      <c r="P109" s="21"/>
-      <c r="Q109" s="21"/>
-      <c r="R109" s="21"/>
-      <c r="S109" s="21"/>
-      <c r="T109" s="21"/>
-      <c r="U109" s="21"/>
-      <c r="V109" s="21"/>
-      <c r="W109" s="21"/>
-      <c r="X109" s="21"/>
+      <c r="L109" s="9"/>
+      <c r="M109" s="9"/>
+      <c r="N109" s="9"/>
+      <c r="O109" s="9"/>
+      <c r="P109" s="9"/>
+      <c r="Q109" s="9"/>
+      <c r="R109" s="9"/>
+      <c r="S109" s="9"/>
+      <c r="T109" s="9"/>
+      <c r="U109" s="9"/>
+      <c r="V109" s="9"/>
+      <c r="W109" s="9"/>
+      <c r="X109" s="9"/>
     </row>
     <row r="110" spans="3:26" x14ac:dyDescent="0.3">
-      <c r="E110" s="21" t="s">
+      <c r="E110" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="F110" s="21"/>
-      <c r="G110" s="21"/>
-      <c r="H110" s="21"/>
-      <c r="I110" s="21"/>
-      <c r="J110" s="21"/>
-      <c r="K110" s="21" t="s">
+      <c r="F110" s="9"/>
+      <c r="G110" s="9"/>
+      <c r="H110" s="9"/>
+      <c r="I110" s="9"/>
+      <c r="J110" s="9"/>
+      <c r="K110" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="L110" s="21"/>
-      <c r="M110" s="21"/>
-      <c r="N110" s="21"/>
-      <c r="O110" s="21"/>
-      <c r="P110" s="21"/>
-      <c r="Q110" s="21"/>
-      <c r="R110" s="21"/>
-      <c r="S110" s="21"/>
-      <c r="T110" s="21"/>
-      <c r="U110" s="21"/>
-      <c r="V110" s="21"/>
-      <c r="W110" s="21"/>
-      <c r="X110" s="21"/>
+      <c r="L110" s="9"/>
+      <c r="M110" s="9"/>
+      <c r="N110" s="9"/>
+      <c r="O110" s="9"/>
+      <c r="P110" s="9"/>
+      <c r="Q110" s="9"/>
+      <c r="R110" s="9"/>
+      <c r="S110" s="9"/>
+      <c r="T110" s="9"/>
+      <c r="U110" s="9"/>
+      <c r="V110" s="9"/>
+      <c r="W110" s="9"/>
+      <c r="X110" s="9"/>
     </row>
     <row r="111" spans="3:26" x14ac:dyDescent="0.3">
-      <c r="E111" s="21" t="s">
+      <c r="E111" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="F111" s="21"/>
-      <c r="G111" s="21"/>
-      <c r="H111" s="21"/>
-      <c r="I111" s="21"/>
-      <c r="J111" s="21"/>
-      <c r="K111" s="21" t="s">
+      <c r="F111" s="9"/>
+      <c r="G111" s="9"/>
+      <c r="H111" s="9"/>
+      <c r="I111" s="9"/>
+      <c r="J111" s="9"/>
+      <c r="K111" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="L111" s="21"/>
-      <c r="M111" s="21"/>
-      <c r="N111" s="21"/>
-      <c r="O111" s="21"/>
-      <c r="P111" s="21"/>
-      <c r="Q111" s="21"/>
-      <c r="R111" s="21"/>
-      <c r="S111" s="21"/>
-      <c r="T111" s="21"/>
-      <c r="U111" s="21"/>
-      <c r="V111" s="21"/>
-      <c r="W111" s="21"/>
-      <c r="X111" s="21"/>
+      <c r="L111" s="9"/>
+      <c r="M111" s="9"/>
+      <c r="N111" s="9"/>
+      <c r="O111" s="9"/>
+      <c r="P111" s="9"/>
+      <c r="Q111" s="9"/>
+      <c r="R111" s="9"/>
+      <c r="S111" s="9"/>
+      <c r="T111" s="9"/>
+      <c r="U111" s="9"/>
+      <c r="V111" s="9"/>
+      <c r="W111" s="9"/>
+      <c r="X111" s="9"/>
     </row>
     <row r="112" spans="3:26" x14ac:dyDescent="0.3">
-      <c r="E112" s="21" t="s">
+      <c r="E112" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="F112" s="21"/>
-      <c r="G112" s="21"/>
-      <c r="H112" s="21"/>
-      <c r="I112" s="21"/>
-      <c r="J112" s="21"/>
-      <c r="K112" s="21" t="s">
+      <c r="F112" s="9"/>
+      <c r="G112" s="9"/>
+      <c r="H112" s="9"/>
+      <c r="I112" s="9"/>
+      <c r="J112" s="9"/>
+      <c r="K112" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="L112" s="21"/>
-      <c r="M112" s="21"/>
-      <c r="N112" s="21"/>
-      <c r="O112" s="21"/>
-      <c r="P112" s="21"/>
-      <c r="Q112" s="21"/>
-      <c r="R112" s="21"/>
-      <c r="S112" s="21"/>
-      <c r="T112" s="21"/>
-      <c r="U112" s="21"/>
-      <c r="V112" s="21"/>
-      <c r="W112" s="21"/>
-      <c r="X112" s="21"/>
+      <c r="L112" s="9"/>
+      <c r="M112" s="9"/>
+      <c r="N112" s="9"/>
+      <c r="O112" s="9"/>
+      <c r="P112" s="9"/>
+      <c r="Q112" s="9"/>
+      <c r="R112" s="9"/>
+      <c r="S112" s="9"/>
+      <c r="T112" s="9"/>
+      <c r="U112" s="9"/>
+      <c r="V112" s="9"/>
+      <c r="W112" s="9"/>
+      <c r="X112" s="9"/>
     </row>
     <row r="113" spans="4:25" x14ac:dyDescent="0.3">
-      <c r="E113" s="21" t="s">
+      <c r="E113" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="F113" s="21"/>
-      <c r="G113" s="21"/>
-      <c r="H113" s="21"/>
-      <c r="I113" s="21"/>
-      <c r="J113" s="21"/>
-      <c r="K113" s="21" t="s">
+      <c r="F113" s="9"/>
+      <c r="G113" s="9"/>
+      <c r="H113" s="9"/>
+      <c r="I113" s="9"/>
+      <c r="J113" s="9"/>
+      <c r="K113" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="L113" s="21"/>
-      <c r="M113" s="21"/>
-      <c r="N113" s="21"/>
-      <c r="O113" s="21"/>
-      <c r="P113" s="21"/>
-      <c r="Q113" s="21"/>
-      <c r="R113" s="21"/>
-      <c r="S113" s="21"/>
-      <c r="T113" s="21"/>
-      <c r="U113" s="21"/>
-      <c r="V113" s="21"/>
-      <c r="W113" s="21"/>
-      <c r="X113" s="21"/>
+      <c r="L113" s="9"/>
+      <c r="M113" s="9"/>
+      <c r="N113" s="9"/>
+      <c r="O113" s="9"/>
+      <c r="P113" s="9"/>
+      <c r="Q113" s="9"/>
+      <c r="R113" s="9"/>
+      <c r="S113" s="9"/>
+      <c r="T113" s="9"/>
+      <c r="U113" s="9"/>
+      <c r="V113" s="9"/>
+      <c r="W113" s="9"/>
+      <c r="X113" s="9"/>
     </row>
     <row r="114" spans="4:25" x14ac:dyDescent="0.3">
-      <c r="E114" s="21" t="s">
+      <c r="E114" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="F114" s="21"/>
-      <c r="G114" s="21"/>
-      <c r="H114" s="21"/>
-      <c r="I114" s="21"/>
-      <c r="J114" s="21"/>
-      <c r="K114" s="21" t="s">
+      <c r="F114" s="9"/>
+      <c r="G114" s="9"/>
+      <c r="H114" s="9"/>
+      <c r="I114" s="9"/>
+      <c r="J114" s="9"/>
+      <c r="K114" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="L114" s="21"/>
-      <c r="M114" s="21"/>
-      <c r="N114" s="21"/>
-      <c r="O114" s="21"/>
-      <c r="P114" s="21"/>
-      <c r="Q114" s="21"/>
-      <c r="R114" s="21"/>
-      <c r="S114" s="21"/>
-      <c r="T114" s="21"/>
-      <c r="U114" s="21"/>
-      <c r="V114" s="21"/>
-      <c r="W114" s="21"/>
-      <c r="X114" s="21"/>
+      <c r="L114" s="9"/>
+      <c r="M114" s="9"/>
+      <c r="N114" s="9"/>
+      <c r="O114" s="9"/>
+      <c r="P114" s="9"/>
+      <c r="Q114" s="9"/>
+      <c r="R114" s="9"/>
+      <c r="S114" s="9"/>
+      <c r="T114" s="9"/>
+      <c r="U114" s="9"/>
+      <c r="V114" s="9"/>
+      <c r="W114" s="9"/>
+      <c r="X114" s="9"/>
     </row>
     <row r="116" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D116" s="2" t="s">
@@ -2844,14 +2940,14 @@
       <c r="J119" s="8"/>
     </row>
     <row r="120" spans="4:25" x14ac:dyDescent="0.3">
-      <c r="E120" s="18" t="s">
+      <c r="E120" s="17" t="s">
         <v>115</v>
       </c>
-      <c r="F120" s="19"/>
-      <c r="G120" s="19"/>
-      <c r="H120" s="19"/>
-      <c r="I120" s="19"/>
-      <c r="J120" s="20"/>
+      <c r="F120" s="18"/>
+      <c r="G120" s="18"/>
+      <c r="H120" s="18"/>
+      <c r="I120" s="18"/>
+      <c r="J120" s="19"/>
       <c r="K120" s="4" t="s">
         <v>117</v>
       </c>
@@ -3015,29 +3111,29 @@
       </c>
       <c r="F131" s="8"/>
       <c r="G131" s="8"/>
-      <c r="H131" s="22" t="s">
+      <c r="H131" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="I131" s="22"/>
-      <c r="J131" s="22"/>
-      <c r="K131" s="22"/>
-      <c r="L131" s="22"/>
-      <c r="M131" s="22"/>
-      <c r="N131" s="22"/>
-      <c r="O131" s="22"/>
-      <c r="P131" s="22" t="s">
+      <c r="I131" s="10"/>
+      <c r="J131" s="10"/>
+      <c r="K131" s="10"/>
+      <c r="L131" s="10"/>
+      <c r="M131" s="10"/>
+      <c r="N131" s="10"/>
+      <c r="O131" s="10"/>
+      <c r="P131" s="10" t="s">
         <v>138</v>
       </c>
-      <c r="Q131" s="22"/>
-      <c r="R131" s="22"/>
-      <c r="S131" s="22"/>
-      <c r="T131" s="22"/>
-      <c r="U131" s="22"/>
-      <c r="V131" s="22"/>
-      <c r="W131" s="22"/>
-      <c r="X131" s="22"/>
-      <c r="Y131" s="22"/>
-      <c r="Z131" s="22"/>
+      <c r="Q131" s="10"/>
+      <c r="R131" s="10"/>
+      <c r="S131" s="10"/>
+      <c r="T131" s="10"/>
+      <c r="U131" s="10"/>
+      <c r="V131" s="10"/>
+      <c r="W131" s="10"/>
+      <c r="X131" s="10"/>
+      <c r="Y131" s="10"/>
+      <c r="Z131" s="10"/>
     </row>
     <row r="132" spans="3:26" x14ac:dyDescent="0.3">
       <c r="E132" s="8" t="s">
@@ -3045,29 +3141,29 @@
       </c>
       <c r="F132" s="8"/>
       <c r="G132" s="8"/>
-      <c r="H132" s="22" t="s">
+      <c r="H132" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="I132" s="22"/>
-      <c r="J132" s="22"/>
-      <c r="K132" s="22"/>
-      <c r="L132" s="22"/>
-      <c r="M132" s="22"/>
-      <c r="N132" s="22"/>
-      <c r="O132" s="22"/>
-      <c r="P132" s="22" t="s">
+      <c r="I132" s="10"/>
+      <c r="J132" s="10"/>
+      <c r="K132" s="10"/>
+      <c r="L132" s="10"/>
+      <c r="M132" s="10"/>
+      <c r="N132" s="10"/>
+      <c r="O132" s="10"/>
+      <c r="P132" s="10" t="s">
         <v>139</v>
       </c>
-      <c r="Q132" s="22"/>
-      <c r="R132" s="22"/>
-      <c r="S132" s="22"/>
-      <c r="T132" s="22"/>
-      <c r="U132" s="22"/>
-      <c r="V132" s="22"/>
-      <c r="W132" s="22"/>
-      <c r="X132" s="22"/>
-      <c r="Y132" s="22"/>
-      <c r="Z132" s="22"/>
+      <c r="Q132" s="10"/>
+      <c r="R132" s="10"/>
+      <c r="S132" s="10"/>
+      <c r="T132" s="10"/>
+      <c r="U132" s="10"/>
+      <c r="V132" s="10"/>
+      <c r="W132" s="10"/>
+      <c r="X132" s="10"/>
+      <c r="Y132" s="10"/>
+      <c r="Z132" s="10"/>
     </row>
     <row r="133" spans="3:26" x14ac:dyDescent="0.3">
       <c r="E133" s="8" t="s">
@@ -3075,29 +3171,29 @@
       </c>
       <c r="F133" s="8"/>
       <c r="G133" s="8"/>
-      <c r="H133" s="22" t="s">
+      <c r="H133" s="10" t="s">
         <v>135</v>
       </c>
-      <c r="I133" s="22"/>
-      <c r="J133" s="22"/>
-      <c r="K133" s="22"/>
-      <c r="L133" s="22"/>
-      <c r="M133" s="22"/>
-      <c r="N133" s="22"/>
-      <c r="O133" s="22"/>
-      <c r="P133" s="22" t="s">
+      <c r="I133" s="10"/>
+      <c r="J133" s="10"/>
+      <c r="K133" s="10"/>
+      <c r="L133" s="10"/>
+      <c r="M133" s="10"/>
+      <c r="N133" s="10"/>
+      <c r="O133" s="10"/>
+      <c r="P133" s="10" t="s">
         <v>140</v>
       </c>
-      <c r="Q133" s="22"/>
-      <c r="R133" s="22"/>
-      <c r="S133" s="22"/>
-      <c r="T133" s="22"/>
-      <c r="U133" s="22"/>
-      <c r="V133" s="22"/>
-      <c r="W133" s="22"/>
-      <c r="X133" s="22"/>
-      <c r="Y133" s="22"/>
-      <c r="Z133" s="22"/>
+      <c r="Q133" s="10"/>
+      <c r="R133" s="10"/>
+      <c r="S133" s="10"/>
+      <c r="T133" s="10"/>
+      <c r="U133" s="10"/>
+      <c r="V133" s="10"/>
+      <c r="W133" s="10"/>
+      <c r="X133" s="10"/>
+      <c r="Y133" s="10"/>
+      <c r="Z133" s="10"/>
     </row>
     <row r="134" spans="3:26" x14ac:dyDescent="0.3">
       <c r="E134" s="8" t="s">
@@ -3105,83 +3201,83 @@
       </c>
       <c r="F134" s="8"/>
       <c r="G134" s="8"/>
-      <c r="H134" s="22" t="s">
+      <c r="H134" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="I134" s="22"/>
-      <c r="J134" s="22"/>
-      <c r="K134" s="22"/>
-      <c r="L134" s="22"/>
-      <c r="M134" s="22"/>
-      <c r="N134" s="22"/>
-      <c r="O134" s="22"/>
-      <c r="P134" s="22" t="s">
+      <c r="I134" s="10"/>
+      <c r="J134" s="10"/>
+      <c r="K134" s="10"/>
+      <c r="L134" s="10"/>
+      <c r="M134" s="10"/>
+      <c r="N134" s="10"/>
+      <c r="O134" s="10"/>
+      <c r="P134" s="10" t="s">
         <v>141</v>
       </c>
-      <c r="Q134" s="22"/>
-      <c r="R134" s="22"/>
-      <c r="S134" s="22"/>
-      <c r="T134" s="22"/>
-      <c r="U134" s="22"/>
-      <c r="V134" s="22"/>
-      <c r="W134" s="22"/>
-      <c r="X134" s="22"/>
-      <c r="Y134" s="22"/>
-      <c r="Z134" s="22"/>
+      <c r="Q134" s="10"/>
+      <c r="R134" s="10"/>
+      <c r="S134" s="10"/>
+      <c r="T134" s="10"/>
+      <c r="U134" s="10"/>
+      <c r="V134" s="10"/>
+      <c r="W134" s="10"/>
+      <c r="X134" s="10"/>
+      <c r="Y134" s="10"/>
+      <c r="Z134" s="10"/>
     </row>
     <row r="136" spans="3:26" x14ac:dyDescent="0.3">
-      <c r="C136" s="9" t="s">
+      <c r="C136" s="11" t="s">
         <v>169</v>
       </c>
-      <c r="D136" s="10"/>
-      <c r="E136" s="10"/>
-      <c r="F136" s="10"/>
-      <c r="G136" s="10"/>
-      <c r="H136" s="10"/>
-      <c r="I136" s="10"/>
-      <c r="J136" s="10"/>
-      <c r="K136" s="10"/>
-      <c r="L136" s="10"/>
-      <c r="M136" s="10"/>
-      <c r="N136" s="10"/>
-      <c r="O136" s="10"/>
-      <c r="P136" s="10"/>
-      <c r="Q136" s="10"/>
-      <c r="R136" s="10"/>
-      <c r="S136" s="10"/>
-      <c r="T136" s="10"/>
-      <c r="U136" s="10"/>
-      <c r="V136" s="10"/>
-      <c r="W136" s="10"/>
-      <c r="X136" s="10"/>
-      <c r="Y136" s="10"/>
-      <c r="Z136" s="11"/>
+      <c r="D136" s="12"/>
+      <c r="E136" s="12"/>
+      <c r="F136" s="12"/>
+      <c r="G136" s="12"/>
+      <c r="H136" s="12"/>
+      <c r="I136" s="12"/>
+      <c r="J136" s="12"/>
+      <c r="K136" s="12"/>
+      <c r="L136" s="12"/>
+      <c r="M136" s="12"/>
+      <c r="N136" s="12"/>
+      <c r="O136" s="12"/>
+      <c r="P136" s="12"/>
+      <c r="Q136" s="12"/>
+      <c r="R136" s="12"/>
+      <c r="S136" s="12"/>
+      <c r="T136" s="12"/>
+      <c r="U136" s="12"/>
+      <c r="V136" s="12"/>
+      <c r="W136" s="12"/>
+      <c r="X136" s="12"/>
+      <c r="Y136" s="12"/>
+      <c r="Z136" s="13"/>
     </row>
     <row r="137" spans="3:26" x14ac:dyDescent="0.3">
-      <c r="C137" s="15"/>
-      <c r="D137" s="16"/>
-      <c r="E137" s="16"/>
-      <c r="F137" s="16"/>
-      <c r="G137" s="16"/>
-      <c r="H137" s="16"/>
-      <c r="I137" s="16"/>
-      <c r="J137" s="16"/>
-      <c r="K137" s="16"/>
-      <c r="L137" s="16"/>
-      <c r="M137" s="16"/>
-      <c r="N137" s="16"/>
-      <c r="O137" s="16"/>
-      <c r="P137" s="16"/>
-      <c r="Q137" s="16"/>
-      <c r="R137" s="16"/>
-      <c r="S137" s="16"/>
-      <c r="T137" s="16"/>
-      <c r="U137" s="16"/>
-      <c r="V137" s="16"/>
-      <c r="W137" s="16"/>
-      <c r="X137" s="16"/>
-      <c r="Y137" s="16"/>
-      <c r="Z137" s="17"/>
+      <c r="C137" s="14"/>
+      <c r="D137" s="15"/>
+      <c r="E137" s="15"/>
+      <c r="F137" s="15"/>
+      <c r="G137" s="15"/>
+      <c r="H137" s="15"/>
+      <c r="I137" s="15"/>
+      <c r="J137" s="15"/>
+      <c r="K137" s="15"/>
+      <c r="L137" s="15"/>
+      <c r="M137" s="15"/>
+      <c r="N137" s="15"/>
+      <c r="O137" s="15"/>
+      <c r="P137" s="15"/>
+      <c r="Q137" s="15"/>
+      <c r="R137" s="15"/>
+      <c r="S137" s="15"/>
+      <c r="T137" s="15"/>
+      <c r="U137" s="15"/>
+      <c r="V137" s="15"/>
+      <c r="W137" s="15"/>
+      <c r="X137" s="15"/>
+      <c r="Y137" s="15"/>
+      <c r="Z137" s="16"/>
     </row>
     <row r="138" spans="3:26" x14ac:dyDescent="0.3">
       <c r="C138" s="5"/>
@@ -3242,260 +3338,260 @@
       <c r="Z139" s="8"/>
     </row>
     <row r="140" spans="3:26" x14ac:dyDescent="0.3">
-      <c r="C140" s="21" t="s">
+      <c r="C140" s="9" t="s">
         <v>170</v>
       </c>
-      <c r="D140" s="21"/>
-      <c r="E140" s="21"/>
-      <c r="F140" s="21"/>
-      <c r="G140" s="21"/>
-      <c r="H140" s="21"/>
+      <c r="D140" s="9"/>
+      <c r="E140" s="9"/>
+      <c r="F140" s="9"/>
+      <c r="G140" s="9"/>
+      <c r="H140" s="9"/>
       <c r="I140" s="8" t="s">
         <v>174</v>
       </c>
       <c r="J140" s="8"/>
       <c r="K140" s="8"/>
       <c r="L140" s="8"/>
-      <c r="M140" s="21" t="s">
+      <c r="M140" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="N140" s="21"/>
-      <c r="O140" s="21"/>
-      <c r="P140" s="21"/>
-      <c r="Q140" s="21"/>
-      <c r="R140" s="21"/>
-      <c r="S140" s="21"/>
-      <c r="T140" s="21"/>
-      <c r="U140" s="21"/>
-      <c r="V140" s="21"/>
-      <c r="W140" s="21"/>
-      <c r="X140" s="21"/>
-      <c r="Y140" s="21"/>
-      <c r="Z140" s="21"/>
+      <c r="N140" s="9"/>
+      <c r="O140" s="9"/>
+      <c r="P140" s="9"/>
+      <c r="Q140" s="9"/>
+      <c r="R140" s="9"/>
+      <c r="S140" s="9"/>
+      <c r="T140" s="9"/>
+      <c r="U140" s="9"/>
+      <c r="V140" s="9"/>
+      <c r="W140" s="9"/>
+      <c r="X140" s="9"/>
+      <c r="Y140" s="9"/>
+      <c r="Z140" s="9"/>
     </row>
     <row r="141" spans="3:26" x14ac:dyDescent="0.3">
-      <c r="C141" s="21" t="s">
+      <c r="C141" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="D141" s="21"/>
-      <c r="E141" s="21"/>
-      <c r="F141" s="21"/>
-      <c r="G141" s="21"/>
-      <c r="H141" s="21"/>
+      <c r="D141" s="9"/>
+      <c r="E141" s="9"/>
+      <c r="F141" s="9"/>
+      <c r="G141" s="9"/>
+      <c r="H141" s="9"/>
       <c r="I141" s="8" t="s">
         <v>175</v>
       </c>
       <c r="J141" s="8"/>
       <c r="K141" s="8"/>
       <c r="L141" s="8"/>
-      <c r="M141" s="21" t="s">
+      <c r="M141" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="N141" s="21"/>
-      <c r="O141" s="21"/>
-      <c r="P141" s="21"/>
-      <c r="Q141" s="21"/>
-      <c r="R141" s="21"/>
-      <c r="S141" s="21"/>
-      <c r="T141" s="21"/>
-      <c r="U141" s="21"/>
-      <c r="V141" s="21"/>
-      <c r="W141" s="21"/>
-      <c r="X141" s="21"/>
-      <c r="Y141" s="21"/>
-      <c r="Z141" s="21"/>
+      <c r="N141" s="9"/>
+      <c r="O141" s="9"/>
+      <c r="P141" s="9"/>
+      <c r="Q141" s="9"/>
+      <c r="R141" s="9"/>
+      <c r="S141" s="9"/>
+      <c r="T141" s="9"/>
+      <c r="U141" s="9"/>
+      <c r="V141" s="9"/>
+      <c r="W141" s="9"/>
+      <c r="X141" s="9"/>
+      <c r="Y141" s="9"/>
+      <c r="Z141" s="9"/>
     </row>
     <row r="142" spans="3:26" x14ac:dyDescent="0.3">
-      <c r="C142" s="21" t="s">
+      <c r="C142" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D142" s="21"/>
-      <c r="E142" s="21"/>
-      <c r="F142" s="21"/>
-      <c r="G142" s="21"/>
-      <c r="H142" s="21"/>
+      <c r="D142" s="9"/>
+      <c r="E142" s="9"/>
+      <c r="F142" s="9"/>
+      <c r="G142" s="9"/>
+      <c r="H142" s="9"/>
       <c r="I142" s="8" t="s">
         <v>176</v>
       </c>
       <c r="J142" s="8"/>
       <c r="K142" s="8"/>
       <c r="L142" s="8"/>
-      <c r="M142" s="21" t="s">
+      <c r="M142" s="9" t="s">
         <v>183</v>
       </c>
-      <c r="N142" s="21"/>
-      <c r="O142" s="21"/>
-      <c r="P142" s="21"/>
-      <c r="Q142" s="21"/>
-      <c r="R142" s="21"/>
-      <c r="S142" s="21"/>
-      <c r="T142" s="21"/>
-      <c r="U142" s="21"/>
-      <c r="V142" s="21"/>
-      <c r="W142" s="21"/>
-      <c r="X142" s="21"/>
-      <c r="Y142" s="21"/>
-      <c r="Z142" s="21"/>
+      <c r="N142" s="9"/>
+      <c r="O142" s="9"/>
+      <c r="P142" s="9"/>
+      <c r="Q142" s="9"/>
+      <c r="R142" s="9"/>
+      <c r="S142" s="9"/>
+      <c r="T142" s="9"/>
+      <c r="U142" s="9"/>
+      <c r="V142" s="9"/>
+      <c r="W142" s="9"/>
+      <c r="X142" s="9"/>
+      <c r="Y142" s="9"/>
+      <c r="Z142" s="9"/>
     </row>
     <row r="143" spans="3:26" x14ac:dyDescent="0.3">
-      <c r="C143" s="21" t="s">
+      <c r="C143" s="9" t="s">
         <v>177</v>
       </c>
-      <c r="D143" s="21"/>
-      <c r="E143" s="21"/>
-      <c r="F143" s="21"/>
-      <c r="G143" s="21"/>
-      <c r="H143" s="21"/>
+      <c r="D143" s="9"/>
+      <c r="E143" s="9"/>
+      <c r="F143" s="9"/>
+      <c r="G143" s="9"/>
+      <c r="H143" s="9"/>
       <c r="I143" s="8" t="s">
         <v>176</v>
       </c>
       <c r="J143" s="8"/>
       <c r="K143" s="8"/>
       <c r="L143" s="8"/>
-      <c r="M143" s="21" t="s">
+      <c r="M143" s="9" t="s">
         <v>184</v>
       </c>
-      <c r="N143" s="21"/>
-      <c r="O143" s="21"/>
-      <c r="P143" s="21"/>
-      <c r="Q143" s="21"/>
-      <c r="R143" s="21"/>
-      <c r="S143" s="21"/>
-      <c r="T143" s="21"/>
-      <c r="U143" s="21"/>
-      <c r="V143" s="21"/>
-      <c r="W143" s="21"/>
-      <c r="X143" s="21"/>
-      <c r="Y143" s="21"/>
-      <c r="Z143" s="21"/>
+      <c r="N143" s="9"/>
+      <c r="O143" s="9"/>
+      <c r="P143" s="9"/>
+      <c r="Q143" s="9"/>
+      <c r="R143" s="9"/>
+      <c r="S143" s="9"/>
+      <c r="T143" s="9"/>
+      <c r="U143" s="9"/>
+      <c r="V143" s="9"/>
+      <c r="W143" s="9"/>
+      <c r="X143" s="9"/>
+      <c r="Y143" s="9"/>
+      <c r="Z143" s="9"/>
     </row>
     <row r="144" spans="3:26" x14ac:dyDescent="0.3">
-      <c r="C144" s="21" t="s">
+      <c r="C144" s="9" t="s">
         <v>178</v>
       </c>
-      <c r="D144" s="21"/>
-      <c r="E144" s="21"/>
-      <c r="F144" s="21"/>
-      <c r="G144" s="21"/>
-      <c r="H144" s="21"/>
+      <c r="D144" s="9"/>
+      <c r="E144" s="9"/>
+      <c r="F144" s="9"/>
+      <c r="G144" s="9"/>
+      <c r="H144" s="9"/>
       <c r="I144" s="8" t="s">
         <v>176</v>
       </c>
       <c r="J144" s="8"/>
       <c r="K144" s="8"/>
       <c r="L144" s="8"/>
-      <c r="M144" s="21" t="s">
+      <c r="M144" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="N144" s="21"/>
-      <c r="O144" s="21"/>
-      <c r="P144" s="21"/>
-      <c r="Q144" s="21"/>
-      <c r="R144" s="21"/>
-      <c r="S144" s="21"/>
-      <c r="T144" s="21"/>
-      <c r="U144" s="21"/>
-      <c r="V144" s="21"/>
-      <c r="W144" s="21"/>
-      <c r="X144" s="21"/>
-      <c r="Y144" s="21"/>
-      <c r="Z144" s="21"/>
+      <c r="N144" s="9"/>
+      <c r="O144" s="9"/>
+      <c r="P144" s="9"/>
+      <c r="Q144" s="9"/>
+      <c r="R144" s="9"/>
+      <c r="S144" s="9"/>
+      <c r="T144" s="9"/>
+      <c r="U144" s="9"/>
+      <c r="V144" s="9"/>
+      <c r="W144" s="9"/>
+      <c r="X144" s="9"/>
+      <c r="Y144" s="9"/>
+      <c r="Z144" s="9"/>
     </row>
     <row r="145" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="C145" s="21" t="s">
+      <c r="C145" s="9" t="s">
         <v>186</v>
       </c>
-      <c r="D145" s="21"/>
-      <c r="E145" s="21"/>
-      <c r="F145" s="21"/>
-      <c r="G145" s="21"/>
-      <c r="H145" s="21"/>
+      <c r="D145" s="9"/>
+      <c r="E145" s="9"/>
+      <c r="F145" s="9"/>
+      <c r="G145" s="9"/>
+      <c r="H145" s="9"/>
       <c r="I145" s="8" t="s">
         <v>176</v>
       </c>
       <c r="J145" s="8"/>
       <c r="K145" s="8"/>
       <c r="L145" s="8"/>
-      <c r="M145" s="21" t="s">
+      <c r="M145" s="9" t="s">
         <v>185</v>
       </c>
-      <c r="N145" s="21"/>
-      <c r="O145" s="21"/>
-      <c r="P145" s="21"/>
-      <c r="Q145" s="21"/>
-      <c r="R145" s="21"/>
-      <c r="S145" s="21"/>
-      <c r="T145" s="21"/>
-      <c r="U145" s="21"/>
-      <c r="V145" s="21"/>
-      <c r="W145" s="21"/>
-      <c r="X145" s="21"/>
-      <c r="Y145" s="21"/>
-      <c r="Z145" s="21"/>
+      <c r="N145" s="9"/>
+      <c r="O145" s="9"/>
+      <c r="P145" s="9"/>
+      <c r="Q145" s="9"/>
+      <c r="R145" s="9"/>
+      <c r="S145" s="9"/>
+      <c r="T145" s="9"/>
+      <c r="U145" s="9"/>
+      <c r="V145" s="9"/>
+      <c r="W145" s="9"/>
+      <c r="X145" s="9"/>
+      <c r="Y145" s="9"/>
+      <c r="Z145" s="9"/>
     </row>
     <row r="146" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="C146" s="21" t="s">
+      <c r="C146" s="9" t="s">
         <v>179</v>
       </c>
-      <c r="D146" s="21"/>
-      <c r="E146" s="21"/>
-      <c r="F146" s="21"/>
-      <c r="G146" s="21"/>
-      <c r="H146" s="21"/>
+      <c r="D146" s="9"/>
+      <c r="E146" s="9"/>
+      <c r="F146" s="9"/>
+      <c r="G146" s="9"/>
+      <c r="H146" s="9"/>
       <c r="I146" s="8" t="s">
         <v>176</v>
       </c>
       <c r="J146" s="8"/>
       <c r="K146" s="8"/>
       <c r="L146" s="8"/>
-      <c r="M146" s="21" t="s">
+      <c r="M146" s="9" t="s">
         <v>188</v>
       </c>
-      <c r="N146" s="21"/>
-      <c r="O146" s="21"/>
-      <c r="P146" s="21"/>
-      <c r="Q146" s="21"/>
-      <c r="R146" s="21"/>
-      <c r="S146" s="21"/>
-      <c r="T146" s="21"/>
-      <c r="U146" s="21"/>
-      <c r="V146" s="21"/>
-      <c r="W146" s="21"/>
-      <c r="X146" s="21"/>
-      <c r="Y146" s="21"/>
-      <c r="Z146" s="21"/>
+      <c r="N146" s="9"/>
+      <c r="O146" s="9"/>
+      <c r="P146" s="9"/>
+      <c r="Q146" s="9"/>
+      <c r="R146" s="9"/>
+      <c r="S146" s="9"/>
+      <c r="T146" s="9"/>
+      <c r="U146" s="9"/>
+      <c r="V146" s="9"/>
+      <c r="W146" s="9"/>
+      <c r="X146" s="9"/>
+      <c r="Y146" s="9"/>
+      <c r="Z146" s="9"/>
     </row>
     <row r="147" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="C147" s="21" t="s">
+      <c r="C147" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="D147" s="21"/>
-      <c r="E147" s="21"/>
-      <c r="F147" s="21"/>
-      <c r="G147" s="21"/>
-      <c r="H147" s="21"/>
+      <c r="D147" s="9"/>
+      <c r="E147" s="9"/>
+      <c r="F147" s="9"/>
+      <c r="G147" s="9"/>
+      <c r="H147" s="9"/>
       <c r="I147" s="8" t="s">
         <v>176</v>
       </c>
       <c r="J147" s="8"/>
       <c r="K147" s="8"/>
       <c r="L147" s="8"/>
-      <c r="M147" s="21" t="s">
+      <c r="M147" s="9" t="s">
         <v>189</v>
       </c>
-      <c r="N147" s="21"/>
-      <c r="O147" s="21"/>
-      <c r="P147" s="21"/>
-      <c r="Q147" s="21"/>
-      <c r="R147" s="21"/>
-      <c r="S147" s="21"/>
-      <c r="T147" s="21"/>
-      <c r="U147" s="21"/>
-      <c r="V147" s="21"/>
-      <c r="W147" s="21"/>
-      <c r="X147" s="21"/>
-      <c r="Y147" s="21"/>
-      <c r="Z147" s="21"/>
+      <c r="N147" s="9"/>
+      <c r="O147" s="9"/>
+      <c r="P147" s="9"/>
+      <c r="Q147" s="9"/>
+      <c r="R147" s="9"/>
+      <c r="S147" s="9"/>
+      <c r="T147" s="9"/>
+      <c r="U147" s="9"/>
+      <c r="V147" s="9"/>
+      <c r="W147" s="9"/>
+      <c r="X147" s="9"/>
+      <c r="Y147" s="9"/>
+      <c r="Z147" s="9"/>
     </row>
     <row r="149" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B149" s="8" t="s">
@@ -3555,80 +3651,14 @@
     </row>
   </sheetData>
   <mergeCells count="95">
-    <mergeCell ref="B149:Z150"/>
-    <mergeCell ref="I144:L144"/>
-    <mergeCell ref="I145:L145"/>
-    <mergeCell ref="I146:L146"/>
-    <mergeCell ref="I147:L147"/>
-    <mergeCell ref="M144:Z144"/>
-    <mergeCell ref="C147:H147"/>
-    <mergeCell ref="M139:Z139"/>
-    <mergeCell ref="M140:Z140"/>
-    <mergeCell ref="M141:Z141"/>
-    <mergeCell ref="M142:Z142"/>
-    <mergeCell ref="M143:Z143"/>
-    <mergeCell ref="M145:Z145"/>
-    <mergeCell ref="M146:Z146"/>
-    <mergeCell ref="M147:Z147"/>
-    <mergeCell ref="I143:L143"/>
-    <mergeCell ref="C143:H143"/>
-    <mergeCell ref="C144:H144"/>
-    <mergeCell ref="C145:H145"/>
-    <mergeCell ref="C146:H146"/>
-    <mergeCell ref="C140:H140"/>
-    <mergeCell ref="C139:H139"/>
-    <mergeCell ref="C141:H141"/>
-    <mergeCell ref="C142:H142"/>
-    <mergeCell ref="P134:Z134"/>
-    <mergeCell ref="C136:Z137"/>
-    <mergeCell ref="E134:G134"/>
-    <mergeCell ref="H134:O134"/>
-    <mergeCell ref="I139:L139"/>
-    <mergeCell ref="I140:L140"/>
-    <mergeCell ref="I141:L141"/>
-    <mergeCell ref="I142:L142"/>
-    <mergeCell ref="E133:G133"/>
-    <mergeCell ref="P130:Z130"/>
-    <mergeCell ref="P131:Z131"/>
-    <mergeCell ref="P132:Z132"/>
-    <mergeCell ref="P133:Z133"/>
-    <mergeCell ref="E130:G130"/>
-    <mergeCell ref="H130:O130"/>
-    <mergeCell ref="H131:O131"/>
-    <mergeCell ref="H132:O132"/>
-    <mergeCell ref="H133:O133"/>
-    <mergeCell ref="N124:Y124"/>
-    <mergeCell ref="E126:J126"/>
-    <mergeCell ref="L126:Y126"/>
-    <mergeCell ref="E131:G131"/>
-    <mergeCell ref="E132:G132"/>
-    <mergeCell ref="E125:J125"/>
-    <mergeCell ref="K111:X111"/>
-    <mergeCell ref="K112:X112"/>
-    <mergeCell ref="K113:X113"/>
-    <mergeCell ref="K114:X114"/>
-    <mergeCell ref="E118:J118"/>
-    <mergeCell ref="E119:J119"/>
-    <mergeCell ref="E120:J120"/>
-    <mergeCell ref="L120:Y120"/>
-    <mergeCell ref="E114:J114"/>
-    <mergeCell ref="E112:J112"/>
-    <mergeCell ref="E113:J113"/>
-    <mergeCell ref="E121:J121"/>
-    <mergeCell ref="E122:J122"/>
-    <mergeCell ref="E123:J123"/>
-    <mergeCell ref="E124:J124"/>
-    <mergeCell ref="E106:J106"/>
-    <mergeCell ref="K106:X106"/>
-    <mergeCell ref="K107:X107"/>
-    <mergeCell ref="K108:X108"/>
-    <mergeCell ref="K109:X109"/>
-    <mergeCell ref="E107:J107"/>
-    <mergeCell ref="K110:X110"/>
-    <mergeCell ref="E108:J108"/>
-    <mergeCell ref="E109:J109"/>
-    <mergeCell ref="E110:J110"/>
-    <mergeCell ref="E111:J111"/>
+    <mergeCell ref="E80:G80"/>
+    <mergeCell ref="U80:X80"/>
+    <mergeCell ref="B2:Z4"/>
+    <mergeCell ref="U6:Z6"/>
+    <mergeCell ref="C45:Z46"/>
+    <mergeCell ref="C56:Z57"/>
+    <mergeCell ref="C68:Z69"/>
+    <mergeCell ref="H80:T80"/>
     <mergeCell ref="C101:Z102"/>
     <mergeCell ref="E81:G81"/>
     <mergeCell ref="E82:G82"/>
@@ -3642,14 +3672,80 @@
     <mergeCell ref="U82:X82"/>
     <mergeCell ref="U83:X83"/>
     <mergeCell ref="U84:X84"/>
-    <mergeCell ref="E80:G80"/>
-    <mergeCell ref="U80:X80"/>
-    <mergeCell ref="B2:Z4"/>
-    <mergeCell ref="U6:Z6"/>
-    <mergeCell ref="C45:Z46"/>
-    <mergeCell ref="C56:Z57"/>
-    <mergeCell ref="C68:Z69"/>
-    <mergeCell ref="H80:T80"/>
+    <mergeCell ref="K110:X110"/>
+    <mergeCell ref="E108:J108"/>
+    <mergeCell ref="E109:J109"/>
+    <mergeCell ref="E110:J110"/>
+    <mergeCell ref="E111:J111"/>
+    <mergeCell ref="K106:X106"/>
+    <mergeCell ref="K107:X107"/>
+    <mergeCell ref="K108:X108"/>
+    <mergeCell ref="K109:X109"/>
+    <mergeCell ref="E107:J107"/>
+    <mergeCell ref="E121:J121"/>
+    <mergeCell ref="E122:J122"/>
+    <mergeCell ref="E123:J123"/>
+    <mergeCell ref="E124:J124"/>
+    <mergeCell ref="E106:J106"/>
+    <mergeCell ref="E119:J119"/>
+    <mergeCell ref="E120:J120"/>
+    <mergeCell ref="L120:Y120"/>
+    <mergeCell ref="E114:J114"/>
+    <mergeCell ref="E112:J112"/>
+    <mergeCell ref="E113:J113"/>
+    <mergeCell ref="K111:X111"/>
+    <mergeCell ref="K112:X112"/>
+    <mergeCell ref="K113:X113"/>
+    <mergeCell ref="K114:X114"/>
+    <mergeCell ref="E118:J118"/>
+    <mergeCell ref="N124:Y124"/>
+    <mergeCell ref="E126:J126"/>
+    <mergeCell ref="L126:Y126"/>
+    <mergeCell ref="E131:G131"/>
+    <mergeCell ref="E132:G132"/>
+    <mergeCell ref="E125:J125"/>
+    <mergeCell ref="E133:G133"/>
+    <mergeCell ref="P130:Z130"/>
+    <mergeCell ref="P131:Z131"/>
+    <mergeCell ref="P132:Z132"/>
+    <mergeCell ref="P133:Z133"/>
+    <mergeCell ref="E130:G130"/>
+    <mergeCell ref="H130:O130"/>
+    <mergeCell ref="H131:O131"/>
+    <mergeCell ref="H132:O132"/>
+    <mergeCell ref="H133:O133"/>
+    <mergeCell ref="C140:H140"/>
+    <mergeCell ref="C139:H139"/>
+    <mergeCell ref="C141:H141"/>
+    <mergeCell ref="C142:H142"/>
+    <mergeCell ref="P134:Z134"/>
+    <mergeCell ref="C136:Z137"/>
+    <mergeCell ref="E134:G134"/>
+    <mergeCell ref="H134:O134"/>
+    <mergeCell ref="I139:L139"/>
+    <mergeCell ref="I140:L140"/>
+    <mergeCell ref="I141:L141"/>
+    <mergeCell ref="I142:L142"/>
+    <mergeCell ref="I143:L143"/>
+    <mergeCell ref="C143:H143"/>
+    <mergeCell ref="C144:H144"/>
+    <mergeCell ref="C145:H145"/>
+    <mergeCell ref="C146:H146"/>
+    <mergeCell ref="M139:Z139"/>
+    <mergeCell ref="M140:Z140"/>
+    <mergeCell ref="M141:Z141"/>
+    <mergeCell ref="M142:Z142"/>
+    <mergeCell ref="M143:Z143"/>
+    <mergeCell ref="B149:Z150"/>
+    <mergeCell ref="I144:L144"/>
+    <mergeCell ref="I145:L145"/>
+    <mergeCell ref="I146:L146"/>
+    <mergeCell ref="I147:L147"/>
+    <mergeCell ref="M144:Z144"/>
+    <mergeCell ref="C147:H147"/>
+    <mergeCell ref="M145:Z145"/>
+    <mergeCell ref="M146:Z146"/>
+    <mergeCell ref="M147:Z147"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3974,30 +4070,30 @@
       <c r="AB2" s="6">
         <v>1</v>
       </c>
-      <c r="AC2" s="30" t="s">
+      <c r="AC2" s="29" t="s">
         <v>149</v>
       </c>
-      <c r="AD2" s="30"/>
-      <c r="AE2" s="30"/>
-      <c r="AF2" s="30"/>
-      <c r="AG2" s="30"/>
-      <c r="AH2" s="30"/>
-      <c r="AI2" s="30"/>
-      <c r="AJ2" s="30"/>
+      <c r="AD2" s="29"/>
+      <c r="AE2" s="29"/>
+      <c r="AF2" s="29"/>
+      <c r="AG2" s="29"/>
+      <c r="AH2" s="29"/>
+      <c r="AI2" s="29"/>
+      <c r="AJ2" s="29"/>
       <c r="AK2" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="AL2" s="30" t="s">
+      <c r="AL2" s="29" t="s">
         <v>150</v>
       </c>
-      <c r="AM2" s="30"/>
-      <c r="AN2" s="30"/>
-      <c r="AO2" s="30"/>
-      <c r="AP2" s="30"/>
-      <c r="AQ2" s="30"/>
-      <c r="AR2" s="30"/>
-      <c r="AS2" s="30"/>
-      <c r="AT2" s="30"/>
+      <c r="AM2" s="29"/>
+      <c r="AN2" s="29"/>
+      <c r="AO2" s="29"/>
+      <c r="AP2" s="29"/>
+      <c r="AQ2" s="29"/>
+      <c r="AR2" s="29"/>
+      <c r="AS2" s="29"/>
+      <c r="AT2" s="29"/>
       <c r="AU2" s="31" t="s">
         <v>117</v>
       </c>
@@ -4014,26 +4110,26 @@
       <c r="BD2" s="25"/>
     </row>
     <row r="3" spans="28:56" x14ac:dyDescent="0.3">
-      <c r="AC3" s="29" t="s">
+      <c r="AC3" s="30" t="s">
         <v>114</v>
       </c>
-      <c r="AD3" s="29"/>
-      <c r="AE3" s="29"/>
-      <c r="AF3" s="29"/>
-      <c r="AG3" s="29"/>
-      <c r="AH3" s="29"/>
-      <c r="AI3" s="29"/>
-      <c r="AJ3" s="29"/>
-      <c r="AK3" s="29"/>
-      <c r="AL3" s="29"/>
-      <c r="AM3" s="29"/>
-      <c r="AN3" s="29"/>
-      <c r="AO3" s="29"/>
-      <c r="AP3" s="29"/>
-      <c r="AQ3" s="29"/>
-      <c r="AR3" s="29"/>
-      <c r="AS3" s="29"/>
-      <c r="AT3" s="29"/>
+      <c r="AD3" s="30"/>
+      <c r="AE3" s="30"/>
+      <c r="AF3" s="30"/>
+      <c r="AG3" s="30"/>
+      <c r="AH3" s="30"/>
+      <c r="AI3" s="30"/>
+      <c r="AJ3" s="30"/>
+      <c r="AK3" s="30"/>
+      <c r="AL3" s="30"/>
+      <c r="AM3" s="30"/>
+      <c r="AN3" s="30"/>
+      <c r="AO3" s="30"/>
+      <c r="AP3" s="30"/>
+      <c r="AQ3" s="30"/>
+      <c r="AR3" s="30"/>
+      <c r="AS3" s="30"/>
+      <c r="AT3" s="30"/>
       <c r="AU3" s="32"/>
       <c r="AV3" s="26" t="s">
         <v>147</v>
@@ -4048,30 +4144,30 @@
       <c r="BD3" s="28"/>
     </row>
     <row r="4" spans="28:56" x14ac:dyDescent="0.3">
-      <c r="AC4" s="30" t="s">
+      <c r="AC4" s="29" t="s">
         <v>148</v>
       </c>
-      <c r="AD4" s="30"/>
-      <c r="AE4" s="30"/>
-      <c r="AF4" s="30"/>
-      <c r="AG4" s="30"/>
-      <c r="AH4" s="30"/>
-      <c r="AI4" s="30"/>
-      <c r="AJ4" s="30"/>
+      <c r="AD4" s="29"/>
+      <c r="AE4" s="29"/>
+      <c r="AF4" s="29"/>
+      <c r="AG4" s="29"/>
+      <c r="AH4" s="29"/>
+      <c r="AI4" s="29"/>
+      <c r="AJ4" s="29"/>
       <c r="AK4" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="AL4" s="30" t="s">
+      <c r="AL4" s="29" t="s">
         <v>151</v>
       </c>
-      <c r="AM4" s="30"/>
-      <c r="AN4" s="30"/>
-      <c r="AO4" s="30"/>
-      <c r="AP4" s="30"/>
-      <c r="AQ4" s="30"/>
-      <c r="AR4" s="30"/>
-      <c r="AS4" s="30"/>
-      <c r="AT4" s="30"/>
+      <c r="AM4" s="29"/>
+      <c r="AN4" s="29"/>
+      <c r="AO4" s="29"/>
+      <c r="AP4" s="29"/>
+      <c r="AQ4" s="29"/>
+      <c r="AR4" s="29"/>
+      <c r="AS4" s="29"/>
+      <c r="AT4" s="29"/>
       <c r="AU4" s="31" t="s">
         <v>117</v>
       </c>
@@ -4088,26 +4184,26 @@
       <c r="BD4" s="25"/>
     </row>
     <row r="5" spans="28:56" x14ac:dyDescent="0.3">
-      <c r="AC5" s="29" t="s">
+      <c r="AC5" s="30" t="s">
         <v>114</v>
       </c>
-      <c r="AD5" s="29"/>
-      <c r="AE5" s="29"/>
-      <c r="AF5" s="29"/>
-      <c r="AG5" s="29"/>
-      <c r="AH5" s="29"/>
-      <c r="AI5" s="29"/>
-      <c r="AJ5" s="29"/>
-      <c r="AK5" s="29"/>
-      <c r="AL5" s="29"/>
-      <c r="AM5" s="29"/>
-      <c r="AN5" s="29"/>
-      <c r="AO5" s="29"/>
-      <c r="AP5" s="29"/>
-      <c r="AQ5" s="29"/>
-      <c r="AR5" s="29"/>
-      <c r="AS5" s="29"/>
-      <c r="AT5" s="29"/>
+      <c r="AD5" s="30"/>
+      <c r="AE5" s="30"/>
+      <c r="AF5" s="30"/>
+      <c r="AG5" s="30"/>
+      <c r="AH5" s="30"/>
+      <c r="AI5" s="30"/>
+      <c r="AJ5" s="30"/>
+      <c r="AK5" s="30"/>
+      <c r="AL5" s="30"/>
+      <c r="AM5" s="30"/>
+      <c r="AN5" s="30"/>
+      <c r="AO5" s="30"/>
+      <c r="AP5" s="30"/>
+      <c r="AQ5" s="30"/>
+      <c r="AR5" s="30"/>
+      <c r="AS5" s="30"/>
+      <c r="AT5" s="30"/>
       <c r="AU5" s="32"/>
       <c r="AV5" s="26" t="s">
         <v>159</v>
@@ -4122,30 +4218,30 @@
       <c r="BD5" s="28"/>
     </row>
     <row r="6" spans="28:56" x14ac:dyDescent="0.3">
-      <c r="AC6" s="30" t="s">
+      <c r="AC6" s="29" t="s">
         <v>152</v>
       </c>
-      <c r="AD6" s="30"/>
-      <c r="AE6" s="30"/>
-      <c r="AF6" s="30"/>
-      <c r="AG6" s="30"/>
-      <c r="AH6" s="30"/>
-      <c r="AI6" s="30"/>
-      <c r="AJ6" s="30"/>
+      <c r="AD6" s="29"/>
+      <c r="AE6" s="29"/>
+      <c r="AF6" s="29"/>
+      <c r="AG6" s="29"/>
+      <c r="AH6" s="29"/>
+      <c r="AI6" s="29"/>
+      <c r="AJ6" s="29"/>
       <c r="AK6" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="AL6" s="30" t="s">
+      <c r="AL6" s="29" t="s">
         <v>153</v>
       </c>
-      <c r="AM6" s="30"/>
-      <c r="AN6" s="30"/>
-      <c r="AO6" s="30"/>
-      <c r="AP6" s="30"/>
-      <c r="AQ6" s="30"/>
-      <c r="AR6" s="30"/>
-      <c r="AS6" s="30"/>
-      <c r="AT6" s="30"/>
+      <c r="AM6" s="29"/>
+      <c r="AN6" s="29"/>
+      <c r="AO6" s="29"/>
+      <c r="AP6" s="29"/>
+      <c r="AQ6" s="29"/>
+      <c r="AR6" s="29"/>
+      <c r="AS6" s="29"/>
+      <c r="AT6" s="29"/>
       <c r="AU6" s="31" t="s">
         <v>117</v>
       </c>
@@ -4162,26 +4258,26 @@
       <c r="BD6" s="25"/>
     </row>
     <row r="7" spans="28:56" x14ac:dyDescent="0.3">
-      <c r="AC7" s="29" t="s">
+      <c r="AC7" s="30" t="s">
         <v>114</v>
       </c>
-      <c r="AD7" s="29"/>
-      <c r="AE7" s="29"/>
-      <c r="AF7" s="29"/>
-      <c r="AG7" s="29"/>
-      <c r="AH7" s="29"/>
-      <c r="AI7" s="29"/>
-      <c r="AJ7" s="29"/>
-      <c r="AK7" s="29"/>
-      <c r="AL7" s="29"/>
-      <c r="AM7" s="29"/>
-      <c r="AN7" s="29"/>
-      <c r="AO7" s="29"/>
-      <c r="AP7" s="29"/>
-      <c r="AQ7" s="29"/>
-      <c r="AR7" s="29"/>
-      <c r="AS7" s="29"/>
-      <c r="AT7" s="29"/>
+      <c r="AD7" s="30"/>
+      <c r="AE7" s="30"/>
+      <c r="AF7" s="30"/>
+      <c r="AG7" s="30"/>
+      <c r="AH7" s="30"/>
+      <c r="AI7" s="30"/>
+      <c r="AJ7" s="30"/>
+      <c r="AK7" s="30"/>
+      <c r="AL7" s="30"/>
+      <c r="AM7" s="30"/>
+      <c r="AN7" s="30"/>
+      <c r="AO7" s="30"/>
+      <c r="AP7" s="30"/>
+      <c r="AQ7" s="30"/>
+      <c r="AR7" s="30"/>
+      <c r="AS7" s="30"/>
+      <c r="AT7" s="30"/>
       <c r="AU7" s="32"/>
       <c r="AV7" s="26" t="s">
         <v>161</v>
@@ -4196,114 +4292,114 @@
       <c r="BD7" s="28"/>
     </row>
     <row r="8" spans="28:56" x14ac:dyDescent="0.3">
-      <c r="AC8" s="30" t="s">
+      <c r="AC8" s="29" t="s">
         <v>154</v>
       </c>
-      <c r="AD8" s="30"/>
-      <c r="AE8" s="30"/>
-      <c r="AF8" s="30"/>
-      <c r="AG8" s="30"/>
-      <c r="AH8" s="30"/>
-      <c r="AI8" s="30"/>
-      <c r="AJ8" s="30"/>
-      <c r="AK8" s="30"/>
-      <c r="AL8" s="30"/>
-      <c r="AM8" s="30"/>
-      <c r="AN8" s="30"/>
-      <c r="AO8" s="30"/>
-      <c r="AP8" s="30"/>
-      <c r="AQ8" s="30"/>
-      <c r="AR8" s="30"/>
-      <c r="AS8" s="30"/>
-      <c r="AT8" s="30"/>
+      <c r="AD8" s="29"/>
+      <c r="AE8" s="29"/>
+      <c r="AF8" s="29"/>
+      <c r="AG8" s="29"/>
+      <c r="AH8" s="29"/>
+      <c r="AI8" s="29"/>
+      <c r="AJ8" s="29"/>
+      <c r="AK8" s="29"/>
+      <c r="AL8" s="29"/>
+      <c r="AM8" s="29"/>
+      <c r="AN8" s="29"/>
+      <c r="AO8" s="29"/>
+      <c r="AP8" s="29"/>
+      <c r="AQ8" s="29"/>
+      <c r="AR8" s="29"/>
+      <c r="AS8" s="29"/>
+      <c r="AT8" s="29"/>
     </row>
     <row r="9" spans="28:56" x14ac:dyDescent="0.3">
-      <c r="AC9" s="29" t="s">
+      <c r="AC9" s="30" t="s">
         <v>114</v>
       </c>
-      <c r="AD9" s="29"/>
-      <c r="AE9" s="29"/>
-      <c r="AF9" s="29"/>
-      <c r="AG9" s="29"/>
-      <c r="AH9" s="29"/>
-      <c r="AI9" s="29"/>
-      <c r="AJ9" s="29"/>
-      <c r="AK9" s="29"/>
-      <c r="AL9" s="29"/>
-      <c r="AM9" s="29"/>
-      <c r="AN9" s="29"/>
-      <c r="AO9" s="29"/>
-      <c r="AP9" s="29"/>
-      <c r="AQ9" s="29"/>
-      <c r="AR9" s="29"/>
-      <c r="AS9" s="29"/>
-      <c r="AT9" s="29"/>
+      <c r="AD9" s="30"/>
+      <c r="AE9" s="30"/>
+      <c r="AF9" s="30"/>
+      <c r="AG9" s="30"/>
+      <c r="AH9" s="30"/>
+      <c r="AI9" s="30"/>
+      <c r="AJ9" s="30"/>
+      <c r="AK9" s="30"/>
+      <c r="AL9" s="30"/>
+      <c r="AM9" s="30"/>
+      <c r="AN9" s="30"/>
+      <c r="AO9" s="30"/>
+      <c r="AP9" s="30"/>
+      <c r="AQ9" s="30"/>
+      <c r="AR9" s="30"/>
+      <c r="AS9" s="30"/>
+      <c r="AT9" s="30"/>
     </row>
     <row r="10" spans="28:56" x14ac:dyDescent="0.3">
-      <c r="AC10" s="30" t="s">
+      <c r="AC10" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="AD10" s="30"/>
-      <c r="AE10" s="30"/>
-      <c r="AF10" s="30"/>
-      <c r="AG10" s="30"/>
-      <c r="AH10" s="30"/>
-      <c r="AI10" s="30"/>
-      <c r="AJ10" s="30"/>
-      <c r="AK10" s="30"/>
-      <c r="AL10" s="30"/>
-      <c r="AM10" s="30"/>
-      <c r="AN10" s="30"/>
-      <c r="AO10" s="30"/>
-      <c r="AP10" s="30"/>
-      <c r="AQ10" s="30"/>
-      <c r="AR10" s="30"/>
-      <c r="AS10" s="30"/>
-      <c r="AT10" s="30"/>
+      <c r="AD10" s="29"/>
+      <c r="AE10" s="29"/>
+      <c r="AF10" s="29"/>
+      <c r="AG10" s="29"/>
+      <c r="AH10" s="29"/>
+      <c r="AI10" s="29"/>
+      <c r="AJ10" s="29"/>
+      <c r="AK10" s="29"/>
+      <c r="AL10" s="29"/>
+      <c r="AM10" s="29"/>
+      <c r="AN10" s="29"/>
+      <c r="AO10" s="29"/>
+      <c r="AP10" s="29"/>
+      <c r="AQ10" s="29"/>
+      <c r="AR10" s="29"/>
+      <c r="AS10" s="29"/>
+      <c r="AT10" s="29"/>
     </row>
     <row r="11" spans="28:56" x14ac:dyDescent="0.3">
-      <c r="AC11" s="29" t="s">
+      <c r="AC11" s="30" t="s">
         <v>114</v>
       </c>
-      <c r="AD11" s="29"/>
-      <c r="AE11" s="29"/>
-      <c r="AF11" s="29"/>
-      <c r="AG11" s="29"/>
-      <c r="AH11" s="29"/>
-      <c r="AI11" s="29"/>
-      <c r="AJ11" s="29"/>
-      <c r="AK11" s="29"/>
-      <c r="AL11" s="29"/>
-      <c r="AM11" s="29"/>
-      <c r="AN11" s="29"/>
-      <c r="AO11" s="29"/>
-      <c r="AP11" s="29"/>
-      <c r="AQ11" s="29"/>
-      <c r="AR11" s="29"/>
-      <c r="AS11" s="29"/>
-      <c r="AT11" s="29"/>
+      <c r="AD11" s="30"/>
+      <c r="AE11" s="30"/>
+      <c r="AF11" s="30"/>
+      <c r="AG11" s="30"/>
+      <c r="AH11" s="30"/>
+      <c r="AI11" s="30"/>
+      <c r="AJ11" s="30"/>
+      <c r="AK11" s="30"/>
+      <c r="AL11" s="30"/>
+      <c r="AM11" s="30"/>
+      <c r="AN11" s="30"/>
+      <c r="AO11" s="30"/>
+      <c r="AP11" s="30"/>
+      <c r="AQ11" s="30"/>
+      <c r="AR11" s="30"/>
+      <c r="AS11" s="30"/>
+      <c r="AT11" s="30"/>
     </row>
     <row r="12" spans="28:56" x14ac:dyDescent="0.3">
-      <c r="AC12" s="30" t="s">
+      <c r="AC12" s="29" t="s">
         <v>156</v>
       </c>
-      <c r="AD12" s="30"/>
-      <c r="AE12" s="30"/>
-      <c r="AF12" s="30"/>
-      <c r="AG12" s="30"/>
-      <c r="AH12" s="30"/>
-      <c r="AI12" s="30"/>
-      <c r="AJ12" s="30"/>
-      <c r="AK12" s="30"/>
-      <c r="AL12" s="30"/>
-      <c r="AM12" s="30"/>
-      <c r="AN12" s="30"/>
-      <c r="AO12" s="30"/>
-      <c r="AP12" s="30"/>
-      <c r="AQ12" s="30"/>
-      <c r="AR12" s="30"/>
-      <c r="AS12" s="30"/>
-      <c r="AT12" s="30"/>
+      <c r="AD12" s="29"/>
+      <c r="AE12" s="29"/>
+      <c r="AF12" s="29"/>
+      <c r="AG12" s="29"/>
+      <c r="AH12" s="29"/>
+      <c r="AI12" s="29"/>
+      <c r="AJ12" s="29"/>
+      <c r="AK12" s="29"/>
+      <c r="AL12" s="29"/>
+      <c r="AM12" s="29"/>
+      <c r="AN12" s="29"/>
+      <c r="AO12" s="29"/>
+      <c r="AP12" s="29"/>
+      <c r="AQ12" s="29"/>
+      <c r="AR12" s="29"/>
+      <c r="AS12" s="29"/>
+      <c r="AT12" s="29"/>
     </row>
     <row r="17" spans="28:29" x14ac:dyDescent="0.3">
       <c r="AB17" s="6">
@@ -4320,11 +4416,8 @@
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="AV6:BD6"/>
-    <mergeCell ref="AV7:BD7"/>
-    <mergeCell ref="AC8:AT8"/>
-    <mergeCell ref="AC9:AT9"/>
-    <mergeCell ref="AC10:AT10"/>
+    <mergeCell ref="AV5:BD5"/>
+    <mergeCell ref="AU6:AU7"/>
     <mergeCell ref="AC11:AT11"/>
     <mergeCell ref="AC12:AT12"/>
     <mergeCell ref="AV2:BD2"/>
@@ -4341,8 +4434,11 @@
     <mergeCell ref="AL6:AT6"/>
     <mergeCell ref="AU4:AU5"/>
     <mergeCell ref="AV4:BD4"/>
-    <mergeCell ref="AV5:BD5"/>
-    <mergeCell ref="AU6:AU7"/>
+    <mergeCell ref="AV6:BD6"/>
+    <mergeCell ref="AV7:BD7"/>
+    <mergeCell ref="AC8:AT8"/>
+    <mergeCell ref="AC9:AT9"/>
+    <mergeCell ref="AC10:AT10"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4419,12 +4515,447 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AA1"/>
+  <dimension ref="A2:AA31"/>
   <sheetFormatPr defaultColWidth="2.875" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="27" width="2.875" style="2"/>
   </cols>
-  <sheetData/>
+  <sheetData>
+    <row r="2" spans="2:26" x14ac:dyDescent="0.3">
+      <c r="B2" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="12"/>
+      <c r="J2" s="12"/>
+      <c r="K2" s="12"/>
+      <c r="L2" s="12"/>
+      <c r="M2" s="12"/>
+      <c r="N2" s="12"/>
+      <c r="O2" s="12"/>
+      <c r="P2" s="12"/>
+      <c r="Q2" s="12"/>
+      <c r="R2" s="12"/>
+      <c r="S2" s="12"/>
+      <c r="T2" s="12"/>
+      <c r="U2" s="12"/>
+      <c r="V2" s="12"/>
+      <c r="W2" s="12"/>
+      <c r="X2" s="12"/>
+      <c r="Y2" s="12"/>
+      <c r="Z2" s="13"/>
+    </row>
+    <row r="3" spans="2:26" x14ac:dyDescent="0.3">
+      <c r="B3" s="20"/>
+      <c r="C3" s="21"/>
+      <c r="D3" s="21"/>
+      <c r="E3" s="21"/>
+      <c r="F3" s="21"/>
+      <c r="G3" s="21"/>
+      <c r="H3" s="21"/>
+      <c r="I3" s="21"/>
+      <c r="J3" s="21"/>
+      <c r="K3" s="21"/>
+      <c r="L3" s="21"/>
+      <c r="M3" s="21"/>
+      <c r="N3" s="21"/>
+      <c r="O3" s="21"/>
+      <c r="P3" s="21"/>
+      <c r="Q3" s="21"/>
+      <c r="R3" s="21"/>
+      <c r="S3" s="21"/>
+      <c r="T3" s="21"/>
+      <c r="U3" s="21"/>
+      <c r="V3" s="21"/>
+      <c r="W3" s="21"/>
+      <c r="X3" s="21"/>
+      <c r="Y3" s="21"/>
+      <c r="Z3" s="22"/>
+    </row>
+    <row r="4" spans="2:26" x14ac:dyDescent="0.3">
+      <c r="B4" s="14"/>
+      <c r="C4" s="15"/>
+      <c r="D4" s="15"/>
+      <c r="E4" s="15"/>
+      <c r="F4" s="15"/>
+      <c r="G4" s="15"/>
+      <c r="H4" s="15"/>
+      <c r="I4" s="15"/>
+      <c r="J4" s="15"/>
+      <c r="K4" s="15"/>
+      <c r="L4" s="15"/>
+      <c r="M4" s="15"/>
+      <c r="N4" s="15"/>
+      <c r="O4" s="15"/>
+      <c r="P4" s="15"/>
+      <c r="Q4" s="15"/>
+      <c r="R4" s="15"/>
+      <c r="S4" s="15"/>
+      <c r="T4" s="15"/>
+      <c r="U4" s="15"/>
+      <c r="V4" s="15"/>
+      <c r="W4" s="15"/>
+      <c r="X4" s="15"/>
+      <c r="Y4" s="15"/>
+      <c r="Z4" s="16"/>
+    </row>
+    <row r="6" spans="2:26" x14ac:dyDescent="0.3">
+      <c r="V6" s="17" t="s">
+        <v>213</v>
+      </c>
+      <c r="W6" s="18"/>
+      <c r="X6" s="18"/>
+      <c r="Y6" s="18"/>
+      <c r="Z6" s="19"/>
+    </row>
+    <row r="8" spans="2:26" x14ac:dyDescent="0.3">
+      <c r="C8" s="2" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="10" spans="2:26" x14ac:dyDescent="0.3">
+      <c r="D10" s="2">
+        <v>1</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="11" spans="2:26" x14ac:dyDescent="0.3">
+      <c r="D11" s="2">
+        <v>2</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="12" spans="2:26" x14ac:dyDescent="0.3">
+      <c r="D12" s="2">
+        <v>3</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="13" spans="2:26" x14ac:dyDescent="0.3">
+      <c r="D13" s="2">
+        <v>4</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="16" spans="2:26" x14ac:dyDescent="0.3">
+      <c r="C16" s="11" t="s">
+        <v>220</v>
+      </c>
+      <c r="D16" s="12"/>
+      <c r="E16" s="12"/>
+      <c r="F16" s="12"/>
+      <c r="G16" s="12"/>
+      <c r="H16" s="12"/>
+      <c r="I16" s="12"/>
+      <c r="J16" s="12"/>
+      <c r="K16" s="12"/>
+      <c r="L16" s="12"/>
+      <c r="M16" s="12"/>
+      <c r="N16" s="12"/>
+      <c r="O16" s="12"/>
+      <c r="P16" s="12"/>
+      <c r="Q16" s="12"/>
+      <c r="R16" s="12"/>
+      <c r="S16" s="12"/>
+      <c r="T16" s="12"/>
+      <c r="U16" s="12"/>
+      <c r="V16" s="12"/>
+      <c r="W16" s="12"/>
+      <c r="X16" s="12"/>
+      <c r="Y16" s="12"/>
+      <c r="Z16" s="13"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="C17" s="14"/>
+      <c r="D17" s="15"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="15"/>
+      <c r="G17" s="15"/>
+      <c r="H17" s="15"/>
+      <c r="I17" s="15"/>
+      <c r="J17" s="15"/>
+      <c r="K17" s="15"/>
+      <c r="L17" s="15"/>
+      <c r="M17" s="15"/>
+      <c r="N17" s="15"/>
+      <c r="O17" s="15"/>
+      <c r="P17" s="15"/>
+      <c r="Q17" s="15"/>
+      <c r="R17" s="15"/>
+      <c r="S17" s="15"/>
+      <c r="T17" s="15"/>
+      <c r="U17" s="15"/>
+      <c r="V17" s="15"/>
+      <c r="W17" s="15"/>
+      <c r="X17" s="15"/>
+      <c r="Y17" s="15"/>
+      <c r="Z17" s="16"/>
+    </row>
+    <row r="19" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="D19" s="2">
+        <v>1</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="D20" s="2">
+        <v>2</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="21" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="D21" s="2">
+        <v>3</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="22" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="D22" s="2">
+        <v>4</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="D23" s="2">
+        <v>5</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="24" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="E24" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="25" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="E25" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="E26" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="27" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="E27" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="28" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="E28" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="C30" s="11" t="s">
+        <v>236</v>
+      </c>
+      <c r="D30" s="12"/>
+      <c r="E30" s="12"/>
+      <c r="F30" s="12"/>
+      <c r="G30" s="12"/>
+      <c r="H30" s="12"/>
+      <c r="I30" s="12"/>
+      <c r="J30" s="12"/>
+      <c r="K30" s="12"/>
+      <c r="L30" s="12"/>
+      <c r="M30" s="12"/>
+      <c r="N30" s="12"/>
+      <c r="O30" s="12"/>
+      <c r="P30" s="12"/>
+      <c r="Q30" s="12"/>
+      <c r="R30" s="12"/>
+      <c r="S30" s="12"/>
+      <c r="T30" s="12"/>
+      <c r="U30" s="12"/>
+      <c r="V30" s="12"/>
+      <c r="W30" s="12"/>
+      <c r="X30" s="12"/>
+      <c r="Y30" s="12"/>
+      <c r="Z30" s="13"/>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="C31" s="14"/>
+      <c r="D31" s="15"/>
+      <c r="E31" s="15"/>
+      <c r="F31" s="15"/>
+      <c r="G31" s="15"/>
+      <c r="H31" s="15"/>
+      <c r="I31" s="15"/>
+      <c r="J31" s="15"/>
+      <c r="K31" s="15"/>
+      <c r="L31" s="15"/>
+      <c r="M31" s="15"/>
+      <c r="N31" s="15"/>
+      <c r="O31" s="15"/>
+      <c r="P31" s="15"/>
+      <c r="Q31" s="15"/>
+      <c r="R31" s="15"/>
+      <c r="S31" s="15"/>
+      <c r="T31" s="15"/>
+      <c r="U31" s="15"/>
+      <c r="V31" s="15"/>
+      <c r="W31" s="15"/>
+      <c r="X31" s="15"/>
+      <c r="Y31" s="15"/>
+      <c r="Z31" s="16"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="B2:Z4"/>
+    <mergeCell ref="V6:Z6"/>
+    <mergeCell ref="C16:Z17"/>
+    <mergeCell ref="C30:Z31"/>
+  </mergeCells>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A2:AA6"/>
+  <sheetFormatPr defaultColWidth="2.875" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="27" width="2.875" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:26" x14ac:dyDescent="0.3">
+      <c r="B2" s="11" t="s">
+        <v>214</v>
+      </c>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="12"/>
+      <c r="J2" s="12"/>
+      <c r="K2" s="12"/>
+      <c r="L2" s="12"/>
+      <c r="M2" s="12"/>
+      <c r="N2" s="12"/>
+      <c r="O2" s="12"/>
+      <c r="P2" s="12"/>
+      <c r="Q2" s="12"/>
+      <c r="R2" s="12"/>
+      <c r="S2" s="12"/>
+      <c r="T2" s="12"/>
+      <c r="U2" s="12"/>
+      <c r="V2" s="12"/>
+      <c r="W2" s="12"/>
+      <c r="X2" s="12"/>
+      <c r="Y2" s="12"/>
+      <c r="Z2" s="13"/>
+    </row>
+    <row r="3" spans="2:26" x14ac:dyDescent="0.3">
+      <c r="B3" s="20"/>
+      <c r="C3" s="21"/>
+      <c r="D3" s="21"/>
+      <c r="E3" s="21"/>
+      <c r="F3" s="21"/>
+      <c r="G3" s="21"/>
+      <c r="H3" s="21"/>
+      <c r="I3" s="21"/>
+      <c r="J3" s="21"/>
+      <c r="K3" s="21"/>
+      <c r="L3" s="21"/>
+      <c r="M3" s="21"/>
+      <c r="N3" s="21"/>
+      <c r="O3" s="21"/>
+      <c r="P3" s="21"/>
+      <c r="Q3" s="21"/>
+      <c r="R3" s="21"/>
+      <c r="S3" s="21"/>
+      <c r="T3" s="21"/>
+      <c r="U3" s="21"/>
+      <c r="V3" s="21"/>
+      <c r="W3" s="21"/>
+      <c r="X3" s="21"/>
+      <c r="Y3" s="21"/>
+      <c r="Z3" s="22"/>
+    </row>
+    <row r="4" spans="2:26" x14ac:dyDescent="0.3">
+      <c r="B4" s="14"/>
+      <c r="C4" s="15"/>
+      <c r="D4" s="15"/>
+      <c r="E4" s="15"/>
+      <c r="F4" s="15"/>
+      <c r="G4" s="15"/>
+      <c r="H4" s="15"/>
+      <c r="I4" s="15"/>
+      <c r="J4" s="15"/>
+      <c r="K4" s="15"/>
+      <c r="L4" s="15"/>
+      <c r="M4" s="15"/>
+      <c r="N4" s="15"/>
+      <c r="O4" s="15"/>
+      <c r="P4" s="15"/>
+      <c r="Q4" s="15"/>
+      <c r="R4" s="15"/>
+      <c r="S4" s="15"/>
+      <c r="T4" s="15"/>
+      <c r="U4" s="15"/>
+      <c r="V4" s="15"/>
+      <c r="W4" s="15"/>
+      <c r="X4" s="15"/>
+      <c r="Y4" s="15"/>
+      <c r="Z4" s="16"/>
+    </row>
+    <row r="6" spans="2:26" x14ac:dyDescent="0.3">
+      <c r="V6" s="17" t="s">
+        <v>213</v>
+      </c>
+      <c r="W6" s="18"/>
+      <c r="X6" s="18"/>
+      <c r="Y6" s="18"/>
+      <c r="Z6" s="19"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:Z4"/>
+    <mergeCell ref="V6:Z6"/>
+  </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/D2B2_기획_문서/003_시스템_기획서/006_미션_시스템/Project_D2B2_시스템기획서_미션_시스템.xlsx
+++ b/D2B2_기획_문서/003_시스템_기획서/006_미션_시스템/Project_D2B2_시스템기획서_미션_시스템.xlsx
@@ -9,15 +9,14 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12165" activeTab="4"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12165" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="미션 시스템 기획서" sheetId="2" r:id="rId1"/>
     <sheet name="테이블 예시" sheetId="1" r:id="rId2"/>
     <sheet name="미션 트리거 예시" sheetId="3" r:id="rId3"/>
-    <sheet name="튜토리얼 이미지" sheetId="5" r:id="rId4"/>
-    <sheet name="튜토리얼 미션&amp;트리거" sheetId="6" r:id="rId5"/>
-    <sheet name="1챕터 미션&amp;트리거" sheetId="4" r:id="rId6"/>
+    <sheet name="튜토리얼 미션&amp;트리거" sheetId="6" r:id="rId4"/>
+    <sheet name="1챕터 미션&amp;트리거" sheetId="4" r:id="rId5"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -29,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="283">
   <si>
     <t>챕터</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -821,143 +820,324 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>작성자 김준성</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>미션 시스템 - 1챕터</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>미션 시스템 - 튜토리얼</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>목차</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>챕터 목표</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>전체 미션 흐름</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>개별 미션 상세</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>챕터 목표</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>VR게임의 조작법과 상호작용에 익숙해지도록 플레이어를 유도함</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>보행 교육에 앞서 이 게임에서 사용될 기본 입력 및 반응 구조에 대한 학습</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>교육 목표 동작 및 상호작용</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>i</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>이동(Arm Swing Locomotion기반 이동)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ii</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>정지(Arm Swing Locomotion기반 이동)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>iii</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>시선 돌리기</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>iv</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>손 들기</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>v</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Controller Ray로 오브젝트 선택/상호작용</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>자신의 신체 조건에 맞는 플레이 환경을 구축</t>
+  </si>
+  <si>
+    <t>챕터에서 사용될 계정을 생성</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>전체 미션 흐름</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>계정 생성</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>이름 정도만 기입/개인정보 수집하지 않음/플레이어 식별용</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>NPC 선택</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>안전 가이드/챕터3 미니게임 등에서 활용될 동반자 선택</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>초기 설정</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>색약 옵션, 볼륨, 밝기 등 초기 사용자 설정(이 값은 서버로 전송됨)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>튜토리얼 시작</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>튜토리얼 상세</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>튜토리얼 종료 및 1화면으로 복귀. 플레이어는 챕터2 기기로 이동</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>앞으로 전진</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>전방 10m앞 지역이 하이라이트되고, Arm Swing Locomotion을</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>이용하여 해당 지역까지 움직이면 성공.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>실패조건 없음.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1분 이상 이동이 없을 시 안내 멘트(ex"어서 움직여" 등) 출력</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>좌우 살피기</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>좌우 살피기 인디케이터가 출력된 다음, 좌우측 인디케이터가</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>가득 찰 때까지 양측면을 살펴보면 성공.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>실패조건 없음.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1분이상 인디케이터가 변동되지 않을 시 안내 멘트 출력</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>손 들기</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>손 들기 인디케이터가 출력된 다음, 손 들기 인디케이터가</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>머리 높이 이상인 상태를 5초간 유지하면 성공.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>실패조건 없음.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>손 들고 걷기</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>전방 10m앞 지역이 하이라이트되고, Arm Swing Locomotion을</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>단, 이때는 손 들기 인디케이터가 머리 높이 이상인 상태를</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>유지하고 있어야 성공으로 인정됨.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1분 이상 이동이 없거나, 손 들기 인디케이터가 머리 높이 이하로</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>내려온 경우 안내 멘트 출력</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>튜토리얼 종료</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>동반자 npc가 플레이어를 칭찬하는 애니메이션 출력.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>계정 생성</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>게임 시작 시, 이름을 입력하라는 UI가 호출된다.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>여기서 입력된 이름은 챕터 진행 동안의 ID로 사용된다.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>만약 동명이인이 있을 시 등록된 순서에 따라</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>김철수</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>김철수A</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>김철수B</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>등으로 자동 매핑된다.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>이후, NPC 선택 화면으로 넘어간다.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">컨트롤러의 Ray가 닿은 NPC는 한 발자국 앞으로 전진하고, </t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>컨트롤러의 확인/취소 버튼을 UI로 크게 노출시켜</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>NPC를 선택하거나 선택 취소 할 수 있도록 유도한다.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>작성자 김준성</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>미션 시스템 - 1챕터</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>미션 시스템 - 튜토리얼</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>목차</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>챕터 목표</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>전체 미션 흐름</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>개별 미션 상세</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>챕터 목표</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>VR게임의 조작법과 상호작용에 익숙해지도록 플레이어를 유도함</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>보행 교육에 앞서 이 게임에서 사용될 기본 입력 및 반응 구조에 대한 학습</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>교육 목표 동작 및 상호작용</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>i</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>이동(Arm Swing Locomotion기반 이동)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ii</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>정지(Arm Swing Locomotion기반 이동)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>iii</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>시선 돌리기</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>iv</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>손 들기</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>v</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Controller Ray로 오브젝트 선택/상호작용</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>자신의 신체 조건에 맞는 플레이 환경을 구축</t>
-  </si>
-  <si>
-    <t>챕터에서 사용될 계정을 생성</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>전체 미션 흐름</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>동명이인이 있다면, 서버에 등록된 순서대로 김철수, 김철수A, 김철수B</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>등으로 구분짓는다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>이를 위해, 아이디 등록 후 자신의 아이디를 확인시켜준다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>이후 밝기, 사운드, 색약 옵션 등 초기 사용자 설정 UI를 호출한다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>이후 동반자 NPC 선택 화면으로 넘어간다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본적으로 컨트롤러와 컨트롤러의 RAY가 적용되어 있으며, RAY에 맞은</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>NPC는 하이라이트된다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1초 이상 하이라이트가 지속되면 해당 NPC가 선택된 것으로 취급되며</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1초 이상 하이라이트가 지속되었다는 것을 보여주기 위한 UI가 출력된다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">선택된 NPC는 한 발자국 앞으로 나오며, 머리 위에 선택되었다는 표시가 </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>나타난다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>컨트롤러 근처에 예/아니오를 선택하라는 Pannel이 출력되어 최종 선택이</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>가능해진다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>NPC 선택이 최종적으로 완료되면, 해당 NPC의 애니메이션(좌우 확인, 손 들기)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>을 따라하며 기본적인 조작 방법을 익힌다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>NPC 최종 선택이 완료되면, NPC의 위치로 이동하는 미션을 통해</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Arm Swing Locomoion 기반 이동을 학습한다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>NPC의 위치로 이동이 끝나면, 아날로그 스틱을 이용한 좌/우 이동 및</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>후진 기능을 학습할 수 있다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">기본 동작 학습이 모두 끝난다면, NPC와 함께 응용 이동(손 들고 걷기)을 </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>학습하는 것으로 튜토리얼 파트가 종료된다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">플레이어 정보는 서버로 전송되고, </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>튜토리얼로 셋팅된 기기는 초기 화면으로 돌아간다.</t>
   </si>
 </sst>
 </file>
@@ -1195,7 +1375,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1223,12 +1403,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1236,6 +1410,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1256,13 +1439,31 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1274,26 +1475,41 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1301,6 +1517,11 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFF3131"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1335,7 +1556,13 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="email">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1445,7 +1672,13 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="email">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1599,18 +1832,102 @@
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>209550</xdr:colOff>
+      <xdr:row>206</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>218</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="19" name="직사각형 18"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="647700" y="43300650"/>
+          <a:ext cx="5057775" cy="2381250"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1800"/>
+            <a:t>축하합니다</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1800"/>
+            <a:t>!</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1400"/>
+            <a:t>튜토리얼을 모두 마쳤습니다</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1400"/>
+            <a:t>.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1400"/>
+            <a:t>다음 챕터로 이동하세요</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1400"/>
+            <a:t>.</a:t>
+          </a:r>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1400"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>57150</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>114301</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>25</xdr:col>
-      <xdr:colOff>194094</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>104775</xdr:rowOff>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>84</xdr:row>
+      <xdr:rowOff>156935</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1620,15 +1937,21 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="email">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="276225" y="285750"/>
-          <a:ext cx="5394744" cy="2962275"/>
+          <a:off x="676275" y="14992351"/>
+          <a:ext cx="5038725" cy="2766784"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1639,16 +1962,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>76201</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>104775</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>9526</xdr:colOff>
+      <xdr:row>87</xdr:row>
+      <xdr:rowOff>76201</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>25</xdr:col>
-      <xdr:colOff>178643</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>190500</xdr:rowOff>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>19051</xdr:colOff>
+      <xdr:row>100</xdr:row>
+      <xdr:rowOff>191471</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1658,15 +1981,21 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="email">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="295276" y="6391275"/>
-          <a:ext cx="5360242" cy="3019425"/>
+          <a:off x="666751" y="18516601"/>
+          <a:ext cx="5048250" cy="2839420"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1677,16 +2006,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>85725</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>104</xdr:row>
+      <xdr:rowOff>85726</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>25</xdr:col>
-      <xdr:colOff>180564</xdr:colOff>
-      <xdr:row>59</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>9526</xdr:colOff>
+      <xdr:row>117</xdr:row>
+      <xdr:rowOff>200996</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1696,15 +2025,375 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="email">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="304800" y="9458325"/>
-          <a:ext cx="5352639" cy="3000375"/>
+          <a:off x="657226" y="21878926"/>
+          <a:ext cx="5048250" cy="2839420"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>209549</xdr:colOff>
+      <xdr:row>104</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>9524</xdr:colOff>
+      <xdr:row>117</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="직사각형 4"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="647699" y="21869400"/>
+          <a:ext cx="5057775" cy="2809875"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent3">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent3"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent3"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100"/>
+            <a:t>설정창 들어갈 공간</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>120</xdr:row>
+      <xdr:rowOff>114301</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>134</xdr:row>
+      <xdr:rowOff>24281</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="그림 5"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="email">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="657225" y="25260301"/>
+          <a:ext cx="5048250" cy="2843680"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>209550</xdr:colOff>
+      <xdr:row>125</xdr:row>
+      <xdr:rowOff>19051</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>128</xdr:row>
+      <xdr:rowOff>114301</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="직사각형 6"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2619375" y="26212801"/>
+          <a:ext cx="885825" cy="723900"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FF3131">
+            <a:alpha val="50196"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100"/>
+            <a:t>아웃라인</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100"/>
+            <a:t>하이라이트</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100"/>
+            <a:t>시각효과</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>171450</xdr:colOff>
+      <xdr:row>127</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>104775</xdr:colOff>
+      <xdr:row>129</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="타원 7"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3019425" y="26774775"/>
+          <a:ext cx="371475" cy="371475"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="76200">
+          <a:solidFill>
+            <a:srgbClr val="92D050"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>130969</xdr:colOff>
+      <xdr:row>127</xdr:row>
+      <xdr:rowOff>125015</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>154782</xdr:colOff>
+      <xdr:row>129</xdr:row>
+      <xdr:rowOff>196454</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="막힌 원호 8"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2994422" y="26586656"/>
+          <a:ext cx="464344" cy="488157"/>
+        </a:xfrm>
+        <a:prstGeom prst="blockArc">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 15769887"/>
+            <a:gd name="adj2" fmla="val 21498184"/>
+            <a:gd name="adj3" fmla="val 18183"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FF0000"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>140</xdr:row>
+      <xdr:rowOff>85726</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>9526</xdr:colOff>
+      <xdr:row>153</xdr:row>
+      <xdr:rowOff>191328</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="그림 9"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="email">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="657226" y="29422726"/>
+          <a:ext cx="5048250" cy="2829752"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1715,34 +2404,488 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>66675</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>171449</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>178</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>25</xdr:col>
-      <xdr:colOff>177158</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>47624</xdr:rowOff>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>36314</xdr:colOff>
+      <xdr:row>189</xdr:row>
+      <xdr:rowOff>57151</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="그림 4"/>
+        <xdr:cNvPr id="11" name="그림 10"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5" cstate="email">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="285750" y="3314699"/>
-          <a:ext cx="5368283" cy="3019425"/>
+          <a:off x="657225" y="33528001"/>
+          <a:ext cx="5075039" cy="2362200"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>160</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>32976</xdr:colOff>
+      <xdr:row>171</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="그림 11"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6" cstate="email">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="657226" y="33528000"/>
+          <a:ext cx="5071700" cy="2371725"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>161</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>170</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="13" name="그림 12"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7" cstate="email">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4429125" y="33823275"/>
+          <a:ext cx="1276350" cy="1914525"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>162</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>57150</xdr:colOff>
+      <xdr:row>165</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="14" name="TextBox 13"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4610100" y="33947100"/>
+          <a:ext cx="923925" cy="800100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1400"/>
+            <a:t>앞으로 전진해요</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1400"/>
+            <a:t>!</a:t>
+          </a:r>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1400"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>179</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>188</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="15" name="그림 14"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7" cstate="email">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4457700" y="37623750"/>
+          <a:ext cx="1276350" cy="1914525"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>180</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>85725</xdr:colOff>
+      <xdr:row>183</xdr:row>
+      <xdr:rowOff>200025</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="16" name="TextBox 15"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4638675" y="37747575"/>
+          <a:ext cx="923925" cy="800100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1200"/>
+            <a:t>손을 높이</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1200"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1200"/>
+            <a:t>들어 봐요</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1200"/>
+            <a:t>!</a:t>
+          </a:r>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1200"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>192</xdr:row>
+      <xdr:rowOff>85726</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>17212</xdr:colOff>
+      <xdr:row>203</xdr:row>
+      <xdr:rowOff>142876</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="17" name="그림 16"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8" cstate="email">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="657225" y="40319326"/>
+          <a:ext cx="5055937" cy="2362200"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>220</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>233</xdr:row>
+      <xdr:rowOff>185509</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="20" name="그림 19"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="email">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="666750" y="46243875"/>
+          <a:ext cx="5038725" cy="2766784"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>218</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>171450</xdr:colOff>
+      <xdr:row>220</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="21" name="오른쪽 화살표 20"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="5400000">
+          <a:off x="2895600" y="45596175"/>
+          <a:ext cx="371475" cy="752475"/>
+        </a:xfrm>
+        <a:prstGeom prst="rightArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent2">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent2"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>200025</xdr:colOff>
+      <xdr:row>215</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>19392</xdr:colOff>
+      <xdr:row>218</xdr:row>
+      <xdr:rowOff>65</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="22" name="그림 21"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3267075" y="45215175"/>
+          <a:ext cx="2448267" cy="466790"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2024,97 +3167,97 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="9" t="s">
         <v>191</v>
       </c>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="12"/>
-      <c r="I2" s="12"/>
-      <c r="J2" s="12"/>
-      <c r="K2" s="12"/>
-      <c r="L2" s="12"/>
-      <c r="M2" s="12"/>
-      <c r="N2" s="12"/>
-      <c r="O2" s="12"/>
-      <c r="P2" s="12"/>
-      <c r="Q2" s="12"/>
-      <c r="R2" s="12"/>
-      <c r="S2" s="12"/>
-      <c r="T2" s="12"/>
-      <c r="U2" s="12"/>
-      <c r="V2" s="12"/>
-      <c r="W2" s="12"/>
-      <c r="X2" s="12"/>
-      <c r="Y2" s="12"/>
-      <c r="Z2" s="13"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10"/>
+      <c r="N2" s="10"/>
+      <c r="O2" s="10"/>
+      <c r="P2" s="10"/>
+      <c r="Q2" s="10"/>
+      <c r="R2" s="10"/>
+      <c r="S2" s="10"/>
+      <c r="T2" s="10"/>
+      <c r="U2" s="10"/>
+      <c r="V2" s="10"/>
+      <c r="W2" s="10"/>
+      <c r="X2" s="10"/>
+      <c r="Y2" s="10"/>
+      <c r="Z2" s="11"/>
     </row>
     <row r="3" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B3" s="20"/>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="21"/>
-      <c r="F3" s="21"/>
-      <c r="G3" s="21"/>
-      <c r="H3" s="21"/>
-      <c r="I3" s="21"/>
-      <c r="J3" s="21"/>
-      <c r="K3" s="21"/>
-      <c r="L3" s="21"/>
-      <c r="M3" s="21"/>
-      <c r="N3" s="21"/>
-      <c r="O3" s="21"/>
-      <c r="P3" s="21"/>
-      <c r="Q3" s="21"/>
-      <c r="R3" s="21"/>
-      <c r="S3" s="21"/>
-      <c r="T3" s="21"/>
-      <c r="U3" s="21"/>
-      <c r="V3" s="21"/>
-      <c r="W3" s="21"/>
-      <c r="X3" s="21"/>
-      <c r="Y3" s="21"/>
-      <c r="Z3" s="22"/>
+      <c r="B3" s="12"/>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
+      <c r="H3" s="13"/>
+      <c r="I3" s="13"/>
+      <c r="J3" s="13"/>
+      <c r="K3" s="13"/>
+      <c r="L3" s="13"/>
+      <c r="M3" s="13"/>
+      <c r="N3" s="13"/>
+      <c r="O3" s="13"/>
+      <c r="P3" s="13"/>
+      <c r="Q3" s="13"/>
+      <c r="R3" s="13"/>
+      <c r="S3" s="13"/>
+      <c r="T3" s="13"/>
+      <c r="U3" s="13"/>
+      <c r="V3" s="13"/>
+      <c r="W3" s="13"/>
+      <c r="X3" s="13"/>
+      <c r="Y3" s="13"/>
+      <c r="Z3" s="14"/>
     </row>
     <row r="4" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B4" s="14"/>
-      <c r="C4" s="15"/>
-      <c r="D4" s="15"/>
-      <c r="E4" s="15"/>
-      <c r="F4" s="15"/>
-      <c r="G4" s="15"/>
-      <c r="H4" s="15"/>
-      <c r="I4" s="15"/>
-      <c r="J4" s="15"/>
-      <c r="K4" s="15"/>
-      <c r="L4" s="15"/>
-      <c r="M4" s="15"/>
-      <c r="N4" s="15"/>
-      <c r="O4" s="15"/>
-      <c r="P4" s="15"/>
-      <c r="Q4" s="15"/>
-      <c r="R4" s="15"/>
-      <c r="S4" s="15"/>
-      <c r="T4" s="15"/>
-      <c r="U4" s="15"/>
-      <c r="V4" s="15"/>
-      <c r="W4" s="15"/>
-      <c r="X4" s="15"/>
-      <c r="Y4" s="15"/>
-      <c r="Z4" s="16"/>
+      <c r="B4" s="15"/>
+      <c r="C4" s="16"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="16"/>
+      <c r="H4" s="16"/>
+      <c r="I4" s="16"/>
+      <c r="J4" s="16"/>
+      <c r="K4" s="16"/>
+      <c r="L4" s="16"/>
+      <c r="M4" s="16"/>
+      <c r="N4" s="16"/>
+      <c r="O4" s="16"/>
+      <c r="P4" s="16"/>
+      <c r="Q4" s="16"/>
+      <c r="R4" s="16"/>
+      <c r="S4" s="16"/>
+      <c r="T4" s="16"/>
+      <c r="U4" s="16"/>
+      <c r="V4" s="16"/>
+      <c r="W4" s="16"/>
+      <c r="X4" s="16"/>
+      <c r="Y4" s="16"/>
+      <c r="Z4" s="17"/>
     </row>
     <row r="6" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="U6" s="17" t="s">
+      <c r="U6" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="V6" s="18"/>
-      <c r="W6" s="18"/>
-      <c r="X6" s="18"/>
-      <c r="Y6" s="18"/>
-      <c r="Z6" s="19"/>
+      <c r="V6" s="19"/>
+      <c r="W6" s="19"/>
+      <c r="X6" s="19"/>
+      <c r="Y6" s="19"/>
+      <c r="Z6" s="20"/>
     </row>
     <row r="8" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B8" s="2">
@@ -2165,58 +3308,58 @@
       </c>
     </row>
     <row r="45" spans="3:26" x14ac:dyDescent="0.3">
-      <c r="C45" s="11" t="s">
+      <c r="C45" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="D45" s="12"/>
-      <c r="E45" s="12"/>
-      <c r="F45" s="12"/>
-      <c r="G45" s="12"/>
-      <c r="H45" s="12"/>
-      <c r="I45" s="12"/>
-      <c r="J45" s="12"/>
-      <c r="K45" s="12"/>
-      <c r="L45" s="12"/>
-      <c r="M45" s="12"/>
-      <c r="N45" s="12"/>
-      <c r="O45" s="12"/>
-      <c r="P45" s="12"/>
-      <c r="Q45" s="12"/>
-      <c r="R45" s="12"/>
-      <c r="S45" s="12"/>
-      <c r="T45" s="12"/>
-      <c r="U45" s="12"/>
-      <c r="V45" s="12"/>
-      <c r="W45" s="12"/>
-      <c r="X45" s="12"/>
-      <c r="Y45" s="12"/>
-      <c r="Z45" s="13"/>
+      <c r="D45" s="10"/>
+      <c r="E45" s="10"/>
+      <c r="F45" s="10"/>
+      <c r="G45" s="10"/>
+      <c r="H45" s="10"/>
+      <c r="I45" s="10"/>
+      <c r="J45" s="10"/>
+      <c r="K45" s="10"/>
+      <c r="L45" s="10"/>
+      <c r="M45" s="10"/>
+      <c r="N45" s="10"/>
+      <c r="O45" s="10"/>
+      <c r="P45" s="10"/>
+      <c r="Q45" s="10"/>
+      <c r="R45" s="10"/>
+      <c r="S45" s="10"/>
+      <c r="T45" s="10"/>
+      <c r="U45" s="10"/>
+      <c r="V45" s="10"/>
+      <c r="W45" s="10"/>
+      <c r="X45" s="10"/>
+      <c r="Y45" s="10"/>
+      <c r="Z45" s="11"/>
     </row>
     <row r="46" spans="3:26" x14ac:dyDescent="0.3">
-      <c r="C46" s="14"/>
-      <c r="D46" s="15"/>
-      <c r="E46" s="15"/>
-      <c r="F46" s="15"/>
-      <c r="G46" s="15"/>
-      <c r="H46" s="15"/>
-      <c r="I46" s="15"/>
-      <c r="J46" s="15"/>
-      <c r="K46" s="15"/>
-      <c r="L46" s="15"/>
-      <c r="M46" s="15"/>
-      <c r="N46" s="15"/>
-      <c r="O46" s="15"/>
-      <c r="P46" s="15"/>
-      <c r="Q46" s="15"/>
-      <c r="R46" s="15"/>
-      <c r="S46" s="15"/>
-      <c r="T46" s="15"/>
-      <c r="U46" s="15"/>
-      <c r="V46" s="15"/>
-      <c r="W46" s="15"/>
-      <c r="X46" s="15"/>
-      <c r="Y46" s="15"/>
-      <c r="Z46" s="16"/>
+      <c r="C46" s="15"/>
+      <c r="D46" s="16"/>
+      <c r="E46" s="16"/>
+      <c r="F46" s="16"/>
+      <c r="G46" s="16"/>
+      <c r="H46" s="16"/>
+      <c r="I46" s="16"/>
+      <c r="J46" s="16"/>
+      <c r="K46" s="16"/>
+      <c r="L46" s="16"/>
+      <c r="M46" s="16"/>
+      <c r="N46" s="16"/>
+      <c r="O46" s="16"/>
+      <c r="P46" s="16"/>
+      <c r="Q46" s="16"/>
+      <c r="R46" s="16"/>
+      <c r="S46" s="16"/>
+      <c r="T46" s="16"/>
+      <c r="U46" s="16"/>
+      <c r="V46" s="16"/>
+      <c r="W46" s="16"/>
+      <c r="X46" s="16"/>
+      <c r="Y46" s="16"/>
+      <c r="Z46" s="17"/>
     </row>
     <row r="48" spans="3:26" x14ac:dyDescent="0.3">
       <c r="D48" s="2" t="s">
@@ -2249,58 +3392,58 @@
       </c>
     </row>
     <row r="56" spans="3:26" x14ac:dyDescent="0.3">
-      <c r="C56" s="11" t="s">
+      <c r="C56" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="D56" s="12"/>
-      <c r="E56" s="12"/>
-      <c r="F56" s="12"/>
-      <c r="G56" s="12"/>
-      <c r="H56" s="12"/>
-      <c r="I56" s="12"/>
-      <c r="J56" s="12"/>
-      <c r="K56" s="12"/>
-      <c r="L56" s="12"/>
-      <c r="M56" s="12"/>
-      <c r="N56" s="12"/>
-      <c r="O56" s="12"/>
-      <c r="P56" s="12"/>
-      <c r="Q56" s="12"/>
-      <c r="R56" s="12"/>
-      <c r="S56" s="12"/>
-      <c r="T56" s="12"/>
-      <c r="U56" s="12"/>
-      <c r="V56" s="12"/>
-      <c r="W56" s="12"/>
-      <c r="X56" s="12"/>
-      <c r="Y56" s="12"/>
-      <c r="Z56" s="13"/>
+      <c r="D56" s="10"/>
+      <c r="E56" s="10"/>
+      <c r="F56" s="10"/>
+      <c r="G56" s="10"/>
+      <c r="H56" s="10"/>
+      <c r="I56" s="10"/>
+      <c r="J56" s="10"/>
+      <c r="K56" s="10"/>
+      <c r="L56" s="10"/>
+      <c r="M56" s="10"/>
+      <c r="N56" s="10"/>
+      <c r="O56" s="10"/>
+      <c r="P56" s="10"/>
+      <c r="Q56" s="10"/>
+      <c r="R56" s="10"/>
+      <c r="S56" s="10"/>
+      <c r="T56" s="10"/>
+      <c r="U56" s="10"/>
+      <c r="V56" s="10"/>
+      <c r="W56" s="10"/>
+      <c r="X56" s="10"/>
+      <c r="Y56" s="10"/>
+      <c r="Z56" s="11"/>
     </row>
     <row r="57" spans="3:26" x14ac:dyDescent="0.3">
-      <c r="C57" s="14"/>
-      <c r="D57" s="15"/>
-      <c r="E57" s="15"/>
-      <c r="F57" s="15"/>
-      <c r="G57" s="15"/>
-      <c r="H57" s="15"/>
-      <c r="I57" s="15"/>
-      <c r="J57" s="15"/>
-      <c r="K57" s="15"/>
-      <c r="L57" s="15"/>
-      <c r="M57" s="15"/>
-      <c r="N57" s="15"/>
-      <c r="O57" s="15"/>
-      <c r="P57" s="15"/>
-      <c r="Q57" s="15"/>
-      <c r="R57" s="15"/>
-      <c r="S57" s="15"/>
-      <c r="T57" s="15"/>
-      <c r="U57" s="15"/>
-      <c r="V57" s="15"/>
-      <c r="W57" s="15"/>
-      <c r="X57" s="15"/>
-      <c r="Y57" s="15"/>
-      <c r="Z57" s="16"/>
+      <c r="C57" s="15"/>
+      <c r="D57" s="16"/>
+      <c r="E57" s="16"/>
+      <c r="F57" s="16"/>
+      <c r="G57" s="16"/>
+      <c r="H57" s="16"/>
+      <c r="I57" s="16"/>
+      <c r="J57" s="16"/>
+      <c r="K57" s="16"/>
+      <c r="L57" s="16"/>
+      <c r="M57" s="16"/>
+      <c r="N57" s="16"/>
+      <c r="O57" s="16"/>
+      <c r="P57" s="16"/>
+      <c r="Q57" s="16"/>
+      <c r="R57" s="16"/>
+      <c r="S57" s="16"/>
+      <c r="T57" s="16"/>
+      <c r="U57" s="16"/>
+      <c r="V57" s="16"/>
+      <c r="W57" s="16"/>
+      <c r="X57" s="16"/>
+      <c r="Y57" s="16"/>
+      <c r="Z57" s="17"/>
     </row>
     <row r="59" spans="3:26" x14ac:dyDescent="0.3">
       <c r="D59" s="2" t="s">
@@ -2333,58 +3476,58 @@
       </c>
     </row>
     <row r="68" spans="3:26" x14ac:dyDescent="0.3">
-      <c r="C68" s="11" t="s">
+      <c r="C68" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="D68" s="12"/>
-      <c r="E68" s="12"/>
-      <c r="F68" s="12"/>
-      <c r="G68" s="12"/>
-      <c r="H68" s="12"/>
-      <c r="I68" s="12"/>
-      <c r="J68" s="12"/>
-      <c r="K68" s="12"/>
-      <c r="L68" s="12"/>
-      <c r="M68" s="12"/>
-      <c r="N68" s="12"/>
-      <c r="O68" s="12"/>
-      <c r="P68" s="12"/>
-      <c r="Q68" s="12"/>
-      <c r="R68" s="12"/>
-      <c r="S68" s="12"/>
-      <c r="T68" s="12"/>
-      <c r="U68" s="12"/>
-      <c r="V68" s="12"/>
-      <c r="W68" s="12"/>
-      <c r="X68" s="12"/>
-      <c r="Y68" s="12"/>
-      <c r="Z68" s="13"/>
+      <c r="D68" s="10"/>
+      <c r="E68" s="10"/>
+      <c r="F68" s="10"/>
+      <c r="G68" s="10"/>
+      <c r="H68" s="10"/>
+      <c r="I68" s="10"/>
+      <c r="J68" s="10"/>
+      <c r="K68" s="10"/>
+      <c r="L68" s="10"/>
+      <c r="M68" s="10"/>
+      <c r="N68" s="10"/>
+      <c r="O68" s="10"/>
+      <c r="P68" s="10"/>
+      <c r="Q68" s="10"/>
+      <c r="R68" s="10"/>
+      <c r="S68" s="10"/>
+      <c r="T68" s="10"/>
+      <c r="U68" s="10"/>
+      <c r="V68" s="10"/>
+      <c r="W68" s="10"/>
+      <c r="X68" s="10"/>
+      <c r="Y68" s="10"/>
+      <c r="Z68" s="11"/>
     </row>
     <row r="69" spans="3:26" x14ac:dyDescent="0.3">
-      <c r="C69" s="14"/>
-      <c r="D69" s="15"/>
-      <c r="E69" s="15"/>
-      <c r="F69" s="15"/>
-      <c r="G69" s="15"/>
-      <c r="H69" s="15"/>
-      <c r="I69" s="15"/>
-      <c r="J69" s="15"/>
-      <c r="K69" s="15"/>
-      <c r="L69" s="15"/>
-      <c r="M69" s="15"/>
-      <c r="N69" s="15"/>
-      <c r="O69" s="15"/>
-      <c r="P69" s="15"/>
-      <c r="Q69" s="15"/>
-      <c r="R69" s="15"/>
-      <c r="S69" s="15"/>
-      <c r="T69" s="15"/>
-      <c r="U69" s="15"/>
-      <c r="V69" s="15"/>
-      <c r="W69" s="15"/>
-      <c r="X69" s="15"/>
-      <c r="Y69" s="15"/>
-      <c r="Z69" s="16"/>
+      <c r="C69" s="15"/>
+      <c r="D69" s="16"/>
+      <c r="E69" s="16"/>
+      <c r="F69" s="16"/>
+      <c r="G69" s="16"/>
+      <c r="H69" s="16"/>
+      <c r="I69" s="16"/>
+      <c r="J69" s="16"/>
+      <c r="K69" s="16"/>
+      <c r="L69" s="16"/>
+      <c r="M69" s="16"/>
+      <c r="N69" s="16"/>
+      <c r="O69" s="16"/>
+      <c r="P69" s="16"/>
+      <c r="Q69" s="16"/>
+      <c r="R69" s="16"/>
+      <c r="S69" s="16"/>
+      <c r="T69" s="16"/>
+      <c r="U69" s="16"/>
+      <c r="V69" s="16"/>
+      <c r="W69" s="16"/>
+      <c r="X69" s="16"/>
+      <c r="Y69" s="16"/>
+      <c r="Z69" s="17"/>
     </row>
     <row r="71" spans="3:26" x14ac:dyDescent="0.3">
       <c r="D71" s="2" t="s">
@@ -2622,58 +3765,58 @@
       </c>
     </row>
     <row r="101" spans="3:26" x14ac:dyDescent="0.3">
-      <c r="C101" s="11" t="s">
+      <c r="C101" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="D101" s="12"/>
-      <c r="E101" s="12"/>
-      <c r="F101" s="12"/>
-      <c r="G101" s="12"/>
-      <c r="H101" s="12"/>
-      <c r="I101" s="12"/>
-      <c r="J101" s="12"/>
-      <c r="K101" s="12"/>
-      <c r="L101" s="12"/>
-      <c r="M101" s="12"/>
-      <c r="N101" s="12"/>
-      <c r="O101" s="12"/>
-      <c r="P101" s="12"/>
-      <c r="Q101" s="12"/>
-      <c r="R101" s="12"/>
-      <c r="S101" s="12"/>
-      <c r="T101" s="12"/>
-      <c r="U101" s="12"/>
-      <c r="V101" s="12"/>
-      <c r="W101" s="12"/>
-      <c r="X101" s="12"/>
-      <c r="Y101" s="12"/>
-      <c r="Z101" s="13"/>
+      <c r="D101" s="10"/>
+      <c r="E101" s="10"/>
+      <c r="F101" s="10"/>
+      <c r="G101" s="10"/>
+      <c r="H101" s="10"/>
+      <c r="I101" s="10"/>
+      <c r="J101" s="10"/>
+      <c r="K101" s="10"/>
+      <c r="L101" s="10"/>
+      <c r="M101" s="10"/>
+      <c r="N101" s="10"/>
+      <c r="O101" s="10"/>
+      <c r="P101" s="10"/>
+      <c r="Q101" s="10"/>
+      <c r="R101" s="10"/>
+      <c r="S101" s="10"/>
+      <c r="T101" s="10"/>
+      <c r="U101" s="10"/>
+      <c r="V101" s="10"/>
+      <c r="W101" s="10"/>
+      <c r="X101" s="10"/>
+      <c r="Y101" s="10"/>
+      <c r="Z101" s="11"/>
     </row>
     <row r="102" spans="3:26" x14ac:dyDescent="0.3">
-      <c r="C102" s="14"/>
-      <c r="D102" s="15"/>
-      <c r="E102" s="15"/>
-      <c r="F102" s="15"/>
-      <c r="G102" s="15"/>
-      <c r="H102" s="15"/>
-      <c r="I102" s="15"/>
-      <c r="J102" s="15"/>
-      <c r="K102" s="15"/>
-      <c r="L102" s="15"/>
-      <c r="M102" s="15"/>
-      <c r="N102" s="15"/>
-      <c r="O102" s="15"/>
-      <c r="P102" s="15"/>
-      <c r="Q102" s="15"/>
-      <c r="R102" s="15"/>
-      <c r="S102" s="15"/>
-      <c r="T102" s="15"/>
-      <c r="U102" s="15"/>
-      <c r="V102" s="15"/>
-      <c r="W102" s="15"/>
-      <c r="X102" s="15"/>
-      <c r="Y102" s="15"/>
-      <c r="Z102" s="16"/>
+      <c r="C102" s="15"/>
+      <c r="D102" s="16"/>
+      <c r="E102" s="16"/>
+      <c r="F102" s="16"/>
+      <c r="G102" s="16"/>
+      <c r="H102" s="16"/>
+      <c r="I102" s="16"/>
+      <c r="J102" s="16"/>
+      <c r="K102" s="16"/>
+      <c r="L102" s="16"/>
+      <c r="M102" s="16"/>
+      <c r="N102" s="16"/>
+      <c r="O102" s="16"/>
+      <c r="P102" s="16"/>
+      <c r="Q102" s="16"/>
+      <c r="R102" s="16"/>
+      <c r="S102" s="16"/>
+      <c r="T102" s="16"/>
+      <c r="U102" s="16"/>
+      <c r="V102" s="16"/>
+      <c r="W102" s="16"/>
+      <c r="X102" s="16"/>
+      <c r="Y102" s="16"/>
+      <c r="Z102" s="17"/>
     </row>
     <row r="104" spans="3:26" x14ac:dyDescent="0.3">
       <c r="D104" s="2" t="s">
@@ -2707,212 +3850,212 @@
       <c r="X106" s="8"/>
     </row>
     <row r="107" spans="3:26" x14ac:dyDescent="0.3">
-      <c r="E107" s="9" t="s">
+      <c r="E107" s="21" t="s">
         <v>96</v>
       </c>
-      <c r="F107" s="9"/>
-      <c r="G107" s="9"/>
-      <c r="H107" s="9"/>
-      <c r="I107" s="9"/>
-      <c r="J107" s="9"/>
-      <c r="K107" s="9" t="s">
+      <c r="F107" s="21"/>
+      <c r="G107" s="21"/>
+      <c r="H107" s="21"/>
+      <c r="I107" s="21"/>
+      <c r="J107" s="21"/>
+      <c r="K107" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="L107" s="9"/>
-      <c r="M107" s="9"/>
-      <c r="N107" s="9"/>
-      <c r="O107" s="9"/>
-      <c r="P107" s="9"/>
-      <c r="Q107" s="9"/>
-      <c r="R107" s="9"/>
-      <c r="S107" s="9"/>
-      <c r="T107" s="9"/>
-      <c r="U107" s="9"/>
-      <c r="V107" s="9"/>
-      <c r="W107" s="9"/>
-      <c r="X107" s="9"/>
+      <c r="L107" s="21"/>
+      <c r="M107" s="21"/>
+      <c r="N107" s="21"/>
+      <c r="O107" s="21"/>
+      <c r="P107" s="21"/>
+      <c r="Q107" s="21"/>
+      <c r="R107" s="21"/>
+      <c r="S107" s="21"/>
+      <c r="T107" s="21"/>
+      <c r="U107" s="21"/>
+      <c r="V107" s="21"/>
+      <c r="W107" s="21"/>
+      <c r="X107" s="21"/>
     </row>
     <row r="108" spans="3:26" x14ac:dyDescent="0.3">
-      <c r="E108" s="9" t="s">
+      <c r="E108" s="21" t="s">
         <v>97</v>
       </c>
-      <c r="F108" s="9"/>
-      <c r="G108" s="9"/>
-      <c r="H108" s="9"/>
-      <c r="I108" s="9"/>
-      <c r="J108" s="9"/>
-      <c r="K108" s="9" t="s">
+      <c r="F108" s="21"/>
+      <c r="G108" s="21"/>
+      <c r="H108" s="21"/>
+      <c r="I108" s="21"/>
+      <c r="J108" s="21"/>
+      <c r="K108" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="L108" s="9"/>
-      <c r="M108" s="9"/>
-      <c r="N108" s="9"/>
-      <c r="O108" s="9"/>
-      <c r="P108" s="9"/>
-      <c r="Q108" s="9"/>
-      <c r="R108" s="9"/>
-      <c r="S108" s="9"/>
-      <c r="T108" s="9"/>
-      <c r="U108" s="9"/>
-      <c r="V108" s="9"/>
-      <c r="W108" s="9"/>
-      <c r="X108" s="9"/>
+      <c r="L108" s="21"/>
+      <c r="M108" s="21"/>
+      <c r="N108" s="21"/>
+      <c r="O108" s="21"/>
+      <c r="P108" s="21"/>
+      <c r="Q108" s="21"/>
+      <c r="R108" s="21"/>
+      <c r="S108" s="21"/>
+      <c r="T108" s="21"/>
+      <c r="U108" s="21"/>
+      <c r="V108" s="21"/>
+      <c r="W108" s="21"/>
+      <c r="X108" s="21"/>
     </row>
     <row r="109" spans="3:26" x14ac:dyDescent="0.3">
-      <c r="E109" s="9" t="s">
+      <c r="E109" s="21" t="s">
         <v>98</v>
       </c>
-      <c r="F109" s="9"/>
-      <c r="G109" s="9"/>
-      <c r="H109" s="9"/>
-      <c r="I109" s="9"/>
-      <c r="J109" s="9"/>
-      <c r="K109" s="9" t="s">
+      <c r="F109" s="21"/>
+      <c r="G109" s="21"/>
+      <c r="H109" s="21"/>
+      <c r="I109" s="21"/>
+      <c r="J109" s="21"/>
+      <c r="K109" s="21" t="s">
         <v>105</v>
       </c>
-      <c r="L109" s="9"/>
-      <c r="M109" s="9"/>
-      <c r="N109" s="9"/>
-      <c r="O109" s="9"/>
-      <c r="P109" s="9"/>
-      <c r="Q109" s="9"/>
-      <c r="R109" s="9"/>
-      <c r="S109" s="9"/>
-      <c r="T109" s="9"/>
-      <c r="U109" s="9"/>
-      <c r="V109" s="9"/>
-      <c r="W109" s="9"/>
-      <c r="X109" s="9"/>
+      <c r="L109" s="21"/>
+      <c r="M109" s="21"/>
+      <c r="N109" s="21"/>
+      <c r="O109" s="21"/>
+      <c r="P109" s="21"/>
+      <c r="Q109" s="21"/>
+      <c r="R109" s="21"/>
+      <c r="S109" s="21"/>
+      <c r="T109" s="21"/>
+      <c r="U109" s="21"/>
+      <c r="V109" s="21"/>
+      <c r="W109" s="21"/>
+      <c r="X109" s="21"/>
     </row>
     <row r="110" spans="3:26" x14ac:dyDescent="0.3">
-      <c r="E110" s="9" t="s">
+      <c r="E110" s="21" t="s">
         <v>107</v>
       </c>
-      <c r="F110" s="9"/>
-      <c r="G110" s="9"/>
-      <c r="H110" s="9"/>
-      <c r="I110" s="9"/>
-      <c r="J110" s="9"/>
-      <c r="K110" s="9" t="s">
+      <c r="F110" s="21"/>
+      <c r="G110" s="21"/>
+      <c r="H110" s="21"/>
+      <c r="I110" s="21"/>
+      <c r="J110" s="21"/>
+      <c r="K110" s="21" t="s">
         <v>106</v>
       </c>
-      <c r="L110" s="9"/>
-      <c r="M110" s="9"/>
-      <c r="N110" s="9"/>
-      <c r="O110" s="9"/>
-      <c r="P110" s="9"/>
-      <c r="Q110" s="9"/>
-      <c r="R110" s="9"/>
-      <c r="S110" s="9"/>
-      <c r="T110" s="9"/>
-      <c r="U110" s="9"/>
-      <c r="V110" s="9"/>
-      <c r="W110" s="9"/>
-      <c r="X110" s="9"/>
+      <c r="L110" s="21"/>
+      <c r="M110" s="21"/>
+      <c r="N110" s="21"/>
+      <c r="O110" s="21"/>
+      <c r="P110" s="21"/>
+      <c r="Q110" s="21"/>
+      <c r="R110" s="21"/>
+      <c r="S110" s="21"/>
+      <c r="T110" s="21"/>
+      <c r="U110" s="21"/>
+      <c r="V110" s="21"/>
+      <c r="W110" s="21"/>
+      <c r="X110" s="21"/>
     </row>
     <row r="111" spans="3:26" x14ac:dyDescent="0.3">
-      <c r="E111" s="9" t="s">
+      <c r="E111" s="21" t="s">
         <v>99</v>
       </c>
-      <c r="F111" s="9"/>
-      <c r="G111" s="9"/>
-      <c r="H111" s="9"/>
-      <c r="I111" s="9"/>
-      <c r="J111" s="9"/>
-      <c r="K111" s="9" t="s">
+      <c r="F111" s="21"/>
+      <c r="G111" s="21"/>
+      <c r="H111" s="21"/>
+      <c r="I111" s="21"/>
+      <c r="J111" s="21"/>
+      <c r="K111" s="21" t="s">
         <v>108</v>
       </c>
-      <c r="L111" s="9"/>
-      <c r="M111" s="9"/>
-      <c r="N111" s="9"/>
-      <c r="O111" s="9"/>
-      <c r="P111" s="9"/>
-      <c r="Q111" s="9"/>
-      <c r="R111" s="9"/>
-      <c r="S111" s="9"/>
-      <c r="T111" s="9"/>
-      <c r="U111" s="9"/>
-      <c r="V111" s="9"/>
-      <c r="W111" s="9"/>
-      <c r="X111" s="9"/>
+      <c r="L111" s="21"/>
+      <c r="M111" s="21"/>
+      <c r="N111" s="21"/>
+      <c r="O111" s="21"/>
+      <c r="P111" s="21"/>
+      <c r="Q111" s="21"/>
+      <c r="R111" s="21"/>
+      <c r="S111" s="21"/>
+      <c r="T111" s="21"/>
+      <c r="U111" s="21"/>
+      <c r="V111" s="21"/>
+      <c r="W111" s="21"/>
+      <c r="X111" s="21"/>
     </row>
     <row r="112" spans="3:26" x14ac:dyDescent="0.3">
-      <c r="E112" s="9" t="s">
+      <c r="E112" s="21" t="s">
         <v>101</v>
       </c>
-      <c r="F112" s="9"/>
-      <c r="G112" s="9"/>
-      <c r="H112" s="9"/>
-      <c r="I112" s="9"/>
-      <c r="J112" s="9"/>
-      <c r="K112" s="9" t="s">
+      <c r="F112" s="21"/>
+      <c r="G112" s="21"/>
+      <c r="H112" s="21"/>
+      <c r="I112" s="21"/>
+      <c r="J112" s="21"/>
+      <c r="K112" s="21" t="s">
         <v>109</v>
       </c>
-      <c r="L112" s="9"/>
-      <c r="M112" s="9"/>
-      <c r="N112" s="9"/>
-      <c r="O112" s="9"/>
-      <c r="P112" s="9"/>
-      <c r="Q112" s="9"/>
-      <c r="R112" s="9"/>
-      <c r="S112" s="9"/>
-      <c r="T112" s="9"/>
-      <c r="U112" s="9"/>
-      <c r="V112" s="9"/>
-      <c r="W112" s="9"/>
-      <c r="X112" s="9"/>
+      <c r="L112" s="21"/>
+      <c r="M112" s="21"/>
+      <c r="N112" s="21"/>
+      <c r="O112" s="21"/>
+      <c r="P112" s="21"/>
+      <c r="Q112" s="21"/>
+      <c r="R112" s="21"/>
+      <c r="S112" s="21"/>
+      <c r="T112" s="21"/>
+      <c r="U112" s="21"/>
+      <c r="V112" s="21"/>
+      <c r="W112" s="21"/>
+      <c r="X112" s="21"/>
     </row>
     <row r="113" spans="4:25" x14ac:dyDescent="0.3">
-      <c r="E113" s="9" t="s">
+      <c r="E113" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="F113" s="9"/>
-      <c r="G113" s="9"/>
-      <c r="H113" s="9"/>
-      <c r="I113" s="9"/>
-      <c r="J113" s="9"/>
-      <c r="K113" s="9" t="s">
+      <c r="F113" s="21"/>
+      <c r="G113" s="21"/>
+      <c r="H113" s="21"/>
+      <c r="I113" s="21"/>
+      <c r="J113" s="21"/>
+      <c r="K113" s="21" t="s">
         <v>110</v>
       </c>
-      <c r="L113" s="9"/>
-      <c r="M113" s="9"/>
-      <c r="N113" s="9"/>
-      <c r="O113" s="9"/>
-      <c r="P113" s="9"/>
-      <c r="Q113" s="9"/>
-      <c r="R113" s="9"/>
-      <c r="S113" s="9"/>
-      <c r="T113" s="9"/>
-      <c r="U113" s="9"/>
-      <c r="V113" s="9"/>
-      <c r="W113" s="9"/>
-      <c r="X113" s="9"/>
+      <c r="L113" s="21"/>
+      <c r="M113" s="21"/>
+      <c r="N113" s="21"/>
+      <c r="O113" s="21"/>
+      <c r="P113" s="21"/>
+      <c r="Q113" s="21"/>
+      <c r="R113" s="21"/>
+      <c r="S113" s="21"/>
+      <c r="T113" s="21"/>
+      <c r="U113" s="21"/>
+      <c r="V113" s="21"/>
+      <c r="W113" s="21"/>
+      <c r="X113" s="21"/>
     </row>
     <row r="114" spans="4:25" x14ac:dyDescent="0.3">
-      <c r="E114" s="9" t="s">
+      <c r="E114" s="21" t="s">
         <v>100</v>
       </c>
-      <c r="F114" s="9"/>
-      <c r="G114" s="9"/>
-      <c r="H114" s="9"/>
-      <c r="I114" s="9"/>
-      <c r="J114" s="9"/>
-      <c r="K114" s="9" t="s">
+      <c r="F114" s="21"/>
+      <c r="G114" s="21"/>
+      <c r="H114" s="21"/>
+      <c r="I114" s="21"/>
+      <c r="J114" s="21"/>
+      <c r="K114" s="21" t="s">
         <v>111</v>
       </c>
-      <c r="L114" s="9"/>
-      <c r="M114" s="9"/>
-      <c r="N114" s="9"/>
-      <c r="O114" s="9"/>
-      <c r="P114" s="9"/>
-      <c r="Q114" s="9"/>
-      <c r="R114" s="9"/>
-      <c r="S114" s="9"/>
-      <c r="T114" s="9"/>
-      <c r="U114" s="9"/>
-      <c r="V114" s="9"/>
-      <c r="W114" s="9"/>
-      <c r="X114" s="9"/>
+      <c r="L114" s="21"/>
+      <c r="M114" s="21"/>
+      <c r="N114" s="21"/>
+      <c r="O114" s="21"/>
+      <c r="P114" s="21"/>
+      <c r="Q114" s="21"/>
+      <c r="R114" s="21"/>
+      <c r="S114" s="21"/>
+      <c r="T114" s="21"/>
+      <c r="U114" s="21"/>
+      <c r="V114" s="21"/>
+      <c r="W114" s="21"/>
+      <c r="X114" s="21"/>
     </row>
     <row r="116" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D116" s="2" t="s">
@@ -2940,14 +4083,14 @@
       <c r="J119" s="8"/>
     </row>
     <row r="120" spans="4:25" x14ac:dyDescent="0.3">
-      <c r="E120" s="17" t="s">
+      <c r="E120" s="18" t="s">
         <v>115</v>
       </c>
-      <c r="F120" s="18"/>
-      <c r="G120" s="18"/>
-      <c r="H120" s="18"/>
-      <c r="I120" s="18"/>
-      <c r="J120" s="19"/>
+      <c r="F120" s="19"/>
+      <c r="G120" s="19"/>
+      <c r="H120" s="19"/>
+      <c r="I120" s="19"/>
+      <c r="J120" s="20"/>
       <c r="K120" s="4" t="s">
         <v>117</v>
       </c>
@@ -3111,29 +4254,29 @@
       </c>
       <c r="F131" s="8"/>
       <c r="G131" s="8"/>
-      <c r="H131" s="10" t="s">
+      <c r="H131" s="22" t="s">
         <v>133</v>
       </c>
-      <c r="I131" s="10"/>
-      <c r="J131" s="10"/>
-      <c r="K131" s="10"/>
-      <c r="L131" s="10"/>
-      <c r="M131" s="10"/>
-      <c r="N131" s="10"/>
-      <c r="O131" s="10"/>
-      <c r="P131" s="10" t="s">
+      <c r="I131" s="22"/>
+      <c r="J131" s="22"/>
+      <c r="K131" s="22"/>
+      <c r="L131" s="22"/>
+      <c r="M131" s="22"/>
+      <c r="N131" s="22"/>
+      <c r="O131" s="22"/>
+      <c r="P131" s="22" t="s">
         <v>138</v>
       </c>
-      <c r="Q131" s="10"/>
-      <c r="R131" s="10"/>
-      <c r="S131" s="10"/>
-      <c r="T131" s="10"/>
-      <c r="U131" s="10"/>
-      <c r="V131" s="10"/>
-      <c r="W131" s="10"/>
-      <c r="X131" s="10"/>
-      <c r="Y131" s="10"/>
-      <c r="Z131" s="10"/>
+      <c r="Q131" s="22"/>
+      <c r="R131" s="22"/>
+      <c r="S131" s="22"/>
+      <c r="T131" s="22"/>
+      <c r="U131" s="22"/>
+      <c r="V131" s="22"/>
+      <c r="W131" s="22"/>
+      <c r="X131" s="22"/>
+      <c r="Y131" s="22"/>
+      <c r="Z131" s="22"/>
     </row>
     <row r="132" spans="3:26" x14ac:dyDescent="0.3">
       <c r="E132" s="8" t="s">
@@ -3141,29 +4284,29 @@
       </c>
       <c r="F132" s="8"/>
       <c r="G132" s="8"/>
-      <c r="H132" s="10" t="s">
+      <c r="H132" s="22" t="s">
         <v>134</v>
       </c>
-      <c r="I132" s="10"/>
-      <c r="J132" s="10"/>
-      <c r="K132" s="10"/>
-      <c r="L132" s="10"/>
-      <c r="M132" s="10"/>
-      <c r="N132" s="10"/>
-      <c r="O132" s="10"/>
-      <c r="P132" s="10" t="s">
+      <c r="I132" s="22"/>
+      <c r="J132" s="22"/>
+      <c r="K132" s="22"/>
+      <c r="L132" s="22"/>
+      <c r="M132" s="22"/>
+      <c r="N132" s="22"/>
+      <c r="O132" s="22"/>
+      <c r="P132" s="22" t="s">
         <v>139</v>
       </c>
-      <c r="Q132" s="10"/>
-      <c r="R132" s="10"/>
-      <c r="S132" s="10"/>
-      <c r="T132" s="10"/>
-      <c r="U132" s="10"/>
-      <c r="V132" s="10"/>
-      <c r="W132" s="10"/>
-      <c r="X132" s="10"/>
-      <c r="Y132" s="10"/>
-      <c r="Z132" s="10"/>
+      <c r="Q132" s="22"/>
+      <c r="R132" s="22"/>
+      <c r="S132" s="22"/>
+      <c r="T132" s="22"/>
+      <c r="U132" s="22"/>
+      <c r="V132" s="22"/>
+      <c r="W132" s="22"/>
+      <c r="X132" s="22"/>
+      <c r="Y132" s="22"/>
+      <c r="Z132" s="22"/>
     </row>
     <row r="133" spans="3:26" x14ac:dyDescent="0.3">
       <c r="E133" s="8" t="s">
@@ -3171,29 +4314,29 @@
       </c>
       <c r="F133" s="8"/>
       <c r="G133" s="8"/>
-      <c r="H133" s="10" t="s">
+      <c r="H133" s="22" t="s">
         <v>135</v>
       </c>
-      <c r="I133" s="10"/>
-      <c r="J133" s="10"/>
-      <c r="K133" s="10"/>
-      <c r="L133" s="10"/>
-      <c r="M133" s="10"/>
-      <c r="N133" s="10"/>
-      <c r="O133" s="10"/>
-      <c r="P133" s="10" t="s">
+      <c r="I133" s="22"/>
+      <c r="J133" s="22"/>
+      <c r="K133" s="22"/>
+      <c r="L133" s="22"/>
+      <c r="M133" s="22"/>
+      <c r="N133" s="22"/>
+      <c r="O133" s="22"/>
+      <c r="P133" s="22" t="s">
         <v>140</v>
       </c>
-      <c r="Q133" s="10"/>
-      <c r="R133" s="10"/>
-      <c r="S133" s="10"/>
-      <c r="T133" s="10"/>
-      <c r="U133" s="10"/>
-      <c r="V133" s="10"/>
-      <c r="W133" s="10"/>
-      <c r="X133" s="10"/>
-      <c r="Y133" s="10"/>
-      <c r="Z133" s="10"/>
+      <c r="Q133" s="22"/>
+      <c r="R133" s="22"/>
+      <c r="S133" s="22"/>
+      <c r="T133" s="22"/>
+      <c r="U133" s="22"/>
+      <c r="V133" s="22"/>
+      <c r="W133" s="22"/>
+      <c r="X133" s="22"/>
+      <c r="Y133" s="22"/>
+      <c r="Z133" s="22"/>
     </row>
     <row r="134" spans="3:26" x14ac:dyDescent="0.3">
       <c r="E134" s="8" t="s">
@@ -3201,83 +4344,83 @@
       </c>
       <c r="F134" s="8"/>
       <c r="G134" s="8"/>
-      <c r="H134" s="10" t="s">
+      <c r="H134" s="22" t="s">
         <v>136</v>
       </c>
-      <c r="I134" s="10"/>
-      <c r="J134" s="10"/>
-      <c r="K134" s="10"/>
-      <c r="L134" s="10"/>
-      <c r="M134" s="10"/>
-      <c r="N134" s="10"/>
-      <c r="O134" s="10"/>
-      <c r="P134" s="10" t="s">
+      <c r="I134" s="22"/>
+      <c r="J134" s="22"/>
+      <c r="K134" s="22"/>
+      <c r="L134" s="22"/>
+      <c r="M134" s="22"/>
+      <c r="N134" s="22"/>
+      <c r="O134" s="22"/>
+      <c r="P134" s="22" t="s">
         <v>141</v>
       </c>
-      <c r="Q134" s="10"/>
-      <c r="R134" s="10"/>
-      <c r="S134" s="10"/>
-      <c r="T134" s="10"/>
-      <c r="U134" s="10"/>
-      <c r="V134" s="10"/>
-      <c r="W134" s="10"/>
-      <c r="X134" s="10"/>
-      <c r="Y134" s="10"/>
-      <c r="Z134" s="10"/>
+      <c r="Q134" s="22"/>
+      <c r="R134" s="22"/>
+      <c r="S134" s="22"/>
+      <c r="T134" s="22"/>
+      <c r="U134" s="22"/>
+      <c r="V134" s="22"/>
+      <c r="W134" s="22"/>
+      <c r="X134" s="22"/>
+      <c r="Y134" s="22"/>
+      <c r="Z134" s="22"/>
     </row>
     <row r="136" spans="3:26" x14ac:dyDescent="0.3">
-      <c r="C136" s="11" t="s">
+      <c r="C136" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="D136" s="12"/>
-      <c r="E136" s="12"/>
-      <c r="F136" s="12"/>
-      <c r="G136" s="12"/>
-      <c r="H136" s="12"/>
-      <c r="I136" s="12"/>
-      <c r="J136" s="12"/>
-      <c r="K136" s="12"/>
-      <c r="L136" s="12"/>
-      <c r="M136" s="12"/>
-      <c r="N136" s="12"/>
-      <c r="O136" s="12"/>
-      <c r="P136" s="12"/>
-      <c r="Q136" s="12"/>
-      <c r="R136" s="12"/>
-      <c r="S136" s="12"/>
-      <c r="T136" s="12"/>
-      <c r="U136" s="12"/>
-      <c r="V136" s="12"/>
-      <c r="W136" s="12"/>
-      <c r="X136" s="12"/>
-      <c r="Y136" s="12"/>
-      <c r="Z136" s="13"/>
+      <c r="D136" s="10"/>
+      <c r="E136" s="10"/>
+      <c r="F136" s="10"/>
+      <c r="G136" s="10"/>
+      <c r="H136" s="10"/>
+      <c r="I136" s="10"/>
+      <c r="J136" s="10"/>
+      <c r="K136" s="10"/>
+      <c r="L136" s="10"/>
+      <c r="M136" s="10"/>
+      <c r="N136" s="10"/>
+      <c r="O136" s="10"/>
+      <c r="P136" s="10"/>
+      <c r="Q136" s="10"/>
+      <c r="R136" s="10"/>
+      <c r="S136" s="10"/>
+      <c r="T136" s="10"/>
+      <c r="U136" s="10"/>
+      <c r="V136" s="10"/>
+      <c r="W136" s="10"/>
+      <c r="X136" s="10"/>
+      <c r="Y136" s="10"/>
+      <c r="Z136" s="11"/>
     </row>
     <row r="137" spans="3:26" x14ac:dyDescent="0.3">
-      <c r="C137" s="14"/>
-      <c r="D137" s="15"/>
-      <c r="E137" s="15"/>
-      <c r="F137" s="15"/>
-      <c r="G137" s="15"/>
-      <c r="H137" s="15"/>
-      <c r="I137" s="15"/>
-      <c r="J137" s="15"/>
-      <c r="K137" s="15"/>
-      <c r="L137" s="15"/>
-      <c r="M137" s="15"/>
-      <c r="N137" s="15"/>
-      <c r="O137" s="15"/>
-      <c r="P137" s="15"/>
-      <c r="Q137" s="15"/>
-      <c r="R137" s="15"/>
-      <c r="S137" s="15"/>
-      <c r="T137" s="15"/>
-      <c r="U137" s="15"/>
-      <c r="V137" s="15"/>
-      <c r="W137" s="15"/>
-      <c r="X137" s="15"/>
-      <c r="Y137" s="15"/>
-      <c r="Z137" s="16"/>
+      <c r="C137" s="15"/>
+      <c r="D137" s="16"/>
+      <c r="E137" s="16"/>
+      <c r="F137" s="16"/>
+      <c r="G137" s="16"/>
+      <c r="H137" s="16"/>
+      <c r="I137" s="16"/>
+      <c r="J137" s="16"/>
+      <c r="K137" s="16"/>
+      <c r="L137" s="16"/>
+      <c r="M137" s="16"/>
+      <c r="N137" s="16"/>
+      <c r="O137" s="16"/>
+      <c r="P137" s="16"/>
+      <c r="Q137" s="16"/>
+      <c r="R137" s="16"/>
+      <c r="S137" s="16"/>
+      <c r="T137" s="16"/>
+      <c r="U137" s="16"/>
+      <c r="V137" s="16"/>
+      <c r="W137" s="16"/>
+      <c r="X137" s="16"/>
+      <c r="Y137" s="16"/>
+      <c r="Z137" s="17"/>
     </row>
     <row r="138" spans="3:26" x14ac:dyDescent="0.3">
       <c r="C138" s="5"/>
@@ -3338,260 +4481,260 @@
       <c r="Z139" s="8"/>
     </row>
     <row r="140" spans="3:26" x14ac:dyDescent="0.3">
-      <c r="C140" s="9" t="s">
+      <c r="C140" s="21" t="s">
         <v>170</v>
       </c>
-      <c r="D140" s="9"/>
-      <c r="E140" s="9"/>
-      <c r="F140" s="9"/>
-      <c r="G140" s="9"/>
-      <c r="H140" s="9"/>
+      <c r="D140" s="21"/>
+      <c r="E140" s="21"/>
+      <c r="F140" s="21"/>
+      <c r="G140" s="21"/>
+      <c r="H140" s="21"/>
       <c r="I140" s="8" t="s">
         <v>174</v>
       </c>
       <c r="J140" s="8"/>
       <c r="K140" s="8"/>
       <c r="L140" s="8"/>
-      <c r="M140" s="9" t="s">
+      <c r="M140" s="21" t="s">
         <v>181</v>
       </c>
-      <c r="N140" s="9"/>
-      <c r="O140" s="9"/>
-      <c r="P140" s="9"/>
-      <c r="Q140" s="9"/>
-      <c r="R140" s="9"/>
-      <c r="S140" s="9"/>
-      <c r="T140" s="9"/>
-      <c r="U140" s="9"/>
-      <c r="V140" s="9"/>
-      <c r="W140" s="9"/>
-      <c r="X140" s="9"/>
-      <c r="Y140" s="9"/>
-      <c r="Z140" s="9"/>
+      <c r="N140" s="21"/>
+      <c r="O140" s="21"/>
+      <c r="P140" s="21"/>
+      <c r="Q140" s="21"/>
+      <c r="R140" s="21"/>
+      <c r="S140" s="21"/>
+      <c r="T140" s="21"/>
+      <c r="U140" s="21"/>
+      <c r="V140" s="21"/>
+      <c r="W140" s="21"/>
+      <c r="X140" s="21"/>
+      <c r="Y140" s="21"/>
+      <c r="Z140" s="21"/>
     </row>
     <row r="141" spans="3:26" x14ac:dyDescent="0.3">
-      <c r="C141" s="9" t="s">
+      <c r="C141" s="21" t="s">
         <v>171</v>
       </c>
-      <c r="D141" s="9"/>
-      <c r="E141" s="9"/>
-      <c r="F141" s="9"/>
-      <c r="G141" s="9"/>
-      <c r="H141" s="9"/>
+      <c r="D141" s="21"/>
+      <c r="E141" s="21"/>
+      <c r="F141" s="21"/>
+      <c r="G141" s="21"/>
+      <c r="H141" s="21"/>
       <c r="I141" s="8" t="s">
         <v>175</v>
       </c>
       <c r="J141" s="8"/>
       <c r="K141" s="8"/>
       <c r="L141" s="8"/>
-      <c r="M141" s="9" t="s">
+      <c r="M141" s="21" t="s">
         <v>182</v>
       </c>
-      <c r="N141" s="9"/>
-      <c r="O141" s="9"/>
-      <c r="P141" s="9"/>
-      <c r="Q141" s="9"/>
-      <c r="R141" s="9"/>
-      <c r="S141" s="9"/>
-      <c r="T141" s="9"/>
-      <c r="U141" s="9"/>
-      <c r="V141" s="9"/>
-      <c r="W141" s="9"/>
-      <c r="X141" s="9"/>
-      <c r="Y141" s="9"/>
-      <c r="Z141" s="9"/>
+      <c r="N141" s="21"/>
+      <c r="O141" s="21"/>
+      <c r="P141" s="21"/>
+      <c r="Q141" s="21"/>
+      <c r="R141" s="21"/>
+      <c r="S141" s="21"/>
+      <c r="T141" s="21"/>
+      <c r="U141" s="21"/>
+      <c r="V141" s="21"/>
+      <c r="W141" s="21"/>
+      <c r="X141" s="21"/>
+      <c r="Y141" s="21"/>
+      <c r="Z141" s="21"/>
     </row>
     <row r="142" spans="3:26" x14ac:dyDescent="0.3">
-      <c r="C142" s="9" t="s">
+      <c r="C142" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="D142" s="9"/>
-      <c r="E142" s="9"/>
-      <c r="F142" s="9"/>
-      <c r="G142" s="9"/>
-      <c r="H142" s="9"/>
+      <c r="D142" s="21"/>
+      <c r="E142" s="21"/>
+      <c r="F142" s="21"/>
+      <c r="G142" s="21"/>
+      <c r="H142" s="21"/>
       <c r="I142" s="8" t="s">
         <v>176</v>
       </c>
       <c r="J142" s="8"/>
       <c r="K142" s="8"/>
       <c r="L142" s="8"/>
-      <c r="M142" s="9" t="s">
+      <c r="M142" s="21" t="s">
         <v>183</v>
       </c>
-      <c r="N142" s="9"/>
-      <c r="O142" s="9"/>
-      <c r="P142" s="9"/>
-      <c r="Q142" s="9"/>
-      <c r="R142" s="9"/>
-      <c r="S142" s="9"/>
-      <c r="T142" s="9"/>
-      <c r="U142" s="9"/>
-      <c r="V142" s="9"/>
-      <c r="W142" s="9"/>
-      <c r="X142" s="9"/>
-      <c r="Y142" s="9"/>
-      <c r="Z142" s="9"/>
+      <c r="N142" s="21"/>
+      <c r="O142" s="21"/>
+      <c r="P142" s="21"/>
+      <c r="Q142" s="21"/>
+      <c r="R142" s="21"/>
+      <c r="S142" s="21"/>
+      <c r="T142" s="21"/>
+      <c r="U142" s="21"/>
+      <c r="V142" s="21"/>
+      <c r="W142" s="21"/>
+      <c r="X142" s="21"/>
+      <c r="Y142" s="21"/>
+      <c r="Z142" s="21"/>
     </row>
     <row r="143" spans="3:26" x14ac:dyDescent="0.3">
-      <c r="C143" s="9" t="s">
+      <c r="C143" s="21" t="s">
         <v>177</v>
       </c>
-      <c r="D143" s="9"/>
-      <c r="E143" s="9"/>
-      <c r="F143" s="9"/>
-      <c r="G143" s="9"/>
-      <c r="H143" s="9"/>
+      <c r="D143" s="21"/>
+      <c r="E143" s="21"/>
+      <c r="F143" s="21"/>
+      <c r="G143" s="21"/>
+      <c r="H143" s="21"/>
       <c r="I143" s="8" t="s">
         <v>176</v>
       </c>
       <c r="J143" s="8"/>
       <c r="K143" s="8"/>
       <c r="L143" s="8"/>
-      <c r="M143" s="9" t="s">
+      <c r="M143" s="21" t="s">
         <v>184</v>
       </c>
-      <c r="N143" s="9"/>
-      <c r="O143" s="9"/>
-      <c r="P143" s="9"/>
-      <c r="Q143" s="9"/>
-      <c r="R143" s="9"/>
-      <c r="S143" s="9"/>
-      <c r="T143" s="9"/>
-      <c r="U143" s="9"/>
-      <c r="V143" s="9"/>
-      <c r="W143" s="9"/>
-      <c r="X143" s="9"/>
-      <c r="Y143" s="9"/>
-      <c r="Z143" s="9"/>
+      <c r="N143" s="21"/>
+      <c r="O143" s="21"/>
+      <c r="P143" s="21"/>
+      <c r="Q143" s="21"/>
+      <c r="R143" s="21"/>
+      <c r="S143" s="21"/>
+      <c r="T143" s="21"/>
+      <c r="U143" s="21"/>
+      <c r="V143" s="21"/>
+      <c r="W143" s="21"/>
+      <c r="X143" s="21"/>
+      <c r="Y143" s="21"/>
+      <c r="Z143" s="21"/>
     </row>
     <row r="144" spans="3:26" x14ac:dyDescent="0.3">
-      <c r="C144" s="9" t="s">
+      <c r="C144" s="21" t="s">
         <v>178</v>
       </c>
-      <c r="D144" s="9"/>
-      <c r="E144" s="9"/>
-      <c r="F144" s="9"/>
-      <c r="G144" s="9"/>
-      <c r="H144" s="9"/>
+      <c r="D144" s="21"/>
+      <c r="E144" s="21"/>
+      <c r="F144" s="21"/>
+      <c r="G144" s="21"/>
+      <c r="H144" s="21"/>
       <c r="I144" s="8" t="s">
         <v>176</v>
       </c>
       <c r="J144" s="8"/>
       <c r="K144" s="8"/>
       <c r="L144" s="8"/>
-      <c r="M144" s="9" t="s">
+      <c r="M144" s="21" t="s">
         <v>190</v>
       </c>
-      <c r="N144" s="9"/>
-      <c r="O144" s="9"/>
-      <c r="P144" s="9"/>
-      <c r="Q144" s="9"/>
-      <c r="R144" s="9"/>
-      <c r="S144" s="9"/>
-      <c r="T144" s="9"/>
-      <c r="U144" s="9"/>
-      <c r="V144" s="9"/>
-      <c r="W144" s="9"/>
-      <c r="X144" s="9"/>
-      <c r="Y144" s="9"/>
-      <c r="Z144" s="9"/>
+      <c r="N144" s="21"/>
+      <c r="O144" s="21"/>
+      <c r="P144" s="21"/>
+      <c r="Q144" s="21"/>
+      <c r="R144" s="21"/>
+      <c r="S144" s="21"/>
+      <c r="T144" s="21"/>
+      <c r="U144" s="21"/>
+      <c r="V144" s="21"/>
+      <c r="W144" s="21"/>
+      <c r="X144" s="21"/>
+      <c r="Y144" s="21"/>
+      <c r="Z144" s="21"/>
     </row>
     <row r="145" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="C145" s="9" t="s">
+      <c r="C145" s="21" t="s">
         <v>186</v>
       </c>
-      <c r="D145" s="9"/>
-      <c r="E145" s="9"/>
-      <c r="F145" s="9"/>
-      <c r="G145" s="9"/>
-      <c r="H145" s="9"/>
+      <c r="D145" s="21"/>
+      <c r="E145" s="21"/>
+      <c r="F145" s="21"/>
+      <c r="G145" s="21"/>
+      <c r="H145" s="21"/>
       <c r="I145" s="8" t="s">
         <v>176</v>
       </c>
       <c r="J145" s="8"/>
       <c r="K145" s="8"/>
       <c r="L145" s="8"/>
-      <c r="M145" s="9" t="s">
+      <c r="M145" s="21" t="s">
         <v>185</v>
       </c>
-      <c r="N145" s="9"/>
-      <c r="O145" s="9"/>
-      <c r="P145" s="9"/>
-      <c r="Q145" s="9"/>
-      <c r="R145" s="9"/>
-      <c r="S145" s="9"/>
-      <c r="T145" s="9"/>
-      <c r="U145" s="9"/>
-      <c r="V145" s="9"/>
-      <c r="W145" s="9"/>
-      <c r="X145" s="9"/>
-      <c r="Y145" s="9"/>
-      <c r="Z145" s="9"/>
+      <c r="N145" s="21"/>
+      <c r="O145" s="21"/>
+      <c r="P145" s="21"/>
+      <c r="Q145" s="21"/>
+      <c r="R145" s="21"/>
+      <c r="S145" s="21"/>
+      <c r="T145" s="21"/>
+      <c r="U145" s="21"/>
+      <c r="V145" s="21"/>
+      <c r="W145" s="21"/>
+      <c r="X145" s="21"/>
+      <c r="Y145" s="21"/>
+      <c r="Z145" s="21"/>
     </row>
     <row r="146" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="C146" s="9" t="s">
+      <c r="C146" s="21" t="s">
         <v>179</v>
       </c>
-      <c r="D146" s="9"/>
-      <c r="E146" s="9"/>
-      <c r="F146" s="9"/>
-      <c r="G146" s="9"/>
-      <c r="H146" s="9"/>
+      <c r="D146" s="21"/>
+      <c r="E146" s="21"/>
+      <c r="F146" s="21"/>
+      <c r="G146" s="21"/>
+      <c r="H146" s="21"/>
       <c r="I146" s="8" t="s">
         <v>176</v>
       </c>
       <c r="J146" s="8"/>
       <c r="K146" s="8"/>
       <c r="L146" s="8"/>
-      <c r="M146" s="9" t="s">
+      <c r="M146" s="21" t="s">
         <v>188</v>
       </c>
-      <c r="N146" s="9"/>
-      <c r="O146" s="9"/>
-      <c r="P146" s="9"/>
-      <c r="Q146" s="9"/>
-      <c r="R146" s="9"/>
-      <c r="S146" s="9"/>
-      <c r="T146" s="9"/>
-      <c r="U146" s="9"/>
-      <c r="V146" s="9"/>
-      <c r="W146" s="9"/>
-      <c r="X146" s="9"/>
-      <c r="Y146" s="9"/>
-      <c r="Z146" s="9"/>
+      <c r="N146" s="21"/>
+      <c r="O146" s="21"/>
+      <c r="P146" s="21"/>
+      <c r="Q146" s="21"/>
+      <c r="R146" s="21"/>
+      <c r="S146" s="21"/>
+      <c r="T146" s="21"/>
+      <c r="U146" s="21"/>
+      <c r="V146" s="21"/>
+      <c r="W146" s="21"/>
+      <c r="X146" s="21"/>
+      <c r="Y146" s="21"/>
+      <c r="Z146" s="21"/>
     </row>
     <row r="147" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="C147" s="9" t="s">
+      <c r="C147" s="21" t="s">
         <v>187</v>
       </c>
-      <c r="D147" s="9"/>
-      <c r="E147" s="9"/>
-      <c r="F147" s="9"/>
-      <c r="G147" s="9"/>
-      <c r="H147" s="9"/>
+      <c r="D147" s="21"/>
+      <c r="E147" s="21"/>
+      <c r="F147" s="21"/>
+      <c r="G147" s="21"/>
+      <c r="H147" s="21"/>
       <c r="I147" s="8" t="s">
         <v>176</v>
       </c>
       <c r="J147" s="8"/>
       <c r="K147" s="8"/>
       <c r="L147" s="8"/>
-      <c r="M147" s="9" t="s">
+      <c r="M147" s="21" t="s">
         <v>189</v>
       </c>
-      <c r="N147" s="9"/>
-      <c r="O147" s="9"/>
-      <c r="P147" s="9"/>
-      <c r="Q147" s="9"/>
-      <c r="R147" s="9"/>
-      <c r="S147" s="9"/>
-      <c r="T147" s="9"/>
-      <c r="U147" s="9"/>
-      <c r="V147" s="9"/>
-      <c r="W147" s="9"/>
-      <c r="X147" s="9"/>
-      <c r="Y147" s="9"/>
-      <c r="Z147" s="9"/>
+      <c r="N147" s="21"/>
+      <c r="O147" s="21"/>
+      <c r="P147" s="21"/>
+      <c r="Q147" s="21"/>
+      <c r="R147" s="21"/>
+      <c r="S147" s="21"/>
+      <c r="T147" s="21"/>
+      <c r="U147" s="21"/>
+      <c r="V147" s="21"/>
+      <c r="W147" s="21"/>
+      <c r="X147" s="21"/>
+      <c r="Y147" s="21"/>
+      <c r="Z147" s="21"/>
     </row>
     <row r="149" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B149" s="8" t="s">
@@ -3651,14 +4794,80 @@
     </row>
   </sheetData>
   <mergeCells count="95">
-    <mergeCell ref="E80:G80"/>
-    <mergeCell ref="U80:X80"/>
-    <mergeCell ref="B2:Z4"/>
-    <mergeCell ref="U6:Z6"/>
-    <mergeCell ref="C45:Z46"/>
-    <mergeCell ref="C56:Z57"/>
-    <mergeCell ref="C68:Z69"/>
-    <mergeCell ref="H80:T80"/>
+    <mergeCell ref="M143:Z143"/>
+    <mergeCell ref="B149:Z150"/>
+    <mergeCell ref="I144:L144"/>
+    <mergeCell ref="I145:L145"/>
+    <mergeCell ref="I146:L146"/>
+    <mergeCell ref="I147:L147"/>
+    <mergeCell ref="M144:Z144"/>
+    <mergeCell ref="C147:H147"/>
+    <mergeCell ref="M145:Z145"/>
+    <mergeCell ref="M146:Z146"/>
+    <mergeCell ref="M147:Z147"/>
+    <mergeCell ref="I143:L143"/>
+    <mergeCell ref="C143:H143"/>
+    <mergeCell ref="C144:H144"/>
+    <mergeCell ref="C145:H145"/>
+    <mergeCell ref="C146:H146"/>
+    <mergeCell ref="C140:H140"/>
+    <mergeCell ref="C139:H139"/>
+    <mergeCell ref="C141:H141"/>
+    <mergeCell ref="C142:H142"/>
+    <mergeCell ref="P134:Z134"/>
+    <mergeCell ref="C136:Z137"/>
+    <mergeCell ref="E134:G134"/>
+    <mergeCell ref="H134:O134"/>
+    <mergeCell ref="I139:L139"/>
+    <mergeCell ref="I140:L140"/>
+    <mergeCell ref="I141:L141"/>
+    <mergeCell ref="I142:L142"/>
+    <mergeCell ref="M139:Z139"/>
+    <mergeCell ref="M140:Z140"/>
+    <mergeCell ref="M141:Z141"/>
+    <mergeCell ref="M142:Z142"/>
+    <mergeCell ref="E133:G133"/>
+    <mergeCell ref="P130:Z130"/>
+    <mergeCell ref="P131:Z131"/>
+    <mergeCell ref="P132:Z132"/>
+    <mergeCell ref="P133:Z133"/>
+    <mergeCell ref="E130:G130"/>
+    <mergeCell ref="H130:O130"/>
+    <mergeCell ref="H131:O131"/>
+    <mergeCell ref="H132:O132"/>
+    <mergeCell ref="H133:O133"/>
+    <mergeCell ref="N124:Y124"/>
+    <mergeCell ref="E126:J126"/>
+    <mergeCell ref="L126:Y126"/>
+    <mergeCell ref="E131:G131"/>
+    <mergeCell ref="E132:G132"/>
+    <mergeCell ref="E125:J125"/>
+    <mergeCell ref="L120:Y120"/>
+    <mergeCell ref="E114:J114"/>
+    <mergeCell ref="E112:J112"/>
+    <mergeCell ref="E113:J113"/>
+    <mergeCell ref="K111:X111"/>
+    <mergeCell ref="K112:X112"/>
+    <mergeCell ref="K113:X113"/>
+    <mergeCell ref="K114:X114"/>
+    <mergeCell ref="E118:J118"/>
+    <mergeCell ref="E121:J121"/>
+    <mergeCell ref="E122:J122"/>
+    <mergeCell ref="E123:J123"/>
+    <mergeCell ref="E124:J124"/>
+    <mergeCell ref="E106:J106"/>
+    <mergeCell ref="E119:J119"/>
+    <mergeCell ref="E120:J120"/>
+    <mergeCell ref="K106:X106"/>
+    <mergeCell ref="K107:X107"/>
+    <mergeCell ref="K108:X108"/>
+    <mergeCell ref="K109:X109"/>
+    <mergeCell ref="E107:J107"/>
+    <mergeCell ref="K110:X110"/>
+    <mergeCell ref="E108:J108"/>
+    <mergeCell ref="E109:J109"/>
+    <mergeCell ref="E110:J110"/>
+    <mergeCell ref="E111:J111"/>
     <mergeCell ref="C101:Z102"/>
     <mergeCell ref="E81:G81"/>
     <mergeCell ref="E82:G82"/>
@@ -3672,80 +4881,14 @@
     <mergeCell ref="U82:X82"/>
     <mergeCell ref="U83:X83"/>
     <mergeCell ref="U84:X84"/>
-    <mergeCell ref="K110:X110"/>
-    <mergeCell ref="E108:J108"/>
-    <mergeCell ref="E109:J109"/>
-    <mergeCell ref="E110:J110"/>
-    <mergeCell ref="E111:J111"/>
-    <mergeCell ref="K106:X106"/>
-    <mergeCell ref="K107:X107"/>
-    <mergeCell ref="K108:X108"/>
-    <mergeCell ref="K109:X109"/>
-    <mergeCell ref="E107:J107"/>
-    <mergeCell ref="E121:J121"/>
-    <mergeCell ref="E122:J122"/>
-    <mergeCell ref="E123:J123"/>
-    <mergeCell ref="E124:J124"/>
-    <mergeCell ref="E106:J106"/>
-    <mergeCell ref="E119:J119"/>
-    <mergeCell ref="E120:J120"/>
-    <mergeCell ref="L120:Y120"/>
-    <mergeCell ref="E114:J114"/>
-    <mergeCell ref="E112:J112"/>
-    <mergeCell ref="E113:J113"/>
-    <mergeCell ref="K111:X111"/>
-    <mergeCell ref="K112:X112"/>
-    <mergeCell ref="K113:X113"/>
-    <mergeCell ref="K114:X114"/>
-    <mergeCell ref="E118:J118"/>
-    <mergeCell ref="N124:Y124"/>
-    <mergeCell ref="E126:J126"/>
-    <mergeCell ref="L126:Y126"/>
-    <mergeCell ref="E131:G131"/>
-    <mergeCell ref="E132:G132"/>
-    <mergeCell ref="E125:J125"/>
-    <mergeCell ref="E133:G133"/>
-    <mergeCell ref="P130:Z130"/>
-    <mergeCell ref="P131:Z131"/>
-    <mergeCell ref="P132:Z132"/>
-    <mergeCell ref="P133:Z133"/>
-    <mergeCell ref="E130:G130"/>
-    <mergeCell ref="H130:O130"/>
-    <mergeCell ref="H131:O131"/>
-    <mergeCell ref="H132:O132"/>
-    <mergeCell ref="H133:O133"/>
-    <mergeCell ref="C140:H140"/>
-    <mergeCell ref="C139:H139"/>
-    <mergeCell ref="C141:H141"/>
-    <mergeCell ref="C142:H142"/>
-    <mergeCell ref="P134:Z134"/>
-    <mergeCell ref="C136:Z137"/>
-    <mergeCell ref="E134:G134"/>
-    <mergeCell ref="H134:O134"/>
-    <mergeCell ref="I139:L139"/>
-    <mergeCell ref="I140:L140"/>
-    <mergeCell ref="I141:L141"/>
-    <mergeCell ref="I142:L142"/>
-    <mergeCell ref="I143:L143"/>
-    <mergeCell ref="C143:H143"/>
-    <mergeCell ref="C144:H144"/>
-    <mergeCell ref="C145:H145"/>
-    <mergeCell ref="C146:H146"/>
-    <mergeCell ref="M139:Z139"/>
-    <mergeCell ref="M140:Z140"/>
-    <mergeCell ref="M141:Z141"/>
-    <mergeCell ref="M142:Z142"/>
-    <mergeCell ref="M143:Z143"/>
-    <mergeCell ref="B149:Z150"/>
-    <mergeCell ref="I144:L144"/>
-    <mergeCell ref="I145:L145"/>
-    <mergeCell ref="I146:L146"/>
-    <mergeCell ref="I147:L147"/>
-    <mergeCell ref="M144:Z144"/>
-    <mergeCell ref="C147:H147"/>
-    <mergeCell ref="M145:Z145"/>
-    <mergeCell ref="M146:Z146"/>
-    <mergeCell ref="M147:Z147"/>
+    <mergeCell ref="E80:G80"/>
+    <mergeCell ref="U80:X80"/>
+    <mergeCell ref="B2:Z4"/>
+    <mergeCell ref="U6:Z6"/>
+    <mergeCell ref="C45:Z46"/>
+    <mergeCell ref="C56:Z57"/>
+    <mergeCell ref="C68:Z69"/>
+    <mergeCell ref="H80:T80"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4094,54 +5237,54 @@
       <c r="AR2" s="29"/>
       <c r="AS2" s="29"/>
       <c r="AT2" s="29"/>
-      <c r="AU2" s="31" t="s">
+      <c r="AU2" s="26" t="s">
         <v>117</v>
       </c>
-      <c r="AV2" s="23" t="s">
+      <c r="AV2" s="30" t="s">
         <v>157</v>
       </c>
-      <c r="AW2" s="24"/>
-      <c r="AX2" s="24"/>
-      <c r="AY2" s="24"/>
-      <c r="AZ2" s="24"/>
-      <c r="BA2" s="24"/>
-      <c r="BB2" s="24"/>
-      <c r="BC2" s="24"/>
-      <c r="BD2" s="25"/>
+      <c r="AW2" s="31"/>
+      <c r="AX2" s="31"/>
+      <c r="AY2" s="31"/>
+      <c r="AZ2" s="31"/>
+      <c r="BA2" s="31"/>
+      <c r="BB2" s="31"/>
+      <c r="BC2" s="31"/>
+      <c r="BD2" s="32"/>
     </row>
     <row r="3" spans="28:56" x14ac:dyDescent="0.3">
-      <c r="AC3" s="30" t="s">
+      <c r="AC3" s="28" t="s">
         <v>114</v>
       </c>
-      <c r="AD3" s="30"/>
-      <c r="AE3" s="30"/>
-      <c r="AF3" s="30"/>
-      <c r="AG3" s="30"/>
-      <c r="AH3" s="30"/>
-      <c r="AI3" s="30"/>
-      <c r="AJ3" s="30"/>
-      <c r="AK3" s="30"/>
-      <c r="AL3" s="30"/>
-      <c r="AM3" s="30"/>
-      <c r="AN3" s="30"/>
-      <c r="AO3" s="30"/>
-      <c r="AP3" s="30"/>
-      <c r="AQ3" s="30"/>
-      <c r="AR3" s="30"/>
-      <c r="AS3" s="30"/>
-      <c r="AT3" s="30"/>
-      <c r="AU3" s="32"/>
-      <c r="AV3" s="26" t="s">
+      <c r="AD3" s="28"/>
+      <c r="AE3" s="28"/>
+      <c r="AF3" s="28"/>
+      <c r="AG3" s="28"/>
+      <c r="AH3" s="28"/>
+      <c r="AI3" s="28"/>
+      <c r="AJ3" s="28"/>
+      <c r="AK3" s="28"/>
+      <c r="AL3" s="28"/>
+      <c r="AM3" s="28"/>
+      <c r="AN3" s="28"/>
+      <c r="AO3" s="28"/>
+      <c r="AP3" s="28"/>
+      <c r="AQ3" s="28"/>
+      <c r="AR3" s="28"/>
+      <c r="AS3" s="28"/>
+      <c r="AT3" s="28"/>
+      <c r="AU3" s="27"/>
+      <c r="AV3" s="23" t="s">
         <v>147</v>
       </c>
-      <c r="AW3" s="27"/>
-      <c r="AX3" s="27"/>
-      <c r="AY3" s="27"/>
-      <c r="AZ3" s="27"/>
-      <c r="BA3" s="27"/>
-      <c r="BB3" s="27"/>
-      <c r="BC3" s="27"/>
-      <c r="BD3" s="28"/>
+      <c r="AW3" s="24"/>
+      <c r="AX3" s="24"/>
+      <c r="AY3" s="24"/>
+      <c r="AZ3" s="24"/>
+      <c r="BA3" s="24"/>
+      <c r="BB3" s="24"/>
+      <c r="BC3" s="24"/>
+      <c r="BD3" s="25"/>
     </row>
     <row r="4" spans="28:56" x14ac:dyDescent="0.3">
       <c r="AC4" s="29" t="s">
@@ -4168,54 +5311,54 @@
       <c r="AR4" s="29"/>
       <c r="AS4" s="29"/>
       <c r="AT4" s="29"/>
-      <c r="AU4" s="31" t="s">
+      <c r="AU4" s="26" t="s">
         <v>117</v>
       </c>
-      <c r="AV4" s="23" t="s">
+      <c r="AV4" s="30" t="s">
         <v>158</v>
       </c>
-      <c r="AW4" s="24"/>
-      <c r="AX4" s="24"/>
-      <c r="AY4" s="24"/>
-      <c r="AZ4" s="24"/>
-      <c r="BA4" s="24"/>
-      <c r="BB4" s="24"/>
-      <c r="BC4" s="24"/>
-      <c r="BD4" s="25"/>
+      <c r="AW4" s="31"/>
+      <c r="AX4" s="31"/>
+      <c r="AY4" s="31"/>
+      <c r="AZ4" s="31"/>
+      <c r="BA4" s="31"/>
+      <c r="BB4" s="31"/>
+      <c r="BC4" s="31"/>
+      <c r="BD4" s="32"/>
     </row>
     <row r="5" spans="28:56" x14ac:dyDescent="0.3">
-      <c r="AC5" s="30" t="s">
+      <c r="AC5" s="28" t="s">
         <v>114</v>
       </c>
-      <c r="AD5" s="30"/>
-      <c r="AE5" s="30"/>
-      <c r="AF5" s="30"/>
-      <c r="AG5" s="30"/>
-      <c r="AH5" s="30"/>
-      <c r="AI5" s="30"/>
-      <c r="AJ5" s="30"/>
-      <c r="AK5" s="30"/>
-      <c r="AL5" s="30"/>
-      <c r="AM5" s="30"/>
-      <c r="AN5" s="30"/>
-      <c r="AO5" s="30"/>
-      <c r="AP5" s="30"/>
-      <c r="AQ5" s="30"/>
-      <c r="AR5" s="30"/>
-      <c r="AS5" s="30"/>
-      <c r="AT5" s="30"/>
-      <c r="AU5" s="32"/>
-      <c r="AV5" s="26" t="s">
+      <c r="AD5" s="28"/>
+      <c r="AE5" s="28"/>
+      <c r="AF5" s="28"/>
+      <c r="AG5" s="28"/>
+      <c r="AH5" s="28"/>
+      <c r="AI5" s="28"/>
+      <c r="AJ5" s="28"/>
+      <c r="AK5" s="28"/>
+      <c r="AL5" s="28"/>
+      <c r="AM5" s="28"/>
+      <c r="AN5" s="28"/>
+      <c r="AO5" s="28"/>
+      <c r="AP5" s="28"/>
+      <c r="AQ5" s="28"/>
+      <c r="AR5" s="28"/>
+      <c r="AS5" s="28"/>
+      <c r="AT5" s="28"/>
+      <c r="AU5" s="27"/>
+      <c r="AV5" s="23" t="s">
         <v>159</v>
       </c>
-      <c r="AW5" s="27"/>
-      <c r="AX5" s="27"/>
-      <c r="AY5" s="27"/>
-      <c r="AZ5" s="27"/>
-      <c r="BA5" s="27"/>
-      <c r="BB5" s="27"/>
-      <c r="BC5" s="27"/>
-      <c r="BD5" s="28"/>
+      <c r="AW5" s="24"/>
+      <c r="AX5" s="24"/>
+      <c r="AY5" s="24"/>
+      <c r="AZ5" s="24"/>
+      <c r="BA5" s="24"/>
+      <c r="BB5" s="24"/>
+      <c r="BC5" s="24"/>
+      <c r="BD5" s="25"/>
     </row>
     <row r="6" spans="28:56" x14ac:dyDescent="0.3">
       <c r="AC6" s="29" t="s">
@@ -4242,54 +5385,54 @@
       <c r="AR6" s="29"/>
       <c r="AS6" s="29"/>
       <c r="AT6" s="29"/>
-      <c r="AU6" s="31" t="s">
+      <c r="AU6" s="26" t="s">
         <v>117</v>
       </c>
-      <c r="AV6" s="23" t="s">
+      <c r="AV6" s="30" t="s">
         <v>160</v>
       </c>
-      <c r="AW6" s="24"/>
-      <c r="AX6" s="24"/>
-      <c r="AY6" s="24"/>
-      <c r="AZ6" s="24"/>
-      <c r="BA6" s="24"/>
-      <c r="BB6" s="24"/>
-      <c r="BC6" s="24"/>
-      <c r="BD6" s="25"/>
+      <c r="AW6" s="31"/>
+      <c r="AX6" s="31"/>
+      <c r="AY6" s="31"/>
+      <c r="AZ6" s="31"/>
+      <c r="BA6" s="31"/>
+      <c r="BB6" s="31"/>
+      <c r="BC6" s="31"/>
+      <c r="BD6" s="32"/>
     </row>
     <row r="7" spans="28:56" x14ac:dyDescent="0.3">
-      <c r="AC7" s="30" t="s">
+      <c r="AC7" s="28" t="s">
         <v>114</v>
       </c>
-      <c r="AD7" s="30"/>
-      <c r="AE7" s="30"/>
-      <c r="AF7" s="30"/>
-      <c r="AG7" s="30"/>
-      <c r="AH7" s="30"/>
-      <c r="AI7" s="30"/>
-      <c r="AJ7" s="30"/>
-      <c r="AK7" s="30"/>
-      <c r="AL7" s="30"/>
-      <c r="AM7" s="30"/>
-      <c r="AN7" s="30"/>
-      <c r="AO7" s="30"/>
-      <c r="AP7" s="30"/>
-      <c r="AQ7" s="30"/>
-      <c r="AR7" s="30"/>
-      <c r="AS7" s="30"/>
-      <c r="AT7" s="30"/>
-      <c r="AU7" s="32"/>
-      <c r="AV7" s="26" t="s">
+      <c r="AD7" s="28"/>
+      <c r="AE7" s="28"/>
+      <c r="AF7" s="28"/>
+      <c r="AG7" s="28"/>
+      <c r="AH7" s="28"/>
+      <c r="AI7" s="28"/>
+      <c r="AJ7" s="28"/>
+      <c r="AK7" s="28"/>
+      <c r="AL7" s="28"/>
+      <c r="AM7" s="28"/>
+      <c r="AN7" s="28"/>
+      <c r="AO7" s="28"/>
+      <c r="AP7" s="28"/>
+      <c r="AQ7" s="28"/>
+      <c r="AR7" s="28"/>
+      <c r="AS7" s="28"/>
+      <c r="AT7" s="28"/>
+      <c r="AU7" s="27"/>
+      <c r="AV7" s="23" t="s">
         <v>161</v>
       </c>
-      <c r="AW7" s="27"/>
-      <c r="AX7" s="27"/>
-      <c r="AY7" s="27"/>
-      <c r="AZ7" s="27"/>
-      <c r="BA7" s="27"/>
-      <c r="BB7" s="27"/>
-      <c r="BC7" s="27"/>
-      <c r="BD7" s="28"/>
+      <c r="AW7" s="24"/>
+      <c r="AX7" s="24"/>
+      <c r="AY7" s="24"/>
+      <c r="AZ7" s="24"/>
+      <c r="BA7" s="24"/>
+      <c r="BB7" s="24"/>
+      <c r="BC7" s="24"/>
+      <c r="BD7" s="25"/>
     </row>
     <row r="8" spans="28:56" x14ac:dyDescent="0.3">
       <c r="AC8" s="29" t="s">
@@ -4314,26 +5457,26 @@
       <c r="AT8" s="29"/>
     </row>
     <row r="9" spans="28:56" x14ac:dyDescent="0.3">
-      <c r="AC9" s="30" t="s">
+      <c r="AC9" s="28" t="s">
         <v>114</v>
       </c>
-      <c r="AD9" s="30"/>
-      <c r="AE9" s="30"/>
-      <c r="AF9" s="30"/>
-      <c r="AG9" s="30"/>
-      <c r="AH9" s="30"/>
-      <c r="AI9" s="30"/>
-      <c r="AJ9" s="30"/>
-      <c r="AK9" s="30"/>
-      <c r="AL9" s="30"/>
-      <c r="AM9" s="30"/>
-      <c r="AN9" s="30"/>
-      <c r="AO9" s="30"/>
-      <c r="AP9" s="30"/>
-      <c r="AQ9" s="30"/>
-      <c r="AR9" s="30"/>
-      <c r="AS9" s="30"/>
-      <c r="AT9" s="30"/>
+      <c r="AD9" s="28"/>
+      <c r="AE9" s="28"/>
+      <c r="AF9" s="28"/>
+      <c r="AG9" s="28"/>
+      <c r="AH9" s="28"/>
+      <c r="AI9" s="28"/>
+      <c r="AJ9" s="28"/>
+      <c r="AK9" s="28"/>
+      <c r="AL9" s="28"/>
+      <c r="AM9" s="28"/>
+      <c r="AN9" s="28"/>
+      <c r="AO9" s="28"/>
+      <c r="AP9" s="28"/>
+      <c r="AQ9" s="28"/>
+      <c r="AR9" s="28"/>
+      <c r="AS9" s="28"/>
+      <c r="AT9" s="28"/>
     </row>
     <row r="10" spans="28:56" x14ac:dyDescent="0.3">
       <c r="AC10" s="29" t="s">
@@ -4358,26 +5501,26 @@
       <c r="AT10" s="29"/>
     </row>
     <row r="11" spans="28:56" x14ac:dyDescent="0.3">
-      <c r="AC11" s="30" t="s">
+      <c r="AC11" s="28" t="s">
         <v>114</v>
       </c>
-      <c r="AD11" s="30"/>
-      <c r="AE11" s="30"/>
-      <c r="AF11" s="30"/>
-      <c r="AG11" s="30"/>
-      <c r="AH11" s="30"/>
-      <c r="AI11" s="30"/>
-      <c r="AJ11" s="30"/>
-      <c r="AK11" s="30"/>
-      <c r="AL11" s="30"/>
-      <c r="AM11" s="30"/>
-      <c r="AN11" s="30"/>
-      <c r="AO11" s="30"/>
-      <c r="AP11" s="30"/>
-      <c r="AQ11" s="30"/>
-      <c r="AR11" s="30"/>
-      <c r="AS11" s="30"/>
-      <c r="AT11" s="30"/>
+      <c r="AD11" s="28"/>
+      <c r="AE11" s="28"/>
+      <c r="AF11" s="28"/>
+      <c r="AG11" s="28"/>
+      <c r="AH11" s="28"/>
+      <c r="AI11" s="28"/>
+      <c r="AJ11" s="28"/>
+      <c r="AK11" s="28"/>
+      <c r="AL11" s="28"/>
+      <c r="AM11" s="28"/>
+      <c r="AN11" s="28"/>
+      <c r="AO11" s="28"/>
+      <c r="AP11" s="28"/>
+      <c r="AQ11" s="28"/>
+      <c r="AR11" s="28"/>
+      <c r="AS11" s="28"/>
+      <c r="AT11" s="28"/>
     </row>
     <row r="12" spans="28:56" x14ac:dyDescent="0.3">
       <c r="AC12" s="29" t="s">
@@ -4416,6 +5559,13 @@
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="AC9:AT9"/>
+    <mergeCell ref="AC10:AT10"/>
+    <mergeCell ref="AU4:AU5"/>
+    <mergeCell ref="AV4:BD4"/>
+    <mergeCell ref="AV6:BD6"/>
+    <mergeCell ref="AV7:BD7"/>
+    <mergeCell ref="AC8:AT8"/>
     <mergeCell ref="AV5:BD5"/>
     <mergeCell ref="AU6:AU7"/>
     <mergeCell ref="AC11:AT11"/>
@@ -4432,13 +5582,6 @@
     <mergeCell ref="AL4:AT4"/>
     <mergeCell ref="AC5:AT5"/>
     <mergeCell ref="AL6:AT6"/>
-    <mergeCell ref="AU4:AU5"/>
-    <mergeCell ref="AV4:BD4"/>
-    <mergeCell ref="AV6:BD6"/>
-    <mergeCell ref="AV7:BD7"/>
-    <mergeCell ref="AC8:AT8"/>
-    <mergeCell ref="AC9:AT9"/>
-    <mergeCell ref="AC10:AT10"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4448,174 +5591,107 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="AB3:AB48"/>
-  <sheetFormatPr defaultColWidth="2.875" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="3" spans="28:28" x14ac:dyDescent="0.3">
-      <c r="AB3" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="4" spans="28:28" x14ac:dyDescent="0.3">
-      <c r="AB4" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="17" spans="28:28" x14ac:dyDescent="0.3">
-      <c r="AB17" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="18" spans="28:28" x14ac:dyDescent="0.3">
-      <c r="AB18" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="19" spans="28:28" x14ac:dyDescent="0.3">
-      <c r="AB19" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="20" spans="28:28" x14ac:dyDescent="0.3">
-      <c r="AB20" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="22" spans="28:28" x14ac:dyDescent="0.3">
-      <c r="AB22" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="32" spans="28:28" x14ac:dyDescent="0.3">
-      <c r="AB32" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="46" spans="28:28" x14ac:dyDescent="0.3">
-      <c r="AB46" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="47" spans="28:28" x14ac:dyDescent="0.3">
-      <c r="AB47" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="48" spans="28:28" x14ac:dyDescent="0.3">
-      <c r="AB48" t="s">
-        <v>212</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:AA31"/>
+  <dimension ref="A2:AA237"/>
   <sheetFormatPr defaultColWidth="2.875" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="27" width="2.875" style="2"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B2" s="11" t="s">
-        <v>215</v>
-      </c>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="12"/>
-      <c r="I2" s="12"/>
-      <c r="J2" s="12"/>
-      <c r="K2" s="12"/>
-      <c r="L2" s="12"/>
-      <c r="M2" s="12"/>
-      <c r="N2" s="12"/>
-      <c r="O2" s="12"/>
-      <c r="P2" s="12"/>
-      <c r="Q2" s="12"/>
-      <c r="R2" s="12"/>
-      <c r="S2" s="12"/>
-      <c r="T2" s="12"/>
-      <c r="U2" s="12"/>
-      <c r="V2" s="12"/>
-      <c r="W2" s="12"/>
-      <c r="X2" s="12"/>
-      <c r="Y2" s="12"/>
-      <c r="Z2" s="13"/>
+      <c r="B2" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10"/>
+      <c r="N2" s="10"/>
+      <c r="O2" s="10"/>
+      <c r="P2" s="10"/>
+      <c r="Q2" s="10"/>
+      <c r="R2" s="10"/>
+      <c r="S2" s="10"/>
+      <c r="T2" s="10"/>
+      <c r="U2" s="10"/>
+      <c r="V2" s="10"/>
+      <c r="W2" s="10"/>
+      <c r="X2" s="10"/>
+      <c r="Y2" s="10"/>
+      <c r="Z2" s="11"/>
     </row>
     <row r="3" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B3" s="20"/>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="21"/>
-      <c r="F3" s="21"/>
-      <c r="G3" s="21"/>
-      <c r="H3" s="21"/>
-      <c r="I3" s="21"/>
-      <c r="J3" s="21"/>
-      <c r="K3" s="21"/>
-      <c r="L3" s="21"/>
-      <c r="M3" s="21"/>
-      <c r="N3" s="21"/>
-      <c r="O3" s="21"/>
-      <c r="P3" s="21"/>
-      <c r="Q3" s="21"/>
-      <c r="R3" s="21"/>
-      <c r="S3" s="21"/>
-      <c r="T3" s="21"/>
-      <c r="U3" s="21"/>
-      <c r="V3" s="21"/>
-      <c r="W3" s="21"/>
-      <c r="X3" s="21"/>
-      <c r="Y3" s="21"/>
-      <c r="Z3" s="22"/>
+      <c r="B3" s="12"/>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
+      <c r="H3" s="13"/>
+      <c r="I3" s="13"/>
+      <c r="J3" s="13"/>
+      <c r="K3" s="13"/>
+      <c r="L3" s="13"/>
+      <c r="M3" s="13"/>
+      <c r="N3" s="13"/>
+      <c r="O3" s="13"/>
+      <c r="P3" s="13"/>
+      <c r="Q3" s="13"/>
+      <c r="R3" s="13"/>
+      <c r="S3" s="13"/>
+      <c r="T3" s="13"/>
+      <c r="U3" s="13"/>
+      <c r="V3" s="13"/>
+      <c r="W3" s="13"/>
+      <c r="X3" s="13"/>
+      <c r="Y3" s="13"/>
+      <c r="Z3" s="14"/>
     </row>
     <row r="4" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B4" s="14"/>
-      <c r="C4" s="15"/>
-      <c r="D4" s="15"/>
-      <c r="E4" s="15"/>
-      <c r="F4" s="15"/>
-      <c r="G4" s="15"/>
-      <c r="H4" s="15"/>
-      <c r="I4" s="15"/>
-      <c r="J4" s="15"/>
-      <c r="K4" s="15"/>
-      <c r="L4" s="15"/>
-      <c r="M4" s="15"/>
-      <c r="N4" s="15"/>
-      <c r="O4" s="15"/>
-      <c r="P4" s="15"/>
-      <c r="Q4" s="15"/>
-      <c r="R4" s="15"/>
-      <c r="S4" s="15"/>
-      <c r="T4" s="15"/>
-      <c r="U4" s="15"/>
-      <c r="V4" s="15"/>
-      <c r="W4" s="15"/>
-      <c r="X4" s="15"/>
-      <c r="Y4" s="15"/>
-      <c r="Z4" s="16"/>
+      <c r="B4" s="15"/>
+      <c r="C4" s="16"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="16"/>
+      <c r="H4" s="16"/>
+      <c r="I4" s="16"/>
+      <c r="J4" s="16"/>
+      <c r="K4" s="16"/>
+      <c r="L4" s="16"/>
+      <c r="M4" s="16"/>
+      <c r="N4" s="16"/>
+      <c r="O4" s="16"/>
+      <c r="P4" s="16"/>
+      <c r="Q4" s="16"/>
+      <c r="R4" s="16"/>
+      <c r="S4" s="16"/>
+      <c r="T4" s="16"/>
+      <c r="U4" s="16"/>
+      <c r="V4" s="16"/>
+      <c r="W4" s="16"/>
+      <c r="X4" s="16"/>
+      <c r="Y4" s="16"/>
+      <c r="Z4" s="17"/>
     </row>
     <row r="6" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="V6" s="17" t="s">
-        <v>213</v>
-      </c>
-      <c r="W6" s="18"/>
-      <c r="X6" s="18"/>
-      <c r="Y6" s="18"/>
-      <c r="Z6" s="19"/>
+      <c r="V6" s="18" t="s">
+        <v>202</v>
+      </c>
+      <c r="W6" s="19"/>
+      <c r="X6" s="19"/>
+      <c r="Y6" s="19"/>
+      <c r="Z6" s="20"/>
     </row>
     <row r="8" spans="2:26" x14ac:dyDescent="0.3">
       <c r="C8" s="2" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
     </row>
     <row r="10" spans="2:26" x14ac:dyDescent="0.3">
@@ -4623,7 +5699,7 @@
         <v>1</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>217</v>
+        <v>206</v>
       </c>
     </row>
     <row r="11" spans="2:26" x14ac:dyDescent="0.3">
@@ -4631,7 +5707,7 @@
         <v>2</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
     </row>
     <row r="12" spans="2:26" x14ac:dyDescent="0.3">
@@ -4639,7 +5715,7 @@
         <v>3</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>219</v>
+        <v>208</v>
       </c>
     </row>
     <row r="13" spans="2:26" x14ac:dyDescent="0.3">
@@ -4651,65 +5727,65 @@
       </c>
     </row>
     <row r="16" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="C16" s="11" t="s">
-        <v>220</v>
-      </c>
-      <c r="D16" s="12"/>
-      <c r="E16" s="12"/>
-      <c r="F16" s="12"/>
-      <c r="G16" s="12"/>
-      <c r="H16" s="12"/>
-      <c r="I16" s="12"/>
-      <c r="J16" s="12"/>
-      <c r="K16" s="12"/>
-      <c r="L16" s="12"/>
-      <c r="M16" s="12"/>
-      <c r="N16" s="12"/>
-      <c r="O16" s="12"/>
-      <c r="P16" s="12"/>
-      <c r="Q16" s="12"/>
-      <c r="R16" s="12"/>
-      <c r="S16" s="12"/>
-      <c r="T16" s="12"/>
-      <c r="U16" s="12"/>
-      <c r="V16" s="12"/>
-      <c r="W16" s="12"/>
-      <c r="X16" s="12"/>
-      <c r="Y16" s="12"/>
-      <c r="Z16" s="13"/>
+      <c r="C16" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="D16" s="10"/>
+      <c r="E16" s="10"/>
+      <c r="F16" s="10"/>
+      <c r="G16" s="10"/>
+      <c r="H16" s="10"/>
+      <c r="I16" s="10"/>
+      <c r="J16" s="10"/>
+      <c r="K16" s="10"/>
+      <c r="L16" s="10"/>
+      <c r="M16" s="10"/>
+      <c r="N16" s="10"/>
+      <c r="O16" s="10"/>
+      <c r="P16" s="10"/>
+      <c r="Q16" s="10"/>
+      <c r="R16" s="10"/>
+      <c r="S16" s="10"/>
+      <c r="T16" s="10"/>
+      <c r="U16" s="10"/>
+      <c r="V16" s="10"/>
+      <c r="W16" s="10"/>
+      <c r="X16" s="10"/>
+      <c r="Y16" s="10"/>
+      <c r="Z16" s="11"/>
     </row>
     <row r="17" spans="3:26" x14ac:dyDescent="0.3">
-      <c r="C17" s="14"/>
-      <c r="D17" s="15"/>
-      <c r="E17" s="15"/>
-      <c r="F17" s="15"/>
-      <c r="G17" s="15"/>
-      <c r="H17" s="15"/>
-      <c r="I17" s="15"/>
-      <c r="J17" s="15"/>
-      <c r="K17" s="15"/>
-      <c r="L17" s="15"/>
-      <c r="M17" s="15"/>
-      <c r="N17" s="15"/>
-      <c r="O17" s="15"/>
-      <c r="P17" s="15"/>
-      <c r="Q17" s="15"/>
-      <c r="R17" s="15"/>
-      <c r="S17" s="15"/>
-      <c r="T17" s="15"/>
-      <c r="U17" s="15"/>
-      <c r="V17" s="15"/>
-      <c r="W17" s="15"/>
-      <c r="X17" s="15"/>
-      <c r="Y17" s="15"/>
-      <c r="Z17" s="16"/>
+      <c r="C17" s="15"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="16"/>
+      <c r="F17" s="16"/>
+      <c r="G17" s="16"/>
+      <c r="H17" s="16"/>
+      <c r="I17" s="16"/>
+      <c r="J17" s="16"/>
+      <c r="K17" s="16"/>
+      <c r="L17" s="16"/>
+      <c r="M17" s="16"/>
+      <c r="N17" s="16"/>
+      <c r="O17" s="16"/>
+      <c r="P17" s="16"/>
+      <c r="Q17" s="16"/>
+      <c r="R17" s="16"/>
+      <c r="S17" s="16"/>
+      <c r="T17" s="16"/>
+      <c r="U17" s="16"/>
+      <c r="V17" s="16"/>
+      <c r="W17" s="16"/>
+      <c r="X17" s="16"/>
+      <c r="Y17" s="16"/>
+      <c r="Z17" s="17"/>
     </row>
     <row r="19" spans="3:26" x14ac:dyDescent="0.3">
       <c r="D19" s="2">
         <v>1</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>235</v>
+        <v>224</v>
       </c>
     </row>
     <row r="20" spans="3:26" x14ac:dyDescent="0.3">
@@ -4717,7 +5793,7 @@
         <v>2</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
     </row>
     <row r="21" spans="3:26" x14ac:dyDescent="0.3">
@@ -4725,7 +5801,7 @@
         <v>3</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
     </row>
     <row r="22" spans="3:26" x14ac:dyDescent="0.3">
@@ -4733,7 +5809,7 @@
         <v>4</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>222</v>
+        <v>211</v>
       </c>
     </row>
     <row r="23" spans="3:26" x14ac:dyDescent="0.3">
@@ -4741,117 +5817,1143 @@
         <v>5</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>223</v>
+        <v>212</v>
       </c>
     </row>
     <row r="24" spans="3:26" x14ac:dyDescent="0.3">
       <c r="E24" s="2" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>225</v>
+        <v>214</v>
       </c>
     </row>
     <row r="25" spans="3:26" x14ac:dyDescent="0.3">
       <c r="E25" s="2" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
     </row>
     <row r="26" spans="3:26" x14ac:dyDescent="0.3">
       <c r="E26" s="2" t="s">
-        <v>228</v>
+        <v>217</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
     </row>
     <row r="27" spans="3:26" x14ac:dyDescent="0.3">
       <c r="E27" s="2" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
     </row>
     <row r="28" spans="3:26" x14ac:dyDescent="0.3">
       <c r="E28" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="C30" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="D30" s="10"/>
+      <c r="E30" s="10"/>
+      <c r="F30" s="10"/>
+      <c r="G30" s="10"/>
+      <c r="H30" s="10"/>
+      <c r="I30" s="10"/>
+      <c r="J30" s="10"/>
+      <c r="K30" s="10"/>
+      <c r="L30" s="10"/>
+      <c r="M30" s="10"/>
+      <c r="N30" s="10"/>
+      <c r="O30" s="10"/>
+      <c r="P30" s="10"/>
+      <c r="Q30" s="10"/>
+      <c r="R30" s="10"/>
+      <c r="S30" s="10"/>
+      <c r="T30" s="10"/>
+      <c r="U30" s="10"/>
+      <c r="V30" s="10"/>
+      <c r="W30" s="10"/>
+      <c r="X30" s="10"/>
+      <c r="Y30" s="10"/>
+      <c r="Z30" s="11"/>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="C31" s="15"/>
+      <c r="D31" s="16"/>
+      <c r="E31" s="16"/>
+      <c r="F31" s="16"/>
+      <c r="G31" s="16"/>
+      <c r="H31" s="16"/>
+      <c r="I31" s="16"/>
+      <c r="J31" s="16"/>
+      <c r="K31" s="16"/>
+      <c r="L31" s="16"/>
+      <c r="M31" s="16"/>
+      <c r="N31" s="16"/>
+      <c r="O31" s="16"/>
+      <c r="P31" s="16"/>
+      <c r="Q31" s="16"/>
+      <c r="R31" s="16"/>
+      <c r="S31" s="16"/>
+      <c r="T31" s="16"/>
+      <c r="U31" s="16"/>
+      <c r="V31" s="16"/>
+      <c r="W31" s="16"/>
+      <c r="X31" s="16"/>
+      <c r="Y31" s="16"/>
+      <c r="Z31" s="17"/>
+    </row>
+    <row r="33" spans="4:26" x14ac:dyDescent="0.3">
+      <c r="D33" s="2">
+        <v>1</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="I33" s="2" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="34" spans="4:26" x14ac:dyDescent="0.3">
+      <c r="D34" s="2">
+        <v>2</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="I34" s="2" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="35" spans="4:26" x14ac:dyDescent="0.3">
+      <c r="D35" s="2">
+        <v>3</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="I35" s="2" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="36" spans="4:26" x14ac:dyDescent="0.3">
+      <c r="D36" s="2">
+        <v>4</v>
+      </c>
+      <c r="E36" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="F28" s="2" t="s">
+    </row>
+    <row r="37" spans="4:26" x14ac:dyDescent="0.3">
+      <c r="D37" s="2">
+        <v>5</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="39" spans="4:26" x14ac:dyDescent="0.3">
+      <c r="D39" s="9" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.3">
-      <c r="C30" s="11" t="s">
+      <c r="E39" s="10"/>
+      <c r="F39" s="10"/>
+      <c r="G39" s="10"/>
+      <c r="H39" s="10"/>
+      <c r="I39" s="10"/>
+      <c r="J39" s="10"/>
+      <c r="K39" s="10"/>
+      <c r="L39" s="10"/>
+      <c r="M39" s="10"/>
+      <c r="N39" s="10"/>
+      <c r="O39" s="10"/>
+      <c r="P39" s="10"/>
+      <c r="Q39" s="10"/>
+      <c r="R39" s="10"/>
+      <c r="S39" s="10"/>
+      <c r="T39" s="10"/>
+      <c r="U39" s="10"/>
+      <c r="V39" s="10"/>
+      <c r="W39" s="10"/>
+      <c r="X39" s="10"/>
+      <c r="Y39" s="10"/>
+      <c r="Z39" s="11"/>
+    </row>
+    <row r="40" spans="4:26" x14ac:dyDescent="0.3">
+      <c r="D40" s="15"/>
+      <c r="E40" s="16"/>
+      <c r="F40" s="16"/>
+      <c r="G40" s="16"/>
+      <c r="H40" s="16"/>
+      <c r="I40" s="16"/>
+      <c r="J40" s="16"/>
+      <c r="K40" s="16"/>
+      <c r="L40" s="16"/>
+      <c r="M40" s="16"/>
+      <c r="N40" s="16"/>
+      <c r="O40" s="16"/>
+      <c r="P40" s="16"/>
+      <c r="Q40" s="16"/>
+      <c r="R40" s="16"/>
+      <c r="S40" s="16"/>
+      <c r="T40" s="16"/>
+      <c r="U40" s="16"/>
+      <c r="V40" s="16"/>
+      <c r="W40" s="16"/>
+      <c r="X40" s="16"/>
+      <c r="Y40" s="16"/>
+      <c r="Z40" s="17"/>
+    </row>
+    <row r="42" spans="4:26" x14ac:dyDescent="0.3">
+      <c r="E42" s="2">
+        <v>1</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="43" spans="4:26" x14ac:dyDescent="0.3">
+      <c r="G43" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="D30" s="12"/>
-      <c r="E30" s="12"/>
-      <c r="F30" s="12"/>
-      <c r="G30" s="12"/>
-      <c r="H30" s="12"/>
-      <c r="I30" s="12"/>
-      <c r="J30" s="12"/>
-      <c r="K30" s="12"/>
-      <c r="L30" s="12"/>
-      <c r="M30" s="12"/>
-      <c r="N30" s="12"/>
-      <c r="O30" s="12"/>
-      <c r="P30" s="12"/>
-      <c r="Q30" s="12"/>
-      <c r="R30" s="12"/>
-      <c r="S30" s="12"/>
-      <c r="T30" s="12"/>
-      <c r="U30" s="12"/>
-      <c r="V30" s="12"/>
-      <c r="W30" s="12"/>
-      <c r="X30" s="12"/>
-      <c r="Y30" s="12"/>
-      <c r="Z30" s="13"/>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.3">
-      <c r="C31" s="14"/>
-      <c r="D31" s="15"/>
-      <c r="E31" s="15"/>
-      <c r="F31" s="15"/>
-      <c r="G31" s="15"/>
-      <c r="H31" s="15"/>
-      <c r="I31" s="15"/>
-      <c r="J31" s="15"/>
-      <c r="K31" s="15"/>
-      <c r="L31" s="15"/>
-      <c r="M31" s="15"/>
-      <c r="N31" s="15"/>
-      <c r="O31" s="15"/>
-      <c r="P31" s="15"/>
-      <c r="Q31" s="15"/>
-      <c r="R31" s="15"/>
-      <c r="S31" s="15"/>
-      <c r="T31" s="15"/>
-      <c r="U31" s="15"/>
-      <c r="V31" s="15"/>
-      <c r="W31" s="15"/>
-      <c r="X31" s="15"/>
-      <c r="Y31" s="15"/>
-      <c r="Z31" s="16"/>
+    </row>
+    <row r="44" spans="4:26" x14ac:dyDescent="0.3">
+      <c r="G44" s="2" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="45" spans="4:26" x14ac:dyDescent="0.3">
+      <c r="G45" s="2" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="46" spans="4:26" x14ac:dyDescent="0.3">
+      <c r="G46" s="2" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="47" spans="4:26" x14ac:dyDescent="0.3">
+      <c r="E47" s="2">
+        <v>2</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="48" spans="4:26" x14ac:dyDescent="0.3">
+      <c r="G48" s="2" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="49" spans="5:7" x14ac:dyDescent="0.3">
+      <c r="G49" s="2" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="50" spans="5:7" x14ac:dyDescent="0.3">
+      <c r="G50" s="2" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="51" spans="5:7" x14ac:dyDescent="0.3">
+      <c r="G51" s="2" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="52" spans="5:7" x14ac:dyDescent="0.3">
+      <c r="E52" s="2">
+        <v>3</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="53" spans="5:7" x14ac:dyDescent="0.3">
+      <c r="G53" s="2" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="54" spans="5:7" x14ac:dyDescent="0.3">
+      <c r="G54" s="2" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="55" spans="5:7" x14ac:dyDescent="0.3">
+      <c r="G55" s="2" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="56" spans="5:7" x14ac:dyDescent="0.3">
+      <c r="G56" s="2" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="57" spans="5:7" x14ac:dyDescent="0.3">
+      <c r="E57" s="2">
+        <v>4</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="58" spans="5:7" x14ac:dyDescent="0.3">
+      <c r="G58" s="2" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="59" spans="5:7" x14ac:dyDescent="0.3">
+      <c r="G59" s="2" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="60" spans="5:7" x14ac:dyDescent="0.3">
+      <c r="G60" s="2" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="61" spans="5:7" x14ac:dyDescent="0.3">
+      <c r="G61" s="2" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="62" spans="5:7" x14ac:dyDescent="0.3">
+      <c r="G62" s="2" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="63" spans="5:7" x14ac:dyDescent="0.3">
+      <c r="G63" s="2" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="64" spans="5:7" x14ac:dyDescent="0.3">
+      <c r="G64" s="2" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="65" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="E65" s="2">
+        <v>5</v>
+      </c>
+      <c r="F65" s="2" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="66" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="G66" s="2" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="68" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="C68" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="D68" s="10"/>
+      <c r="E68" s="10"/>
+      <c r="F68" s="10"/>
+      <c r="G68" s="10"/>
+      <c r="H68" s="10"/>
+      <c r="I68" s="10"/>
+      <c r="J68" s="10"/>
+      <c r="K68" s="10"/>
+      <c r="L68" s="10"/>
+      <c r="M68" s="10"/>
+      <c r="N68" s="10"/>
+      <c r="O68" s="10"/>
+      <c r="P68" s="10"/>
+      <c r="Q68" s="10"/>
+      <c r="R68" s="10"/>
+      <c r="S68" s="10"/>
+      <c r="T68" s="10"/>
+      <c r="U68" s="10"/>
+      <c r="V68" s="10"/>
+      <c r="W68" s="10"/>
+      <c r="X68" s="10"/>
+      <c r="Y68" s="10"/>
+      <c r="Z68" s="11"/>
+    </row>
+    <row r="69" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="C69" s="15"/>
+      <c r="D69" s="16"/>
+      <c r="E69" s="16"/>
+      <c r="F69" s="16"/>
+      <c r="G69" s="16"/>
+      <c r="H69" s="16"/>
+      <c r="I69" s="16"/>
+      <c r="J69" s="16"/>
+      <c r="K69" s="16"/>
+      <c r="L69" s="16"/>
+      <c r="M69" s="16"/>
+      <c r="N69" s="16"/>
+      <c r="O69" s="16"/>
+      <c r="P69" s="16"/>
+      <c r="Q69" s="16"/>
+      <c r="R69" s="16"/>
+      <c r="S69" s="16"/>
+      <c r="T69" s="16"/>
+      <c r="U69" s="16"/>
+      <c r="V69" s="16"/>
+      <c r="W69" s="16"/>
+      <c r="X69" s="16"/>
+      <c r="Y69" s="16"/>
+      <c r="Z69" s="17"/>
+    </row>
+    <row r="71" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="D71" s="18" t="s">
+        <v>257</v>
+      </c>
+      <c r="E71" s="19"/>
+      <c r="F71" s="19"/>
+      <c r="G71" s="19"/>
+      <c r="H71" s="19"/>
+      <c r="I71" s="19"/>
+      <c r="J71" s="19"/>
+      <c r="K71" s="19"/>
+      <c r="L71" s="19"/>
+      <c r="M71" s="19"/>
+      <c r="N71" s="19"/>
+      <c r="O71" s="19"/>
+      <c r="P71" s="19"/>
+      <c r="Q71" s="19"/>
+      <c r="R71" s="19"/>
+      <c r="S71" s="19"/>
+      <c r="T71" s="19"/>
+      <c r="U71" s="19"/>
+      <c r="V71" s="19"/>
+      <c r="W71" s="19"/>
+      <c r="X71" s="19"/>
+      <c r="Y71" s="19"/>
+      <c r="Z71" s="20"/>
+    </row>
+    <row r="86" spans="4:26" x14ac:dyDescent="0.3">
+      <c r="D86" s="33" t="s">
+        <v>258</v>
+      </c>
+      <c r="E86" s="34"/>
+      <c r="F86" s="34"/>
+      <c r="G86" s="34"/>
+      <c r="H86" s="34"/>
+      <c r="I86" s="34"/>
+      <c r="J86" s="34"/>
+      <c r="K86" s="34"/>
+      <c r="L86" s="34"/>
+      <c r="M86" s="34"/>
+      <c r="N86" s="34"/>
+      <c r="O86" s="34"/>
+      <c r="P86" s="34"/>
+      <c r="Q86" s="34"/>
+      <c r="R86" s="34"/>
+      <c r="S86" s="34"/>
+      <c r="T86" s="34"/>
+      <c r="U86" s="34"/>
+      <c r="V86" s="34"/>
+      <c r="W86" s="34"/>
+      <c r="X86" s="34"/>
+      <c r="Y86" s="34"/>
+      <c r="Z86" s="35"/>
+    </row>
+    <row r="87" spans="4:26" x14ac:dyDescent="0.3">
+      <c r="D87" s="39" t="s">
+        <v>259</v>
+      </c>
+      <c r="E87" s="40"/>
+      <c r="F87" s="40"/>
+      <c r="G87" s="40"/>
+      <c r="H87" s="40"/>
+      <c r="I87" s="40"/>
+      <c r="J87" s="40"/>
+      <c r="K87" s="40"/>
+      <c r="L87" s="40"/>
+      <c r="M87" s="40"/>
+      <c r="N87" s="40"/>
+      <c r="O87" s="40"/>
+      <c r="P87" s="40"/>
+      <c r="Q87" s="40"/>
+      <c r="R87" s="40"/>
+      <c r="S87" s="40"/>
+      <c r="T87" s="40"/>
+      <c r="U87" s="40"/>
+      <c r="V87" s="40"/>
+      <c r="W87" s="40"/>
+      <c r="X87" s="40"/>
+      <c r="Y87" s="40"/>
+      <c r="Z87" s="41"/>
+    </row>
+    <row r="102" spans="4:26" x14ac:dyDescent="0.3">
+      <c r="D102" s="33" t="s">
+        <v>260</v>
+      </c>
+      <c r="E102" s="34"/>
+      <c r="F102" s="34"/>
+      <c r="G102" s="34"/>
+      <c r="H102" s="34"/>
+      <c r="I102" s="34"/>
+      <c r="J102" s="34"/>
+      <c r="K102" s="34"/>
+      <c r="L102" s="34"/>
+      <c r="M102" s="34"/>
+      <c r="N102" s="34"/>
+      <c r="O102" s="34"/>
+      <c r="P102" s="34"/>
+      <c r="Q102" s="34"/>
+      <c r="R102" s="34"/>
+      <c r="S102" s="34"/>
+      <c r="T102" s="34"/>
+      <c r="U102" s="34"/>
+      <c r="V102" s="34"/>
+      <c r="W102" s="34"/>
+      <c r="X102" s="34"/>
+      <c r="Y102" s="34"/>
+      <c r="Z102" s="35"/>
+    </row>
+    <row r="103" spans="4:26" x14ac:dyDescent="0.3">
+      <c r="D103" s="36" t="s">
+        <v>261</v>
+      </c>
+      <c r="E103" s="37"/>
+      <c r="F103" s="37"/>
+      <c r="G103" s="37"/>
+      <c r="H103" s="37"/>
+      <c r="I103" s="37"/>
+      <c r="J103" s="37"/>
+      <c r="K103" s="37"/>
+      <c r="L103" s="37"/>
+      <c r="M103" s="37"/>
+      <c r="N103" s="37"/>
+      <c r="O103" s="37"/>
+      <c r="P103" s="37"/>
+      <c r="Q103" s="37"/>
+      <c r="R103" s="37"/>
+      <c r="S103" s="37"/>
+      <c r="T103" s="37"/>
+      <c r="U103" s="37"/>
+      <c r="V103" s="37"/>
+      <c r="W103" s="37"/>
+      <c r="X103" s="37"/>
+      <c r="Y103" s="37"/>
+      <c r="Z103" s="38"/>
+    </row>
+    <row r="104" spans="4:26" x14ac:dyDescent="0.3">
+      <c r="D104" s="39" t="s">
+        <v>262</v>
+      </c>
+      <c r="E104" s="40"/>
+      <c r="F104" s="40"/>
+      <c r="G104" s="40"/>
+      <c r="H104" s="40"/>
+      <c r="I104" s="40"/>
+      <c r="J104" s="40"/>
+      <c r="K104" s="40"/>
+      <c r="L104" s="40"/>
+      <c r="M104" s="40"/>
+      <c r="N104" s="40"/>
+      <c r="O104" s="40"/>
+      <c r="P104" s="40"/>
+      <c r="Q104" s="40"/>
+      <c r="R104" s="40"/>
+      <c r="S104" s="40"/>
+      <c r="T104" s="40"/>
+      <c r="U104" s="40"/>
+      <c r="V104" s="40"/>
+      <c r="W104" s="40"/>
+      <c r="X104" s="40"/>
+      <c r="Y104" s="40"/>
+      <c r="Z104" s="41"/>
+    </row>
+    <row r="120" spans="4:26" x14ac:dyDescent="0.3">
+      <c r="D120" s="42" t="s">
+        <v>263</v>
+      </c>
+      <c r="E120" s="43"/>
+      <c r="F120" s="43"/>
+      <c r="G120" s="43"/>
+      <c r="H120" s="43"/>
+      <c r="I120" s="43"/>
+      <c r="J120" s="43"/>
+      <c r="K120" s="43"/>
+      <c r="L120" s="43"/>
+      <c r="M120" s="43"/>
+      <c r="N120" s="43"/>
+      <c r="O120" s="43"/>
+      <c r="P120" s="43"/>
+      <c r="Q120" s="43"/>
+      <c r="R120" s="43"/>
+      <c r="S120" s="43"/>
+      <c r="T120" s="43"/>
+      <c r="U120" s="43"/>
+      <c r="V120" s="43"/>
+      <c r="W120" s="43"/>
+      <c r="X120" s="43"/>
+      <c r="Y120" s="43"/>
+      <c r="Z120" s="44"/>
+    </row>
+    <row r="136" spans="4:26" x14ac:dyDescent="0.3">
+      <c r="D136" s="33" t="s">
+        <v>264</v>
+      </c>
+      <c r="E136" s="34"/>
+      <c r="F136" s="34"/>
+      <c r="G136" s="34"/>
+      <c r="H136" s="34"/>
+      <c r="I136" s="34"/>
+      <c r="J136" s="34"/>
+      <c r="K136" s="34"/>
+      <c r="L136" s="34"/>
+      <c r="M136" s="34"/>
+      <c r="N136" s="34"/>
+      <c r="O136" s="34"/>
+      <c r="P136" s="34"/>
+      <c r="Q136" s="34"/>
+      <c r="R136" s="34"/>
+      <c r="S136" s="34"/>
+      <c r="T136" s="34"/>
+      <c r="U136" s="34"/>
+      <c r="V136" s="34"/>
+      <c r="W136" s="34"/>
+      <c r="X136" s="34"/>
+      <c r="Y136" s="34"/>
+      <c r="Z136" s="35"/>
+    </row>
+    <row r="137" spans="4:26" x14ac:dyDescent="0.3">
+      <c r="D137" s="36" t="s">
+        <v>265</v>
+      </c>
+      <c r="E137" s="37"/>
+      <c r="F137" s="37"/>
+      <c r="G137" s="37"/>
+      <c r="H137" s="37"/>
+      <c r="I137" s="37"/>
+      <c r="J137" s="37"/>
+      <c r="K137" s="37"/>
+      <c r="L137" s="37"/>
+      <c r="M137" s="37"/>
+      <c r="N137" s="37"/>
+      <c r="O137" s="37"/>
+      <c r="P137" s="37"/>
+      <c r="Q137" s="37"/>
+      <c r="R137" s="37"/>
+      <c r="S137" s="37"/>
+      <c r="T137" s="37"/>
+      <c r="U137" s="37"/>
+      <c r="V137" s="37"/>
+      <c r="W137" s="37"/>
+      <c r="X137" s="37"/>
+      <c r="Y137" s="37"/>
+      <c r="Z137" s="38"/>
+    </row>
+    <row r="138" spans="4:26" x14ac:dyDescent="0.3">
+      <c r="D138" s="36" t="s">
+        <v>266</v>
+      </c>
+      <c r="E138" s="37"/>
+      <c r="F138" s="37"/>
+      <c r="G138" s="37"/>
+      <c r="H138" s="37"/>
+      <c r="I138" s="37"/>
+      <c r="J138" s="37"/>
+      <c r="K138" s="37"/>
+      <c r="L138" s="37"/>
+      <c r="M138" s="37"/>
+      <c r="N138" s="37"/>
+      <c r="O138" s="37"/>
+      <c r="P138" s="37"/>
+      <c r="Q138" s="37"/>
+      <c r="R138" s="37"/>
+      <c r="S138" s="37"/>
+      <c r="T138" s="37"/>
+      <c r="U138" s="37"/>
+      <c r="V138" s="37"/>
+      <c r="W138" s="37"/>
+      <c r="X138" s="37"/>
+      <c r="Y138" s="37"/>
+      <c r="Z138" s="38"/>
+    </row>
+    <row r="139" spans="4:26" x14ac:dyDescent="0.3">
+      <c r="D139" s="36" t="s">
+        <v>267</v>
+      </c>
+      <c r="E139" s="37"/>
+      <c r="F139" s="37"/>
+      <c r="G139" s="37"/>
+      <c r="H139" s="37"/>
+      <c r="I139" s="37"/>
+      <c r="J139" s="37"/>
+      <c r="K139" s="37"/>
+      <c r="L139" s="37"/>
+      <c r="M139" s="37"/>
+      <c r="N139" s="37"/>
+      <c r="O139" s="37"/>
+      <c r="P139" s="37"/>
+      <c r="Q139" s="37"/>
+      <c r="R139" s="37"/>
+      <c r="S139" s="37"/>
+      <c r="T139" s="37"/>
+      <c r="U139" s="37"/>
+      <c r="V139" s="37"/>
+      <c r="W139" s="37"/>
+      <c r="X139" s="37"/>
+      <c r="Y139" s="37"/>
+      <c r="Z139" s="38"/>
+    </row>
+    <row r="140" spans="4:26" x14ac:dyDescent="0.3">
+      <c r="D140" s="39" t="s">
+        <v>268</v>
+      </c>
+      <c r="E140" s="40"/>
+      <c r="F140" s="40"/>
+      <c r="G140" s="40"/>
+      <c r="H140" s="40"/>
+      <c r="I140" s="40"/>
+      <c r="J140" s="40"/>
+      <c r="K140" s="40"/>
+      <c r="L140" s="40"/>
+      <c r="M140" s="40"/>
+      <c r="N140" s="40"/>
+      <c r="O140" s="40"/>
+      <c r="P140" s="40"/>
+      <c r="Q140" s="40"/>
+      <c r="R140" s="40"/>
+      <c r="S140" s="40"/>
+      <c r="T140" s="40"/>
+      <c r="U140" s="40"/>
+      <c r="V140" s="40"/>
+      <c r="W140" s="40"/>
+      <c r="X140" s="40"/>
+      <c r="Y140" s="40"/>
+      <c r="Z140" s="41"/>
+    </row>
+    <row r="156" spans="4:26" x14ac:dyDescent="0.3">
+      <c r="D156" s="33" t="s">
+        <v>269</v>
+      </c>
+      <c r="E156" s="34"/>
+      <c r="F156" s="34"/>
+      <c r="G156" s="34"/>
+      <c r="H156" s="34"/>
+      <c r="I156" s="34"/>
+      <c r="J156" s="34"/>
+      <c r="K156" s="34"/>
+      <c r="L156" s="34"/>
+      <c r="M156" s="34"/>
+      <c r="N156" s="34"/>
+      <c r="O156" s="34"/>
+      <c r="P156" s="34"/>
+      <c r="Q156" s="34"/>
+      <c r="R156" s="34"/>
+      <c r="S156" s="34"/>
+      <c r="T156" s="34"/>
+      <c r="U156" s="34"/>
+      <c r="V156" s="34"/>
+      <c r="W156" s="34"/>
+      <c r="X156" s="34"/>
+      <c r="Y156" s="34"/>
+      <c r="Z156" s="35"/>
+    </row>
+    <row r="157" spans="4:26" x14ac:dyDescent="0.3">
+      <c r="D157" s="36" t="s">
+        <v>270</v>
+      </c>
+      <c r="E157" s="37"/>
+      <c r="F157" s="37"/>
+      <c r="G157" s="37"/>
+      <c r="H157" s="37"/>
+      <c r="I157" s="37"/>
+      <c r="J157" s="37"/>
+      <c r="K157" s="37"/>
+      <c r="L157" s="37"/>
+      <c r="M157" s="37"/>
+      <c r="N157" s="37"/>
+      <c r="O157" s="37"/>
+      <c r="P157" s="37"/>
+      <c r="Q157" s="37"/>
+      <c r="R157" s="37"/>
+      <c r="S157" s="37"/>
+      <c r="T157" s="37"/>
+      <c r="U157" s="37"/>
+      <c r="V157" s="37"/>
+      <c r="W157" s="37"/>
+      <c r="X157" s="37"/>
+      <c r="Y157" s="37"/>
+      <c r="Z157" s="38"/>
+    </row>
+    <row r="158" spans="4:26" x14ac:dyDescent="0.3">
+      <c r="D158" s="36" t="s">
+        <v>271</v>
+      </c>
+      <c r="E158" s="37"/>
+      <c r="F158" s="37"/>
+      <c r="G158" s="37"/>
+      <c r="H158" s="37"/>
+      <c r="I158" s="37"/>
+      <c r="J158" s="37"/>
+      <c r="K158" s="37"/>
+      <c r="L158" s="37"/>
+      <c r="M158" s="37"/>
+      <c r="N158" s="37"/>
+      <c r="O158" s="37"/>
+      <c r="P158" s="37"/>
+      <c r="Q158" s="37"/>
+      <c r="R158" s="37"/>
+      <c r="S158" s="37"/>
+      <c r="T158" s="37"/>
+      <c r="U158" s="37"/>
+      <c r="V158" s="37"/>
+      <c r="W158" s="37"/>
+      <c r="X158" s="37"/>
+      <c r="Y158" s="37"/>
+      <c r="Z158" s="38"/>
+    </row>
+    <row r="159" spans="4:26" x14ac:dyDescent="0.3">
+      <c r="D159" s="39" t="s">
+        <v>272</v>
+      </c>
+      <c r="E159" s="40"/>
+      <c r="F159" s="40"/>
+      <c r="G159" s="40"/>
+      <c r="H159" s="40"/>
+      <c r="I159" s="40"/>
+      <c r="J159" s="40"/>
+      <c r="K159" s="40"/>
+      <c r="L159" s="40"/>
+      <c r="M159" s="40"/>
+      <c r="N159" s="40"/>
+      <c r="O159" s="40"/>
+      <c r="P159" s="40"/>
+      <c r="Q159" s="40"/>
+      <c r="R159" s="40"/>
+      <c r="S159" s="40"/>
+      <c r="T159" s="40"/>
+      <c r="U159" s="40"/>
+      <c r="V159" s="40"/>
+      <c r="W159" s="40"/>
+      <c r="X159" s="40"/>
+      <c r="Y159" s="40"/>
+      <c r="Z159" s="41"/>
+    </row>
+    <row r="173" spans="4:26" x14ac:dyDescent="0.3">
+      <c r="D173" s="33" t="s">
+        <v>275</v>
+      </c>
+      <c r="E173" s="34"/>
+      <c r="F173" s="34"/>
+      <c r="G173" s="34"/>
+      <c r="H173" s="34"/>
+      <c r="I173" s="34"/>
+      <c r="J173" s="34"/>
+      <c r="K173" s="34"/>
+      <c r="L173" s="34"/>
+      <c r="M173" s="34"/>
+      <c r="N173" s="34"/>
+      <c r="O173" s="34"/>
+      <c r="P173" s="34"/>
+      <c r="Q173" s="34"/>
+      <c r="R173" s="34"/>
+      <c r="S173" s="34"/>
+      <c r="T173" s="34"/>
+      <c r="U173" s="34"/>
+      <c r="V173" s="34"/>
+      <c r="W173" s="34"/>
+      <c r="X173" s="34"/>
+      <c r="Y173" s="34"/>
+      <c r="Z173" s="35"/>
+    </row>
+    <row r="174" spans="4:26" x14ac:dyDescent="0.3">
+      <c r="D174" s="36" t="s">
+        <v>276</v>
+      </c>
+      <c r="E174" s="37"/>
+      <c r="F174" s="37"/>
+      <c r="G174" s="37"/>
+      <c r="H174" s="37"/>
+      <c r="I174" s="37"/>
+      <c r="J174" s="37"/>
+      <c r="K174" s="37"/>
+      <c r="L174" s="37"/>
+      <c r="M174" s="37"/>
+      <c r="N174" s="37"/>
+      <c r="O174" s="37"/>
+      <c r="P174" s="37"/>
+      <c r="Q174" s="37"/>
+      <c r="R174" s="37"/>
+      <c r="S174" s="37"/>
+      <c r="T174" s="37"/>
+      <c r="U174" s="37"/>
+      <c r="V174" s="37"/>
+      <c r="W174" s="37"/>
+      <c r="X174" s="37"/>
+      <c r="Y174" s="37"/>
+      <c r="Z174" s="38"/>
+    </row>
+    <row r="175" spans="4:26" x14ac:dyDescent="0.3">
+      <c r="D175" s="36"/>
+      <c r="E175" s="37"/>
+      <c r="F175" s="37"/>
+      <c r="G175" s="37"/>
+      <c r="H175" s="37"/>
+      <c r="I175" s="37"/>
+      <c r="J175" s="37"/>
+      <c r="K175" s="37"/>
+      <c r="L175" s="37"/>
+      <c r="M175" s="37"/>
+      <c r="N175" s="37"/>
+      <c r="O175" s="37"/>
+      <c r="P175" s="37"/>
+      <c r="Q175" s="37"/>
+      <c r="R175" s="37"/>
+      <c r="S175" s="37"/>
+      <c r="T175" s="37"/>
+      <c r="U175" s="37"/>
+      <c r="V175" s="37"/>
+      <c r="W175" s="37"/>
+      <c r="X175" s="37"/>
+      <c r="Y175" s="37"/>
+      <c r="Z175" s="38"/>
+    </row>
+    <row r="176" spans="4:26" x14ac:dyDescent="0.3">
+      <c r="D176" s="36" t="s">
+        <v>277</v>
+      </c>
+      <c r="E176" s="37"/>
+      <c r="F176" s="37"/>
+      <c r="G176" s="37"/>
+      <c r="H176" s="37"/>
+      <c r="I176" s="37"/>
+      <c r="J176" s="37"/>
+      <c r="K176" s="37"/>
+      <c r="L176" s="37"/>
+      <c r="M176" s="37"/>
+      <c r="N176" s="37"/>
+      <c r="O176" s="37"/>
+      <c r="P176" s="37"/>
+      <c r="Q176" s="37"/>
+      <c r="R176" s="37"/>
+      <c r="S176" s="37"/>
+      <c r="T176" s="37"/>
+      <c r="U176" s="37"/>
+      <c r="V176" s="37"/>
+      <c r="W176" s="37"/>
+      <c r="X176" s="37"/>
+      <c r="Y176" s="37"/>
+      <c r="Z176" s="38"/>
+    </row>
+    <row r="177" spans="4:26" x14ac:dyDescent="0.3">
+      <c r="D177" s="39" t="s">
+        <v>278</v>
+      </c>
+      <c r="E177" s="40"/>
+      <c r="F177" s="40"/>
+      <c r="G177" s="40"/>
+      <c r="H177" s="40"/>
+      <c r="I177" s="40"/>
+      <c r="J177" s="40"/>
+      <c r="K177" s="40"/>
+      <c r="L177" s="40"/>
+      <c r="M177" s="40"/>
+      <c r="N177" s="40"/>
+      <c r="O177" s="40"/>
+      <c r="P177" s="40"/>
+      <c r="Q177" s="40"/>
+      <c r="R177" s="40"/>
+      <c r="S177" s="40"/>
+      <c r="T177" s="40"/>
+      <c r="U177" s="40"/>
+      <c r="V177" s="40"/>
+      <c r="W177" s="40"/>
+      <c r="X177" s="40"/>
+      <c r="Y177" s="40"/>
+      <c r="Z177" s="41"/>
+    </row>
+    <row r="191" spans="4:26" x14ac:dyDescent="0.3">
+      <c r="D191" s="33" t="s">
+        <v>273</v>
+      </c>
+      <c r="E191" s="34"/>
+      <c r="F191" s="34"/>
+      <c r="G191" s="34"/>
+      <c r="H191" s="34"/>
+      <c r="I191" s="34"/>
+      <c r="J191" s="34"/>
+      <c r="K191" s="34"/>
+      <c r="L191" s="34"/>
+      <c r="M191" s="34"/>
+      <c r="N191" s="34"/>
+      <c r="O191" s="34"/>
+      <c r="P191" s="34"/>
+      <c r="Q191" s="34"/>
+      <c r="R191" s="34"/>
+      <c r="S191" s="34"/>
+      <c r="T191" s="34"/>
+      <c r="U191" s="34"/>
+      <c r="V191" s="34"/>
+      <c r="W191" s="34"/>
+      <c r="X191" s="34"/>
+      <c r="Y191" s="34"/>
+      <c r="Z191" s="35"/>
+    </row>
+    <row r="192" spans="4:26" x14ac:dyDescent="0.3">
+      <c r="D192" s="39" t="s">
+        <v>274</v>
+      </c>
+      <c r="E192" s="40"/>
+      <c r="F192" s="40"/>
+      <c r="G192" s="40"/>
+      <c r="H192" s="40"/>
+      <c r="I192" s="40"/>
+      <c r="J192" s="40"/>
+      <c r="K192" s="40"/>
+      <c r="L192" s="40"/>
+      <c r="M192" s="40"/>
+      <c r="N192" s="40"/>
+      <c r="O192" s="40"/>
+      <c r="P192" s="40"/>
+      <c r="Q192" s="40"/>
+      <c r="R192" s="40"/>
+      <c r="S192" s="40"/>
+      <c r="T192" s="40"/>
+      <c r="U192" s="40"/>
+      <c r="V192" s="40"/>
+      <c r="W192" s="40"/>
+      <c r="X192" s="40"/>
+      <c r="Y192" s="40"/>
+      <c r="Z192" s="41"/>
+    </row>
+    <row r="205" spans="4:26" x14ac:dyDescent="0.3">
+      <c r="D205" s="33" t="s">
+        <v>279</v>
+      </c>
+      <c r="E205" s="34"/>
+      <c r="F205" s="34"/>
+      <c r="G205" s="34"/>
+      <c r="H205" s="34"/>
+      <c r="I205" s="34"/>
+      <c r="J205" s="34"/>
+      <c r="K205" s="34"/>
+      <c r="L205" s="34"/>
+      <c r="M205" s="34"/>
+      <c r="N205" s="34"/>
+      <c r="O205" s="34"/>
+      <c r="P205" s="34"/>
+      <c r="Q205" s="34"/>
+      <c r="R205" s="34"/>
+      <c r="S205" s="34"/>
+      <c r="T205" s="34"/>
+      <c r="U205" s="34"/>
+      <c r="V205" s="34"/>
+      <c r="W205" s="34"/>
+      <c r="X205" s="34"/>
+      <c r="Y205" s="34"/>
+      <c r="Z205" s="35"/>
+    </row>
+    <row r="206" spans="4:26" x14ac:dyDescent="0.3">
+      <c r="D206" s="39" t="s">
+        <v>280</v>
+      </c>
+      <c r="E206" s="40"/>
+      <c r="F206" s="40"/>
+      <c r="G206" s="40"/>
+      <c r="H206" s="40"/>
+      <c r="I206" s="40"/>
+      <c r="J206" s="40"/>
+      <c r="K206" s="40"/>
+      <c r="L206" s="40"/>
+      <c r="M206" s="40"/>
+      <c r="N206" s="40"/>
+      <c r="O206" s="40"/>
+      <c r="P206" s="40"/>
+      <c r="Q206" s="40"/>
+      <c r="R206" s="40"/>
+      <c r="S206" s="40"/>
+      <c r="T206" s="40"/>
+      <c r="U206" s="40"/>
+      <c r="V206" s="40"/>
+      <c r="W206" s="40"/>
+      <c r="X206" s="40"/>
+      <c r="Y206" s="40"/>
+      <c r="Z206" s="41"/>
+    </row>
+    <row r="236" spans="4:26" x14ac:dyDescent="0.3">
+      <c r="D236" s="33" t="s">
+        <v>281</v>
+      </c>
+      <c r="E236" s="34"/>
+      <c r="F236" s="34"/>
+      <c r="G236" s="34"/>
+      <c r="H236" s="34"/>
+      <c r="I236" s="34"/>
+      <c r="J236" s="34"/>
+      <c r="K236" s="34"/>
+      <c r="L236" s="34"/>
+      <c r="M236" s="34"/>
+      <c r="N236" s="34"/>
+      <c r="O236" s="34"/>
+      <c r="P236" s="34"/>
+      <c r="Q236" s="34"/>
+      <c r="R236" s="34"/>
+      <c r="S236" s="34"/>
+      <c r="T236" s="34"/>
+      <c r="U236" s="34"/>
+      <c r="V236" s="34"/>
+      <c r="W236" s="34"/>
+      <c r="X236" s="34"/>
+      <c r="Y236" s="34"/>
+      <c r="Z236" s="35"/>
+    </row>
+    <row r="237" spans="4:26" x14ac:dyDescent="0.3">
+      <c r="D237" s="39" t="s">
+        <v>282</v>
+      </c>
+      <c r="E237" s="40"/>
+      <c r="F237" s="40"/>
+      <c r="G237" s="40"/>
+      <c r="H237" s="40"/>
+      <c r="I237" s="40"/>
+      <c r="J237" s="40"/>
+      <c r="K237" s="40"/>
+      <c r="L237" s="40"/>
+      <c r="M237" s="40"/>
+      <c r="N237" s="40"/>
+      <c r="O237" s="40"/>
+      <c r="P237" s="40"/>
+      <c r="Q237" s="40"/>
+      <c r="R237" s="40"/>
+      <c r="S237" s="40"/>
+      <c r="T237" s="40"/>
+      <c r="U237" s="40"/>
+      <c r="V237" s="40"/>
+      <c r="W237" s="40"/>
+      <c r="X237" s="40"/>
+      <c r="Y237" s="40"/>
+      <c r="Z237" s="41"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="7">
+    <mergeCell ref="C68:Z69"/>
+    <mergeCell ref="D71:Z71"/>
     <mergeCell ref="B2:Z4"/>
     <mergeCell ref="V6:Z6"/>
     <mergeCell ref="C16:Z17"/>
     <mergeCell ref="C30:Z31"/>
+    <mergeCell ref="D39:Z40"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A2:AA6"/>
   <sheetFormatPr defaultColWidth="2.875" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -4860,96 +6962,96 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B2" s="11" t="s">
-        <v>214</v>
-      </c>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="12"/>
-      <c r="I2" s="12"/>
-      <c r="J2" s="12"/>
-      <c r="K2" s="12"/>
-      <c r="L2" s="12"/>
-      <c r="M2" s="12"/>
-      <c r="N2" s="12"/>
-      <c r="O2" s="12"/>
-      <c r="P2" s="12"/>
-      <c r="Q2" s="12"/>
-      <c r="R2" s="12"/>
-      <c r="S2" s="12"/>
-      <c r="T2" s="12"/>
-      <c r="U2" s="12"/>
-      <c r="V2" s="12"/>
-      <c r="W2" s="12"/>
-      <c r="X2" s="12"/>
-      <c r="Y2" s="12"/>
-      <c r="Z2" s="13"/>
+      <c r="B2" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10"/>
+      <c r="N2" s="10"/>
+      <c r="O2" s="10"/>
+      <c r="P2" s="10"/>
+      <c r="Q2" s="10"/>
+      <c r="R2" s="10"/>
+      <c r="S2" s="10"/>
+      <c r="T2" s="10"/>
+      <c r="U2" s="10"/>
+      <c r="V2" s="10"/>
+      <c r="W2" s="10"/>
+      <c r="X2" s="10"/>
+      <c r="Y2" s="10"/>
+      <c r="Z2" s="11"/>
     </row>
     <row r="3" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B3" s="20"/>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="21"/>
-      <c r="F3" s="21"/>
-      <c r="G3" s="21"/>
-      <c r="H3" s="21"/>
-      <c r="I3" s="21"/>
-      <c r="J3" s="21"/>
-      <c r="K3" s="21"/>
-      <c r="L3" s="21"/>
-      <c r="M3" s="21"/>
-      <c r="N3" s="21"/>
-      <c r="O3" s="21"/>
-      <c r="P3" s="21"/>
-      <c r="Q3" s="21"/>
-      <c r="R3" s="21"/>
-      <c r="S3" s="21"/>
-      <c r="T3" s="21"/>
-      <c r="U3" s="21"/>
-      <c r="V3" s="21"/>
-      <c r="W3" s="21"/>
-      <c r="X3" s="21"/>
-      <c r="Y3" s="21"/>
-      <c r="Z3" s="22"/>
+      <c r="B3" s="12"/>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
+      <c r="H3" s="13"/>
+      <c r="I3" s="13"/>
+      <c r="J3" s="13"/>
+      <c r="K3" s="13"/>
+      <c r="L3" s="13"/>
+      <c r="M3" s="13"/>
+      <c r="N3" s="13"/>
+      <c r="O3" s="13"/>
+      <c r="P3" s="13"/>
+      <c r="Q3" s="13"/>
+      <c r="R3" s="13"/>
+      <c r="S3" s="13"/>
+      <c r="T3" s="13"/>
+      <c r="U3" s="13"/>
+      <c r="V3" s="13"/>
+      <c r="W3" s="13"/>
+      <c r="X3" s="13"/>
+      <c r="Y3" s="13"/>
+      <c r="Z3" s="14"/>
     </row>
     <row r="4" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B4" s="14"/>
-      <c r="C4" s="15"/>
-      <c r="D4" s="15"/>
-      <c r="E4" s="15"/>
-      <c r="F4" s="15"/>
-      <c r="G4" s="15"/>
-      <c r="H4" s="15"/>
-      <c r="I4" s="15"/>
-      <c r="J4" s="15"/>
-      <c r="K4" s="15"/>
-      <c r="L4" s="15"/>
-      <c r="M4" s="15"/>
-      <c r="N4" s="15"/>
-      <c r="O4" s="15"/>
-      <c r="P4" s="15"/>
-      <c r="Q4" s="15"/>
-      <c r="R4" s="15"/>
-      <c r="S4" s="15"/>
-      <c r="T4" s="15"/>
-      <c r="U4" s="15"/>
-      <c r="V4" s="15"/>
-      <c r="W4" s="15"/>
-      <c r="X4" s="15"/>
-      <c r="Y4" s="15"/>
-      <c r="Z4" s="16"/>
+      <c r="B4" s="15"/>
+      <c r="C4" s="16"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="16"/>
+      <c r="H4" s="16"/>
+      <c r="I4" s="16"/>
+      <c r="J4" s="16"/>
+      <c r="K4" s="16"/>
+      <c r="L4" s="16"/>
+      <c r="M4" s="16"/>
+      <c r="N4" s="16"/>
+      <c r="O4" s="16"/>
+      <c r="P4" s="16"/>
+      <c r="Q4" s="16"/>
+      <c r="R4" s="16"/>
+      <c r="S4" s="16"/>
+      <c r="T4" s="16"/>
+      <c r="U4" s="16"/>
+      <c r="V4" s="16"/>
+      <c r="W4" s="16"/>
+      <c r="X4" s="16"/>
+      <c r="Y4" s="16"/>
+      <c r="Z4" s="17"/>
     </row>
     <row r="6" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="V6" s="17" t="s">
-        <v>213</v>
-      </c>
-      <c r="W6" s="18"/>
-      <c r="X6" s="18"/>
-      <c r="Y6" s="18"/>
-      <c r="Z6" s="19"/>
+      <c r="V6" s="18" t="s">
+        <v>202</v>
+      </c>
+      <c r="W6" s="19"/>
+      <c r="X6" s="19"/>
+      <c r="Y6" s="19"/>
+      <c r="Z6" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/D2B2_기획_문서/003_시스템_기획서/006_미션_시스템/Project_D2B2_시스템기획서_미션_시스템.xlsx
+++ b/D2B2_기획_문서/003_시스템_기획서/006_미션_시스템/Project_D2B2_시스템기획서_미션_시스템.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12165" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12165" firstSheet="1" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="미션 시스템 기획서" sheetId="2" r:id="rId1"/>
@@ -17,6 +17,9 @@
     <sheet name="미션 트리거 예시" sheetId="3" r:id="rId3"/>
     <sheet name="튜토리얼 미션&amp;트리거" sheetId="6" r:id="rId4"/>
     <sheet name="1챕터 미션&amp;트리거" sheetId="4" r:id="rId5"/>
+    <sheet name="2챕터 미션&amp;트리거" sheetId="7" r:id="rId6"/>
+    <sheet name="3챕터 이미지" sheetId="9" r:id="rId7"/>
+    <sheet name="3챕터 미션&amp;트리거" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -28,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="353">
   <si>
     <t>챕터</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -1138,13 +1141,293 @@
   </si>
   <si>
     <t>튜토리얼로 셋팅된 기기는 초기 화면으로 돌아간다.</t>
+  </si>
+  <si>
+    <t>미션 시스템 - 챕터 2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>불법 주정차 차량 등으로 시야가 제한된 골목길에서 자주 발생하는 위험 요소를</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>체험한다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>차량의 사각지대에 대한 이해와, 시야 바깥에서 접근 중인 차량을 예상하는</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>방법을 학습한다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,2의 과정을 통해 시야 확보, 차량 움직임 예측, 차량 내부 시야 예측 등</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>고차원적인 보행 전략을 훈련한다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>반복적인 실패와 교육 과정을 통해 '보이지 않는 위험'을 인지하고 대처하는</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>능력을 함양한다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>전체 미션 흐름</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>목적지 인식</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>길 건너편 NPC의 머리 위에 강조 표시가 나타나고,</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>강조 표시, UI, 나레이션을 통해 목적지를 인식</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>안전 영역 인식</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>시야 너머 상황 인식</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">불법 주정차, 이중주차 차량 중 시동이 걸린(정차된) </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>차량의 사각지대를 피해 '안전한' 횡단 구역을 스스로 판단</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>주정차 차량으로 가려진 시야 너머에서 차량이 접근하고</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>있는지, 시야 너머의 상황은 안전한지 스스로 판단</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>횡단 시작</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>파악된 정보를 바탕으로 안전한 이면도로 횡단을 실시</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>게임 루프 종료 및 초기 화면으로 복귀.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>개별 미션 상세</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>목적지 인식</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>게임 시작 후 5초동안 목적지 NPC를 강조, UI 출력 등</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>플레이어가 목표 지점을 인식할 수 있도록 유도함.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>안전 영역 인식</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>빨간 차량은 시동이 걸린 차량으로 취급한다.(이미지는 추후 변경 가능)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>시동이 걸린 차량의 근처에서는 엔진 공회전 사운드가 출력되며</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>공회전 차량의 후방 사각지대에 점근하게 된다면 미션 실패 판정이 된다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">주기적, 혹은 랜덤하게 차량이 스폰된다(일방통행으로 가정하여 한 </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>방향에서만 스폰한다.)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>헤드라이트, 엔진음 등을 통해 플레이어는 차량의 접근을 알 수 있으며,</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>헤드라이트 범위에 플레이어가 존재한다면 미션 실패 판정이 된다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>초록색 영역</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>안전 영역(변동하지 않음)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>노란색 영역</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>빨간색 영역</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>위험 영역(차량 접근 상태에 따라 변동 가능)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>주의 영역(차량 접근 상태에 따라 변동 가능)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>시야 너머 상황 인식</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>플레이어는 자동차 엔진음, 헤드라이트 등을 활용하여</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>시야 밖에서 차량이 접근 중인지 여부를 확인할 수 있다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>횡단 시작</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>플레이어는</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>차량이 시야 너머에서 접근하고 있지 않을 때</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>정차 중인 차량의 사각지대가 아닌 장소에서</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>이면도로 횡단을 시도할 수 있다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">좌/우 도로 상황을 확실히 확인한 뒤, 머리 높이 위로 손을 들고 반대편 </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>도로에 도착한 다음, 목표 지역까지 이동에 성공하면</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>골목길 보행 챕터를 클리어한다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>만일 플레이어가 차량의 사각지대에 침입하여 미션을 실패한 경우</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>3.1'</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>실패 처리</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>실패 처리</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[안전 가이드-차량 사각지대 체험]을 호출한다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>만일 플레이어가 시야 너머 차량의 접근을 예상하지 못하여 미션을 실패한</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>경우, [안전 가이드-시야 너머 차량 예측]을 호출한다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>그 외 실패 요소(손 들지 않고 길 건너기, 좌우 살피지 않기 등)는 1챕터의</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>안전 가이드를 동일하게 호출한다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>End Of Document</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>미션 시스템 - 챕터 3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">초록색 </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>챕터 목표</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>이전 챕터에서 학습한 안전 보행 수칙을 얼마나 체득하였는지 평가</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>타인의 보행 습관을 평가함으로써, 플레이어 스스로의 인지 수준을 증진</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>행동의 안전/위험 수준을 판별하는 인지 능력과 사고력을 강화함</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>타인과의 협동/경쟁을 통해 플레이어 간 위험 판단의 기준을 비교하고</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>스스로의 안전 보행 교육 이수 정도를 확인할 수 있음.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>전체 미션 흐름</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1176,8 +1459,32 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="20"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="20"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1202,8 +1509,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="15">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -1369,13 +1688,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1403,77 +1733,8 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -1511,6 +1772,165 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1520,6 +1940,8 @@
   <colors>
     <mruColors>
       <color rgb="FFFF3131"/>
+      <color rgb="FFFF0000"/>
+      <color rgb="FF92D050"/>
     </mruColors>
   </colors>
   <extLst>
@@ -2151,16 +2573,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>209550</xdr:colOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>28575</xdr:colOff>
       <xdr:row>125</xdr:row>
-      <xdr:rowOff>19051</xdr:rowOff>
+      <xdr:rowOff>47626</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:colOff>38100</xdr:colOff>
       <xdr:row>128</xdr:row>
-      <xdr:rowOff>114301</xdr:rowOff>
+      <xdr:rowOff>142876</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2169,7 +2591,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2619375" y="26212801"/>
+          <a:off x="2657475" y="26241376"/>
           <a:ext cx="885825" cy="723900"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2495,13 +2917,13 @@
       <xdr:col>20</xdr:col>
       <xdr:colOff>47625</xdr:colOff>
       <xdr:row>161</xdr:row>
-      <xdr:rowOff>85725</xdr:rowOff>
+      <xdr:rowOff>95250</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>26</xdr:col>
       <xdr:colOff>9525</xdr:colOff>
       <xdr:row>170</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2524,7 +2946,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4429125" y="33823275"/>
+          <a:off x="4429125" y="33832800"/>
           <a:ext cx="1276350" cy="1914525"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2897,6 +3319,1656 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>28946</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="그림 1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="email">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="657226" y="9220200"/>
+          <a:ext cx="5067670" cy="2381250"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>142875</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="아래쪽 화살표 2"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2867025" y="9591675"/>
+          <a:ext cx="342900" cy="342900"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FF0000"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent2">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent2"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>200025</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>200025</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="그림 8"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="email">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3962400" y="9420225"/>
+          <a:ext cx="1276350" cy="1914525"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>200025</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>28575</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name="TextBox 9"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4143375" y="9534525"/>
+          <a:ext cx="923925" cy="800100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100"/>
+            <a:t>친구와</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100"/>
+            <a:t/>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100"/>
+          </a:br>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100"/>
+            <a:t>만나 보세요</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>209549</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>158364</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>23180</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="그림 10"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="email">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="647699" y="12731364"/>
+          <a:ext cx="5071431" cy="2356236"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>104775</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>69</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12" name="직사각형 11"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2733675" y="13306425"/>
+          <a:ext cx="647700" cy="1190625"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF3131"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>133350</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>85726</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>104775</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>66676</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="13" name="직사각형 12"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3200400" y="13287376"/>
+          <a:ext cx="190500" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FF0000"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100"/>
+            <a:t>1</a:t>
+          </a:r>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>200025</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="14" name="직사각형 13"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1000125" y="13668375"/>
+          <a:ext cx="952500" cy="638175"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF3131"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>28576</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>209550</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>9526</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="15" name="직사각형 14"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1771650" y="13649326"/>
+          <a:ext cx="190500" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FF0000"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100"/>
+            <a:t>2</a:t>
+          </a:r>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>200024</xdr:colOff>
+      <xdr:row>80</xdr:row>
+      <xdr:rowOff>63114</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>13655</xdr:colOff>
+      <xdr:row>91</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="16" name="그림 15"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="email">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="638174" y="16827114"/>
+          <a:ext cx="5071431" cy="2356236"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>200024</xdr:colOff>
+      <xdr:row>82</xdr:row>
+      <xdr:rowOff>133351</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>104775</xdr:colOff>
+      <xdr:row>83</xdr:row>
+      <xdr:rowOff>38101</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="17" name="직사각형 16"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2390774" y="17316451"/>
+          <a:ext cx="2971801" cy="114300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="92D050">
+            <a:alpha val="40000"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>85725</xdr:colOff>
+      <xdr:row>88</xdr:row>
+      <xdr:rowOff>123826</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>89</xdr:row>
+      <xdr:rowOff>28576</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="19" name="직사각형 18"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2714625" y="18564226"/>
+          <a:ext cx="2876550" cy="114300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="92D050">
+            <a:alpha val="40000"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>219074</xdr:colOff>
+      <xdr:row>83</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>142875</xdr:colOff>
+      <xdr:row>84</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="21" name="직사각형 20"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2409824" y="17440275"/>
+          <a:ext cx="361951" cy="342900"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FF0000">
+            <a:alpha val="40000"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>114299</xdr:colOff>
+      <xdr:row>84</xdr:row>
+      <xdr:rowOff>180974</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>171450</xdr:colOff>
+      <xdr:row>87</xdr:row>
+      <xdr:rowOff>38099</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="22" name="직사각형 21"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1866899" y="17783174"/>
+          <a:ext cx="1590676" cy="485775"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FF0000">
+            <a:alpha val="40000"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>76199</xdr:colOff>
+      <xdr:row>87</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>88</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="23" name="직사각형 22"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3362324" y="18268950"/>
+          <a:ext cx="361951" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FF0000">
+            <a:alpha val="40000"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>133349</xdr:colOff>
+      <xdr:row>83</xdr:row>
+      <xdr:rowOff>123824</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>87</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="24" name="직사각형 23"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4076699" y="17516474"/>
+          <a:ext cx="1409701" cy="847726"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent4">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+            <a:alpha val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>87</xdr:row>
+      <xdr:rowOff>133351</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>88</xdr:row>
+      <xdr:rowOff>125185</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="25" name="직사각형 24"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3720193" y="18600965"/>
+          <a:ext cx="1846489" cy="204106"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="92D050">
+            <a:alpha val="40000"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>87</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>89</xdr:row>
+      <xdr:rowOff>28576</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="26" name="직사각형 25"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="847725" y="18402300"/>
+          <a:ext cx="1857375" cy="276226"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="92D050">
+            <a:alpha val="40000"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>98</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>28945</xdr:colOff>
+      <xdr:row>109</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="27" name="그림 26"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="email">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="657225" y="20535900"/>
+          <a:ext cx="5067670" cy="2381250"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>85725</xdr:colOff>
+      <xdr:row>102</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>66675</xdr:colOff>
+      <xdr:row>104</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="28" name="직사각형 27"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2276475" y="21450300"/>
+          <a:ext cx="1514475" cy="457200"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>102</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>66675</xdr:colOff>
+      <xdr:row>103</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="29" name="직사각형 28"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3600450" y="21440775"/>
+          <a:ext cx="190500" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FF0000"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100"/>
+            <a:t>1</a:t>
+          </a:r>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>115</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>5238</xdr:colOff>
+      <xdr:row>126</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="30" name="그림 29"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="email">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="657225" y="24098250"/>
+          <a:ext cx="5043963" cy="2343150"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>132</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>143</xdr:row>
+      <xdr:rowOff>26506</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="31" name="그림 30"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5" cstate="email">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="657225" y="27451050"/>
+          <a:ext cx="5038725" cy="2331556"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>209550</xdr:colOff>
+      <xdr:row>143</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>154</xdr:row>
+      <xdr:rowOff>151932</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="32" name="그림 31"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6" cstate="email">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="647700" y="29870400"/>
+          <a:ext cx="5048250" cy="2342682"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>200025</xdr:colOff>
+      <xdr:row>161</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>9895</xdr:colOff>
+      <xdr:row>172</xdr:row>
+      <xdr:rowOff>200025</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="33" name="그림 32"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="email">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="638175" y="36795075"/>
+          <a:ext cx="5067670" cy="2381250"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>66675</xdr:colOff>
+      <xdr:row>168</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>169</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="순서도: 수동 연산 4"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="2476500" y="38166675"/>
+          <a:ext cx="1514475" cy="323850"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartManualOperation">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FF3131">
+            <a:alpha val="50196"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>180975</xdr:colOff>
+      <xdr:row>176</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>209920</xdr:colOff>
+      <xdr:row>187</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="34" name="그림 33"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="email">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="619125" y="36937950"/>
+          <a:ext cx="5067670" cy="2381250"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>85728</xdr:colOff>
+      <xdr:row>180</xdr:row>
+      <xdr:rowOff>180981</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>38105</xdr:colOff>
+      <xdr:row>182</xdr:row>
+      <xdr:rowOff>200028</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="35" name="순서도: 수동 연산 34"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="5400000" flipV="1">
+          <a:off x="2800355" y="37376104"/>
+          <a:ext cx="438147" cy="1485902"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartManualOperation">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FF3131">
+            <a:alpha val="50196"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>85725</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>268161</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>143553</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="그림 1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="85725" y="104775"/>
+          <a:ext cx="10469436" cy="4858428"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>163383</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>38778</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="그림 2"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="5029200"/>
+          <a:ext cx="10450383" cy="4858428"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
   <a:themeElements>
@@ -3167,97 +5239,97 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="27" t="s">
         <v>191</v>
       </c>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
-      <c r="K2" s="10"/>
-      <c r="L2" s="10"/>
-      <c r="M2" s="10"/>
-      <c r="N2" s="10"/>
-      <c r="O2" s="10"/>
-      <c r="P2" s="10"/>
-      <c r="Q2" s="10"/>
-      <c r="R2" s="10"/>
-      <c r="S2" s="10"/>
-      <c r="T2" s="10"/>
-      <c r="U2" s="10"/>
-      <c r="V2" s="10"/>
-      <c r="W2" s="10"/>
-      <c r="X2" s="10"/>
-      <c r="Y2" s="10"/>
-      <c r="Z2" s="11"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
+      <c r="I2" s="28"/>
+      <c r="J2" s="28"/>
+      <c r="K2" s="28"/>
+      <c r="L2" s="28"/>
+      <c r="M2" s="28"/>
+      <c r="N2" s="28"/>
+      <c r="O2" s="28"/>
+      <c r="P2" s="28"/>
+      <c r="Q2" s="28"/>
+      <c r="R2" s="28"/>
+      <c r="S2" s="28"/>
+      <c r="T2" s="28"/>
+      <c r="U2" s="28"/>
+      <c r="V2" s="28"/>
+      <c r="W2" s="28"/>
+      <c r="X2" s="28"/>
+      <c r="Y2" s="28"/>
+      <c r="Z2" s="29"/>
     </row>
     <row r="3" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B3" s="12"/>
-      <c r="C3" s="13"/>
-      <c r="D3" s="13"/>
-      <c r="E3" s="13"/>
-      <c r="F3" s="13"/>
-      <c r="G3" s="13"/>
-      <c r="H3" s="13"/>
-      <c r="I3" s="13"/>
-      <c r="J3" s="13"/>
-      <c r="K3" s="13"/>
-      <c r="L3" s="13"/>
-      <c r="M3" s="13"/>
-      <c r="N3" s="13"/>
-      <c r="O3" s="13"/>
-      <c r="P3" s="13"/>
-      <c r="Q3" s="13"/>
-      <c r="R3" s="13"/>
-      <c r="S3" s="13"/>
-      <c r="T3" s="13"/>
-      <c r="U3" s="13"/>
-      <c r="V3" s="13"/>
-      <c r="W3" s="13"/>
-      <c r="X3" s="13"/>
-      <c r="Y3" s="13"/>
-      <c r="Z3" s="14"/>
+      <c r="B3" s="36"/>
+      <c r="C3" s="37"/>
+      <c r="D3" s="37"/>
+      <c r="E3" s="37"/>
+      <c r="F3" s="37"/>
+      <c r="G3" s="37"/>
+      <c r="H3" s="37"/>
+      <c r="I3" s="37"/>
+      <c r="J3" s="37"/>
+      <c r="K3" s="37"/>
+      <c r="L3" s="37"/>
+      <c r="M3" s="37"/>
+      <c r="N3" s="37"/>
+      <c r="O3" s="37"/>
+      <c r="P3" s="37"/>
+      <c r="Q3" s="37"/>
+      <c r="R3" s="37"/>
+      <c r="S3" s="37"/>
+      <c r="T3" s="37"/>
+      <c r="U3" s="37"/>
+      <c r="V3" s="37"/>
+      <c r="W3" s="37"/>
+      <c r="X3" s="37"/>
+      <c r="Y3" s="37"/>
+      <c r="Z3" s="38"/>
     </row>
     <row r="4" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B4" s="15"/>
-      <c r="C4" s="16"/>
-      <c r="D4" s="16"/>
-      <c r="E4" s="16"/>
-      <c r="F4" s="16"/>
-      <c r="G4" s="16"/>
-      <c r="H4" s="16"/>
-      <c r="I4" s="16"/>
-      <c r="J4" s="16"/>
-      <c r="K4" s="16"/>
-      <c r="L4" s="16"/>
-      <c r="M4" s="16"/>
-      <c r="N4" s="16"/>
-      <c r="O4" s="16"/>
-      <c r="P4" s="16"/>
-      <c r="Q4" s="16"/>
-      <c r="R4" s="16"/>
-      <c r="S4" s="16"/>
-      <c r="T4" s="16"/>
-      <c r="U4" s="16"/>
-      <c r="V4" s="16"/>
-      <c r="W4" s="16"/>
-      <c r="X4" s="16"/>
-      <c r="Y4" s="16"/>
-      <c r="Z4" s="17"/>
+      <c r="B4" s="30"/>
+      <c r="C4" s="31"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
+      <c r="H4" s="31"/>
+      <c r="I4" s="31"/>
+      <c r="J4" s="31"/>
+      <c r="K4" s="31"/>
+      <c r="L4" s="31"/>
+      <c r="M4" s="31"/>
+      <c r="N4" s="31"/>
+      <c r="O4" s="31"/>
+      <c r="P4" s="31"/>
+      <c r="Q4" s="31"/>
+      <c r="R4" s="31"/>
+      <c r="S4" s="31"/>
+      <c r="T4" s="31"/>
+      <c r="U4" s="31"/>
+      <c r="V4" s="31"/>
+      <c r="W4" s="31"/>
+      <c r="X4" s="31"/>
+      <c r="Y4" s="31"/>
+      <c r="Z4" s="32"/>
     </row>
     <row r="6" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="U6" s="18" t="s">
+      <c r="U6" s="33" t="s">
         <v>41</v>
       </c>
-      <c r="V6" s="19"/>
-      <c r="W6" s="19"/>
-      <c r="X6" s="19"/>
-      <c r="Y6" s="19"/>
-      <c r="Z6" s="20"/>
+      <c r="V6" s="34"/>
+      <c r="W6" s="34"/>
+      <c r="X6" s="34"/>
+      <c r="Y6" s="34"/>
+      <c r="Z6" s="35"/>
     </row>
     <row r="8" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B8" s="2">
@@ -3308,58 +5380,58 @@
       </c>
     </row>
     <row r="45" spans="3:26" x14ac:dyDescent="0.3">
-      <c r="C45" s="9" t="s">
+      <c r="C45" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="D45" s="10"/>
-      <c r="E45" s="10"/>
-      <c r="F45" s="10"/>
-      <c r="G45" s="10"/>
-      <c r="H45" s="10"/>
-      <c r="I45" s="10"/>
-      <c r="J45" s="10"/>
-      <c r="K45" s="10"/>
-      <c r="L45" s="10"/>
-      <c r="M45" s="10"/>
-      <c r="N45" s="10"/>
-      <c r="O45" s="10"/>
-      <c r="P45" s="10"/>
-      <c r="Q45" s="10"/>
-      <c r="R45" s="10"/>
-      <c r="S45" s="10"/>
-      <c r="T45" s="10"/>
-      <c r="U45" s="10"/>
-      <c r="V45" s="10"/>
-      <c r="W45" s="10"/>
-      <c r="X45" s="10"/>
-      <c r="Y45" s="10"/>
-      <c r="Z45" s="11"/>
+      <c r="D45" s="28"/>
+      <c r="E45" s="28"/>
+      <c r="F45" s="28"/>
+      <c r="G45" s="28"/>
+      <c r="H45" s="28"/>
+      <c r="I45" s="28"/>
+      <c r="J45" s="28"/>
+      <c r="K45" s="28"/>
+      <c r="L45" s="28"/>
+      <c r="M45" s="28"/>
+      <c r="N45" s="28"/>
+      <c r="O45" s="28"/>
+      <c r="P45" s="28"/>
+      <c r="Q45" s="28"/>
+      <c r="R45" s="28"/>
+      <c r="S45" s="28"/>
+      <c r="T45" s="28"/>
+      <c r="U45" s="28"/>
+      <c r="V45" s="28"/>
+      <c r="W45" s="28"/>
+      <c r="X45" s="28"/>
+      <c r="Y45" s="28"/>
+      <c r="Z45" s="29"/>
     </row>
     <row r="46" spans="3:26" x14ac:dyDescent="0.3">
-      <c r="C46" s="15"/>
-      <c r="D46" s="16"/>
-      <c r="E46" s="16"/>
-      <c r="F46" s="16"/>
-      <c r="G46" s="16"/>
-      <c r="H46" s="16"/>
-      <c r="I46" s="16"/>
-      <c r="J46" s="16"/>
-      <c r="K46" s="16"/>
-      <c r="L46" s="16"/>
-      <c r="M46" s="16"/>
-      <c r="N46" s="16"/>
-      <c r="O46" s="16"/>
-      <c r="P46" s="16"/>
-      <c r="Q46" s="16"/>
-      <c r="R46" s="16"/>
-      <c r="S46" s="16"/>
-      <c r="T46" s="16"/>
-      <c r="U46" s="16"/>
-      <c r="V46" s="16"/>
-      <c r="W46" s="16"/>
-      <c r="X46" s="16"/>
-      <c r="Y46" s="16"/>
-      <c r="Z46" s="17"/>
+      <c r="C46" s="30"/>
+      <c r="D46" s="31"/>
+      <c r="E46" s="31"/>
+      <c r="F46" s="31"/>
+      <c r="G46" s="31"/>
+      <c r="H46" s="31"/>
+      <c r="I46" s="31"/>
+      <c r="J46" s="31"/>
+      <c r="K46" s="31"/>
+      <c r="L46" s="31"/>
+      <c r="M46" s="31"/>
+      <c r="N46" s="31"/>
+      <c r="O46" s="31"/>
+      <c r="P46" s="31"/>
+      <c r="Q46" s="31"/>
+      <c r="R46" s="31"/>
+      <c r="S46" s="31"/>
+      <c r="T46" s="31"/>
+      <c r="U46" s="31"/>
+      <c r="V46" s="31"/>
+      <c r="W46" s="31"/>
+      <c r="X46" s="31"/>
+      <c r="Y46" s="31"/>
+      <c r="Z46" s="32"/>
     </row>
     <row r="48" spans="3:26" x14ac:dyDescent="0.3">
       <c r="D48" s="2" t="s">
@@ -3392,58 +5464,58 @@
       </c>
     </row>
     <row r="56" spans="3:26" x14ac:dyDescent="0.3">
-      <c r="C56" s="9" t="s">
+      <c r="C56" s="27" t="s">
         <v>48</v>
       </c>
-      <c r="D56" s="10"/>
-      <c r="E56" s="10"/>
-      <c r="F56" s="10"/>
-      <c r="G56" s="10"/>
-      <c r="H56" s="10"/>
-      <c r="I56" s="10"/>
-      <c r="J56" s="10"/>
-      <c r="K56" s="10"/>
-      <c r="L56" s="10"/>
-      <c r="M56" s="10"/>
-      <c r="N56" s="10"/>
-      <c r="O56" s="10"/>
-      <c r="P56" s="10"/>
-      <c r="Q56" s="10"/>
-      <c r="R56" s="10"/>
-      <c r="S56" s="10"/>
-      <c r="T56" s="10"/>
-      <c r="U56" s="10"/>
-      <c r="V56" s="10"/>
-      <c r="W56" s="10"/>
-      <c r="X56" s="10"/>
-      <c r="Y56" s="10"/>
-      <c r="Z56" s="11"/>
+      <c r="D56" s="28"/>
+      <c r="E56" s="28"/>
+      <c r="F56" s="28"/>
+      <c r="G56" s="28"/>
+      <c r="H56" s="28"/>
+      <c r="I56" s="28"/>
+      <c r="J56" s="28"/>
+      <c r="K56" s="28"/>
+      <c r="L56" s="28"/>
+      <c r="M56" s="28"/>
+      <c r="N56" s="28"/>
+      <c r="O56" s="28"/>
+      <c r="P56" s="28"/>
+      <c r="Q56" s="28"/>
+      <c r="R56" s="28"/>
+      <c r="S56" s="28"/>
+      <c r="T56" s="28"/>
+      <c r="U56" s="28"/>
+      <c r="V56" s="28"/>
+      <c r="W56" s="28"/>
+      <c r="X56" s="28"/>
+      <c r="Y56" s="28"/>
+      <c r="Z56" s="29"/>
     </row>
     <row r="57" spans="3:26" x14ac:dyDescent="0.3">
-      <c r="C57" s="15"/>
-      <c r="D57" s="16"/>
-      <c r="E57" s="16"/>
-      <c r="F57" s="16"/>
-      <c r="G57" s="16"/>
-      <c r="H57" s="16"/>
-      <c r="I57" s="16"/>
-      <c r="J57" s="16"/>
-      <c r="K57" s="16"/>
-      <c r="L57" s="16"/>
-      <c r="M57" s="16"/>
-      <c r="N57" s="16"/>
-      <c r="O57" s="16"/>
-      <c r="P57" s="16"/>
-      <c r="Q57" s="16"/>
-      <c r="R57" s="16"/>
-      <c r="S57" s="16"/>
-      <c r="T57" s="16"/>
-      <c r="U57" s="16"/>
-      <c r="V57" s="16"/>
-      <c r="W57" s="16"/>
-      <c r="X57" s="16"/>
-      <c r="Y57" s="16"/>
-      <c r="Z57" s="17"/>
+      <c r="C57" s="30"/>
+      <c r="D57" s="31"/>
+      <c r="E57" s="31"/>
+      <c r="F57" s="31"/>
+      <c r="G57" s="31"/>
+      <c r="H57" s="31"/>
+      <c r="I57" s="31"/>
+      <c r="J57" s="31"/>
+      <c r="K57" s="31"/>
+      <c r="L57" s="31"/>
+      <c r="M57" s="31"/>
+      <c r="N57" s="31"/>
+      <c r="O57" s="31"/>
+      <c r="P57" s="31"/>
+      <c r="Q57" s="31"/>
+      <c r="R57" s="31"/>
+      <c r="S57" s="31"/>
+      <c r="T57" s="31"/>
+      <c r="U57" s="31"/>
+      <c r="V57" s="31"/>
+      <c r="W57" s="31"/>
+      <c r="X57" s="31"/>
+      <c r="Y57" s="31"/>
+      <c r="Z57" s="32"/>
     </row>
     <row r="59" spans="3:26" x14ac:dyDescent="0.3">
       <c r="D59" s="2" t="s">
@@ -3476,58 +5548,58 @@
       </c>
     </row>
     <row r="68" spans="3:26" x14ac:dyDescent="0.3">
-      <c r="C68" s="9" t="s">
+      <c r="C68" s="27" t="s">
         <v>49</v>
       </c>
-      <c r="D68" s="10"/>
-      <c r="E68" s="10"/>
-      <c r="F68" s="10"/>
-      <c r="G68" s="10"/>
-      <c r="H68" s="10"/>
-      <c r="I68" s="10"/>
-      <c r="J68" s="10"/>
-      <c r="K68" s="10"/>
-      <c r="L68" s="10"/>
-      <c r="M68" s="10"/>
-      <c r="N68" s="10"/>
-      <c r="O68" s="10"/>
-      <c r="P68" s="10"/>
-      <c r="Q68" s="10"/>
-      <c r="R68" s="10"/>
-      <c r="S68" s="10"/>
-      <c r="T68" s="10"/>
-      <c r="U68" s="10"/>
-      <c r="V68" s="10"/>
-      <c r="W68" s="10"/>
-      <c r="X68" s="10"/>
-      <c r="Y68" s="10"/>
-      <c r="Z68" s="11"/>
+      <c r="D68" s="28"/>
+      <c r="E68" s="28"/>
+      <c r="F68" s="28"/>
+      <c r="G68" s="28"/>
+      <c r="H68" s="28"/>
+      <c r="I68" s="28"/>
+      <c r="J68" s="28"/>
+      <c r="K68" s="28"/>
+      <c r="L68" s="28"/>
+      <c r="M68" s="28"/>
+      <c r="N68" s="28"/>
+      <c r="O68" s="28"/>
+      <c r="P68" s="28"/>
+      <c r="Q68" s="28"/>
+      <c r="R68" s="28"/>
+      <c r="S68" s="28"/>
+      <c r="T68" s="28"/>
+      <c r="U68" s="28"/>
+      <c r="V68" s="28"/>
+      <c r="W68" s="28"/>
+      <c r="X68" s="28"/>
+      <c r="Y68" s="28"/>
+      <c r="Z68" s="29"/>
     </row>
     <row r="69" spans="3:26" x14ac:dyDescent="0.3">
-      <c r="C69" s="15"/>
-      <c r="D69" s="16"/>
-      <c r="E69" s="16"/>
-      <c r="F69" s="16"/>
-      <c r="G69" s="16"/>
-      <c r="H69" s="16"/>
-      <c r="I69" s="16"/>
-      <c r="J69" s="16"/>
-      <c r="K69" s="16"/>
-      <c r="L69" s="16"/>
-      <c r="M69" s="16"/>
-      <c r="N69" s="16"/>
-      <c r="O69" s="16"/>
-      <c r="P69" s="16"/>
-      <c r="Q69" s="16"/>
-      <c r="R69" s="16"/>
-      <c r="S69" s="16"/>
-      <c r="T69" s="16"/>
-      <c r="U69" s="16"/>
-      <c r="V69" s="16"/>
-      <c r="W69" s="16"/>
-      <c r="X69" s="16"/>
-      <c r="Y69" s="16"/>
-      <c r="Z69" s="17"/>
+      <c r="C69" s="30"/>
+      <c r="D69" s="31"/>
+      <c r="E69" s="31"/>
+      <c r="F69" s="31"/>
+      <c r="G69" s="31"/>
+      <c r="H69" s="31"/>
+      <c r="I69" s="31"/>
+      <c r="J69" s="31"/>
+      <c r="K69" s="31"/>
+      <c r="L69" s="31"/>
+      <c r="M69" s="31"/>
+      <c r="N69" s="31"/>
+      <c r="O69" s="31"/>
+      <c r="P69" s="31"/>
+      <c r="Q69" s="31"/>
+      <c r="R69" s="31"/>
+      <c r="S69" s="31"/>
+      <c r="T69" s="31"/>
+      <c r="U69" s="31"/>
+      <c r="V69" s="31"/>
+      <c r="W69" s="31"/>
+      <c r="X69" s="31"/>
+      <c r="Y69" s="31"/>
+      <c r="Z69" s="32"/>
     </row>
     <row r="71" spans="3:26" x14ac:dyDescent="0.3">
       <c r="D71" s="2" t="s">
@@ -3565,144 +5637,144 @@
       </c>
     </row>
     <row r="80" spans="3:26" x14ac:dyDescent="0.3">
-      <c r="E80" s="8" t="s">
+      <c r="E80" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="F80" s="8"/>
-      <c r="G80" s="8"/>
-      <c r="H80" s="8" t="s">
+      <c r="F80" s="25"/>
+      <c r="G80" s="25"/>
+      <c r="H80" s="25" t="s">
         <v>73</v>
       </c>
-      <c r="I80" s="8"/>
-      <c r="J80" s="8"/>
-      <c r="K80" s="8"/>
-      <c r="L80" s="8"/>
-      <c r="M80" s="8"/>
-      <c r="N80" s="8"/>
-      <c r="O80" s="8"/>
-      <c r="P80" s="8"/>
-      <c r="Q80" s="8"/>
-      <c r="R80" s="8"/>
-      <c r="S80" s="8"/>
-      <c r="T80" s="8"/>
-      <c r="U80" s="8" t="s">
+      <c r="I80" s="25"/>
+      <c r="J80" s="25"/>
+      <c r="K80" s="25"/>
+      <c r="L80" s="25"/>
+      <c r="M80" s="25"/>
+      <c r="N80" s="25"/>
+      <c r="O80" s="25"/>
+      <c r="P80" s="25"/>
+      <c r="Q80" s="25"/>
+      <c r="R80" s="25"/>
+      <c r="S80" s="25"/>
+      <c r="T80" s="25"/>
+      <c r="U80" s="25" t="s">
         <v>78</v>
       </c>
-      <c r="V80" s="8"/>
-      <c r="W80" s="8"/>
-      <c r="X80" s="8"/>
+      <c r="V80" s="25"/>
+      <c r="W80" s="25"/>
+      <c r="X80" s="25"/>
     </row>
     <row r="81" spans="4:24" x14ac:dyDescent="0.3">
-      <c r="E81" s="8" t="s">
+      <c r="E81" s="25" t="s">
         <v>72</v>
       </c>
-      <c r="F81" s="8"/>
-      <c r="G81" s="8"/>
-      <c r="H81" s="8" t="s">
+      <c r="F81" s="25"/>
+      <c r="G81" s="25"/>
+      <c r="H81" s="25" t="s">
         <v>74</v>
       </c>
-      <c r="I81" s="8"/>
-      <c r="J81" s="8"/>
-      <c r="K81" s="8"/>
-      <c r="L81" s="8"/>
-      <c r="M81" s="8"/>
-      <c r="N81" s="8"/>
-      <c r="O81" s="8"/>
-      <c r="P81" s="8"/>
-      <c r="Q81" s="8"/>
-      <c r="R81" s="8"/>
-      <c r="S81" s="8"/>
-      <c r="T81" s="8"/>
-      <c r="U81" s="8" t="s">
+      <c r="I81" s="25"/>
+      <c r="J81" s="25"/>
+      <c r="K81" s="25"/>
+      <c r="L81" s="25"/>
+      <c r="M81" s="25"/>
+      <c r="N81" s="25"/>
+      <c r="O81" s="25"/>
+      <c r="P81" s="25"/>
+      <c r="Q81" s="25"/>
+      <c r="R81" s="25"/>
+      <c r="S81" s="25"/>
+      <c r="T81" s="25"/>
+      <c r="U81" s="25" t="s">
         <v>79</v>
       </c>
-      <c r="V81" s="8"/>
-      <c r="W81" s="8"/>
-      <c r="X81" s="8"/>
+      <c r="V81" s="25"/>
+      <c r="W81" s="25"/>
+      <c r="X81" s="25"/>
     </row>
     <row r="82" spans="4:24" x14ac:dyDescent="0.3">
-      <c r="E82" s="8" t="s">
+      <c r="E82" s="25" t="s">
         <v>69</v>
       </c>
-      <c r="F82" s="8"/>
-      <c r="G82" s="8"/>
-      <c r="H82" s="8" t="s">
+      <c r="F82" s="25"/>
+      <c r="G82" s="25"/>
+      <c r="H82" s="25" t="s">
         <v>75</v>
       </c>
-      <c r="I82" s="8"/>
-      <c r="J82" s="8"/>
-      <c r="K82" s="8"/>
-      <c r="L82" s="8"/>
-      <c r="M82" s="8"/>
-      <c r="N82" s="8"/>
-      <c r="O82" s="8"/>
-      <c r="P82" s="8"/>
-      <c r="Q82" s="8"/>
-      <c r="R82" s="8"/>
-      <c r="S82" s="8"/>
-      <c r="T82" s="8"/>
-      <c r="U82" s="8" t="s">
+      <c r="I82" s="25"/>
+      <c r="J82" s="25"/>
+      <c r="K82" s="25"/>
+      <c r="L82" s="25"/>
+      <c r="M82" s="25"/>
+      <c r="N82" s="25"/>
+      <c r="O82" s="25"/>
+      <c r="P82" s="25"/>
+      <c r="Q82" s="25"/>
+      <c r="R82" s="25"/>
+      <c r="S82" s="25"/>
+      <c r="T82" s="25"/>
+      <c r="U82" s="25" t="s">
         <v>79</v>
       </c>
-      <c r="V82" s="8"/>
-      <c r="W82" s="8"/>
-      <c r="X82" s="8"/>
+      <c r="V82" s="25"/>
+      <c r="W82" s="25"/>
+      <c r="X82" s="25"/>
     </row>
     <row r="83" spans="4:24" x14ac:dyDescent="0.3">
-      <c r="E83" s="8" t="s">
+      <c r="E83" s="25" t="s">
         <v>70</v>
       </c>
-      <c r="F83" s="8"/>
-      <c r="G83" s="8"/>
-      <c r="H83" s="8" t="s">
+      <c r="F83" s="25"/>
+      <c r="G83" s="25"/>
+      <c r="H83" s="25" t="s">
         <v>76</v>
       </c>
-      <c r="I83" s="8"/>
-      <c r="J83" s="8"/>
-      <c r="K83" s="8"/>
-      <c r="L83" s="8"/>
-      <c r="M83" s="8"/>
-      <c r="N83" s="8"/>
-      <c r="O83" s="8"/>
-      <c r="P83" s="8"/>
-      <c r="Q83" s="8"/>
-      <c r="R83" s="8"/>
-      <c r="S83" s="8"/>
-      <c r="T83" s="8"/>
-      <c r="U83" s="8" t="s">
+      <c r="I83" s="25"/>
+      <c r="J83" s="25"/>
+      <c r="K83" s="25"/>
+      <c r="L83" s="25"/>
+      <c r="M83" s="25"/>
+      <c r="N83" s="25"/>
+      <c r="O83" s="25"/>
+      <c r="P83" s="25"/>
+      <c r="Q83" s="25"/>
+      <c r="R83" s="25"/>
+      <c r="S83" s="25"/>
+      <c r="T83" s="25"/>
+      <c r="U83" s="25" t="s">
         <v>80</v>
       </c>
-      <c r="V83" s="8"/>
-      <c r="W83" s="8"/>
-      <c r="X83" s="8"/>
+      <c r="V83" s="25"/>
+      <c r="W83" s="25"/>
+      <c r="X83" s="25"/>
     </row>
     <row r="84" spans="4:24" x14ac:dyDescent="0.3">
-      <c r="E84" s="8" t="s">
+      <c r="E84" s="25" t="s">
         <v>71</v>
       </c>
-      <c r="F84" s="8"/>
-      <c r="G84" s="8"/>
-      <c r="H84" s="8" t="s">
+      <c r="F84" s="25"/>
+      <c r="G84" s="25"/>
+      <c r="H84" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="I84" s="8"/>
-      <c r="J84" s="8"/>
-      <c r="K84" s="8"/>
-      <c r="L84" s="8"/>
-      <c r="M84" s="8"/>
-      <c r="N84" s="8"/>
-      <c r="O84" s="8"/>
-      <c r="P84" s="8"/>
-      <c r="Q84" s="8"/>
-      <c r="R84" s="8"/>
-      <c r="S84" s="8"/>
-      <c r="T84" s="8"/>
-      <c r="U84" s="8" t="s">
+      <c r="I84" s="25"/>
+      <c r="J84" s="25"/>
+      <c r="K84" s="25"/>
+      <c r="L84" s="25"/>
+      <c r="M84" s="25"/>
+      <c r="N84" s="25"/>
+      <c r="O84" s="25"/>
+      <c r="P84" s="25"/>
+      <c r="Q84" s="25"/>
+      <c r="R84" s="25"/>
+      <c r="S84" s="25"/>
+      <c r="T84" s="25"/>
+      <c r="U84" s="25" t="s">
         <v>81</v>
       </c>
-      <c r="V84" s="8"/>
-      <c r="W84" s="8"/>
-      <c r="X84" s="8"/>
+      <c r="V84" s="25"/>
+      <c r="W84" s="25"/>
+      <c r="X84" s="25"/>
     </row>
     <row r="86" spans="4:24" x14ac:dyDescent="0.3">
       <c r="D86" s="2" t="s">
@@ -3765,58 +5837,58 @@
       </c>
     </row>
     <row r="101" spans="3:26" x14ac:dyDescent="0.3">
-      <c r="C101" s="9" t="s">
+      <c r="C101" s="27" t="s">
         <v>45</v>
       </c>
-      <c r="D101" s="10"/>
-      <c r="E101" s="10"/>
-      <c r="F101" s="10"/>
-      <c r="G101" s="10"/>
-      <c r="H101" s="10"/>
-      <c r="I101" s="10"/>
-      <c r="J101" s="10"/>
-      <c r="K101" s="10"/>
-      <c r="L101" s="10"/>
-      <c r="M101" s="10"/>
-      <c r="N101" s="10"/>
-      <c r="O101" s="10"/>
-      <c r="P101" s="10"/>
-      <c r="Q101" s="10"/>
-      <c r="R101" s="10"/>
-      <c r="S101" s="10"/>
-      <c r="T101" s="10"/>
-      <c r="U101" s="10"/>
-      <c r="V101" s="10"/>
-      <c r="W101" s="10"/>
-      <c r="X101" s="10"/>
-      <c r="Y101" s="10"/>
-      <c r="Z101" s="11"/>
+      <c r="D101" s="28"/>
+      <c r="E101" s="28"/>
+      <c r="F101" s="28"/>
+      <c r="G101" s="28"/>
+      <c r="H101" s="28"/>
+      <c r="I101" s="28"/>
+      <c r="J101" s="28"/>
+      <c r="K101" s="28"/>
+      <c r="L101" s="28"/>
+      <c r="M101" s="28"/>
+      <c r="N101" s="28"/>
+      <c r="O101" s="28"/>
+      <c r="P101" s="28"/>
+      <c r="Q101" s="28"/>
+      <c r="R101" s="28"/>
+      <c r="S101" s="28"/>
+      <c r="T101" s="28"/>
+      <c r="U101" s="28"/>
+      <c r="V101" s="28"/>
+      <c r="W101" s="28"/>
+      <c r="X101" s="28"/>
+      <c r="Y101" s="28"/>
+      <c r="Z101" s="29"/>
     </row>
     <row r="102" spans="3:26" x14ac:dyDescent="0.3">
-      <c r="C102" s="15"/>
-      <c r="D102" s="16"/>
-      <c r="E102" s="16"/>
-      <c r="F102" s="16"/>
-      <c r="G102" s="16"/>
-      <c r="H102" s="16"/>
-      <c r="I102" s="16"/>
-      <c r="J102" s="16"/>
-      <c r="K102" s="16"/>
-      <c r="L102" s="16"/>
-      <c r="M102" s="16"/>
-      <c r="N102" s="16"/>
-      <c r="O102" s="16"/>
-      <c r="P102" s="16"/>
-      <c r="Q102" s="16"/>
-      <c r="R102" s="16"/>
-      <c r="S102" s="16"/>
-      <c r="T102" s="16"/>
-      <c r="U102" s="16"/>
-      <c r="V102" s="16"/>
-      <c r="W102" s="16"/>
-      <c r="X102" s="16"/>
-      <c r="Y102" s="16"/>
-      <c r="Z102" s="17"/>
+      <c r="C102" s="30"/>
+      <c r="D102" s="31"/>
+      <c r="E102" s="31"/>
+      <c r="F102" s="31"/>
+      <c r="G102" s="31"/>
+      <c r="H102" s="31"/>
+      <c r="I102" s="31"/>
+      <c r="J102" s="31"/>
+      <c r="K102" s="31"/>
+      <c r="L102" s="31"/>
+      <c r="M102" s="31"/>
+      <c r="N102" s="31"/>
+      <c r="O102" s="31"/>
+      <c r="P102" s="31"/>
+      <c r="Q102" s="31"/>
+      <c r="R102" s="31"/>
+      <c r="S102" s="31"/>
+      <c r="T102" s="31"/>
+      <c r="U102" s="31"/>
+      <c r="V102" s="31"/>
+      <c r="W102" s="31"/>
+      <c r="X102" s="31"/>
+      <c r="Y102" s="31"/>
+      <c r="Z102" s="32"/>
     </row>
     <row r="104" spans="3:26" x14ac:dyDescent="0.3">
       <c r="D104" s="2" t="s">
@@ -3824,238 +5896,238 @@
       </c>
     </row>
     <row r="106" spans="3:26" x14ac:dyDescent="0.3">
-      <c r="E106" s="8" t="s">
+      <c r="E106" s="25" t="s">
         <v>95</v>
       </c>
-      <c r="F106" s="8"/>
-      <c r="G106" s="8"/>
-      <c r="H106" s="8"/>
-      <c r="I106" s="8"/>
-      <c r="J106" s="8"/>
-      <c r="K106" s="8" t="s">
+      <c r="F106" s="25"/>
+      <c r="G106" s="25"/>
+      <c r="H106" s="25"/>
+      <c r="I106" s="25"/>
+      <c r="J106" s="25"/>
+      <c r="K106" s="25" t="s">
         <v>102</v>
       </c>
-      <c r="L106" s="8"/>
-      <c r="M106" s="8"/>
-      <c r="N106" s="8"/>
-      <c r="O106" s="8"/>
-      <c r="P106" s="8"/>
-      <c r="Q106" s="8"/>
-      <c r="R106" s="8"/>
-      <c r="S106" s="8"/>
-      <c r="T106" s="8"/>
-      <c r="U106" s="8"/>
-      <c r="V106" s="8"/>
-      <c r="W106" s="8"/>
-      <c r="X106" s="8"/>
+      <c r="L106" s="25"/>
+      <c r="M106" s="25"/>
+      <c r="N106" s="25"/>
+      <c r="O106" s="25"/>
+      <c r="P106" s="25"/>
+      <c r="Q106" s="25"/>
+      <c r="R106" s="25"/>
+      <c r="S106" s="25"/>
+      <c r="T106" s="25"/>
+      <c r="U106" s="25"/>
+      <c r="V106" s="25"/>
+      <c r="W106" s="25"/>
+      <c r="X106" s="25"/>
     </row>
     <row r="107" spans="3:26" x14ac:dyDescent="0.3">
-      <c r="E107" s="21" t="s">
+      <c r="E107" s="24" t="s">
         <v>96</v>
       </c>
-      <c r="F107" s="21"/>
-      <c r="G107" s="21"/>
-      <c r="H107" s="21"/>
-      <c r="I107" s="21"/>
-      <c r="J107" s="21"/>
-      <c r="K107" s="21" t="s">
+      <c r="F107" s="24"/>
+      <c r="G107" s="24"/>
+      <c r="H107" s="24"/>
+      <c r="I107" s="24"/>
+      <c r="J107" s="24"/>
+      <c r="K107" s="24" t="s">
         <v>103</v>
       </c>
-      <c r="L107" s="21"/>
-      <c r="M107" s="21"/>
-      <c r="N107" s="21"/>
-      <c r="O107" s="21"/>
-      <c r="P107" s="21"/>
-      <c r="Q107" s="21"/>
-      <c r="R107" s="21"/>
-      <c r="S107" s="21"/>
-      <c r="T107" s="21"/>
-      <c r="U107" s="21"/>
-      <c r="V107" s="21"/>
-      <c r="W107" s="21"/>
-      <c r="X107" s="21"/>
+      <c r="L107" s="24"/>
+      <c r="M107" s="24"/>
+      <c r="N107" s="24"/>
+      <c r="O107" s="24"/>
+      <c r="P107" s="24"/>
+      <c r="Q107" s="24"/>
+      <c r="R107" s="24"/>
+      <c r="S107" s="24"/>
+      <c r="T107" s="24"/>
+      <c r="U107" s="24"/>
+      <c r="V107" s="24"/>
+      <c r="W107" s="24"/>
+      <c r="X107" s="24"/>
     </row>
     <row r="108" spans="3:26" x14ac:dyDescent="0.3">
-      <c r="E108" s="21" t="s">
+      <c r="E108" s="24" t="s">
         <v>97</v>
       </c>
-      <c r="F108" s="21"/>
-      <c r="G108" s="21"/>
-      <c r="H108" s="21"/>
-      <c r="I108" s="21"/>
-      <c r="J108" s="21"/>
-      <c r="K108" s="21" t="s">
+      <c r="F108" s="24"/>
+      <c r="G108" s="24"/>
+      <c r="H108" s="24"/>
+      <c r="I108" s="24"/>
+      <c r="J108" s="24"/>
+      <c r="K108" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="L108" s="21"/>
-      <c r="M108" s="21"/>
-      <c r="N108" s="21"/>
-      <c r="O108" s="21"/>
-      <c r="P108" s="21"/>
-      <c r="Q108" s="21"/>
-      <c r="R108" s="21"/>
-      <c r="S108" s="21"/>
-      <c r="T108" s="21"/>
-      <c r="U108" s="21"/>
-      <c r="V108" s="21"/>
-      <c r="W108" s="21"/>
-      <c r="X108" s="21"/>
+      <c r="L108" s="24"/>
+      <c r="M108" s="24"/>
+      <c r="N108" s="24"/>
+      <c r="O108" s="24"/>
+      <c r="P108" s="24"/>
+      <c r="Q108" s="24"/>
+      <c r="R108" s="24"/>
+      <c r="S108" s="24"/>
+      <c r="T108" s="24"/>
+      <c r="U108" s="24"/>
+      <c r="V108" s="24"/>
+      <c r="W108" s="24"/>
+      <c r="X108" s="24"/>
     </row>
     <row r="109" spans="3:26" x14ac:dyDescent="0.3">
-      <c r="E109" s="21" t="s">
+      <c r="E109" s="24" t="s">
         <v>98</v>
       </c>
-      <c r="F109" s="21"/>
-      <c r="G109" s="21"/>
-      <c r="H109" s="21"/>
-      <c r="I109" s="21"/>
-      <c r="J109" s="21"/>
-      <c r="K109" s="21" t="s">
+      <c r="F109" s="24"/>
+      <c r="G109" s="24"/>
+      <c r="H109" s="24"/>
+      <c r="I109" s="24"/>
+      <c r="J109" s="24"/>
+      <c r="K109" s="24" t="s">
         <v>105</v>
       </c>
-      <c r="L109" s="21"/>
-      <c r="M109" s="21"/>
-      <c r="N109" s="21"/>
-      <c r="O109" s="21"/>
-      <c r="P109" s="21"/>
-      <c r="Q109" s="21"/>
-      <c r="R109" s="21"/>
-      <c r="S109" s="21"/>
-      <c r="T109" s="21"/>
-      <c r="U109" s="21"/>
-      <c r="V109" s="21"/>
-      <c r="W109" s="21"/>
-      <c r="X109" s="21"/>
+      <c r="L109" s="24"/>
+      <c r="M109" s="24"/>
+      <c r="N109" s="24"/>
+      <c r="O109" s="24"/>
+      <c r="P109" s="24"/>
+      <c r="Q109" s="24"/>
+      <c r="R109" s="24"/>
+      <c r="S109" s="24"/>
+      <c r="T109" s="24"/>
+      <c r="U109" s="24"/>
+      <c r="V109" s="24"/>
+      <c r="W109" s="24"/>
+      <c r="X109" s="24"/>
     </row>
     <row r="110" spans="3:26" x14ac:dyDescent="0.3">
-      <c r="E110" s="21" t="s">
+      <c r="E110" s="24" t="s">
         <v>107</v>
       </c>
-      <c r="F110" s="21"/>
-      <c r="G110" s="21"/>
-      <c r="H110" s="21"/>
-      <c r="I110" s="21"/>
-      <c r="J110" s="21"/>
-      <c r="K110" s="21" t="s">
+      <c r="F110" s="24"/>
+      <c r="G110" s="24"/>
+      <c r="H110" s="24"/>
+      <c r="I110" s="24"/>
+      <c r="J110" s="24"/>
+      <c r="K110" s="24" t="s">
         <v>106</v>
       </c>
-      <c r="L110" s="21"/>
-      <c r="M110" s="21"/>
-      <c r="N110" s="21"/>
-      <c r="O110" s="21"/>
-      <c r="P110" s="21"/>
-      <c r="Q110" s="21"/>
-      <c r="R110" s="21"/>
-      <c r="S110" s="21"/>
-      <c r="T110" s="21"/>
-      <c r="U110" s="21"/>
-      <c r="V110" s="21"/>
-      <c r="W110" s="21"/>
-      <c r="X110" s="21"/>
+      <c r="L110" s="24"/>
+      <c r="M110" s="24"/>
+      <c r="N110" s="24"/>
+      <c r="O110" s="24"/>
+      <c r="P110" s="24"/>
+      <c r="Q110" s="24"/>
+      <c r="R110" s="24"/>
+      <c r="S110" s="24"/>
+      <c r="T110" s="24"/>
+      <c r="U110" s="24"/>
+      <c r="V110" s="24"/>
+      <c r="W110" s="24"/>
+      <c r="X110" s="24"/>
     </row>
     <row r="111" spans="3:26" x14ac:dyDescent="0.3">
-      <c r="E111" s="21" t="s">
+      <c r="E111" s="24" t="s">
         <v>99</v>
       </c>
-      <c r="F111" s="21"/>
-      <c r="G111" s="21"/>
-      <c r="H111" s="21"/>
-      <c r="I111" s="21"/>
-      <c r="J111" s="21"/>
-      <c r="K111" s="21" t="s">
+      <c r="F111" s="24"/>
+      <c r="G111" s="24"/>
+      <c r="H111" s="24"/>
+      <c r="I111" s="24"/>
+      <c r="J111" s="24"/>
+      <c r="K111" s="24" t="s">
         <v>108</v>
       </c>
-      <c r="L111" s="21"/>
-      <c r="M111" s="21"/>
-      <c r="N111" s="21"/>
-      <c r="O111" s="21"/>
-      <c r="P111" s="21"/>
-      <c r="Q111" s="21"/>
-      <c r="R111" s="21"/>
-      <c r="S111" s="21"/>
-      <c r="T111" s="21"/>
-      <c r="U111" s="21"/>
-      <c r="V111" s="21"/>
-      <c r="W111" s="21"/>
-      <c r="X111" s="21"/>
+      <c r="L111" s="24"/>
+      <c r="M111" s="24"/>
+      <c r="N111" s="24"/>
+      <c r="O111" s="24"/>
+      <c r="P111" s="24"/>
+      <c r="Q111" s="24"/>
+      <c r="R111" s="24"/>
+      <c r="S111" s="24"/>
+      <c r="T111" s="24"/>
+      <c r="U111" s="24"/>
+      <c r="V111" s="24"/>
+      <c r="W111" s="24"/>
+      <c r="X111" s="24"/>
     </row>
     <row r="112" spans="3:26" x14ac:dyDescent="0.3">
-      <c r="E112" s="21" t="s">
+      <c r="E112" s="24" t="s">
         <v>101</v>
       </c>
-      <c r="F112" s="21"/>
-      <c r="G112" s="21"/>
-      <c r="H112" s="21"/>
-      <c r="I112" s="21"/>
-      <c r="J112" s="21"/>
-      <c r="K112" s="21" t="s">
+      <c r="F112" s="24"/>
+      <c r="G112" s="24"/>
+      <c r="H112" s="24"/>
+      <c r="I112" s="24"/>
+      <c r="J112" s="24"/>
+      <c r="K112" s="24" t="s">
         <v>109</v>
       </c>
-      <c r="L112" s="21"/>
-      <c r="M112" s="21"/>
-      <c r="N112" s="21"/>
-      <c r="O112" s="21"/>
-      <c r="P112" s="21"/>
-      <c r="Q112" s="21"/>
-      <c r="R112" s="21"/>
-      <c r="S112" s="21"/>
-      <c r="T112" s="21"/>
-      <c r="U112" s="21"/>
-      <c r="V112" s="21"/>
-      <c r="W112" s="21"/>
-      <c r="X112" s="21"/>
+      <c r="L112" s="24"/>
+      <c r="M112" s="24"/>
+      <c r="N112" s="24"/>
+      <c r="O112" s="24"/>
+      <c r="P112" s="24"/>
+      <c r="Q112" s="24"/>
+      <c r="R112" s="24"/>
+      <c r="S112" s="24"/>
+      <c r="T112" s="24"/>
+      <c r="U112" s="24"/>
+      <c r="V112" s="24"/>
+      <c r="W112" s="24"/>
+      <c r="X112" s="24"/>
     </row>
     <row r="113" spans="4:25" x14ac:dyDescent="0.3">
-      <c r="E113" s="21" t="s">
+      <c r="E113" s="24" t="s">
         <v>32</v>
       </c>
-      <c r="F113" s="21"/>
-      <c r="G113" s="21"/>
-      <c r="H113" s="21"/>
-      <c r="I113" s="21"/>
-      <c r="J113" s="21"/>
-      <c r="K113" s="21" t="s">
+      <c r="F113" s="24"/>
+      <c r="G113" s="24"/>
+      <c r="H113" s="24"/>
+      <c r="I113" s="24"/>
+      <c r="J113" s="24"/>
+      <c r="K113" s="24" t="s">
         <v>110</v>
       </c>
-      <c r="L113" s="21"/>
-      <c r="M113" s="21"/>
-      <c r="N113" s="21"/>
-      <c r="O113" s="21"/>
-      <c r="P113" s="21"/>
-      <c r="Q113" s="21"/>
-      <c r="R113" s="21"/>
-      <c r="S113" s="21"/>
-      <c r="T113" s="21"/>
-      <c r="U113" s="21"/>
-      <c r="V113" s="21"/>
-      <c r="W113" s="21"/>
-      <c r="X113" s="21"/>
+      <c r="L113" s="24"/>
+      <c r="M113" s="24"/>
+      <c r="N113" s="24"/>
+      <c r="O113" s="24"/>
+      <c r="P113" s="24"/>
+      <c r="Q113" s="24"/>
+      <c r="R113" s="24"/>
+      <c r="S113" s="24"/>
+      <c r="T113" s="24"/>
+      <c r="U113" s="24"/>
+      <c r="V113" s="24"/>
+      <c r="W113" s="24"/>
+      <c r="X113" s="24"/>
     </row>
     <row r="114" spans="4:25" x14ac:dyDescent="0.3">
-      <c r="E114" s="21" t="s">
+      <c r="E114" s="24" t="s">
         <v>100</v>
       </c>
-      <c r="F114" s="21"/>
-      <c r="G114" s="21"/>
-      <c r="H114" s="21"/>
-      <c r="I114" s="21"/>
-      <c r="J114" s="21"/>
-      <c r="K114" s="21" t="s">
+      <c r="F114" s="24"/>
+      <c r="G114" s="24"/>
+      <c r="H114" s="24"/>
+      <c r="I114" s="24"/>
+      <c r="J114" s="24"/>
+      <c r="K114" s="24" t="s">
         <v>111</v>
       </c>
-      <c r="L114" s="21"/>
-      <c r="M114" s="21"/>
-      <c r="N114" s="21"/>
-      <c r="O114" s="21"/>
-      <c r="P114" s="21"/>
-      <c r="Q114" s="21"/>
-      <c r="R114" s="21"/>
-      <c r="S114" s="21"/>
-      <c r="T114" s="21"/>
-      <c r="U114" s="21"/>
-      <c r="V114" s="21"/>
-      <c r="W114" s="21"/>
-      <c r="X114" s="21"/>
+      <c r="L114" s="24"/>
+      <c r="M114" s="24"/>
+      <c r="N114" s="24"/>
+      <c r="O114" s="24"/>
+      <c r="P114" s="24"/>
+      <c r="Q114" s="24"/>
+      <c r="R114" s="24"/>
+      <c r="S114" s="24"/>
+      <c r="T114" s="24"/>
+      <c r="U114" s="24"/>
+      <c r="V114" s="24"/>
+      <c r="W114" s="24"/>
+      <c r="X114" s="24"/>
     </row>
     <row r="116" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D116" s="2" t="s">
@@ -4063,93 +6135,93 @@
       </c>
     </row>
     <row r="118" spans="4:25" x14ac:dyDescent="0.3">
-      <c r="E118" s="8" t="s">
+      <c r="E118" s="25" t="s">
         <v>113</v>
       </c>
-      <c r="F118" s="8"/>
-      <c r="G118" s="8"/>
-      <c r="H118" s="8"/>
-      <c r="I118" s="8"/>
-      <c r="J118" s="8"/>
+      <c r="F118" s="25"/>
+      <c r="G118" s="25"/>
+      <c r="H118" s="25"/>
+      <c r="I118" s="25"/>
+      <c r="J118" s="25"/>
     </row>
     <row r="119" spans="4:25" x14ac:dyDescent="0.3">
-      <c r="E119" s="8" t="s">
+      <c r="E119" s="25" t="s">
         <v>114</v>
       </c>
-      <c r="F119" s="8"/>
-      <c r="G119" s="8"/>
-      <c r="H119" s="8"/>
-      <c r="I119" s="8"/>
-      <c r="J119" s="8"/>
+      <c r="F119" s="25"/>
+      <c r="G119" s="25"/>
+      <c r="H119" s="25"/>
+      <c r="I119" s="25"/>
+      <c r="J119" s="25"/>
     </row>
     <row r="120" spans="4:25" x14ac:dyDescent="0.3">
-      <c r="E120" s="18" t="s">
+      <c r="E120" s="33" t="s">
         <v>115</v>
       </c>
-      <c r="F120" s="19"/>
-      <c r="G120" s="19"/>
-      <c r="H120" s="19"/>
-      <c r="I120" s="19"/>
-      <c r="J120" s="20"/>
+      <c r="F120" s="34"/>
+      <c r="G120" s="34"/>
+      <c r="H120" s="34"/>
+      <c r="I120" s="34"/>
+      <c r="J120" s="35"/>
       <c r="K120" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="L120" s="8" t="s">
+      <c r="L120" s="25" t="s">
         <v>118</v>
       </c>
-      <c r="M120" s="8"/>
-      <c r="N120" s="8"/>
-      <c r="O120" s="8"/>
-      <c r="P120" s="8"/>
-      <c r="Q120" s="8"/>
-      <c r="R120" s="8"/>
-      <c r="S120" s="8"/>
-      <c r="T120" s="8"/>
-      <c r="U120" s="8"/>
-      <c r="V120" s="8"/>
-      <c r="W120" s="8"/>
-      <c r="X120" s="8"/>
-      <c r="Y120" s="8"/>
+      <c r="M120" s="25"/>
+      <c r="N120" s="25"/>
+      <c r="O120" s="25"/>
+      <c r="P120" s="25"/>
+      <c r="Q120" s="25"/>
+      <c r="R120" s="25"/>
+      <c r="S120" s="25"/>
+      <c r="T120" s="25"/>
+      <c r="U120" s="25"/>
+      <c r="V120" s="25"/>
+      <c r="W120" s="25"/>
+      <c r="X120" s="25"/>
+      <c r="Y120" s="25"/>
     </row>
     <row r="121" spans="4:25" x14ac:dyDescent="0.3">
-      <c r="E121" s="8" t="s">
+      <c r="E121" s="25" t="s">
         <v>114</v>
       </c>
-      <c r="F121" s="8"/>
-      <c r="G121" s="8"/>
-      <c r="H121" s="8"/>
-      <c r="I121" s="8"/>
-      <c r="J121" s="8"/>
+      <c r="F121" s="25"/>
+      <c r="G121" s="25"/>
+      <c r="H121" s="25"/>
+      <c r="I121" s="25"/>
+      <c r="J121" s="25"/>
     </row>
     <row r="122" spans="4:25" x14ac:dyDescent="0.3">
-      <c r="E122" s="8" t="s">
+      <c r="E122" s="25" t="s">
         <v>119</v>
       </c>
-      <c r="F122" s="8"/>
-      <c r="G122" s="8"/>
-      <c r="H122" s="8"/>
-      <c r="I122" s="8"/>
-      <c r="J122" s="8"/>
+      <c r="F122" s="25"/>
+      <c r="G122" s="25"/>
+      <c r="H122" s="25"/>
+      <c r="I122" s="25"/>
+      <c r="J122" s="25"/>
     </row>
     <row r="123" spans="4:25" x14ac:dyDescent="0.3">
-      <c r="E123" s="8" t="s">
+      <c r="E123" s="25" t="s">
         <v>114</v>
       </c>
-      <c r="F123" s="8"/>
-      <c r="G123" s="8"/>
-      <c r="H123" s="8"/>
-      <c r="I123" s="8"/>
-      <c r="J123" s="8"/>
+      <c r="F123" s="25"/>
+      <c r="G123" s="25"/>
+      <c r="H123" s="25"/>
+      <c r="I123" s="25"/>
+      <c r="J123" s="25"/>
     </row>
     <row r="124" spans="4:25" x14ac:dyDescent="0.3">
-      <c r="E124" s="8" t="s">
+      <c r="E124" s="25" t="s">
         <v>120</v>
       </c>
-      <c r="F124" s="8"/>
-      <c r="G124" s="8"/>
-      <c r="H124" s="8"/>
-      <c r="I124" s="8"/>
-      <c r="J124" s="8"/>
+      <c r="F124" s="25"/>
+      <c r="G124" s="25"/>
+      <c r="H124" s="25"/>
+      <c r="I124" s="25"/>
+      <c r="J124" s="25"/>
       <c r="K124" s="4" t="s">
         <v>121</v>
       </c>
@@ -4159,59 +6231,59 @@
       <c r="M124" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="N124" s="8" t="s">
+      <c r="N124" s="25" t="s">
         <v>123</v>
       </c>
-      <c r="O124" s="8"/>
-      <c r="P124" s="8"/>
-      <c r="Q124" s="8"/>
-      <c r="R124" s="8"/>
-      <c r="S124" s="8"/>
-      <c r="T124" s="8"/>
-      <c r="U124" s="8"/>
-      <c r="V124" s="8"/>
-      <c r="W124" s="8"/>
-      <c r="X124" s="8"/>
-      <c r="Y124" s="8"/>
+      <c r="O124" s="25"/>
+      <c r="P124" s="25"/>
+      <c r="Q124" s="25"/>
+      <c r="R124" s="25"/>
+      <c r="S124" s="25"/>
+      <c r="T124" s="25"/>
+      <c r="U124" s="25"/>
+      <c r="V124" s="25"/>
+      <c r="W124" s="25"/>
+      <c r="X124" s="25"/>
+      <c r="Y124" s="25"/>
     </row>
     <row r="125" spans="4:25" x14ac:dyDescent="0.3">
-      <c r="E125" s="8" t="s">
+      <c r="E125" s="25" t="s">
         <v>114</v>
       </c>
-      <c r="F125" s="8"/>
-      <c r="G125" s="8"/>
-      <c r="H125" s="8"/>
-      <c r="I125" s="8"/>
-      <c r="J125" s="8"/>
+      <c r="F125" s="25"/>
+      <c r="G125" s="25"/>
+      <c r="H125" s="25"/>
+      <c r="I125" s="25"/>
+      <c r="J125" s="25"/>
     </row>
     <row r="126" spans="4:25" x14ac:dyDescent="0.3">
-      <c r="E126" s="8" t="s">
+      <c r="E126" s="25" t="s">
         <v>124</v>
       </c>
-      <c r="F126" s="8"/>
-      <c r="G126" s="8"/>
-      <c r="H126" s="8"/>
-      <c r="I126" s="8"/>
-      <c r="J126" s="8"/>
+      <c r="F126" s="25"/>
+      <c r="G126" s="25"/>
+      <c r="H126" s="25"/>
+      <c r="I126" s="25"/>
+      <c r="J126" s="25"/>
       <c r="K126" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="L126" s="8" t="s">
+      <c r="L126" s="25" t="s">
         <v>125</v>
       </c>
-      <c r="M126" s="8"/>
-      <c r="N126" s="8"/>
-      <c r="O126" s="8"/>
-      <c r="P126" s="8"/>
-      <c r="Q126" s="8"/>
-      <c r="R126" s="8"/>
-      <c r="S126" s="8"/>
-      <c r="T126" s="8"/>
-      <c r="U126" s="8"/>
-      <c r="V126" s="8"/>
-      <c r="W126" s="8"/>
-      <c r="X126" s="8"/>
-      <c r="Y126" s="8"/>
+      <c r="M126" s="25"/>
+      <c r="N126" s="25"/>
+      <c r="O126" s="25"/>
+      <c r="P126" s="25"/>
+      <c r="Q126" s="25"/>
+      <c r="R126" s="25"/>
+      <c r="S126" s="25"/>
+      <c r="T126" s="25"/>
+      <c r="U126" s="25"/>
+      <c r="V126" s="25"/>
+      <c r="W126" s="25"/>
+      <c r="X126" s="25"/>
+      <c r="Y126" s="25"/>
     </row>
     <row r="128" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D128" s="2" t="s">
@@ -4219,208 +6291,208 @@
       </c>
     </row>
     <row r="130" spans="3:26" x14ac:dyDescent="0.3">
-      <c r="E130" s="8" t="s">
+      <c r="E130" s="25" t="s">
         <v>127</v>
       </c>
-      <c r="F130" s="8"/>
-      <c r="G130" s="8"/>
-      <c r="H130" s="8" t="s">
+      <c r="F130" s="25"/>
+      <c r="G130" s="25"/>
+      <c r="H130" s="25" t="s">
         <v>132</v>
       </c>
-      <c r="I130" s="8"/>
-      <c r="J130" s="8"/>
-      <c r="K130" s="8"/>
-      <c r="L130" s="8"/>
-      <c r="M130" s="8"/>
-      <c r="N130" s="8"/>
-      <c r="O130" s="8"/>
-      <c r="P130" s="8" t="s">
+      <c r="I130" s="25"/>
+      <c r="J130" s="25"/>
+      <c r="K130" s="25"/>
+      <c r="L130" s="25"/>
+      <c r="M130" s="25"/>
+      <c r="N130" s="25"/>
+      <c r="O130" s="25"/>
+      <c r="P130" s="25" t="s">
         <v>137</v>
       </c>
-      <c r="Q130" s="8"/>
-      <c r="R130" s="8"/>
-      <c r="S130" s="8"/>
-      <c r="T130" s="8"/>
-      <c r="U130" s="8"/>
-      <c r="V130" s="8"/>
-      <c r="W130" s="8"/>
-      <c r="X130" s="8"/>
-      <c r="Y130" s="8"/>
-      <c r="Z130" s="8"/>
+      <c r="Q130" s="25"/>
+      <c r="R130" s="25"/>
+      <c r="S130" s="25"/>
+      <c r="T130" s="25"/>
+      <c r="U130" s="25"/>
+      <c r="V130" s="25"/>
+      <c r="W130" s="25"/>
+      <c r="X130" s="25"/>
+      <c r="Y130" s="25"/>
+      <c r="Z130" s="25"/>
     </row>
     <row r="131" spans="3:26" x14ac:dyDescent="0.3">
-      <c r="E131" s="8" t="s">
+      <c r="E131" s="25" t="s">
         <v>128</v>
       </c>
-      <c r="F131" s="8"/>
-      <c r="G131" s="8"/>
-      <c r="H131" s="22" t="s">
+      <c r="F131" s="25"/>
+      <c r="G131" s="25"/>
+      <c r="H131" s="26" t="s">
         <v>133</v>
       </c>
-      <c r="I131" s="22"/>
-      <c r="J131" s="22"/>
-      <c r="K131" s="22"/>
-      <c r="L131" s="22"/>
-      <c r="M131" s="22"/>
-      <c r="N131" s="22"/>
-      <c r="O131" s="22"/>
-      <c r="P131" s="22" t="s">
+      <c r="I131" s="26"/>
+      <c r="J131" s="26"/>
+      <c r="K131" s="26"/>
+      <c r="L131" s="26"/>
+      <c r="M131" s="26"/>
+      <c r="N131" s="26"/>
+      <c r="O131" s="26"/>
+      <c r="P131" s="26" t="s">
         <v>138</v>
       </c>
-      <c r="Q131" s="22"/>
-      <c r="R131" s="22"/>
-      <c r="S131" s="22"/>
-      <c r="T131" s="22"/>
-      <c r="U131" s="22"/>
-      <c r="V131" s="22"/>
-      <c r="W131" s="22"/>
-      <c r="X131" s="22"/>
-      <c r="Y131" s="22"/>
-      <c r="Z131" s="22"/>
+      <c r="Q131" s="26"/>
+      <c r="R131" s="26"/>
+      <c r="S131" s="26"/>
+      <c r="T131" s="26"/>
+      <c r="U131" s="26"/>
+      <c r="V131" s="26"/>
+      <c r="W131" s="26"/>
+      <c r="X131" s="26"/>
+      <c r="Y131" s="26"/>
+      <c r="Z131" s="26"/>
     </row>
     <row r="132" spans="3:26" x14ac:dyDescent="0.3">
-      <c r="E132" s="8" t="s">
+      <c r="E132" s="25" t="s">
         <v>129</v>
       </c>
-      <c r="F132" s="8"/>
-      <c r="G132" s="8"/>
-      <c r="H132" s="22" t="s">
+      <c r="F132" s="25"/>
+      <c r="G132" s="25"/>
+      <c r="H132" s="26" t="s">
         <v>134</v>
       </c>
-      <c r="I132" s="22"/>
-      <c r="J132" s="22"/>
-      <c r="K132" s="22"/>
-      <c r="L132" s="22"/>
-      <c r="M132" s="22"/>
-      <c r="N132" s="22"/>
-      <c r="O132" s="22"/>
-      <c r="P132" s="22" t="s">
+      <c r="I132" s="26"/>
+      <c r="J132" s="26"/>
+      <c r="K132" s="26"/>
+      <c r="L132" s="26"/>
+      <c r="M132" s="26"/>
+      <c r="N132" s="26"/>
+      <c r="O132" s="26"/>
+      <c r="P132" s="26" t="s">
         <v>139</v>
       </c>
-      <c r="Q132" s="22"/>
-      <c r="R132" s="22"/>
-      <c r="S132" s="22"/>
-      <c r="T132" s="22"/>
-      <c r="U132" s="22"/>
-      <c r="V132" s="22"/>
-      <c r="W132" s="22"/>
-      <c r="X132" s="22"/>
-      <c r="Y132" s="22"/>
-      <c r="Z132" s="22"/>
+      <c r="Q132" s="26"/>
+      <c r="R132" s="26"/>
+      <c r="S132" s="26"/>
+      <c r="T132" s="26"/>
+      <c r="U132" s="26"/>
+      <c r="V132" s="26"/>
+      <c r="W132" s="26"/>
+      <c r="X132" s="26"/>
+      <c r="Y132" s="26"/>
+      <c r="Z132" s="26"/>
     </row>
     <row r="133" spans="3:26" x14ac:dyDescent="0.3">
-      <c r="E133" s="8" t="s">
+      <c r="E133" s="25" t="s">
         <v>130</v>
       </c>
-      <c r="F133" s="8"/>
-      <c r="G133" s="8"/>
-      <c r="H133" s="22" t="s">
+      <c r="F133" s="25"/>
+      <c r="G133" s="25"/>
+      <c r="H133" s="26" t="s">
         <v>135</v>
       </c>
-      <c r="I133" s="22"/>
-      <c r="J133" s="22"/>
-      <c r="K133" s="22"/>
-      <c r="L133" s="22"/>
-      <c r="M133" s="22"/>
-      <c r="N133" s="22"/>
-      <c r="O133" s="22"/>
-      <c r="P133" s="22" t="s">
+      <c r="I133" s="26"/>
+      <c r="J133" s="26"/>
+      <c r="K133" s="26"/>
+      <c r="L133" s="26"/>
+      <c r="M133" s="26"/>
+      <c r="N133" s="26"/>
+      <c r="O133" s="26"/>
+      <c r="P133" s="26" t="s">
         <v>140</v>
       </c>
-      <c r="Q133" s="22"/>
-      <c r="R133" s="22"/>
-      <c r="S133" s="22"/>
-      <c r="T133" s="22"/>
-      <c r="U133" s="22"/>
-      <c r="V133" s="22"/>
-      <c r="W133" s="22"/>
-      <c r="X133" s="22"/>
-      <c r="Y133" s="22"/>
-      <c r="Z133" s="22"/>
+      <c r="Q133" s="26"/>
+      <c r="R133" s="26"/>
+      <c r="S133" s="26"/>
+      <c r="T133" s="26"/>
+      <c r="U133" s="26"/>
+      <c r="V133" s="26"/>
+      <c r="W133" s="26"/>
+      <c r="X133" s="26"/>
+      <c r="Y133" s="26"/>
+      <c r="Z133" s="26"/>
     </row>
     <row r="134" spans="3:26" x14ac:dyDescent="0.3">
-      <c r="E134" s="8" t="s">
+      <c r="E134" s="25" t="s">
         <v>131</v>
       </c>
-      <c r="F134" s="8"/>
-      <c r="G134" s="8"/>
-      <c r="H134" s="22" t="s">
+      <c r="F134" s="25"/>
+      <c r="G134" s="25"/>
+      <c r="H134" s="26" t="s">
         <v>136</v>
       </c>
-      <c r="I134" s="22"/>
-      <c r="J134" s="22"/>
-      <c r="K134" s="22"/>
-      <c r="L134" s="22"/>
-      <c r="M134" s="22"/>
-      <c r="N134" s="22"/>
-      <c r="O134" s="22"/>
-      <c r="P134" s="22" t="s">
+      <c r="I134" s="26"/>
+      <c r="J134" s="26"/>
+      <c r="K134" s="26"/>
+      <c r="L134" s="26"/>
+      <c r="M134" s="26"/>
+      <c r="N134" s="26"/>
+      <c r="O134" s="26"/>
+      <c r="P134" s="26" t="s">
         <v>141</v>
       </c>
-      <c r="Q134" s="22"/>
-      <c r="R134" s="22"/>
-      <c r="S134" s="22"/>
-      <c r="T134" s="22"/>
-      <c r="U134" s="22"/>
-      <c r="V134" s="22"/>
-      <c r="W134" s="22"/>
-      <c r="X134" s="22"/>
-      <c r="Y134" s="22"/>
-      <c r="Z134" s="22"/>
+      <c r="Q134" s="26"/>
+      <c r="R134" s="26"/>
+      <c r="S134" s="26"/>
+      <c r="T134" s="26"/>
+      <c r="U134" s="26"/>
+      <c r="V134" s="26"/>
+      <c r="W134" s="26"/>
+      <c r="X134" s="26"/>
+      <c r="Y134" s="26"/>
+      <c r="Z134" s="26"/>
     </row>
     <row r="136" spans="3:26" x14ac:dyDescent="0.3">
-      <c r="C136" s="9" t="s">
+      <c r="C136" s="27" t="s">
         <v>169</v>
       </c>
-      <c r="D136" s="10"/>
-      <c r="E136" s="10"/>
-      <c r="F136" s="10"/>
-      <c r="G136" s="10"/>
-      <c r="H136" s="10"/>
-      <c r="I136" s="10"/>
-      <c r="J136" s="10"/>
-      <c r="K136" s="10"/>
-      <c r="L136" s="10"/>
-      <c r="M136" s="10"/>
-      <c r="N136" s="10"/>
-      <c r="O136" s="10"/>
-      <c r="P136" s="10"/>
-      <c r="Q136" s="10"/>
-      <c r="R136" s="10"/>
-      <c r="S136" s="10"/>
-      <c r="T136" s="10"/>
-      <c r="U136" s="10"/>
-      <c r="V136" s="10"/>
-      <c r="W136" s="10"/>
-      <c r="X136" s="10"/>
-      <c r="Y136" s="10"/>
-      <c r="Z136" s="11"/>
+      <c r="D136" s="28"/>
+      <c r="E136" s="28"/>
+      <c r="F136" s="28"/>
+      <c r="G136" s="28"/>
+      <c r="H136" s="28"/>
+      <c r="I136" s="28"/>
+      <c r="J136" s="28"/>
+      <c r="K136" s="28"/>
+      <c r="L136" s="28"/>
+      <c r="M136" s="28"/>
+      <c r="N136" s="28"/>
+      <c r="O136" s="28"/>
+      <c r="P136" s="28"/>
+      <c r="Q136" s="28"/>
+      <c r="R136" s="28"/>
+      <c r="S136" s="28"/>
+      <c r="T136" s="28"/>
+      <c r="U136" s="28"/>
+      <c r="V136" s="28"/>
+      <c r="W136" s="28"/>
+      <c r="X136" s="28"/>
+      <c r="Y136" s="28"/>
+      <c r="Z136" s="29"/>
     </row>
     <row r="137" spans="3:26" x14ac:dyDescent="0.3">
-      <c r="C137" s="15"/>
-      <c r="D137" s="16"/>
-      <c r="E137" s="16"/>
-      <c r="F137" s="16"/>
-      <c r="G137" s="16"/>
-      <c r="H137" s="16"/>
-      <c r="I137" s="16"/>
-      <c r="J137" s="16"/>
-      <c r="K137" s="16"/>
-      <c r="L137" s="16"/>
-      <c r="M137" s="16"/>
-      <c r="N137" s="16"/>
-      <c r="O137" s="16"/>
-      <c r="P137" s="16"/>
-      <c r="Q137" s="16"/>
-      <c r="R137" s="16"/>
-      <c r="S137" s="16"/>
-      <c r="T137" s="16"/>
-      <c r="U137" s="16"/>
-      <c r="V137" s="16"/>
-      <c r="W137" s="16"/>
-      <c r="X137" s="16"/>
-      <c r="Y137" s="16"/>
-      <c r="Z137" s="17"/>
+      <c r="C137" s="30"/>
+      <c r="D137" s="31"/>
+      <c r="E137" s="31"/>
+      <c r="F137" s="31"/>
+      <c r="G137" s="31"/>
+      <c r="H137" s="31"/>
+      <c r="I137" s="31"/>
+      <c r="J137" s="31"/>
+      <c r="K137" s="31"/>
+      <c r="L137" s="31"/>
+      <c r="M137" s="31"/>
+      <c r="N137" s="31"/>
+      <c r="O137" s="31"/>
+      <c r="P137" s="31"/>
+      <c r="Q137" s="31"/>
+      <c r="R137" s="31"/>
+      <c r="S137" s="31"/>
+      <c r="T137" s="31"/>
+      <c r="U137" s="31"/>
+      <c r="V137" s="31"/>
+      <c r="W137" s="31"/>
+      <c r="X137" s="31"/>
+      <c r="Y137" s="31"/>
+      <c r="Z137" s="32"/>
     </row>
     <row r="138" spans="3:26" x14ac:dyDescent="0.3">
       <c r="C138" s="5"/>
@@ -4449,351 +6521,430 @@
       <c r="Z138" s="5"/>
     </row>
     <row r="139" spans="3:26" x14ac:dyDescent="0.3">
-      <c r="C139" s="8" t="s">
+      <c r="C139" s="25" t="s">
         <v>172</v>
       </c>
-      <c r="D139" s="8"/>
-      <c r="E139" s="8"/>
-      <c r="F139" s="8"/>
-      <c r="G139" s="8"/>
-      <c r="H139" s="8"/>
-      <c r="I139" s="8" t="s">
+      <c r="D139" s="25"/>
+      <c r="E139" s="25"/>
+      <c r="F139" s="25"/>
+      <c r="G139" s="25"/>
+      <c r="H139" s="25"/>
+      <c r="I139" s="25" t="s">
         <v>173</v>
       </c>
-      <c r="J139" s="8"/>
-      <c r="K139" s="8"/>
-      <c r="L139" s="8"/>
-      <c r="M139" s="8" t="s">
+      <c r="J139" s="25"/>
+      <c r="K139" s="25"/>
+      <c r="L139" s="25"/>
+      <c r="M139" s="25" t="s">
         <v>180</v>
       </c>
-      <c r="N139" s="8"/>
-      <c r="O139" s="8"/>
-      <c r="P139" s="8"/>
-      <c r="Q139" s="8"/>
-      <c r="R139" s="8"/>
-      <c r="S139" s="8"/>
-      <c r="T139" s="8"/>
-      <c r="U139" s="8"/>
-      <c r="V139" s="8"/>
-      <c r="W139" s="8"/>
-      <c r="X139" s="8"/>
-      <c r="Y139" s="8"/>
-      <c r="Z139" s="8"/>
+      <c r="N139" s="25"/>
+      <c r="O139" s="25"/>
+      <c r="P139" s="25"/>
+      <c r="Q139" s="25"/>
+      <c r="R139" s="25"/>
+      <c r="S139" s="25"/>
+      <c r="T139" s="25"/>
+      <c r="U139" s="25"/>
+      <c r="V139" s="25"/>
+      <c r="W139" s="25"/>
+      <c r="X139" s="25"/>
+      <c r="Y139" s="25"/>
+      <c r="Z139" s="25"/>
     </row>
     <row r="140" spans="3:26" x14ac:dyDescent="0.3">
-      <c r="C140" s="21" t="s">
+      <c r="C140" s="24" t="s">
         <v>170</v>
       </c>
-      <c r="D140" s="21"/>
-      <c r="E140" s="21"/>
-      <c r="F140" s="21"/>
-      <c r="G140" s="21"/>
-      <c r="H140" s="21"/>
-      <c r="I140" s="8" t="s">
+      <c r="D140" s="24"/>
+      <c r="E140" s="24"/>
+      <c r="F140" s="24"/>
+      <c r="G140" s="24"/>
+      <c r="H140" s="24"/>
+      <c r="I140" s="25" t="s">
         <v>174</v>
       </c>
-      <c r="J140" s="8"/>
-      <c r="K140" s="8"/>
-      <c r="L140" s="8"/>
-      <c r="M140" s="21" t="s">
+      <c r="J140" s="25"/>
+      <c r="K140" s="25"/>
+      <c r="L140" s="25"/>
+      <c r="M140" s="24" t="s">
         <v>181</v>
       </c>
-      <c r="N140" s="21"/>
-      <c r="O140" s="21"/>
-      <c r="P140" s="21"/>
-      <c r="Q140" s="21"/>
-      <c r="R140" s="21"/>
-      <c r="S140" s="21"/>
-      <c r="T140" s="21"/>
-      <c r="U140" s="21"/>
-      <c r="V140" s="21"/>
-      <c r="W140" s="21"/>
-      <c r="X140" s="21"/>
-      <c r="Y140" s="21"/>
-      <c r="Z140" s="21"/>
+      <c r="N140" s="24"/>
+      <c r="O140" s="24"/>
+      <c r="P140" s="24"/>
+      <c r="Q140" s="24"/>
+      <c r="R140" s="24"/>
+      <c r="S140" s="24"/>
+      <c r="T140" s="24"/>
+      <c r="U140" s="24"/>
+      <c r="V140" s="24"/>
+      <c r="W140" s="24"/>
+      <c r="X140" s="24"/>
+      <c r="Y140" s="24"/>
+      <c r="Z140" s="24"/>
     </row>
     <row r="141" spans="3:26" x14ac:dyDescent="0.3">
-      <c r="C141" s="21" t="s">
+      <c r="C141" s="24" t="s">
         <v>171</v>
       </c>
-      <c r="D141" s="21"/>
-      <c r="E141" s="21"/>
-      <c r="F141" s="21"/>
-      <c r="G141" s="21"/>
-      <c r="H141" s="21"/>
-      <c r="I141" s="8" t="s">
+      <c r="D141" s="24"/>
+      <c r="E141" s="24"/>
+      <c r="F141" s="24"/>
+      <c r="G141" s="24"/>
+      <c r="H141" s="24"/>
+      <c r="I141" s="25" t="s">
         <v>175</v>
       </c>
-      <c r="J141" s="8"/>
-      <c r="K141" s="8"/>
-      <c r="L141" s="8"/>
-      <c r="M141" s="21" t="s">
+      <c r="J141" s="25"/>
+      <c r="K141" s="25"/>
+      <c r="L141" s="25"/>
+      <c r="M141" s="24" t="s">
         <v>182</v>
       </c>
-      <c r="N141" s="21"/>
-      <c r="O141" s="21"/>
-      <c r="P141" s="21"/>
-      <c r="Q141" s="21"/>
-      <c r="R141" s="21"/>
-      <c r="S141" s="21"/>
-      <c r="T141" s="21"/>
-      <c r="U141" s="21"/>
-      <c r="V141" s="21"/>
-      <c r="W141" s="21"/>
-      <c r="X141" s="21"/>
-      <c r="Y141" s="21"/>
-      <c r="Z141" s="21"/>
+      <c r="N141" s="24"/>
+      <c r="O141" s="24"/>
+      <c r="P141" s="24"/>
+      <c r="Q141" s="24"/>
+      <c r="R141" s="24"/>
+      <c r="S141" s="24"/>
+      <c r="T141" s="24"/>
+      <c r="U141" s="24"/>
+      <c r="V141" s="24"/>
+      <c r="W141" s="24"/>
+      <c r="X141" s="24"/>
+      <c r="Y141" s="24"/>
+      <c r="Z141" s="24"/>
     </row>
     <row r="142" spans="3:26" x14ac:dyDescent="0.3">
-      <c r="C142" s="21" t="s">
+      <c r="C142" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="D142" s="21"/>
-      <c r="E142" s="21"/>
-      <c r="F142" s="21"/>
-      <c r="G142" s="21"/>
-      <c r="H142" s="21"/>
-      <c r="I142" s="8" t="s">
+      <c r="D142" s="24"/>
+      <c r="E142" s="24"/>
+      <c r="F142" s="24"/>
+      <c r="G142" s="24"/>
+      <c r="H142" s="24"/>
+      <c r="I142" s="25" t="s">
         <v>176</v>
       </c>
-      <c r="J142" s="8"/>
-      <c r="K142" s="8"/>
-      <c r="L142" s="8"/>
-      <c r="M142" s="21" t="s">
+      <c r="J142" s="25"/>
+      <c r="K142" s="25"/>
+      <c r="L142" s="25"/>
+      <c r="M142" s="24" t="s">
         <v>183</v>
       </c>
-      <c r="N142" s="21"/>
-      <c r="O142" s="21"/>
-      <c r="P142" s="21"/>
-      <c r="Q142" s="21"/>
-      <c r="R142" s="21"/>
-      <c r="S142" s="21"/>
-      <c r="T142" s="21"/>
-      <c r="U142" s="21"/>
-      <c r="V142" s="21"/>
-      <c r="W142" s="21"/>
-      <c r="X142" s="21"/>
-      <c r="Y142" s="21"/>
-      <c r="Z142" s="21"/>
+      <c r="N142" s="24"/>
+      <c r="O142" s="24"/>
+      <c r="P142" s="24"/>
+      <c r="Q142" s="24"/>
+      <c r="R142" s="24"/>
+      <c r="S142" s="24"/>
+      <c r="T142" s="24"/>
+      <c r="U142" s="24"/>
+      <c r="V142" s="24"/>
+      <c r="W142" s="24"/>
+      <c r="X142" s="24"/>
+      <c r="Y142" s="24"/>
+      <c r="Z142" s="24"/>
     </row>
     <row r="143" spans="3:26" x14ac:dyDescent="0.3">
-      <c r="C143" s="21" t="s">
+      <c r="C143" s="24" t="s">
         <v>177</v>
       </c>
-      <c r="D143" s="21"/>
-      <c r="E143" s="21"/>
-      <c r="F143" s="21"/>
-      <c r="G143" s="21"/>
-      <c r="H143" s="21"/>
-      <c r="I143" s="8" t="s">
+      <c r="D143" s="24"/>
+      <c r="E143" s="24"/>
+      <c r="F143" s="24"/>
+      <c r="G143" s="24"/>
+      <c r="H143" s="24"/>
+      <c r="I143" s="25" t="s">
         <v>176</v>
       </c>
-      <c r="J143" s="8"/>
-      <c r="K143" s="8"/>
-      <c r="L143" s="8"/>
-      <c r="M143" s="21" t="s">
+      <c r="J143" s="25"/>
+      <c r="K143" s="25"/>
+      <c r="L143" s="25"/>
+      <c r="M143" s="24" t="s">
         <v>184</v>
       </c>
-      <c r="N143" s="21"/>
-      <c r="O143" s="21"/>
-      <c r="P143" s="21"/>
-      <c r="Q143" s="21"/>
-      <c r="R143" s="21"/>
-      <c r="S143" s="21"/>
-      <c r="T143" s="21"/>
-      <c r="U143" s="21"/>
-      <c r="V143" s="21"/>
-      <c r="W143" s="21"/>
-      <c r="X143" s="21"/>
-      <c r="Y143" s="21"/>
-      <c r="Z143" s="21"/>
+      <c r="N143" s="24"/>
+      <c r="O143" s="24"/>
+      <c r="P143" s="24"/>
+      <c r="Q143" s="24"/>
+      <c r="R143" s="24"/>
+      <c r="S143" s="24"/>
+      <c r="T143" s="24"/>
+      <c r="U143" s="24"/>
+      <c r="V143" s="24"/>
+      <c r="W143" s="24"/>
+      <c r="X143" s="24"/>
+      <c r="Y143" s="24"/>
+      <c r="Z143" s="24"/>
     </row>
     <row r="144" spans="3:26" x14ac:dyDescent="0.3">
-      <c r="C144" s="21" t="s">
+      <c r="C144" s="24" t="s">
         <v>178</v>
       </c>
-      <c r="D144" s="21"/>
-      <c r="E144" s="21"/>
-      <c r="F144" s="21"/>
-      <c r="G144" s="21"/>
-      <c r="H144" s="21"/>
-      <c r="I144" s="8" t="s">
+      <c r="D144" s="24"/>
+      <c r="E144" s="24"/>
+      <c r="F144" s="24"/>
+      <c r="G144" s="24"/>
+      <c r="H144" s="24"/>
+      <c r="I144" s="25" t="s">
         <v>176</v>
       </c>
-      <c r="J144" s="8"/>
-      <c r="K144" s="8"/>
-      <c r="L144" s="8"/>
-      <c r="M144" s="21" t="s">
+      <c r="J144" s="25"/>
+      <c r="K144" s="25"/>
+      <c r="L144" s="25"/>
+      <c r="M144" s="24" t="s">
         <v>190</v>
       </c>
-      <c r="N144" s="21"/>
-      <c r="O144" s="21"/>
-      <c r="P144" s="21"/>
-      <c r="Q144" s="21"/>
-      <c r="R144" s="21"/>
-      <c r="S144" s="21"/>
-      <c r="T144" s="21"/>
-      <c r="U144" s="21"/>
-      <c r="V144" s="21"/>
-      <c r="W144" s="21"/>
-      <c r="X144" s="21"/>
-      <c r="Y144" s="21"/>
-      <c r="Z144" s="21"/>
+      <c r="N144" s="24"/>
+      <c r="O144" s="24"/>
+      <c r="P144" s="24"/>
+      <c r="Q144" s="24"/>
+      <c r="R144" s="24"/>
+      <c r="S144" s="24"/>
+      <c r="T144" s="24"/>
+      <c r="U144" s="24"/>
+      <c r="V144" s="24"/>
+      <c r="W144" s="24"/>
+      <c r="X144" s="24"/>
+      <c r="Y144" s="24"/>
+      <c r="Z144" s="24"/>
     </row>
     <row r="145" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="C145" s="21" t="s">
+      <c r="C145" s="24" t="s">
         <v>186</v>
       </c>
-      <c r="D145" s="21"/>
-      <c r="E145" s="21"/>
-      <c r="F145" s="21"/>
-      <c r="G145" s="21"/>
-      <c r="H145" s="21"/>
-      <c r="I145" s="8" t="s">
+      <c r="D145" s="24"/>
+      <c r="E145" s="24"/>
+      <c r="F145" s="24"/>
+      <c r="G145" s="24"/>
+      <c r="H145" s="24"/>
+      <c r="I145" s="25" t="s">
         <v>176</v>
       </c>
-      <c r="J145" s="8"/>
-      <c r="K145" s="8"/>
-      <c r="L145" s="8"/>
-      <c r="M145" s="21" t="s">
+      <c r="J145" s="25"/>
+      <c r="K145" s="25"/>
+      <c r="L145" s="25"/>
+      <c r="M145" s="24" t="s">
         <v>185</v>
       </c>
-      <c r="N145" s="21"/>
-      <c r="O145" s="21"/>
-      <c r="P145" s="21"/>
-      <c r="Q145" s="21"/>
-      <c r="R145" s="21"/>
-      <c r="S145" s="21"/>
-      <c r="T145" s="21"/>
-      <c r="U145" s="21"/>
-      <c r="V145" s="21"/>
-      <c r="W145" s="21"/>
-      <c r="X145" s="21"/>
-      <c r="Y145" s="21"/>
-      <c r="Z145" s="21"/>
+      <c r="N145" s="24"/>
+      <c r="O145" s="24"/>
+      <c r="P145" s="24"/>
+      <c r="Q145" s="24"/>
+      <c r="R145" s="24"/>
+      <c r="S145" s="24"/>
+      <c r="T145" s="24"/>
+      <c r="U145" s="24"/>
+      <c r="V145" s="24"/>
+      <c r="W145" s="24"/>
+      <c r="X145" s="24"/>
+      <c r="Y145" s="24"/>
+      <c r="Z145" s="24"/>
     </row>
     <row r="146" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="C146" s="21" t="s">
+      <c r="C146" s="24" t="s">
         <v>179</v>
       </c>
-      <c r="D146" s="21"/>
-      <c r="E146" s="21"/>
-      <c r="F146" s="21"/>
-      <c r="G146" s="21"/>
-      <c r="H146" s="21"/>
-      <c r="I146" s="8" t="s">
+      <c r="D146" s="24"/>
+      <c r="E146" s="24"/>
+      <c r="F146" s="24"/>
+      <c r="G146" s="24"/>
+      <c r="H146" s="24"/>
+      <c r="I146" s="25" t="s">
         <v>176</v>
       </c>
-      <c r="J146" s="8"/>
-      <c r="K146" s="8"/>
-      <c r="L146" s="8"/>
-      <c r="M146" s="21" t="s">
+      <c r="J146" s="25"/>
+      <c r="K146" s="25"/>
+      <c r="L146" s="25"/>
+      <c r="M146" s="24" t="s">
         <v>188</v>
       </c>
-      <c r="N146" s="21"/>
-      <c r="O146" s="21"/>
-      <c r="P146" s="21"/>
-      <c r="Q146" s="21"/>
-      <c r="R146" s="21"/>
-      <c r="S146" s="21"/>
-      <c r="T146" s="21"/>
-      <c r="U146" s="21"/>
-      <c r="V146" s="21"/>
-      <c r="W146" s="21"/>
-      <c r="X146" s="21"/>
-      <c r="Y146" s="21"/>
-      <c r="Z146" s="21"/>
+      <c r="N146" s="24"/>
+      <c r="O146" s="24"/>
+      <c r="P146" s="24"/>
+      <c r="Q146" s="24"/>
+      <c r="R146" s="24"/>
+      <c r="S146" s="24"/>
+      <c r="T146" s="24"/>
+      <c r="U146" s="24"/>
+      <c r="V146" s="24"/>
+      <c r="W146" s="24"/>
+      <c r="X146" s="24"/>
+      <c r="Y146" s="24"/>
+      <c r="Z146" s="24"/>
     </row>
     <row r="147" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="C147" s="21" t="s">
+      <c r="C147" s="24" t="s">
         <v>187</v>
       </c>
-      <c r="D147" s="21"/>
-      <c r="E147" s="21"/>
-      <c r="F147" s="21"/>
-      <c r="G147" s="21"/>
-      <c r="H147" s="21"/>
-      <c r="I147" s="8" t="s">
+      <c r="D147" s="24"/>
+      <c r="E147" s="24"/>
+      <c r="F147" s="24"/>
+      <c r="G147" s="24"/>
+      <c r="H147" s="24"/>
+      <c r="I147" s="25" t="s">
         <v>176</v>
       </c>
-      <c r="J147" s="8"/>
-      <c r="K147" s="8"/>
-      <c r="L147" s="8"/>
-      <c r="M147" s="21" t="s">
+      <c r="J147" s="25"/>
+      <c r="K147" s="25"/>
+      <c r="L147" s="25"/>
+      <c r="M147" s="24" t="s">
         <v>189</v>
       </c>
-      <c r="N147" s="21"/>
-      <c r="O147" s="21"/>
-      <c r="P147" s="21"/>
-      <c r="Q147" s="21"/>
-      <c r="R147" s="21"/>
-      <c r="S147" s="21"/>
-      <c r="T147" s="21"/>
-      <c r="U147" s="21"/>
-      <c r="V147" s="21"/>
-      <c r="W147" s="21"/>
-      <c r="X147" s="21"/>
-      <c r="Y147" s="21"/>
-      <c r="Z147" s="21"/>
+      <c r="N147" s="24"/>
+      <c r="O147" s="24"/>
+      <c r="P147" s="24"/>
+      <c r="Q147" s="24"/>
+      <c r="R147" s="24"/>
+      <c r="S147" s="24"/>
+      <c r="T147" s="24"/>
+      <c r="U147" s="24"/>
+      <c r="V147" s="24"/>
+      <c r="W147" s="24"/>
+      <c r="X147" s="24"/>
+      <c r="Y147" s="24"/>
+      <c r="Z147" s="24"/>
     </row>
     <row r="149" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B149" s="8" t="s">
+      <c r="B149" s="25" t="s">
         <v>192</v>
       </c>
-      <c r="C149" s="8"/>
-      <c r="D149" s="8"/>
-      <c r="E149" s="8"/>
-      <c r="F149" s="8"/>
-      <c r="G149" s="8"/>
-      <c r="H149" s="8"/>
-      <c r="I149" s="8"/>
-      <c r="J149" s="8"/>
-      <c r="K149" s="8"/>
-      <c r="L149" s="8"/>
-      <c r="M149" s="8"/>
-      <c r="N149" s="8"/>
-      <c r="O149" s="8"/>
-      <c r="P149" s="8"/>
-      <c r="Q149" s="8"/>
-      <c r="R149" s="8"/>
-      <c r="S149" s="8"/>
-      <c r="T149" s="8"/>
-      <c r="U149" s="8"/>
-      <c r="V149" s="8"/>
-      <c r="W149" s="8"/>
-      <c r="X149" s="8"/>
-      <c r="Y149" s="8"/>
-      <c r="Z149" s="8"/>
+      <c r="C149" s="25"/>
+      <c r="D149" s="25"/>
+      <c r="E149" s="25"/>
+      <c r="F149" s="25"/>
+      <c r="G149" s="25"/>
+      <c r="H149" s="25"/>
+      <c r="I149" s="25"/>
+      <c r="J149" s="25"/>
+      <c r="K149" s="25"/>
+      <c r="L149" s="25"/>
+      <c r="M149" s="25"/>
+      <c r="N149" s="25"/>
+      <c r="O149" s="25"/>
+      <c r="P149" s="25"/>
+      <c r="Q149" s="25"/>
+      <c r="R149" s="25"/>
+      <c r="S149" s="25"/>
+      <c r="T149" s="25"/>
+      <c r="U149" s="25"/>
+      <c r="V149" s="25"/>
+      <c r="W149" s="25"/>
+      <c r="X149" s="25"/>
+      <c r="Y149" s="25"/>
+      <c r="Z149" s="25"/>
     </row>
     <row r="150" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B150" s="8"/>
-      <c r="C150" s="8"/>
-      <c r="D150" s="8"/>
-      <c r="E150" s="8"/>
-      <c r="F150" s="8"/>
-      <c r="G150" s="8"/>
-      <c r="H150" s="8"/>
-      <c r="I150" s="8"/>
-      <c r="J150" s="8"/>
-      <c r="K150" s="8"/>
-      <c r="L150" s="8"/>
-      <c r="M150" s="8"/>
-      <c r="N150" s="8"/>
-      <c r="O150" s="8"/>
-      <c r="P150" s="8"/>
-      <c r="Q150" s="8"/>
-      <c r="R150" s="8"/>
-      <c r="S150" s="8"/>
-      <c r="T150" s="8"/>
-      <c r="U150" s="8"/>
-      <c r="V150" s="8"/>
-      <c r="W150" s="8"/>
-      <c r="X150" s="8"/>
-      <c r="Y150" s="8"/>
-      <c r="Z150" s="8"/>
+      <c r="B150" s="25"/>
+      <c r="C150" s="25"/>
+      <c r="D150" s="25"/>
+      <c r="E150" s="25"/>
+      <c r="F150" s="25"/>
+      <c r="G150" s="25"/>
+      <c r="H150" s="25"/>
+      <c r="I150" s="25"/>
+      <c r="J150" s="25"/>
+      <c r="K150" s="25"/>
+      <c r="L150" s="25"/>
+      <c r="M150" s="25"/>
+      <c r="N150" s="25"/>
+      <c r="O150" s="25"/>
+      <c r="P150" s="25"/>
+      <c r="Q150" s="25"/>
+      <c r="R150" s="25"/>
+      <c r="S150" s="25"/>
+      <c r="T150" s="25"/>
+      <c r="U150" s="25"/>
+      <c r="V150" s="25"/>
+      <c r="W150" s="25"/>
+      <c r="X150" s="25"/>
+      <c r="Y150" s="25"/>
+      <c r="Z150" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="95">
+    <mergeCell ref="E80:G80"/>
+    <mergeCell ref="U80:X80"/>
+    <mergeCell ref="B2:Z4"/>
+    <mergeCell ref="U6:Z6"/>
+    <mergeCell ref="C45:Z46"/>
+    <mergeCell ref="C56:Z57"/>
+    <mergeCell ref="C68:Z69"/>
+    <mergeCell ref="H80:T80"/>
+    <mergeCell ref="C101:Z102"/>
+    <mergeCell ref="E81:G81"/>
+    <mergeCell ref="E82:G82"/>
+    <mergeCell ref="E83:G83"/>
+    <mergeCell ref="E84:G84"/>
+    <mergeCell ref="H81:T81"/>
+    <mergeCell ref="H82:T82"/>
+    <mergeCell ref="H83:T83"/>
+    <mergeCell ref="H84:T84"/>
+    <mergeCell ref="U81:X81"/>
+    <mergeCell ref="U82:X82"/>
+    <mergeCell ref="U83:X83"/>
+    <mergeCell ref="U84:X84"/>
+    <mergeCell ref="K110:X110"/>
+    <mergeCell ref="E108:J108"/>
+    <mergeCell ref="E109:J109"/>
+    <mergeCell ref="E110:J110"/>
+    <mergeCell ref="E111:J111"/>
+    <mergeCell ref="K106:X106"/>
+    <mergeCell ref="K107:X107"/>
+    <mergeCell ref="K108:X108"/>
+    <mergeCell ref="K109:X109"/>
+    <mergeCell ref="E107:J107"/>
+    <mergeCell ref="E121:J121"/>
+    <mergeCell ref="E122:J122"/>
+    <mergeCell ref="E123:J123"/>
+    <mergeCell ref="E124:J124"/>
+    <mergeCell ref="E106:J106"/>
+    <mergeCell ref="E119:J119"/>
+    <mergeCell ref="E120:J120"/>
+    <mergeCell ref="L120:Y120"/>
+    <mergeCell ref="E114:J114"/>
+    <mergeCell ref="E112:J112"/>
+    <mergeCell ref="E113:J113"/>
+    <mergeCell ref="K111:X111"/>
+    <mergeCell ref="K112:X112"/>
+    <mergeCell ref="K113:X113"/>
+    <mergeCell ref="K114:X114"/>
+    <mergeCell ref="E118:J118"/>
+    <mergeCell ref="N124:Y124"/>
+    <mergeCell ref="E126:J126"/>
+    <mergeCell ref="L126:Y126"/>
+    <mergeCell ref="E131:G131"/>
+    <mergeCell ref="E132:G132"/>
+    <mergeCell ref="E125:J125"/>
+    <mergeCell ref="E133:G133"/>
+    <mergeCell ref="P130:Z130"/>
+    <mergeCell ref="P131:Z131"/>
+    <mergeCell ref="P132:Z132"/>
+    <mergeCell ref="P133:Z133"/>
+    <mergeCell ref="E130:G130"/>
+    <mergeCell ref="H130:O130"/>
+    <mergeCell ref="H131:O131"/>
+    <mergeCell ref="H132:O132"/>
+    <mergeCell ref="H133:O133"/>
+    <mergeCell ref="C140:H140"/>
+    <mergeCell ref="C139:H139"/>
+    <mergeCell ref="C141:H141"/>
+    <mergeCell ref="C142:H142"/>
+    <mergeCell ref="P134:Z134"/>
+    <mergeCell ref="C136:Z137"/>
+    <mergeCell ref="E134:G134"/>
+    <mergeCell ref="H134:O134"/>
+    <mergeCell ref="I139:L139"/>
+    <mergeCell ref="I140:L140"/>
+    <mergeCell ref="I141:L141"/>
+    <mergeCell ref="I142:L142"/>
+    <mergeCell ref="M139:Z139"/>
+    <mergeCell ref="M140:Z140"/>
+    <mergeCell ref="M141:Z141"/>
+    <mergeCell ref="M142:Z142"/>
     <mergeCell ref="M143:Z143"/>
     <mergeCell ref="B149:Z150"/>
     <mergeCell ref="I144:L144"/>
@@ -4810,85 +6961,6 @@
     <mergeCell ref="C144:H144"/>
     <mergeCell ref="C145:H145"/>
     <mergeCell ref="C146:H146"/>
-    <mergeCell ref="C140:H140"/>
-    <mergeCell ref="C139:H139"/>
-    <mergeCell ref="C141:H141"/>
-    <mergeCell ref="C142:H142"/>
-    <mergeCell ref="P134:Z134"/>
-    <mergeCell ref="C136:Z137"/>
-    <mergeCell ref="E134:G134"/>
-    <mergeCell ref="H134:O134"/>
-    <mergeCell ref="I139:L139"/>
-    <mergeCell ref="I140:L140"/>
-    <mergeCell ref="I141:L141"/>
-    <mergeCell ref="I142:L142"/>
-    <mergeCell ref="M139:Z139"/>
-    <mergeCell ref="M140:Z140"/>
-    <mergeCell ref="M141:Z141"/>
-    <mergeCell ref="M142:Z142"/>
-    <mergeCell ref="E133:G133"/>
-    <mergeCell ref="P130:Z130"/>
-    <mergeCell ref="P131:Z131"/>
-    <mergeCell ref="P132:Z132"/>
-    <mergeCell ref="P133:Z133"/>
-    <mergeCell ref="E130:G130"/>
-    <mergeCell ref="H130:O130"/>
-    <mergeCell ref="H131:O131"/>
-    <mergeCell ref="H132:O132"/>
-    <mergeCell ref="H133:O133"/>
-    <mergeCell ref="N124:Y124"/>
-    <mergeCell ref="E126:J126"/>
-    <mergeCell ref="L126:Y126"/>
-    <mergeCell ref="E131:G131"/>
-    <mergeCell ref="E132:G132"/>
-    <mergeCell ref="E125:J125"/>
-    <mergeCell ref="L120:Y120"/>
-    <mergeCell ref="E114:J114"/>
-    <mergeCell ref="E112:J112"/>
-    <mergeCell ref="E113:J113"/>
-    <mergeCell ref="K111:X111"/>
-    <mergeCell ref="K112:X112"/>
-    <mergeCell ref="K113:X113"/>
-    <mergeCell ref="K114:X114"/>
-    <mergeCell ref="E118:J118"/>
-    <mergeCell ref="E121:J121"/>
-    <mergeCell ref="E122:J122"/>
-    <mergeCell ref="E123:J123"/>
-    <mergeCell ref="E124:J124"/>
-    <mergeCell ref="E106:J106"/>
-    <mergeCell ref="E119:J119"/>
-    <mergeCell ref="E120:J120"/>
-    <mergeCell ref="K106:X106"/>
-    <mergeCell ref="K107:X107"/>
-    <mergeCell ref="K108:X108"/>
-    <mergeCell ref="K109:X109"/>
-    <mergeCell ref="E107:J107"/>
-    <mergeCell ref="K110:X110"/>
-    <mergeCell ref="E108:J108"/>
-    <mergeCell ref="E109:J109"/>
-    <mergeCell ref="E110:J110"/>
-    <mergeCell ref="E111:J111"/>
-    <mergeCell ref="C101:Z102"/>
-    <mergeCell ref="E81:G81"/>
-    <mergeCell ref="E82:G82"/>
-    <mergeCell ref="E83:G83"/>
-    <mergeCell ref="E84:G84"/>
-    <mergeCell ref="H81:T81"/>
-    <mergeCell ref="H82:T82"/>
-    <mergeCell ref="H83:T83"/>
-    <mergeCell ref="H84:T84"/>
-    <mergeCell ref="U81:X81"/>
-    <mergeCell ref="U82:X82"/>
-    <mergeCell ref="U83:X83"/>
-    <mergeCell ref="U84:X84"/>
-    <mergeCell ref="E80:G80"/>
-    <mergeCell ref="U80:X80"/>
-    <mergeCell ref="B2:Z4"/>
-    <mergeCell ref="U6:Z6"/>
-    <mergeCell ref="C45:Z46"/>
-    <mergeCell ref="C56:Z57"/>
-    <mergeCell ref="C68:Z69"/>
-    <mergeCell ref="H80:T80"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5213,336 +7285,336 @@
       <c r="AB2" s="6">
         <v>1</v>
       </c>
-      <c r="AC2" s="29" t="s">
+      <c r="AC2" s="47" t="s">
         <v>149</v>
       </c>
-      <c r="AD2" s="29"/>
-      <c r="AE2" s="29"/>
-      <c r="AF2" s="29"/>
-      <c r="AG2" s="29"/>
-      <c r="AH2" s="29"/>
-      <c r="AI2" s="29"/>
-      <c r="AJ2" s="29"/>
+      <c r="AD2" s="47"/>
+      <c r="AE2" s="47"/>
+      <c r="AF2" s="47"/>
+      <c r="AG2" s="47"/>
+      <c r="AH2" s="47"/>
+      <c r="AI2" s="47"/>
+      <c r="AJ2" s="47"/>
       <c r="AK2" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="AL2" s="29" t="s">
+      <c r="AL2" s="47" t="s">
         <v>150</v>
       </c>
-      <c r="AM2" s="29"/>
-      <c r="AN2" s="29"/>
-      <c r="AO2" s="29"/>
-      <c r="AP2" s="29"/>
-      <c r="AQ2" s="29"/>
-      <c r="AR2" s="29"/>
-      <c r="AS2" s="29"/>
-      <c r="AT2" s="29"/>
-      <c r="AU2" s="26" t="s">
+      <c r="AM2" s="47"/>
+      <c r="AN2" s="47"/>
+      <c r="AO2" s="47"/>
+      <c r="AP2" s="47"/>
+      <c r="AQ2" s="47"/>
+      <c r="AR2" s="47"/>
+      <c r="AS2" s="47"/>
+      <c r="AT2" s="47"/>
+      <c r="AU2" s="39" t="s">
         <v>117</v>
       </c>
-      <c r="AV2" s="30" t="s">
+      <c r="AV2" s="41" t="s">
         <v>157</v>
       </c>
-      <c r="AW2" s="31"/>
-      <c r="AX2" s="31"/>
-      <c r="AY2" s="31"/>
-      <c r="AZ2" s="31"/>
-      <c r="BA2" s="31"/>
-      <c r="BB2" s="31"/>
-      <c r="BC2" s="31"/>
-      <c r="BD2" s="32"/>
+      <c r="AW2" s="42"/>
+      <c r="AX2" s="42"/>
+      <c r="AY2" s="42"/>
+      <c r="AZ2" s="42"/>
+      <c r="BA2" s="42"/>
+      <c r="BB2" s="42"/>
+      <c r="BC2" s="42"/>
+      <c r="BD2" s="43"/>
     </row>
     <row r="3" spans="28:56" x14ac:dyDescent="0.3">
-      <c r="AC3" s="28" t="s">
+      <c r="AC3" s="48" t="s">
         <v>114</v>
       </c>
-      <c r="AD3" s="28"/>
-      <c r="AE3" s="28"/>
-      <c r="AF3" s="28"/>
-      <c r="AG3" s="28"/>
-      <c r="AH3" s="28"/>
-      <c r="AI3" s="28"/>
-      <c r="AJ3" s="28"/>
-      <c r="AK3" s="28"/>
-      <c r="AL3" s="28"/>
-      <c r="AM3" s="28"/>
-      <c r="AN3" s="28"/>
-      <c r="AO3" s="28"/>
-      <c r="AP3" s="28"/>
-      <c r="AQ3" s="28"/>
-      <c r="AR3" s="28"/>
-      <c r="AS3" s="28"/>
-      <c r="AT3" s="28"/>
-      <c r="AU3" s="27"/>
-      <c r="AV3" s="23" t="s">
+      <c r="AD3" s="48"/>
+      <c r="AE3" s="48"/>
+      <c r="AF3" s="48"/>
+      <c r="AG3" s="48"/>
+      <c r="AH3" s="48"/>
+      <c r="AI3" s="48"/>
+      <c r="AJ3" s="48"/>
+      <c r="AK3" s="48"/>
+      <c r="AL3" s="48"/>
+      <c r="AM3" s="48"/>
+      <c r="AN3" s="48"/>
+      <c r="AO3" s="48"/>
+      <c r="AP3" s="48"/>
+      <c r="AQ3" s="48"/>
+      <c r="AR3" s="48"/>
+      <c r="AS3" s="48"/>
+      <c r="AT3" s="48"/>
+      <c r="AU3" s="40"/>
+      <c r="AV3" s="44" t="s">
         <v>147</v>
       </c>
-      <c r="AW3" s="24"/>
-      <c r="AX3" s="24"/>
-      <c r="AY3" s="24"/>
-      <c r="AZ3" s="24"/>
-      <c r="BA3" s="24"/>
-      <c r="BB3" s="24"/>
-      <c r="BC3" s="24"/>
-      <c r="BD3" s="25"/>
+      <c r="AW3" s="45"/>
+      <c r="AX3" s="45"/>
+      <c r="AY3" s="45"/>
+      <c r="AZ3" s="45"/>
+      <c r="BA3" s="45"/>
+      <c r="BB3" s="45"/>
+      <c r="BC3" s="45"/>
+      <c r="BD3" s="46"/>
     </row>
     <row r="4" spans="28:56" x14ac:dyDescent="0.3">
-      <c r="AC4" s="29" t="s">
+      <c r="AC4" s="47" t="s">
         <v>148</v>
       </c>
-      <c r="AD4" s="29"/>
-      <c r="AE4" s="29"/>
-      <c r="AF4" s="29"/>
-      <c r="AG4" s="29"/>
-      <c r="AH4" s="29"/>
-      <c r="AI4" s="29"/>
-      <c r="AJ4" s="29"/>
+      <c r="AD4" s="47"/>
+      <c r="AE4" s="47"/>
+      <c r="AF4" s="47"/>
+      <c r="AG4" s="47"/>
+      <c r="AH4" s="47"/>
+      <c r="AI4" s="47"/>
+      <c r="AJ4" s="47"/>
       <c r="AK4" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="AL4" s="29" t="s">
+      <c r="AL4" s="47" t="s">
         <v>151</v>
       </c>
-      <c r="AM4" s="29"/>
-      <c r="AN4" s="29"/>
-      <c r="AO4" s="29"/>
-      <c r="AP4" s="29"/>
-      <c r="AQ4" s="29"/>
-      <c r="AR4" s="29"/>
-      <c r="AS4" s="29"/>
-      <c r="AT4" s="29"/>
-      <c r="AU4" s="26" t="s">
+      <c r="AM4" s="47"/>
+      <c r="AN4" s="47"/>
+      <c r="AO4" s="47"/>
+      <c r="AP4" s="47"/>
+      <c r="AQ4" s="47"/>
+      <c r="AR4" s="47"/>
+      <c r="AS4" s="47"/>
+      <c r="AT4" s="47"/>
+      <c r="AU4" s="39" t="s">
         <v>117</v>
       </c>
-      <c r="AV4" s="30" t="s">
+      <c r="AV4" s="41" t="s">
         <v>158</v>
       </c>
-      <c r="AW4" s="31"/>
-      <c r="AX4" s="31"/>
-      <c r="AY4" s="31"/>
-      <c r="AZ4" s="31"/>
-      <c r="BA4" s="31"/>
-      <c r="BB4" s="31"/>
-      <c r="BC4" s="31"/>
-      <c r="BD4" s="32"/>
+      <c r="AW4" s="42"/>
+      <c r="AX4" s="42"/>
+      <c r="AY4" s="42"/>
+      <c r="AZ4" s="42"/>
+      <c r="BA4" s="42"/>
+      <c r="BB4" s="42"/>
+      <c r="BC4" s="42"/>
+      <c r="BD4" s="43"/>
     </row>
     <row r="5" spans="28:56" x14ac:dyDescent="0.3">
-      <c r="AC5" s="28" t="s">
+      <c r="AC5" s="48" t="s">
         <v>114</v>
       </c>
-      <c r="AD5" s="28"/>
-      <c r="AE5" s="28"/>
-      <c r="AF5" s="28"/>
-      <c r="AG5" s="28"/>
-      <c r="AH5" s="28"/>
-      <c r="AI5" s="28"/>
-      <c r="AJ5" s="28"/>
-      <c r="AK5" s="28"/>
-      <c r="AL5" s="28"/>
-      <c r="AM5" s="28"/>
-      <c r="AN5" s="28"/>
-      <c r="AO5" s="28"/>
-      <c r="AP5" s="28"/>
-      <c r="AQ5" s="28"/>
-      <c r="AR5" s="28"/>
-      <c r="AS5" s="28"/>
-      <c r="AT5" s="28"/>
-      <c r="AU5" s="27"/>
-      <c r="AV5" s="23" t="s">
+      <c r="AD5" s="48"/>
+      <c r="AE5" s="48"/>
+      <c r="AF5" s="48"/>
+      <c r="AG5" s="48"/>
+      <c r="AH5" s="48"/>
+      <c r="AI5" s="48"/>
+      <c r="AJ5" s="48"/>
+      <c r="AK5" s="48"/>
+      <c r="AL5" s="48"/>
+      <c r="AM5" s="48"/>
+      <c r="AN5" s="48"/>
+      <c r="AO5" s="48"/>
+      <c r="AP5" s="48"/>
+      <c r="AQ5" s="48"/>
+      <c r="AR5" s="48"/>
+      <c r="AS5" s="48"/>
+      <c r="AT5" s="48"/>
+      <c r="AU5" s="40"/>
+      <c r="AV5" s="44" t="s">
         <v>159</v>
       </c>
-      <c r="AW5" s="24"/>
-      <c r="AX5" s="24"/>
-      <c r="AY5" s="24"/>
-      <c r="AZ5" s="24"/>
-      <c r="BA5" s="24"/>
-      <c r="BB5" s="24"/>
-      <c r="BC5" s="24"/>
-      <c r="BD5" s="25"/>
+      <c r="AW5" s="45"/>
+      <c r="AX5" s="45"/>
+      <c r="AY5" s="45"/>
+      <c r="AZ5" s="45"/>
+      <c r="BA5" s="45"/>
+      <c r="BB5" s="45"/>
+      <c r="BC5" s="45"/>
+      <c r="BD5" s="46"/>
     </row>
     <row r="6" spans="28:56" x14ac:dyDescent="0.3">
-      <c r="AC6" s="29" t="s">
+      <c r="AC6" s="47" t="s">
         <v>152</v>
       </c>
-      <c r="AD6" s="29"/>
-      <c r="AE6" s="29"/>
-      <c r="AF6" s="29"/>
-      <c r="AG6" s="29"/>
-      <c r="AH6" s="29"/>
-      <c r="AI6" s="29"/>
-      <c r="AJ6" s="29"/>
+      <c r="AD6" s="47"/>
+      <c r="AE6" s="47"/>
+      <c r="AF6" s="47"/>
+      <c r="AG6" s="47"/>
+      <c r="AH6" s="47"/>
+      <c r="AI6" s="47"/>
+      <c r="AJ6" s="47"/>
       <c r="AK6" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="AL6" s="29" t="s">
+      <c r="AL6" s="47" t="s">
         <v>153</v>
       </c>
-      <c r="AM6" s="29"/>
-      <c r="AN6" s="29"/>
-      <c r="AO6" s="29"/>
-      <c r="AP6" s="29"/>
-      <c r="AQ6" s="29"/>
-      <c r="AR6" s="29"/>
-      <c r="AS6" s="29"/>
-      <c r="AT6" s="29"/>
-      <c r="AU6" s="26" t="s">
+      <c r="AM6" s="47"/>
+      <c r="AN6" s="47"/>
+      <c r="AO6" s="47"/>
+      <c r="AP6" s="47"/>
+      <c r="AQ6" s="47"/>
+      <c r="AR6" s="47"/>
+      <c r="AS6" s="47"/>
+      <c r="AT6" s="47"/>
+      <c r="AU6" s="39" t="s">
         <v>117</v>
       </c>
-      <c r="AV6" s="30" t="s">
+      <c r="AV6" s="41" t="s">
         <v>160</v>
       </c>
-      <c r="AW6" s="31"/>
-      <c r="AX6" s="31"/>
-      <c r="AY6" s="31"/>
-      <c r="AZ6" s="31"/>
-      <c r="BA6" s="31"/>
-      <c r="BB6" s="31"/>
-      <c r="BC6" s="31"/>
-      <c r="BD6" s="32"/>
+      <c r="AW6" s="42"/>
+      <c r="AX6" s="42"/>
+      <c r="AY6" s="42"/>
+      <c r="AZ6" s="42"/>
+      <c r="BA6" s="42"/>
+      <c r="BB6" s="42"/>
+      <c r="BC6" s="42"/>
+      <c r="BD6" s="43"/>
     </row>
     <row r="7" spans="28:56" x14ac:dyDescent="0.3">
-      <c r="AC7" s="28" t="s">
+      <c r="AC7" s="48" t="s">
         <v>114</v>
       </c>
-      <c r="AD7" s="28"/>
-      <c r="AE7" s="28"/>
-      <c r="AF7" s="28"/>
-      <c r="AG7" s="28"/>
-      <c r="AH7" s="28"/>
-      <c r="AI7" s="28"/>
-      <c r="AJ7" s="28"/>
-      <c r="AK7" s="28"/>
-      <c r="AL7" s="28"/>
-      <c r="AM7" s="28"/>
-      <c r="AN7" s="28"/>
-      <c r="AO7" s="28"/>
-      <c r="AP7" s="28"/>
-      <c r="AQ7" s="28"/>
-      <c r="AR7" s="28"/>
-      <c r="AS7" s="28"/>
-      <c r="AT7" s="28"/>
-      <c r="AU7" s="27"/>
-      <c r="AV7" s="23" t="s">
+      <c r="AD7" s="48"/>
+      <c r="AE7" s="48"/>
+      <c r="AF7" s="48"/>
+      <c r="AG7" s="48"/>
+      <c r="AH7" s="48"/>
+      <c r="AI7" s="48"/>
+      <c r="AJ7" s="48"/>
+      <c r="AK7" s="48"/>
+      <c r="AL7" s="48"/>
+      <c r="AM7" s="48"/>
+      <c r="AN7" s="48"/>
+      <c r="AO7" s="48"/>
+      <c r="AP7" s="48"/>
+      <c r="AQ7" s="48"/>
+      <c r="AR7" s="48"/>
+      <c r="AS7" s="48"/>
+      <c r="AT7" s="48"/>
+      <c r="AU7" s="40"/>
+      <c r="AV7" s="44" t="s">
         <v>161</v>
       </c>
-      <c r="AW7" s="24"/>
-      <c r="AX7" s="24"/>
-      <c r="AY7" s="24"/>
-      <c r="AZ7" s="24"/>
-      <c r="BA7" s="24"/>
-      <c r="BB7" s="24"/>
-      <c r="BC7" s="24"/>
-      <c r="BD7" s="25"/>
+      <c r="AW7" s="45"/>
+      <c r="AX7" s="45"/>
+      <c r="AY7" s="45"/>
+      <c r="AZ7" s="45"/>
+      <c r="BA7" s="45"/>
+      <c r="BB7" s="45"/>
+      <c r="BC7" s="45"/>
+      <c r="BD7" s="46"/>
     </row>
     <row r="8" spans="28:56" x14ac:dyDescent="0.3">
-      <c r="AC8" s="29" t="s">
+      <c r="AC8" s="47" t="s">
         <v>154</v>
       </c>
-      <c r="AD8" s="29"/>
-      <c r="AE8" s="29"/>
-      <c r="AF8" s="29"/>
-      <c r="AG8" s="29"/>
-      <c r="AH8" s="29"/>
-      <c r="AI8" s="29"/>
-      <c r="AJ8" s="29"/>
-      <c r="AK8" s="29"/>
-      <c r="AL8" s="29"/>
-      <c r="AM8" s="29"/>
-      <c r="AN8" s="29"/>
-      <c r="AO8" s="29"/>
-      <c r="AP8" s="29"/>
-      <c r="AQ8" s="29"/>
-      <c r="AR8" s="29"/>
-      <c r="AS8" s="29"/>
-      <c r="AT8" s="29"/>
+      <c r="AD8" s="47"/>
+      <c r="AE8" s="47"/>
+      <c r="AF8" s="47"/>
+      <c r="AG8" s="47"/>
+      <c r="AH8" s="47"/>
+      <c r="AI8" s="47"/>
+      <c r="AJ8" s="47"/>
+      <c r="AK8" s="47"/>
+      <c r="AL8" s="47"/>
+      <c r="AM8" s="47"/>
+      <c r="AN8" s="47"/>
+      <c r="AO8" s="47"/>
+      <c r="AP8" s="47"/>
+      <c r="AQ8" s="47"/>
+      <c r="AR8" s="47"/>
+      <c r="AS8" s="47"/>
+      <c r="AT8" s="47"/>
     </row>
     <row r="9" spans="28:56" x14ac:dyDescent="0.3">
-      <c r="AC9" s="28" t="s">
+      <c r="AC9" s="48" t="s">
         <v>114</v>
       </c>
-      <c r="AD9" s="28"/>
-      <c r="AE9" s="28"/>
-      <c r="AF9" s="28"/>
-      <c r="AG9" s="28"/>
-      <c r="AH9" s="28"/>
-      <c r="AI9" s="28"/>
-      <c r="AJ9" s="28"/>
-      <c r="AK9" s="28"/>
-      <c r="AL9" s="28"/>
-      <c r="AM9" s="28"/>
-      <c r="AN9" s="28"/>
-      <c r="AO9" s="28"/>
-      <c r="AP9" s="28"/>
-      <c r="AQ9" s="28"/>
-      <c r="AR9" s="28"/>
-      <c r="AS9" s="28"/>
-      <c r="AT9" s="28"/>
+      <c r="AD9" s="48"/>
+      <c r="AE9" s="48"/>
+      <c r="AF9" s="48"/>
+      <c r="AG9" s="48"/>
+      <c r="AH9" s="48"/>
+      <c r="AI9" s="48"/>
+      <c r="AJ9" s="48"/>
+      <c r="AK9" s="48"/>
+      <c r="AL9" s="48"/>
+      <c r="AM9" s="48"/>
+      <c r="AN9" s="48"/>
+      <c r="AO9" s="48"/>
+      <c r="AP9" s="48"/>
+      <c r="AQ9" s="48"/>
+      <c r="AR9" s="48"/>
+      <c r="AS9" s="48"/>
+      <c r="AT9" s="48"/>
     </row>
     <row r="10" spans="28:56" x14ac:dyDescent="0.3">
-      <c r="AC10" s="29" t="s">
+      <c r="AC10" s="47" t="s">
         <v>155</v>
       </c>
-      <c r="AD10" s="29"/>
-      <c r="AE10" s="29"/>
-      <c r="AF10" s="29"/>
-      <c r="AG10" s="29"/>
-      <c r="AH10" s="29"/>
-      <c r="AI10" s="29"/>
-      <c r="AJ10" s="29"/>
-      <c r="AK10" s="29"/>
-      <c r="AL10" s="29"/>
-      <c r="AM10" s="29"/>
-      <c r="AN10" s="29"/>
-      <c r="AO10" s="29"/>
-      <c r="AP10" s="29"/>
-      <c r="AQ10" s="29"/>
-      <c r="AR10" s="29"/>
-      <c r="AS10" s="29"/>
-      <c r="AT10" s="29"/>
+      <c r="AD10" s="47"/>
+      <c r="AE10" s="47"/>
+      <c r="AF10" s="47"/>
+      <c r="AG10" s="47"/>
+      <c r="AH10" s="47"/>
+      <c r="AI10" s="47"/>
+      <c r="AJ10" s="47"/>
+      <c r="AK10" s="47"/>
+      <c r="AL10" s="47"/>
+      <c r="AM10" s="47"/>
+      <c r="AN10" s="47"/>
+      <c r="AO10" s="47"/>
+      <c r="AP10" s="47"/>
+      <c r="AQ10" s="47"/>
+      <c r="AR10" s="47"/>
+      <c r="AS10" s="47"/>
+      <c r="AT10" s="47"/>
     </row>
     <row r="11" spans="28:56" x14ac:dyDescent="0.3">
-      <c r="AC11" s="28" t="s">
+      <c r="AC11" s="48" t="s">
         <v>114</v>
       </c>
-      <c r="AD11" s="28"/>
-      <c r="AE11" s="28"/>
-      <c r="AF11" s="28"/>
-      <c r="AG11" s="28"/>
-      <c r="AH11" s="28"/>
-      <c r="AI11" s="28"/>
-      <c r="AJ11" s="28"/>
-      <c r="AK11" s="28"/>
-      <c r="AL11" s="28"/>
-      <c r="AM11" s="28"/>
-      <c r="AN11" s="28"/>
-      <c r="AO11" s="28"/>
-      <c r="AP11" s="28"/>
-      <c r="AQ11" s="28"/>
-      <c r="AR11" s="28"/>
-      <c r="AS11" s="28"/>
-      <c r="AT11" s="28"/>
+      <c r="AD11" s="48"/>
+      <c r="AE11" s="48"/>
+      <c r="AF11" s="48"/>
+      <c r="AG11" s="48"/>
+      <c r="AH11" s="48"/>
+      <c r="AI11" s="48"/>
+      <c r="AJ11" s="48"/>
+      <c r="AK11" s="48"/>
+      <c r="AL11" s="48"/>
+      <c r="AM11" s="48"/>
+      <c r="AN11" s="48"/>
+      <c r="AO11" s="48"/>
+      <c r="AP11" s="48"/>
+      <c r="AQ11" s="48"/>
+      <c r="AR11" s="48"/>
+      <c r="AS11" s="48"/>
+      <c r="AT11" s="48"/>
     </row>
     <row r="12" spans="28:56" x14ac:dyDescent="0.3">
-      <c r="AC12" s="29" t="s">
+      <c r="AC12" s="47" t="s">
         <v>156</v>
       </c>
-      <c r="AD12" s="29"/>
-      <c r="AE12" s="29"/>
-      <c r="AF12" s="29"/>
-      <c r="AG12" s="29"/>
-      <c r="AH12" s="29"/>
-      <c r="AI12" s="29"/>
-      <c r="AJ12" s="29"/>
-      <c r="AK12" s="29"/>
-      <c r="AL12" s="29"/>
-      <c r="AM12" s="29"/>
-      <c r="AN12" s="29"/>
-      <c r="AO12" s="29"/>
-      <c r="AP12" s="29"/>
-      <c r="AQ12" s="29"/>
-      <c r="AR12" s="29"/>
-      <c r="AS12" s="29"/>
-      <c r="AT12" s="29"/>
+      <c r="AD12" s="47"/>
+      <c r="AE12" s="47"/>
+      <c r="AF12" s="47"/>
+      <c r="AG12" s="47"/>
+      <c r="AH12" s="47"/>
+      <c r="AI12" s="47"/>
+      <c r="AJ12" s="47"/>
+      <c r="AK12" s="47"/>
+      <c r="AL12" s="47"/>
+      <c r="AM12" s="47"/>
+      <c r="AN12" s="47"/>
+      <c r="AO12" s="47"/>
+      <c r="AP12" s="47"/>
+      <c r="AQ12" s="47"/>
+      <c r="AR12" s="47"/>
+      <c r="AS12" s="47"/>
+      <c r="AT12" s="47"/>
     </row>
     <row r="17" spans="28:29" x14ac:dyDescent="0.3">
       <c r="AB17" s="6">
@@ -5559,15 +7631,6 @@
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="AC9:AT9"/>
-    <mergeCell ref="AC10:AT10"/>
-    <mergeCell ref="AU4:AU5"/>
-    <mergeCell ref="AV4:BD4"/>
-    <mergeCell ref="AV6:BD6"/>
-    <mergeCell ref="AV7:BD7"/>
-    <mergeCell ref="AC8:AT8"/>
-    <mergeCell ref="AV5:BD5"/>
-    <mergeCell ref="AU6:AU7"/>
     <mergeCell ref="AC11:AT11"/>
     <mergeCell ref="AC12:AT12"/>
     <mergeCell ref="AV2:BD2"/>
@@ -5582,6 +7645,15 @@
     <mergeCell ref="AL4:AT4"/>
     <mergeCell ref="AC5:AT5"/>
     <mergeCell ref="AL6:AT6"/>
+    <mergeCell ref="AC9:AT9"/>
+    <mergeCell ref="AC10:AT10"/>
+    <mergeCell ref="AU4:AU5"/>
+    <mergeCell ref="AV4:BD4"/>
+    <mergeCell ref="AV6:BD6"/>
+    <mergeCell ref="AV7:BD7"/>
+    <mergeCell ref="AC8:AT8"/>
+    <mergeCell ref="AV5:BD5"/>
+    <mergeCell ref="AU6:AU7"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5598,96 +7670,96 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="27" t="s">
         <v>204</v>
       </c>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
-      <c r="K2" s="10"/>
-      <c r="L2" s="10"/>
-      <c r="M2" s="10"/>
-      <c r="N2" s="10"/>
-      <c r="O2" s="10"/>
-      <c r="P2" s="10"/>
-      <c r="Q2" s="10"/>
-      <c r="R2" s="10"/>
-      <c r="S2" s="10"/>
-      <c r="T2" s="10"/>
-      <c r="U2" s="10"/>
-      <c r="V2" s="10"/>
-      <c r="W2" s="10"/>
-      <c r="X2" s="10"/>
-      <c r="Y2" s="10"/>
-      <c r="Z2" s="11"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
+      <c r="I2" s="28"/>
+      <c r="J2" s="28"/>
+      <c r="K2" s="28"/>
+      <c r="L2" s="28"/>
+      <c r="M2" s="28"/>
+      <c r="N2" s="28"/>
+      <c r="O2" s="28"/>
+      <c r="P2" s="28"/>
+      <c r="Q2" s="28"/>
+      <c r="R2" s="28"/>
+      <c r="S2" s="28"/>
+      <c r="T2" s="28"/>
+      <c r="U2" s="28"/>
+      <c r="V2" s="28"/>
+      <c r="W2" s="28"/>
+      <c r="X2" s="28"/>
+      <c r="Y2" s="28"/>
+      <c r="Z2" s="29"/>
     </row>
     <row r="3" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B3" s="12"/>
-      <c r="C3" s="13"/>
-      <c r="D3" s="13"/>
-      <c r="E3" s="13"/>
-      <c r="F3" s="13"/>
-      <c r="G3" s="13"/>
-      <c r="H3" s="13"/>
-      <c r="I3" s="13"/>
-      <c r="J3" s="13"/>
-      <c r="K3" s="13"/>
-      <c r="L3" s="13"/>
-      <c r="M3" s="13"/>
-      <c r="N3" s="13"/>
-      <c r="O3" s="13"/>
-      <c r="P3" s="13"/>
-      <c r="Q3" s="13"/>
-      <c r="R3" s="13"/>
-      <c r="S3" s="13"/>
-      <c r="T3" s="13"/>
-      <c r="U3" s="13"/>
-      <c r="V3" s="13"/>
-      <c r="W3" s="13"/>
-      <c r="X3" s="13"/>
-      <c r="Y3" s="13"/>
-      <c r="Z3" s="14"/>
+      <c r="B3" s="36"/>
+      <c r="C3" s="37"/>
+      <c r="D3" s="37"/>
+      <c r="E3" s="37"/>
+      <c r="F3" s="37"/>
+      <c r="G3" s="37"/>
+      <c r="H3" s="37"/>
+      <c r="I3" s="37"/>
+      <c r="J3" s="37"/>
+      <c r="K3" s="37"/>
+      <c r="L3" s="37"/>
+      <c r="M3" s="37"/>
+      <c r="N3" s="37"/>
+      <c r="O3" s="37"/>
+      <c r="P3" s="37"/>
+      <c r="Q3" s="37"/>
+      <c r="R3" s="37"/>
+      <c r="S3" s="37"/>
+      <c r="T3" s="37"/>
+      <c r="U3" s="37"/>
+      <c r="V3" s="37"/>
+      <c r="W3" s="37"/>
+      <c r="X3" s="37"/>
+      <c r="Y3" s="37"/>
+      <c r="Z3" s="38"/>
     </row>
     <row r="4" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B4" s="15"/>
-      <c r="C4" s="16"/>
-      <c r="D4" s="16"/>
-      <c r="E4" s="16"/>
-      <c r="F4" s="16"/>
-      <c r="G4" s="16"/>
-      <c r="H4" s="16"/>
-      <c r="I4" s="16"/>
-      <c r="J4" s="16"/>
-      <c r="K4" s="16"/>
-      <c r="L4" s="16"/>
-      <c r="M4" s="16"/>
-      <c r="N4" s="16"/>
-      <c r="O4" s="16"/>
-      <c r="P4" s="16"/>
-      <c r="Q4" s="16"/>
-      <c r="R4" s="16"/>
-      <c r="S4" s="16"/>
-      <c r="T4" s="16"/>
-      <c r="U4" s="16"/>
-      <c r="V4" s="16"/>
-      <c r="W4" s="16"/>
-      <c r="X4" s="16"/>
-      <c r="Y4" s="16"/>
-      <c r="Z4" s="17"/>
+      <c r="B4" s="30"/>
+      <c r="C4" s="31"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
+      <c r="H4" s="31"/>
+      <c r="I4" s="31"/>
+      <c r="J4" s="31"/>
+      <c r="K4" s="31"/>
+      <c r="L4" s="31"/>
+      <c r="M4" s="31"/>
+      <c r="N4" s="31"/>
+      <c r="O4" s="31"/>
+      <c r="P4" s="31"/>
+      <c r="Q4" s="31"/>
+      <c r="R4" s="31"/>
+      <c r="S4" s="31"/>
+      <c r="T4" s="31"/>
+      <c r="U4" s="31"/>
+      <c r="V4" s="31"/>
+      <c r="W4" s="31"/>
+      <c r="X4" s="31"/>
+      <c r="Y4" s="31"/>
+      <c r="Z4" s="32"/>
     </row>
     <row r="6" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="V6" s="18" t="s">
+      <c r="V6" s="33" t="s">
         <v>202</v>
       </c>
-      <c r="W6" s="19"/>
-      <c r="X6" s="19"/>
-      <c r="Y6" s="19"/>
-      <c r="Z6" s="20"/>
+      <c r="W6" s="34"/>
+      <c r="X6" s="34"/>
+      <c r="Y6" s="34"/>
+      <c r="Z6" s="35"/>
     </row>
     <row r="8" spans="2:26" x14ac:dyDescent="0.3">
       <c r="C8" s="2" t="s">
@@ -5727,58 +7799,58 @@
       </c>
     </row>
     <row r="16" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="C16" s="9" t="s">
+      <c r="C16" s="27" t="s">
         <v>209</v>
       </c>
-      <c r="D16" s="10"/>
-      <c r="E16" s="10"/>
-      <c r="F16" s="10"/>
-      <c r="G16" s="10"/>
-      <c r="H16" s="10"/>
-      <c r="I16" s="10"/>
-      <c r="J16" s="10"/>
-      <c r="K16" s="10"/>
-      <c r="L16" s="10"/>
-      <c r="M16" s="10"/>
-      <c r="N16" s="10"/>
-      <c r="O16" s="10"/>
-      <c r="P16" s="10"/>
-      <c r="Q16" s="10"/>
-      <c r="R16" s="10"/>
-      <c r="S16" s="10"/>
-      <c r="T16" s="10"/>
-      <c r="U16" s="10"/>
-      <c r="V16" s="10"/>
-      <c r="W16" s="10"/>
-      <c r="X16" s="10"/>
-      <c r="Y16" s="10"/>
-      <c r="Z16" s="11"/>
+      <c r="D16" s="28"/>
+      <c r="E16" s="28"/>
+      <c r="F16" s="28"/>
+      <c r="G16" s="28"/>
+      <c r="H16" s="28"/>
+      <c r="I16" s="28"/>
+      <c r="J16" s="28"/>
+      <c r="K16" s="28"/>
+      <c r="L16" s="28"/>
+      <c r="M16" s="28"/>
+      <c r="N16" s="28"/>
+      <c r="O16" s="28"/>
+      <c r="P16" s="28"/>
+      <c r="Q16" s="28"/>
+      <c r="R16" s="28"/>
+      <c r="S16" s="28"/>
+      <c r="T16" s="28"/>
+      <c r="U16" s="28"/>
+      <c r="V16" s="28"/>
+      <c r="W16" s="28"/>
+      <c r="X16" s="28"/>
+      <c r="Y16" s="28"/>
+      <c r="Z16" s="29"/>
     </row>
     <row r="17" spans="3:26" x14ac:dyDescent="0.3">
-      <c r="C17" s="15"/>
-      <c r="D17" s="16"/>
-      <c r="E17" s="16"/>
-      <c r="F17" s="16"/>
-      <c r="G17" s="16"/>
-      <c r="H17" s="16"/>
-      <c r="I17" s="16"/>
-      <c r="J17" s="16"/>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
-      <c r="N17" s="16"/>
-      <c r="O17" s="16"/>
-      <c r="P17" s="16"/>
-      <c r="Q17" s="16"/>
-      <c r="R17" s="16"/>
-      <c r="S17" s="16"/>
-      <c r="T17" s="16"/>
-      <c r="U17" s="16"/>
-      <c r="V17" s="16"/>
-      <c r="W17" s="16"/>
-      <c r="X17" s="16"/>
-      <c r="Y17" s="16"/>
-      <c r="Z17" s="17"/>
+      <c r="C17" s="30"/>
+      <c r="D17" s="31"/>
+      <c r="E17" s="31"/>
+      <c r="F17" s="31"/>
+      <c r="G17" s="31"/>
+      <c r="H17" s="31"/>
+      <c r="I17" s="31"/>
+      <c r="J17" s="31"/>
+      <c r="K17" s="31"/>
+      <c r="L17" s="31"/>
+      <c r="M17" s="31"/>
+      <c r="N17" s="31"/>
+      <c r="O17" s="31"/>
+      <c r="P17" s="31"/>
+      <c r="Q17" s="31"/>
+      <c r="R17" s="31"/>
+      <c r="S17" s="31"/>
+      <c r="T17" s="31"/>
+      <c r="U17" s="31"/>
+      <c r="V17" s="31"/>
+      <c r="W17" s="31"/>
+      <c r="X17" s="31"/>
+      <c r="Y17" s="31"/>
+      <c r="Z17" s="32"/>
     </row>
     <row r="19" spans="3:26" x14ac:dyDescent="0.3">
       <c r="D19" s="2">
@@ -5861,58 +7933,58 @@
       </c>
     </row>
     <row r="30" spans="3:26" x14ac:dyDescent="0.3">
-      <c r="C30" s="9" t="s">
+      <c r="C30" s="27" t="s">
         <v>225</v>
       </c>
-      <c r="D30" s="10"/>
-      <c r="E30" s="10"/>
-      <c r="F30" s="10"/>
-      <c r="G30" s="10"/>
-      <c r="H30" s="10"/>
-      <c r="I30" s="10"/>
-      <c r="J30" s="10"/>
-      <c r="K30" s="10"/>
-      <c r="L30" s="10"/>
-      <c r="M30" s="10"/>
-      <c r="N30" s="10"/>
-      <c r="O30" s="10"/>
-      <c r="P30" s="10"/>
-      <c r="Q30" s="10"/>
-      <c r="R30" s="10"/>
-      <c r="S30" s="10"/>
-      <c r="T30" s="10"/>
-      <c r="U30" s="10"/>
-      <c r="V30" s="10"/>
-      <c r="W30" s="10"/>
-      <c r="X30" s="10"/>
-      <c r="Y30" s="10"/>
-      <c r="Z30" s="11"/>
+      <c r="D30" s="28"/>
+      <c r="E30" s="28"/>
+      <c r="F30" s="28"/>
+      <c r="G30" s="28"/>
+      <c r="H30" s="28"/>
+      <c r="I30" s="28"/>
+      <c r="J30" s="28"/>
+      <c r="K30" s="28"/>
+      <c r="L30" s="28"/>
+      <c r="M30" s="28"/>
+      <c r="N30" s="28"/>
+      <c r="O30" s="28"/>
+      <c r="P30" s="28"/>
+      <c r="Q30" s="28"/>
+      <c r="R30" s="28"/>
+      <c r="S30" s="28"/>
+      <c r="T30" s="28"/>
+      <c r="U30" s="28"/>
+      <c r="V30" s="28"/>
+      <c r="W30" s="28"/>
+      <c r="X30" s="28"/>
+      <c r="Y30" s="28"/>
+      <c r="Z30" s="29"/>
     </row>
     <row r="31" spans="3:26" x14ac:dyDescent="0.3">
-      <c r="C31" s="15"/>
-      <c r="D31" s="16"/>
-      <c r="E31" s="16"/>
-      <c r="F31" s="16"/>
-      <c r="G31" s="16"/>
-      <c r="H31" s="16"/>
-      <c r="I31" s="16"/>
-      <c r="J31" s="16"/>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
-      <c r="M31" s="16"/>
-      <c r="N31" s="16"/>
-      <c r="O31" s="16"/>
-      <c r="P31" s="16"/>
-      <c r="Q31" s="16"/>
-      <c r="R31" s="16"/>
-      <c r="S31" s="16"/>
-      <c r="T31" s="16"/>
-      <c r="U31" s="16"/>
-      <c r="V31" s="16"/>
-      <c r="W31" s="16"/>
-      <c r="X31" s="16"/>
-      <c r="Y31" s="16"/>
-      <c r="Z31" s="17"/>
+      <c r="C31" s="30"/>
+      <c r="D31" s="31"/>
+      <c r="E31" s="31"/>
+      <c r="F31" s="31"/>
+      <c r="G31" s="31"/>
+      <c r="H31" s="31"/>
+      <c r="I31" s="31"/>
+      <c r="J31" s="31"/>
+      <c r="K31" s="31"/>
+      <c r="L31" s="31"/>
+      <c r="M31" s="31"/>
+      <c r="N31" s="31"/>
+      <c r="O31" s="31"/>
+      <c r="P31" s="31"/>
+      <c r="Q31" s="31"/>
+      <c r="R31" s="31"/>
+      <c r="S31" s="31"/>
+      <c r="T31" s="31"/>
+      <c r="U31" s="31"/>
+      <c r="V31" s="31"/>
+      <c r="W31" s="31"/>
+      <c r="X31" s="31"/>
+      <c r="Y31" s="31"/>
+      <c r="Z31" s="32"/>
     </row>
     <row r="33" spans="4:26" x14ac:dyDescent="0.3">
       <c r="D33" s="2">
@@ -5964,56 +8036,56 @@
       </c>
     </row>
     <row r="39" spans="4:26" x14ac:dyDescent="0.3">
-      <c r="D39" s="9" t="s">
+      <c r="D39" s="27" t="s">
         <v>233</v>
       </c>
-      <c r="E39" s="10"/>
-      <c r="F39" s="10"/>
-      <c r="G39" s="10"/>
-      <c r="H39" s="10"/>
-      <c r="I39" s="10"/>
-      <c r="J39" s="10"/>
-      <c r="K39" s="10"/>
-      <c r="L39" s="10"/>
-      <c r="M39" s="10"/>
-      <c r="N39" s="10"/>
-      <c r="O39" s="10"/>
-      <c r="P39" s="10"/>
-      <c r="Q39" s="10"/>
-      <c r="R39" s="10"/>
-      <c r="S39" s="10"/>
-      <c r="T39" s="10"/>
-      <c r="U39" s="10"/>
-      <c r="V39" s="10"/>
-      <c r="W39" s="10"/>
-      <c r="X39" s="10"/>
-      <c r="Y39" s="10"/>
-      <c r="Z39" s="11"/>
+      <c r="E39" s="28"/>
+      <c r="F39" s="28"/>
+      <c r="G39" s="28"/>
+      <c r="H39" s="28"/>
+      <c r="I39" s="28"/>
+      <c r="J39" s="28"/>
+      <c r="K39" s="28"/>
+      <c r="L39" s="28"/>
+      <c r="M39" s="28"/>
+      <c r="N39" s="28"/>
+      <c r="O39" s="28"/>
+      <c r="P39" s="28"/>
+      <c r="Q39" s="28"/>
+      <c r="R39" s="28"/>
+      <c r="S39" s="28"/>
+      <c r="T39" s="28"/>
+      <c r="U39" s="28"/>
+      <c r="V39" s="28"/>
+      <c r="W39" s="28"/>
+      <c r="X39" s="28"/>
+      <c r="Y39" s="28"/>
+      <c r="Z39" s="29"/>
     </row>
     <row r="40" spans="4:26" x14ac:dyDescent="0.3">
-      <c r="D40" s="15"/>
-      <c r="E40" s="16"/>
-      <c r="F40" s="16"/>
-      <c r="G40" s="16"/>
-      <c r="H40" s="16"/>
-      <c r="I40" s="16"/>
-      <c r="J40" s="16"/>
-      <c r="K40" s="16"/>
-      <c r="L40" s="16"/>
-      <c r="M40" s="16"/>
-      <c r="N40" s="16"/>
-      <c r="O40" s="16"/>
-      <c r="P40" s="16"/>
-      <c r="Q40" s="16"/>
-      <c r="R40" s="16"/>
-      <c r="S40" s="16"/>
-      <c r="T40" s="16"/>
-      <c r="U40" s="16"/>
-      <c r="V40" s="16"/>
-      <c r="W40" s="16"/>
-      <c r="X40" s="16"/>
-      <c r="Y40" s="16"/>
-      <c r="Z40" s="17"/>
+      <c r="D40" s="30"/>
+      <c r="E40" s="31"/>
+      <c r="F40" s="31"/>
+      <c r="G40" s="31"/>
+      <c r="H40" s="31"/>
+      <c r="I40" s="31"/>
+      <c r="J40" s="31"/>
+      <c r="K40" s="31"/>
+      <c r="L40" s="31"/>
+      <c r="M40" s="31"/>
+      <c r="N40" s="31"/>
+      <c r="O40" s="31"/>
+      <c r="P40" s="31"/>
+      <c r="Q40" s="31"/>
+      <c r="R40" s="31"/>
+      <c r="S40" s="31"/>
+      <c r="T40" s="31"/>
+      <c r="U40" s="31"/>
+      <c r="V40" s="31"/>
+      <c r="W40" s="31"/>
+      <c r="X40" s="31"/>
+      <c r="Y40" s="31"/>
+      <c r="Z40" s="32"/>
     </row>
     <row r="42" spans="4:26" x14ac:dyDescent="0.3">
       <c r="E42" s="2">
@@ -6156,785 +8228,785 @@
       </c>
     </row>
     <row r="68" spans="3:26" x14ac:dyDescent="0.3">
-      <c r="C68" s="9" t="s">
+      <c r="C68" s="27" t="s">
         <v>208</v>
       </c>
-      <c r="D68" s="10"/>
-      <c r="E68" s="10"/>
-      <c r="F68" s="10"/>
-      <c r="G68" s="10"/>
-      <c r="H68" s="10"/>
-      <c r="I68" s="10"/>
-      <c r="J68" s="10"/>
-      <c r="K68" s="10"/>
-      <c r="L68" s="10"/>
-      <c r="M68" s="10"/>
-      <c r="N68" s="10"/>
-      <c r="O68" s="10"/>
-      <c r="P68" s="10"/>
-      <c r="Q68" s="10"/>
-      <c r="R68" s="10"/>
-      <c r="S68" s="10"/>
-      <c r="T68" s="10"/>
-      <c r="U68" s="10"/>
-      <c r="V68" s="10"/>
-      <c r="W68" s="10"/>
-      <c r="X68" s="10"/>
-      <c r="Y68" s="10"/>
-      <c r="Z68" s="11"/>
+      <c r="D68" s="28"/>
+      <c r="E68" s="28"/>
+      <c r="F68" s="28"/>
+      <c r="G68" s="28"/>
+      <c r="H68" s="28"/>
+      <c r="I68" s="28"/>
+      <c r="J68" s="28"/>
+      <c r="K68" s="28"/>
+      <c r="L68" s="28"/>
+      <c r="M68" s="28"/>
+      <c r="N68" s="28"/>
+      <c r="O68" s="28"/>
+      <c r="P68" s="28"/>
+      <c r="Q68" s="28"/>
+      <c r="R68" s="28"/>
+      <c r="S68" s="28"/>
+      <c r="T68" s="28"/>
+      <c r="U68" s="28"/>
+      <c r="V68" s="28"/>
+      <c r="W68" s="28"/>
+      <c r="X68" s="28"/>
+      <c r="Y68" s="28"/>
+      <c r="Z68" s="29"/>
     </row>
     <row r="69" spans="3:26" x14ac:dyDescent="0.3">
-      <c r="C69" s="15"/>
-      <c r="D69" s="16"/>
-      <c r="E69" s="16"/>
-      <c r="F69" s="16"/>
-      <c r="G69" s="16"/>
-      <c r="H69" s="16"/>
-      <c r="I69" s="16"/>
-      <c r="J69" s="16"/>
-      <c r="K69" s="16"/>
-      <c r="L69" s="16"/>
-      <c r="M69" s="16"/>
-      <c r="N69" s="16"/>
-      <c r="O69" s="16"/>
-      <c r="P69" s="16"/>
-      <c r="Q69" s="16"/>
-      <c r="R69" s="16"/>
-      <c r="S69" s="16"/>
-      <c r="T69" s="16"/>
-      <c r="U69" s="16"/>
-      <c r="V69" s="16"/>
-      <c r="W69" s="16"/>
-      <c r="X69" s="16"/>
-      <c r="Y69" s="16"/>
-      <c r="Z69" s="17"/>
+      <c r="C69" s="30"/>
+      <c r="D69" s="31"/>
+      <c r="E69" s="31"/>
+      <c r="F69" s="31"/>
+      <c r="G69" s="31"/>
+      <c r="H69" s="31"/>
+      <c r="I69" s="31"/>
+      <c r="J69" s="31"/>
+      <c r="K69" s="31"/>
+      <c r="L69" s="31"/>
+      <c r="M69" s="31"/>
+      <c r="N69" s="31"/>
+      <c r="O69" s="31"/>
+      <c r="P69" s="31"/>
+      <c r="Q69" s="31"/>
+      <c r="R69" s="31"/>
+      <c r="S69" s="31"/>
+      <c r="T69" s="31"/>
+      <c r="U69" s="31"/>
+      <c r="V69" s="31"/>
+      <c r="W69" s="31"/>
+      <c r="X69" s="31"/>
+      <c r="Y69" s="31"/>
+      <c r="Z69" s="32"/>
     </row>
     <row r="71" spans="3:26" x14ac:dyDescent="0.3">
-      <c r="D71" s="18" t="s">
+      <c r="D71" s="33" t="s">
         <v>257</v>
       </c>
-      <c r="E71" s="19"/>
-      <c r="F71" s="19"/>
-      <c r="G71" s="19"/>
-      <c r="H71" s="19"/>
-      <c r="I71" s="19"/>
-      <c r="J71" s="19"/>
-      <c r="K71" s="19"/>
-      <c r="L71" s="19"/>
-      <c r="M71" s="19"/>
-      <c r="N71" s="19"/>
-      <c r="O71" s="19"/>
-      <c r="P71" s="19"/>
-      <c r="Q71" s="19"/>
-      <c r="R71" s="19"/>
-      <c r="S71" s="19"/>
-      <c r="T71" s="19"/>
-      <c r="U71" s="19"/>
-      <c r="V71" s="19"/>
-      <c r="W71" s="19"/>
-      <c r="X71" s="19"/>
-      <c r="Y71" s="19"/>
-      <c r="Z71" s="20"/>
+      <c r="E71" s="34"/>
+      <c r="F71" s="34"/>
+      <c r="G71" s="34"/>
+      <c r="H71" s="34"/>
+      <c r="I71" s="34"/>
+      <c r="J71" s="34"/>
+      <c r="K71" s="34"/>
+      <c r="L71" s="34"/>
+      <c r="M71" s="34"/>
+      <c r="N71" s="34"/>
+      <c r="O71" s="34"/>
+      <c r="P71" s="34"/>
+      <c r="Q71" s="34"/>
+      <c r="R71" s="34"/>
+      <c r="S71" s="34"/>
+      <c r="T71" s="34"/>
+      <c r="U71" s="34"/>
+      <c r="V71" s="34"/>
+      <c r="W71" s="34"/>
+      <c r="X71" s="34"/>
+      <c r="Y71" s="34"/>
+      <c r="Z71" s="35"/>
     </row>
     <row r="86" spans="4:26" x14ac:dyDescent="0.3">
-      <c r="D86" s="33" t="s">
+      <c r="D86" s="10" t="s">
         <v>258</v>
       </c>
-      <c r="E86" s="34"/>
-      <c r="F86" s="34"/>
-      <c r="G86" s="34"/>
-      <c r="H86" s="34"/>
-      <c r="I86" s="34"/>
-      <c r="J86" s="34"/>
-      <c r="K86" s="34"/>
-      <c r="L86" s="34"/>
-      <c r="M86" s="34"/>
-      <c r="N86" s="34"/>
-      <c r="O86" s="34"/>
-      <c r="P86" s="34"/>
-      <c r="Q86" s="34"/>
-      <c r="R86" s="34"/>
-      <c r="S86" s="34"/>
-      <c r="T86" s="34"/>
-      <c r="U86" s="34"/>
-      <c r="V86" s="34"/>
-      <c r="W86" s="34"/>
-      <c r="X86" s="34"/>
-      <c r="Y86" s="34"/>
-      <c r="Z86" s="35"/>
+      <c r="E86" s="11"/>
+      <c r="F86" s="11"/>
+      <c r="G86" s="11"/>
+      <c r="H86" s="11"/>
+      <c r="I86" s="11"/>
+      <c r="J86" s="11"/>
+      <c r="K86" s="11"/>
+      <c r="L86" s="11"/>
+      <c r="M86" s="11"/>
+      <c r="N86" s="11"/>
+      <c r="O86" s="11"/>
+      <c r="P86" s="11"/>
+      <c r="Q86" s="11"/>
+      <c r="R86" s="11"/>
+      <c r="S86" s="11"/>
+      <c r="T86" s="11"/>
+      <c r="U86" s="11"/>
+      <c r="V86" s="11"/>
+      <c r="W86" s="11"/>
+      <c r="X86" s="11"/>
+      <c r="Y86" s="11"/>
+      <c r="Z86" s="12"/>
     </row>
     <row r="87" spans="4:26" x14ac:dyDescent="0.3">
-      <c r="D87" s="39" t="s">
+      <c r="D87" s="16" t="s">
         <v>259</v>
       </c>
-      <c r="E87" s="40"/>
-      <c r="F87" s="40"/>
-      <c r="G87" s="40"/>
-      <c r="H87" s="40"/>
-      <c r="I87" s="40"/>
-      <c r="J87" s="40"/>
-      <c r="K87" s="40"/>
-      <c r="L87" s="40"/>
-      <c r="M87" s="40"/>
-      <c r="N87" s="40"/>
-      <c r="O87" s="40"/>
-      <c r="P87" s="40"/>
-      <c r="Q87" s="40"/>
-      <c r="R87" s="40"/>
-      <c r="S87" s="40"/>
-      <c r="T87" s="40"/>
-      <c r="U87" s="40"/>
-      <c r="V87" s="40"/>
-      <c r="W87" s="40"/>
-      <c r="X87" s="40"/>
-      <c r="Y87" s="40"/>
-      <c r="Z87" s="41"/>
+      <c r="E87" s="17"/>
+      <c r="F87" s="17"/>
+      <c r="G87" s="17"/>
+      <c r="H87" s="17"/>
+      <c r="I87" s="17"/>
+      <c r="J87" s="17"/>
+      <c r="K87" s="17"/>
+      <c r="L87" s="17"/>
+      <c r="M87" s="17"/>
+      <c r="N87" s="17"/>
+      <c r="O87" s="17"/>
+      <c r="P87" s="17"/>
+      <c r="Q87" s="17"/>
+      <c r="R87" s="17"/>
+      <c r="S87" s="17"/>
+      <c r="T87" s="17"/>
+      <c r="U87" s="17"/>
+      <c r="V87" s="17"/>
+      <c r="W87" s="17"/>
+      <c r="X87" s="17"/>
+      <c r="Y87" s="17"/>
+      <c r="Z87" s="18"/>
     </row>
     <row r="102" spans="4:26" x14ac:dyDescent="0.3">
-      <c r="D102" s="33" t="s">
+      <c r="D102" s="10" t="s">
         <v>260</v>
       </c>
-      <c r="E102" s="34"/>
-      <c r="F102" s="34"/>
-      <c r="G102" s="34"/>
-      <c r="H102" s="34"/>
-      <c r="I102" s="34"/>
-      <c r="J102" s="34"/>
-      <c r="K102" s="34"/>
-      <c r="L102" s="34"/>
-      <c r="M102" s="34"/>
-      <c r="N102" s="34"/>
-      <c r="O102" s="34"/>
-      <c r="P102" s="34"/>
-      <c r="Q102" s="34"/>
-      <c r="R102" s="34"/>
-      <c r="S102" s="34"/>
-      <c r="T102" s="34"/>
-      <c r="U102" s="34"/>
-      <c r="V102" s="34"/>
-      <c r="W102" s="34"/>
-      <c r="X102" s="34"/>
-      <c r="Y102" s="34"/>
-      <c r="Z102" s="35"/>
+      <c r="E102" s="11"/>
+      <c r="F102" s="11"/>
+      <c r="G102" s="11"/>
+      <c r="H102" s="11"/>
+      <c r="I102" s="11"/>
+      <c r="J102" s="11"/>
+      <c r="K102" s="11"/>
+      <c r="L102" s="11"/>
+      <c r="M102" s="11"/>
+      <c r="N102" s="11"/>
+      <c r="O102" s="11"/>
+      <c r="P102" s="11"/>
+      <c r="Q102" s="11"/>
+      <c r="R102" s="11"/>
+      <c r="S102" s="11"/>
+      <c r="T102" s="11"/>
+      <c r="U102" s="11"/>
+      <c r="V102" s="11"/>
+      <c r="W102" s="11"/>
+      <c r="X102" s="11"/>
+      <c r="Y102" s="11"/>
+      <c r="Z102" s="12"/>
     </row>
     <row r="103" spans="4:26" x14ac:dyDescent="0.3">
-      <c r="D103" s="36" t="s">
+      <c r="D103" s="13" t="s">
         <v>261</v>
       </c>
-      <c r="E103" s="37"/>
-      <c r="F103" s="37"/>
-      <c r="G103" s="37"/>
-      <c r="H103" s="37"/>
-      <c r="I103" s="37"/>
-      <c r="J103" s="37"/>
-      <c r="K103" s="37"/>
-      <c r="L103" s="37"/>
-      <c r="M103" s="37"/>
-      <c r="N103" s="37"/>
-      <c r="O103" s="37"/>
-      <c r="P103" s="37"/>
-      <c r="Q103" s="37"/>
-      <c r="R103" s="37"/>
-      <c r="S103" s="37"/>
-      <c r="T103" s="37"/>
-      <c r="U103" s="37"/>
-      <c r="V103" s="37"/>
-      <c r="W103" s="37"/>
-      <c r="X103" s="37"/>
-      <c r="Y103" s="37"/>
-      <c r="Z103" s="38"/>
+      <c r="E103" s="14"/>
+      <c r="F103" s="14"/>
+      <c r="G103" s="14"/>
+      <c r="H103" s="14"/>
+      <c r="I103" s="14"/>
+      <c r="J103" s="14"/>
+      <c r="K103" s="14"/>
+      <c r="L103" s="14"/>
+      <c r="M103" s="14"/>
+      <c r="N103" s="14"/>
+      <c r="O103" s="14"/>
+      <c r="P103" s="14"/>
+      <c r="Q103" s="14"/>
+      <c r="R103" s="14"/>
+      <c r="S103" s="14"/>
+      <c r="T103" s="14"/>
+      <c r="U103" s="14"/>
+      <c r="V103" s="14"/>
+      <c r="W103" s="14"/>
+      <c r="X103" s="14"/>
+      <c r="Y103" s="14"/>
+      <c r="Z103" s="15"/>
     </row>
     <row r="104" spans="4:26" x14ac:dyDescent="0.3">
-      <c r="D104" s="39" t="s">
+      <c r="D104" s="16" t="s">
         <v>262</v>
       </c>
-      <c r="E104" s="40"/>
-      <c r="F104" s="40"/>
-      <c r="G104" s="40"/>
-      <c r="H104" s="40"/>
-      <c r="I104" s="40"/>
-      <c r="J104" s="40"/>
-      <c r="K104" s="40"/>
-      <c r="L104" s="40"/>
-      <c r="M104" s="40"/>
-      <c r="N104" s="40"/>
-      <c r="O104" s="40"/>
-      <c r="P104" s="40"/>
-      <c r="Q104" s="40"/>
-      <c r="R104" s="40"/>
-      <c r="S104" s="40"/>
-      <c r="T104" s="40"/>
-      <c r="U104" s="40"/>
-      <c r="V104" s="40"/>
-      <c r="W104" s="40"/>
-      <c r="X104" s="40"/>
-      <c r="Y104" s="40"/>
-      <c r="Z104" s="41"/>
+      <c r="E104" s="17"/>
+      <c r="F104" s="17"/>
+      <c r="G104" s="17"/>
+      <c r="H104" s="17"/>
+      <c r="I104" s="17"/>
+      <c r="J104" s="17"/>
+      <c r="K104" s="17"/>
+      <c r="L104" s="17"/>
+      <c r="M104" s="17"/>
+      <c r="N104" s="17"/>
+      <c r="O104" s="17"/>
+      <c r="P104" s="17"/>
+      <c r="Q104" s="17"/>
+      <c r="R104" s="17"/>
+      <c r="S104" s="17"/>
+      <c r="T104" s="17"/>
+      <c r="U104" s="17"/>
+      <c r="V104" s="17"/>
+      <c r="W104" s="17"/>
+      <c r="X104" s="17"/>
+      <c r="Y104" s="17"/>
+      <c r="Z104" s="18"/>
     </row>
     <row r="120" spans="4:26" x14ac:dyDescent="0.3">
-      <c r="D120" s="42" t="s">
+      <c r="D120" s="19" t="s">
         <v>263</v>
       </c>
-      <c r="E120" s="43"/>
-      <c r="F120" s="43"/>
-      <c r="G120" s="43"/>
-      <c r="H120" s="43"/>
-      <c r="I120" s="43"/>
-      <c r="J120" s="43"/>
-      <c r="K120" s="43"/>
-      <c r="L120" s="43"/>
-      <c r="M120" s="43"/>
-      <c r="N120" s="43"/>
-      <c r="O120" s="43"/>
-      <c r="P120" s="43"/>
-      <c r="Q120" s="43"/>
-      <c r="R120" s="43"/>
-      <c r="S120" s="43"/>
-      <c r="T120" s="43"/>
-      <c r="U120" s="43"/>
-      <c r="V120" s="43"/>
-      <c r="W120" s="43"/>
-      <c r="X120" s="43"/>
-      <c r="Y120" s="43"/>
-      <c r="Z120" s="44"/>
+      <c r="E120" s="20"/>
+      <c r="F120" s="20"/>
+      <c r="G120" s="20"/>
+      <c r="H120" s="20"/>
+      <c r="I120" s="20"/>
+      <c r="J120" s="20"/>
+      <c r="K120" s="20"/>
+      <c r="L120" s="20"/>
+      <c r="M120" s="20"/>
+      <c r="N120" s="20"/>
+      <c r="O120" s="20"/>
+      <c r="P120" s="20"/>
+      <c r="Q120" s="20"/>
+      <c r="R120" s="20"/>
+      <c r="S120" s="20"/>
+      <c r="T120" s="20"/>
+      <c r="U120" s="20"/>
+      <c r="V120" s="20"/>
+      <c r="W120" s="20"/>
+      <c r="X120" s="20"/>
+      <c r="Y120" s="20"/>
+      <c r="Z120" s="21"/>
     </row>
     <row r="136" spans="4:26" x14ac:dyDescent="0.3">
-      <c r="D136" s="33" t="s">
+      <c r="D136" s="10" t="s">
         <v>264</v>
       </c>
-      <c r="E136" s="34"/>
-      <c r="F136" s="34"/>
-      <c r="G136" s="34"/>
-      <c r="H136" s="34"/>
-      <c r="I136" s="34"/>
-      <c r="J136" s="34"/>
-      <c r="K136" s="34"/>
-      <c r="L136" s="34"/>
-      <c r="M136" s="34"/>
-      <c r="N136" s="34"/>
-      <c r="O136" s="34"/>
-      <c r="P136" s="34"/>
-      <c r="Q136" s="34"/>
-      <c r="R136" s="34"/>
-      <c r="S136" s="34"/>
-      <c r="T136" s="34"/>
-      <c r="U136" s="34"/>
-      <c r="V136" s="34"/>
-      <c r="W136" s="34"/>
-      <c r="X136" s="34"/>
-      <c r="Y136" s="34"/>
-      <c r="Z136" s="35"/>
+      <c r="E136" s="11"/>
+      <c r="F136" s="11"/>
+      <c r="G136" s="11"/>
+      <c r="H136" s="11"/>
+      <c r="I136" s="11"/>
+      <c r="J136" s="11"/>
+      <c r="K136" s="11"/>
+      <c r="L136" s="11"/>
+      <c r="M136" s="11"/>
+      <c r="N136" s="11"/>
+      <c r="O136" s="11"/>
+      <c r="P136" s="11"/>
+      <c r="Q136" s="11"/>
+      <c r="R136" s="11"/>
+      <c r="S136" s="11"/>
+      <c r="T136" s="11"/>
+      <c r="U136" s="11"/>
+      <c r="V136" s="11"/>
+      <c r="W136" s="11"/>
+      <c r="X136" s="11"/>
+      <c r="Y136" s="11"/>
+      <c r="Z136" s="12"/>
     </row>
     <row r="137" spans="4:26" x14ac:dyDescent="0.3">
-      <c r="D137" s="36" t="s">
+      <c r="D137" s="13" t="s">
         <v>265</v>
       </c>
-      <c r="E137" s="37"/>
-      <c r="F137" s="37"/>
-      <c r="G137" s="37"/>
-      <c r="H137" s="37"/>
-      <c r="I137" s="37"/>
-      <c r="J137" s="37"/>
-      <c r="K137" s="37"/>
-      <c r="L137" s="37"/>
-      <c r="M137" s="37"/>
-      <c r="N137" s="37"/>
-      <c r="O137" s="37"/>
-      <c r="P137" s="37"/>
-      <c r="Q137" s="37"/>
-      <c r="R137" s="37"/>
-      <c r="S137" s="37"/>
-      <c r="T137" s="37"/>
-      <c r="U137" s="37"/>
-      <c r="V137" s="37"/>
-      <c r="W137" s="37"/>
-      <c r="X137" s="37"/>
-      <c r="Y137" s="37"/>
-      <c r="Z137" s="38"/>
+      <c r="E137" s="14"/>
+      <c r="F137" s="14"/>
+      <c r="G137" s="14"/>
+      <c r="H137" s="14"/>
+      <c r="I137" s="14"/>
+      <c r="J137" s="14"/>
+      <c r="K137" s="14"/>
+      <c r="L137" s="14"/>
+      <c r="M137" s="14"/>
+      <c r="N137" s="14"/>
+      <c r="O137" s="14"/>
+      <c r="P137" s="14"/>
+      <c r="Q137" s="14"/>
+      <c r="R137" s="14"/>
+      <c r="S137" s="14"/>
+      <c r="T137" s="14"/>
+      <c r="U137" s="14"/>
+      <c r="V137" s="14"/>
+      <c r="W137" s="14"/>
+      <c r="X137" s="14"/>
+      <c r="Y137" s="14"/>
+      <c r="Z137" s="15"/>
     </row>
     <row r="138" spans="4:26" x14ac:dyDescent="0.3">
-      <c r="D138" s="36" t="s">
+      <c r="D138" s="13" t="s">
         <v>266</v>
       </c>
-      <c r="E138" s="37"/>
-      <c r="F138" s="37"/>
-      <c r="G138" s="37"/>
-      <c r="H138" s="37"/>
-      <c r="I138" s="37"/>
-      <c r="J138" s="37"/>
-      <c r="K138" s="37"/>
-      <c r="L138" s="37"/>
-      <c r="M138" s="37"/>
-      <c r="N138" s="37"/>
-      <c r="O138" s="37"/>
-      <c r="P138" s="37"/>
-      <c r="Q138" s="37"/>
-      <c r="R138" s="37"/>
-      <c r="S138" s="37"/>
-      <c r="T138" s="37"/>
-      <c r="U138" s="37"/>
-      <c r="V138" s="37"/>
-      <c r="W138" s="37"/>
-      <c r="X138" s="37"/>
-      <c r="Y138" s="37"/>
-      <c r="Z138" s="38"/>
+      <c r="E138" s="14"/>
+      <c r="F138" s="14"/>
+      <c r="G138" s="14"/>
+      <c r="H138" s="14"/>
+      <c r="I138" s="14"/>
+      <c r="J138" s="14"/>
+      <c r="K138" s="14"/>
+      <c r="L138" s="14"/>
+      <c r="M138" s="14"/>
+      <c r="N138" s="14"/>
+      <c r="O138" s="14"/>
+      <c r="P138" s="14"/>
+      <c r="Q138" s="14"/>
+      <c r="R138" s="14"/>
+      <c r="S138" s="14"/>
+      <c r="T138" s="14"/>
+      <c r="U138" s="14"/>
+      <c r="V138" s="14"/>
+      <c r="W138" s="14"/>
+      <c r="X138" s="14"/>
+      <c r="Y138" s="14"/>
+      <c r="Z138" s="15"/>
     </row>
     <row r="139" spans="4:26" x14ac:dyDescent="0.3">
-      <c r="D139" s="36" t="s">
+      <c r="D139" s="13" t="s">
         <v>267</v>
       </c>
-      <c r="E139" s="37"/>
-      <c r="F139" s="37"/>
-      <c r="G139" s="37"/>
-      <c r="H139" s="37"/>
-      <c r="I139" s="37"/>
-      <c r="J139" s="37"/>
-      <c r="K139" s="37"/>
-      <c r="L139" s="37"/>
-      <c r="M139" s="37"/>
-      <c r="N139" s="37"/>
-      <c r="O139" s="37"/>
-      <c r="P139" s="37"/>
-      <c r="Q139" s="37"/>
-      <c r="R139" s="37"/>
-      <c r="S139" s="37"/>
-      <c r="T139" s="37"/>
-      <c r="U139" s="37"/>
-      <c r="V139" s="37"/>
-      <c r="W139" s="37"/>
-      <c r="X139" s="37"/>
-      <c r="Y139" s="37"/>
-      <c r="Z139" s="38"/>
+      <c r="E139" s="14"/>
+      <c r="F139" s="14"/>
+      <c r="G139" s="14"/>
+      <c r="H139" s="14"/>
+      <c r="I139" s="14"/>
+      <c r="J139" s="14"/>
+      <c r="K139" s="14"/>
+      <c r="L139" s="14"/>
+      <c r="M139" s="14"/>
+      <c r="N139" s="14"/>
+      <c r="O139" s="14"/>
+      <c r="P139" s="14"/>
+      <c r="Q139" s="14"/>
+      <c r="R139" s="14"/>
+      <c r="S139" s="14"/>
+      <c r="T139" s="14"/>
+      <c r="U139" s="14"/>
+      <c r="V139" s="14"/>
+      <c r="W139" s="14"/>
+      <c r="X139" s="14"/>
+      <c r="Y139" s="14"/>
+      <c r="Z139" s="15"/>
     </row>
     <row r="140" spans="4:26" x14ac:dyDescent="0.3">
-      <c r="D140" s="39" t="s">
+      <c r="D140" s="16" t="s">
         <v>268</v>
       </c>
-      <c r="E140" s="40"/>
-      <c r="F140" s="40"/>
-      <c r="G140" s="40"/>
-      <c r="H140" s="40"/>
-      <c r="I140" s="40"/>
-      <c r="J140" s="40"/>
-      <c r="K140" s="40"/>
-      <c r="L140" s="40"/>
-      <c r="M140" s="40"/>
-      <c r="N140" s="40"/>
-      <c r="O140" s="40"/>
-      <c r="P140" s="40"/>
-      <c r="Q140" s="40"/>
-      <c r="R140" s="40"/>
-      <c r="S140" s="40"/>
-      <c r="T140" s="40"/>
-      <c r="U140" s="40"/>
-      <c r="V140" s="40"/>
-      <c r="W140" s="40"/>
-      <c r="X140" s="40"/>
-      <c r="Y140" s="40"/>
-      <c r="Z140" s="41"/>
+      <c r="E140" s="17"/>
+      <c r="F140" s="17"/>
+      <c r="G140" s="17"/>
+      <c r="H140" s="17"/>
+      <c r="I140" s="17"/>
+      <c r="J140" s="17"/>
+      <c r="K140" s="17"/>
+      <c r="L140" s="17"/>
+      <c r="M140" s="17"/>
+      <c r="N140" s="17"/>
+      <c r="O140" s="17"/>
+      <c r="P140" s="17"/>
+      <c r="Q140" s="17"/>
+      <c r="R140" s="17"/>
+      <c r="S140" s="17"/>
+      <c r="T140" s="17"/>
+      <c r="U140" s="17"/>
+      <c r="V140" s="17"/>
+      <c r="W140" s="17"/>
+      <c r="X140" s="17"/>
+      <c r="Y140" s="17"/>
+      <c r="Z140" s="18"/>
     </row>
     <row r="156" spans="4:26" x14ac:dyDescent="0.3">
-      <c r="D156" s="33" t="s">
+      <c r="D156" s="10" t="s">
         <v>269</v>
       </c>
-      <c r="E156" s="34"/>
-      <c r="F156" s="34"/>
-      <c r="G156" s="34"/>
-      <c r="H156" s="34"/>
-      <c r="I156" s="34"/>
-      <c r="J156" s="34"/>
-      <c r="K156" s="34"/>
-      <c r="L156" s="34"/>
-      <c r="M156" s="34"/>
-      <c r="N156" s="34"/>
-      <c r="O156" s="34"/>
-      <c r="P156" s="34"/>
-      <c r="Q156" s="34"/>
-      <c r="R156" s="34"/>
-      <c r="S156" s="34"/>
-      <c r="T156" s="34"/>
-      <c r="U156" s="34"/>
-      <c r="V156" s="34"/>
-      <c r="W156" s="34"/>
-      <c r="X156" s="34"/>
-      <c r="Y156" s="34"/>
-      <c r="Z156" s="35"/>
+      <c r="E156" s="11"/>
+      <c r="F156" s="11"/>
+      <c r="G156" s="11"/>
+      <c r="H156" s="11"/>
+      <c r="I156" s="11"/>
+      <c r="J156" s="11"/>
+      <c r="K156" s="11"/>
+      <c r="L156" s="11"/>
+      <c r="M156" s="11"/>
+      <c r="N156" s="11"/>
+      <c r="O156" s="11"/>
+      <c r="P156" s="11"/>
+      <c r="Q156" s="11"/>
+      <c r="R156" s="11"/>
+      <c r="S156" s="11"/>
+      <c r="T156" s="11"/>
+      <c r="U156" s="11"/>
+      <c r="V156" s="11"/>
+      <c r="W156" s="11"/>
+      <c r="X156" s="11"/>
+      <c r="Y156" s="11"/>
+      <c r="Z156" s="12"/>
     </row>
     <row r="157" spans="4:26" x14ac:dyDescent="0.3">
-      <c r="D157" s="36" t="s">
+      <c r="D157" s="13" t="s">
         <v>270</v>
       </c>
-      <c r="E157" s="37"/>
-      <c r="F157" s="37"/>
-      <c r="G157" s="37"/>
-      <c r="H157" s="37"/>
-      <c r="I157" s="37"/>
-      <c r="J157" s="37"/>
-      <c r="K157" s="37"/>
-      <c r="L157" s="37"/>
-      <c r="M157" s="37"/>
-      <c r="N157" s="37"/>
-      <c r="O157" s="37"/>
-      <c r="P157" s="37"/>
-      <c r="Q157" s="37"/>
-      <c r="R157" s="37"/>
-      <c r="S157" s="37"/>
-      <c r="T157" s="37"/>
-      <c r="U157" s="37"/>
-      <c r="V157" s="37"/>
-      <c r="W157" s="37"/>
-      <c r="X157" s="37"/>
-      <c r="Y157" s="37"/>
-      <c r="Z157" s="38"/>
+      <c r="E157" s="14"/>
+      <c r="F157" s="14"/>
+      <c r="G157" s="14"/>
+      <c r="H157" s="14"/>
+      <c r="I157" s="14"/>
+      <c r="J157" s="14"/>
+      <c r="K157" s="14"/>
+      <c r="L157" s="14"/>
+      <c r="M157" s="14"/>
+      <c r="N157" s="14"/>
+      <c r="O157" s="14"/>
+      <c r="P157" s="14"/>
+      <c r="Q157" s="14"/>
+      <c r="R157" s="14"/>
+      <c r="S157" s="14"/>
+      <c r="T157" s="14"/>
+      <c r="U157" s="14"/>
+      <c r="V157" s="14"/>
+      <c r="W157" s="14"/>
+      <c r="X157" s="14"/>
+      <c r="Y157" s="14"/>
+      <c r="Z157" s="15"/>
     </row>
     <row r="158" spans="4:26" x14ac:dyDescent="0.3">
-      <c r="D158" s="36" t="s">
+      <c r="D158" s="13" t="s">
         <v>271</v>
       </c>
-      <c r="E158" s="37"/>
-      <c r="F158" s="37"/>
-      <c r="G158" s="37"/>
-      <c r="H158" s="37"/>
-      <c r="I158" s="37"/>
-      <c r="J158" s="37"/>
-      <c r="K158" s="37"/>
-      <c r="L158" s="37"/>
-      <c r="M158" s="37"/>
-      <c r="N158" s="37"/>
-      <c r="O158" s="37"/>
-      <c r="P158" s="37"/>
-      <c r="Q158" s="37"/>
-      <c r="R158" s="37"/>
-      <c r="S158" s="37"/>
-      <c r="T158" s="37"/>
-      <c r="U158" s="37"/>
-      <c r="V158" s="37"/>
-      <c r="W158" s="37"/>
-      <c r="X158" s="37"/>
-      <c r="Y158" s="37"/>
-      <c r="Z158" s="38"/>
+      <c r="E158" s="14"/>
+      <c r="F158" s="14"/>
+      <c r="G158" s="14"/>
+      <c r="H158" s="14"/>
+      <c r="I158" s="14"/>
+      <c r="J158" s="14"/>
+      <c r="K158" s="14"/>
+      <c r="L158" s="14"/>
+      <c r="M158" s="14"/>
+      <c r="N158" s="14"/>
+      <c r="O158" s="14"/>
+      <c r="P158" s="14"/>
+      <c r="Q158" s="14"/>
+      <c r="R158" s="14"/>
+      <c r="S158" s="14"/>
+      <c r="T158" s="14"/>
+      <c r="U158" s="14"/>
+      <c r="V158" s="14"/>
+      <c r="W158" s="14"/>
+      <c r="X158" s="14"/>
+      <c r="Y158" s="14"/>
+      <c r="Z158" s="15"/>
     </row>
     <row r="159" spans="4:26" x14ac:dyDescent="0.3">
-      <c r="D159" s="39" t="s">
+      <c r="D159" s="16" t="s">
         <v>272</v>
       </c>
-      <c r="E159" s="40"/>
-      <c r="F159" s="40"/>
-      <c r="G159" s="40"/>
-      <c r="H159" s="40"/>
-      <c r="I159" s="40"/>
-      <c r="J159" s="40"/>
-      <c r="K159" s="40"/>
-      <c r="L159" s="40"/>
-      <c r="M159" s="40"/>
-      <c r="N159" s="40"/>
-      <c r="O159" s="40"/>
-      <c r="P159" s="40"/>
-      <c r="Q159" s="40"/>
-      <c r="R159" s="40"/>
-      <c r="S159" s="40"/>
-      <c r="T159" s="40"/>
-      <c r="U159" s="40"/>
-      <c r="V159" s="40"/>
-      <c r="W159" s="40"/>
-      <c r="X159" s="40"/>
-      <c r="Y159" s="40"/>
-      <c r="Z159" s="41"/>
+      <c r="E159" s="17"/>
+      <c r="F159" s="17"/>
+      <c r="G159" s="17"/>
+      <c r="H159" s="17"/>
+      <c r="I159" s="17"/>
+      <c r="J159" s="17"/>
+      <c r="K159" s="17"/>
+      <c r="L159" s="17"/>
+      <c r="M159" s="17"/>
+      <c r="N159" s="17"/>
+      <c r="O159" s="17"/>
+      <c r="P159" s="17"/>
+      <c r="Q159" s="17"/>
+      <c r="R159" s="17"/>
+      <c r="S159" s="17"/>
+      <c r="T159" s="17"/>
+      <c r="U159" s="17"/>
+      <c r="V159" s="17"/>
+      <c r="W159" s="17"/>
+      <c r="X159" s="17"/>
+      <c r="Y159" s="17"/>
+      <c r="Z159" s="18"/>
     </row>
     <row r="173" spans="4:26" x14ac:dyDescent="0.3">
-      <c r="D173" s="33" t="s">
+      <c r="D173" s="10" t="s">
         <v>275</v>
       </c>
-      <c r="E173" s="34"/>
-      <c r="F173" s="34"/>
-      <c r="G173" s="34"/>
-      <c r="H173" s="34"/>
-      <c r="I173" s="34"/>
-      <c r="J173" s="34"/>
-      <c r="K173" s="34"/>
-      <c r="L173" s="34"/>
-      <c r="M173" s="34"/>
-      <c r="N173" s="34"/>
-      <c r="O173" s="34"/>
-      <c r="P173" s="34"/>
-      <c r="Q173" s="34"/>
-      <c r="R173" s="34"/>
-      <c r="S173" s="34"/>
-      <c r="T173" s="34"/>
-      <c r="U173" s="34"/>
-      <c r="V173" s="34"/>
-      <c r="W173" s="34"/>
-      <c r="X173" s="34"/>
-      <c r="Y173" s="34"/>
-      <c r="Z173" s="35"/>
+      <c r="E173" s="11"/>
+      <c r="F173" s="11"/>
+      <c r="G173" s="11"/>
+      <c r="H173" s="11"/>
+      <c r="I173" s="11"/>
+      <c r="J173" s="11"/>
+      <c r="K173" s="11"/>
+      <c r="L173" s="11"/>
+      <c r="M173" s="11"/>
+      <c r="N173" s="11"/>
+      <c r="O173" s="11"/>
+      <c r="P173" s="11"/>
+      <c r="Q173" s="11"/>
+      <c r="R173" s="11"/>
+      <c r="S173" s="11"/>
+      <c r="T173" s="11"/>
+      <c r="U173" s="11"/>
+      <c r="V173" s="11"/>
+      <c r="W173" s="11"/>
+      <c r="X173" s="11"/>
+      <c r="Y173" s="11"/>
+      <c r="Z173" s="12"/>
     </row>
     <row r="174" spans="4:26" x14ac:dyDescent="0.3">
-      <c r="D174" s="36" t="s">
+      <c r="D174" s="13" t="s">
         <v>276</v>
       </c>
-      <c r="E174" s="37"/>
-      <c r="F174" s="37"/>
-      <c r="G174" s="37"/>
-      <c r="H174" s="37"/>
-      <c r="I174" s="37"/>
-      <c r="J174" s="37"/>
-      <c r="K174" s="37"/>
-      <c r="L174" s="37"/>
-      <c r="M174" s="37"/>
-      <c r="N174" s="37"/>
-      <c r="O174" s="37"/>
-      <c r="P174" s="37"/>
-      <c r="Q174" s="37"/>
-      <c r="R174" s="37"/>
-      <c r="S174" s="37"/>
-      <c r="T174" s="37"/>
-      <c r="U174" s="37"/>
-      <c r="V174" s="37"/>
-      <c r="W174" s="37"/>
-      <c r="X174" s="37"/>
-      <c r="Y174" s="37"/>
-      <c r="Z174" s="38"/>
+      <c r="E174" s="14"/>
+      <c r="F174" s="14"/>
+      <c r="G174" s="14"/>
+      <c r="H174" s="14"/>
+      <c r="I174" s="14"/>
+      <c r="J174" s="14"/>
+      <c r="K174" s="14"/>
+      <c r="L174" s="14"/>
+      <c r="M174" s="14"/>
+      <c r="N174" s="14"/>
+      <c r="O174" s="14"/>
+      <c r="P174" s="14"/>
+      <c r="Q174" s="14"/>
+      <c r="R174" s="14"/>
+      <c r="S174" s="14"/>
+      <c r="T174" s="14"/>
+      <c r="U174" s="14"/>
+      <c r="V174" s="14"/>
+      <c r="W174" s="14"/>
+      <c r="X174" s="14"/>
+      <c r="Y174" s="14"/>
+      <c r="Z174" s="15"/>
     </row>
     <row r="175" spans="4:26" x14ac:dyDescent="0.3">
-      <c r="D175" s="36"/>
-      <c r="E175" s="37"/>
-      <c r="F175" s="37"/>
-      <c r="G175" s="37"/>
-      <c r="H175" s="37"/>
-      <c r="I175" s="37"/>
-      <c r="J175" s="37"/>
-      <c r="K175" s="37"/>
-      <c r="L175" s="37"/>
-      <c r="M175" s="37"/>
-      <c r="N175" s="37"/>
-      <c r="O175" s="37"/>
-      <c r="P175" s="37"/>
-      <c r="Q175" s="37"/>
-      <c r="R175" s="37"/>
-      <c r="S175" s="37"/>
-      <c r="T175" s="37"/>
-      <c r="U175" s="37"/>
-      <c r="V175" s="37"/>
-      <c r="W175" s="37"/>
-      <c r="X175" s="37"/>
-      <c r="Y175" s="37"/>
-      <c r="Z175" s="38"/>
+      <c r="D175" s="13"/>
+      <c r="E175" s="14"/>
+      <c r="F175" s="14"/>
+      <c r="G175" s="14"/>
+      <c r="H175" s="14"/>
+      <c r="I175" s="14"/>
+      <c r="J175" s="14"/>
+      <c r="K175" s="14"/>
+      <c r="L175" s="14"/>
+      <c r="M175" s="14"/>
+      <c r="N175" s="14"/>
+      <c r="O175" s="14"/>
+      <c r="P175" s="14"/>
+      <c r="Q175" s="14"/>
+      <c r="R175" s="14"/>
+      <c r="S175" s="14"/>
+      <c r="T175" s="14"/>
+      <c r="U175" s="14"/>
+      <c r="V175" s="14"/>
+      <c r="W175" s="14"/>
+      <c r="X175" s="14"/>
+      <c r="Y175" s="14"/>
+      <c r="Z175" s="15"/>
     </row>
     <row r="176" spans="4:26" x14ac:dyDescent="0.3">
-      <c r="D176" s="36" t="s">
+      <c r="D176" s="13" t="s">
         <v>277</v>
       </c>
-      <c r="E176" s="37"/>
-      <c r="F176" s="37"/>
-      <c r="G176" s="37"/>
-      <c r="H176" s="37"/>
-      <c r="I176" s="37"/>
-      <c r="J176" s="37"/>
-      <c r="K176" s="37"/>
-      <c r="L176" s="37"/>
-      <c r="M176" s="37"/>
-      <c r="N176" s="37"/>
-      <c r="O176" s="37"/>
-      <c r="P176" s="37"/>
-      <c r="Q176" s="37"/>
-      <c r="R176" s="37"/>
-      <c r="S176" s="37"/>
-      <c r="T176" s="37"/>
-      <c r="U176" s="37"/>
-      <c r="V176" s="37"/>
-      <c r="W176" s="37"/>
-      <c r="X176" s="37"/>
-      <c r="Y176" s="37"/>
-      <c r="Z176" s="38"/>
+      <c r="E176" s="14"/>
+      <c r="F176" s="14"/>
+      <c r="G176" s="14"/>
+      <c r="H176" s="14"/>
+      <c r="I176" s="14"/>
+      <c r="J176" s="14"/>
+      <c r="K176" s="14"/>
+      <c r="L176" s="14"/>
+      <c r="M176" s="14"/>
+      <c r="N176" s="14"/>
+      <c r="O176" s="14"/>
+      <c r="P176" s="14"/>
+      <c r="Q176" s="14"/>
+      <c r="R176" s="14"/>
+      <c r="S176" s="14"/>
+      <c r="T176" s="14"/>
+      <c r="U176" s="14"/>
+      <c r="V176" s="14"/>
+      <c r="W176" s="14"/>
+      <c r="X176" s="14"/>
+      <c r="Y176" s="14"/>
+      <c r="Z176" s="15"/>
     </row>
     <row r="177" spans="4:26" x14ac:dyDescent="0.3">
-      <c r="D177" s="39" t="s">
+      <c r="D177" s="16" t="s">
         <v>278</v>
       </c>
-      <c r="E177" s="40"/>
-      <c r="F177" s="40"/>
-      <c r="G177" s="40"/>
-      <c r="H177" s="40"/>
-      <c r="I177" s="40"/>
-      <c r="J177" s="40"/>
-      <c r="K177" s="40"/>
-      <c r="L177" s="40"/>
-      <c r="M177" s="40"/>
-      <c r="N177" s="40"/>
-      <c r="O177" s="40"/>
-      <c r="P177" s="40"/>
-      <c r="Q177" s="40"/>
-      <c r="R177" s="40"/>
-      <c r="S177" s="40"/>
-      <c r="T177" s="40"/>
-      <c r="U177" s="40"/>
-      <c r="V177" s="40"/>
-      <c r="W177" s="40"/>
-      <c r="X177" s="40"/>
-      <c r="Y177" s="40"/>
-      <c r="Z177" s="41"/>
+      <c r="E177" s="17"/>
+      <c r="F177" s="17"/>
+      <c r="G177" s="17"/>
+      <c r="H177" s="17"/>
+      <c r="I177" s="17"/>
+      <c r="J177" s="17"/>
+      <c r="K177" s="17"/>
+      <c r="L177" s="17"/>
+      <c r="M177" s="17"/>
+      <c r="N177" s="17"/>
+      <c r="O177" s="17"/>
+      <c r="P177" s="17"/>
+      <c r="Q177" s="17"/>
+      <c r="R177" s="17"/>
+      <c r="S177" s="17"/>
+      <c r="T177" s="17"/>
+      <c r="U177" s="17"/>
+      <c r="V177" s="17"/>
+      <c r="W177" s="17"/>
+      <c r="X177" s="17"/>
+      <c r="Y177" s="17"/>
+      <c r="Z177" s="18"/>
     </row>
     <row r="191" spans="4:26" x14ac:dyDescent="0.3">
-      <c r="D191" s="33" t="s">
+      <c r="D191" s="10" t="s">
         <v>273</v>
       </c>
-      <c r="E191" s="34"/>
-      <c r="F191" s="34"/>
-      <c r="G191" s="34"/>
-      <c r="H191" s="34"/>
-      <c r="I191" s="34"/>
-      <c r="J191" s="34"/>
-      <c r="K191" s="34"/>
-      <c r="L191" s="34"/>
-      <c r="M191" s="34"/>
-      <c r="N191" s="34"/>
-      <c r="O191" s="34"/>
-      <c r="P191" s="34"/>
-      <c r="Q191" s="34"/>
-      <c r="R191" s="34"/>
-      <c r="S191" s="34"/>
-      <c r="T191" s="34"/>
-      <c r="U191" s="34"/>
-      <c r="V191" s="34"/>
-      <c r="W191" s="34"/>
-      <c r="X191" s="34"/>
-      <c r="Y191" s="34"/>
-      <c r="Z191" s="35"/>
+      <c r="E191" s="11"/>
+      <c r="F191" s="11"/>
+      <c r="G191" s="11"/>
+      <c r="H191" s="11"/>
+      <c r="I191" s="11"/>
+      <c r="J191" s="11"/>
+      <c r="K191" s="11"/>
+      <c r="L191" s="11"/>
+      <c r="M191" s="11"/>
+      <c r="N191" s="11"/>
+      <c r="O191" s="11"/>
+      <c r="P191" s="11"/>
+      <c r="Q191" s="11"/>
+      <c r="R191" s="11"/>
+      <c r="S191" s="11"/>
+      <c r="T191" s="11"/>
+      <c r="U191" s="11"/>
+      <c r="V191" s="11"/>
+      <c r="W191" s="11"/>
+      <c r="X191" s="11"/>
+      <c r="Y191" s="11"/>
+      <c r="Z191" s="12"/>
     </row>
     <row r="192" spans="4:26" x14ac:dyDescent="0.3">
-      <c r="D192" s="39" t="s">
+      <c r="D192" s="16" t="s">
         <v>274</v>
       </c>
-      <c r="E192" s="40"/>
-      <c r="F192" s="40"/>
-      <c r="G192" s="40"/>
-      <c r="H192" s="40"/>
-      <c r="I192" s="40"/>
-      <c r="J192" s="40"/>
-      <c r="K192" s="40"/>
-      <c r="L192" s="40"/>
-      <c r="M192" s="40"/>
-      <c r="N192" s="40"/>
-      <c r="O192" s="40"/>
-      <c r="P192" s="40"/>
-      <c r="Q192" s="40"/>
-      <c r="R192" s="40"/>
-      <c r="S192" s="40"/>
-      <c r="T192" s="40"/>
-      <c r="U192" s="40"/>
-      <c r="V192" s="40"/>
-      <c r="W192" s="40"/>
-      <c r="X192" s="40"/>
-      <c r="Y192" s="40"/>
-      <c r="Z192" s="41"/>
+      <c r="E192" s="17"/>
+      <c r="F192" s="17"/>
+      <c r="G192" s="17"/>
+      <c r="H192" s="17"/>
+      <c r="I192" s="17"/>
+      <c r="J192" s="17"/>
+      <c r="K192" s="17"/>
+      <c r="L192" s="17"/>
+      <c r="M192" s="17"/>
+      <c r="N192" s="17"/>
+      <c r="O192" s="17"/>
+      <c r="P192" s="17"/>
+      <c r="Q192" s="17"/>
+      <c r="R192" s="17"/>
+      <c r="S192" s="17"/>
+      <c r="T192" s="17"/>
+      <c r="U192" s="17"/>
+      <c r="V192" s="17"/>
+      <c r="W192" s="17"/>
+      <c r="X192" s="17"/>
+      <c r="Y192" s="17"/>
+      <c r="Z192" s="18"/>
     </row>
     <row r="205" spans="4:26" x14ac:dyDescent="0.3">
-      <c r="D205" s="33" t="s">
+      <c r="D205" s="10" t="s">
         <v>279</v>
       </c>
-      <c r="E205" s="34"/>
-      <c r="F205" s="34"/>
-      <c r="G205" s="34"/>
-      <c r="H205" s="34"/>
-      <c r="I205" s="34"/>
-      <c r="J205" s="34"/>
-      <c r="K205" s="34"/>
-      <c r="L205" s="34"/>
-      <c r="M205" s="34"/>
-      <c r="N205" s="34"/>
-      <c r="O205" s="34"/>
-      <c r="P205" s="34"/>
-      <c r="Q205" s="34"/>
-      <c r="R205" s="34"/>
-      <c r="S205" s="34"/>
-      <c r="T205" s="34"/>
-      <c r="U205" s="34"/>
-      <c r="V205" s="34"/>
-      <c r="W205" s="34"/>
-      <c r="X205" s="34"/>
-      <c r="Y205" s="34"/>
-      <c r="Z205" s="35"/>
+      <c r="E205" s="11"/>
+      <c r="F205" s="11"/>
+      <c r="G205" s="11"/>
+      <c r="H205" s="11"/>
+      <c r="I205" s="11"/>
+      <c r="J205" s="11"/>
+      <c r="K205" s="11"/>
+      <c r="L205" s="11"/>
+      <c r="M205" s="11"/>
+      <c r="N205" s="11"/>
+      <c r="O205" s="11"/>
+      <c r="P205" s="11"/>
+      <c r="Q205" s="11"/>
+      <c r="R205" s="11"/>
+      <c r="S205" s="11"/>
+      <c r="T205" s="11"/>
+      <c r="U205" s="11"/>
+      <c r="V205" s="11"/>
+      <c r="W205" s="11"/>
+      <c r="X205" s="11"/>
+      <c r="Y205" s="11"/>
+      <c r="Z205" s="12"/>
     </row>
     <row r="206" spans="4:26" x14ac:dyDescent="0.3">
-      <c r="D206" s="39" t="s">
+      <c r="D206" s="16" t="s">
         <v>280</v>
       </c>
-      <c r="E206" s="40"/>
-      <c r="F206" s="40"/>
-      <c r="G206" s="40"/>
-      <c r="H206" s="40"/>
-      <c r="I206" s="40"/>
-      <c r="J206" s="40"/>
-      <c r="K206" s="40"/>
-      <c r="L206" s="40"/>
-      <c r="M206" s="40"/>
-      <c r="N206" s="40"/>
-      <c r="O206" s="40"/>
-      <c r="P206" s="40"/>
-      <c r="Q206" s="40"/>
-      <c r="R206" s="40"/>
-      <c r="S206" s="40"/>
-      <c r="T206" s="40"/>
-      <c r="U206" s="40"/>
-      <c r="V206" s="40"/>
-      <c r="W206" s="40"/>
-      <c r="X206" s="40"/>
-      <c r="Y206" s="40"/>
-      <c r="Z206" s="41"/>
+      <c r="E206" s="17"/>
+      <c r="F206" s="17"/>
+      <c r="G206" s="17"/>
+      <c r="H206" s="17"/>
+      <c r="I206" s="17"/>
+      <c r="J206" s="17"/>
+      <c r="K206" s="17"/>
+      <c r="L206" s="17"/>
+      <c r="M206" s="17"/>
+      <c r="N206" s="17"/>
+      <c r="O206" s="17"/>
+      <c r="P206" s="17"/>
+      <c r="Q206" s="17"/>
+      <c r="R206" s="17"/>
+      <c r="S206" s="17"/>
+      <c r="T206" s="17"/>
+      <c r="U206" s="17"/>
+      <c r="V206" s="17"/>
+      <c r="W206" s="17"/>
+      <c r="X206" s="17"/>
+      <c r="Y206" s="17"/>
+      <c r="Z206" s="18"/>
     </row>
     <row r="236" spans="4:26" x14ac:dyDescent="0.3">
-      <c r="D236" s="33" t="s">
+      <c r="D236" s="10" t="s">
         <v>281</v>
       </c>
-      <c r="E236" s="34"/>
-      <c r="F236" s="34"/>
-      <c r="G236" s="34"/>
-      <c r="H236" s="34"/>
-      <c r="I236" s="34"/>
-      <c r="J236" s="34"/>
-      <c r="K236" s="34"/>
-      <c r="L236" s="34"/>
-      <c r="M236" s="34"/>
-      <c r="N236" s="34"/>
-      <c r="O236" s="34"/>
-      <c r="P236" s="34"/>
-      <c r="Q236" s="34"/>
-      <c r="R236" s="34"/>
-      <c r="S236" s="34"/>
-      <c r="T236" s="34"/>
-      <c r="U236" s="34"/>
-      <c r="V236" s="34"/>
-      <c r="W236" s="34"/>
-      <c r="X236" s="34"/>
-      <c r="Y236" s="34"/>
-      <c r="Z236" s="35"/>
+      <c r="E236" s="11"/>
+      <c r="F236" s="11"/>
+      <c r="G236" s="11"/>
+      <c r="H236" s="11"/>
+      <c r="I236" s="11"/>
+      <c r="J236" s="11"/>
+      <c r="K236" s="11"/>
+      <c r="L236" s="11"/>
+      <c r="M236" s="11"/>
+      <c r="N236" s="11"/>
+      <c r="O236" s="11"/>
+      <c r="P236" s="11"/>
+      <c r="Q236" s="11"/>
+      <c r="R236" s="11"/>
+      <c r="S236" s="11"/>
+      <c r="T236" s="11"/>
+      <c r="U236" s="11"/>
+      <c r="V236" s="11"/>
+      <c r="W236" s="11"/>
+      <c r="X236" s="11"/>
+      <c r="Y236" s="11"/>
+      <c r="Z236" s="12"/>
     </row>
     <row r="237" spans="4:26" x14ac:dyDescent="0.3">
-      <c r="D237" s="39" t="s">
+      <c r="D237" s="16" t="s">
         <v>282</v>
       </c>
-      <c r="E237" s="40"/>
-      <c r="F237" s="40"/>
-      <c r="G237" s="40"/>
-      <c r="H237" s="40"/>
-      <c r="I237" s="40"/>
-      <c r="J237" s="40"/>
-      <c r="K237" s="40"/>
-      <c r="L237" s="40"/>
-      <c r="M237" s="40"/>
-      <c r="N237" s="40"/>
-      <c r="O237" s="40"/>
-      <c r="P237" s="40"/>
-      <c r="Q237" s="40"/>
-      <c r="R237" s="40"/>
-      <c r="S237" s="40"/>
-      <c r="T237" s="40"/>
-      <c r="U237" s="40"/>
-      <c r="V237" s="40"/>
-      <c r="W237" s="40"/>
-      <c r="X237" s="40"/>
-      <c r="Y237" s="40"/>
-      <c r="Z237" s="41"/>
+      <c r="E237" s="17"/>
+      <c r="F237" s="17"/>
+      <c r="G237" s="17"/>
+      <c r="H237" s="17"/>
+      <c r="I237" s="17"/>
+      <c r="J237" s="17"/>
+      <c r="K237" s="17"/>
+      <c r="L237" s="17"/>
+      <c r="M237" s="17"/>
+      <c r="N237" s="17"/>
+      <c r="O237" s="17"/>
+      <c r="P237" s="17"/>
+      <c r="Q237" s="17"/>
+      <c r="R237" s="17"/>
+      <c r="S237" s="17"/>
+      <c r="T237" s="17"/>
+      <c r="U237" s="17"/>
+      <c r="V237" s="17"/>
+      <c r="W237" s="17"/>
+      <c r="X237" s="17"/>
+      <c r="Y237" s="17"/>
+      <c r="Z237" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -6962,96 +9034,96 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="27" t="s">
         <v>203</v>
       </c>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
-      <c r="K2" s="10"/>
-      <c r="L2" s="10"/>
-      <c r="M2" s="10"/>
-      <c r="N2" s="10"/>
-      <c r="O2" s="10"/>
-      <c r="P2" s="10"/>
-      <c r="Q2" s="10"/>
-      <c r="R2" s="10"/>
-      <c r="S2" s="10"/>
-      <c r="T2" s="10"/>
-      <c r="U2" s="10"/>
-      <c r="V2" s="10"/>
-      <c r="W2" s="10"/>
-      <c r="X2" s="10"/>
-      <c r="Y2" s="10"/>
-      <c r="Z2" s="11"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
+      <c r="I2" s="28"/>
+      <c r="J2" s="28"/>
+      <c r="K2" s="28"/>
+      <c r="L2" s="28"/>
+      <c r="M2" s="28"/>
+      <c r="N2" s="28"/>
+      <c r="O2" s="28"/>
+      <c r="P2" s="28"/>
+      <c r="Q2" s="28"/>
+      <c r="R2" s="28"/>
+      <c r="S2" s="28"/>
+      <c r="T2" s="28"/>
+      <c r="U2" s="28"/>
+      <c r="V2" s="28"/>
+      <c r="W2" s="28"/>
+      <c r="X2" s="28"/>
+      <c r="Y2" s="28"/>
+      <c r="Z2" s="29"/>
     </row>
     <row r="3" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B3" s="12"/>
-      <c r="C3" s="13"/>
-      <c r="D3" s="13"/>
-      <c r="E3" s="13"/>
-      <c r="F3" s="13"/>
-      <c r="G3" s="13"/>
-      <c r="H3" s="13"/>
-      <c r="I3" s="13"/>
-      <c r="J3" s="13"/>
-      <c r="K3" s="13"/>
-      <c r="L3" s="13"/>
-      <c r="M3" s="13"/>
-      <c r="N3" s="13"/>
-      <c r="O3" s="13"/>
-      <c r="P3" s="13"/>
-      <c r="Q3" s="13"/>
-      <c r="R3" s="13"/>
-      <c r="S3" s="13"/>
-      <c r="T3" s="13"/>
-      <c r="U3" s="13"/>
-      <c r="V3" s="13"/>
-      <c r="W3" s="13"/>
-      <c r="X3" s="13"/>
-      <c r="Y3" s="13"/>
-      <c r="Z3" s="14"/>
+      <c r="B3" s="36"/>
+      <c r="C3" s="37"/>
+      <c r="D3" s="37"/>
+      <c r="E3" s="37"/>
+      <c r="F3" s="37"/>
+      <c r="G3" s="37"/>
+      <c r="H3" s="37"/>
+      <c r="I3" s="37"/>
+      <c r="J3" s="37"/>
+      <c r="K3" s="37"/>
+      <c r="L3" s="37"/>
+      <c r="M3" s="37"/>
+      <c r="N3" s="37"/>
+      <c r="O3" s="37"/>
+      <c r="P3" s="37"/>
+      <c r="Q3" s="37"/>
+      <c r="R3" s="37"/>
+      <c r="S3" s="37"/>
+      <c r="T3" s="37"/>
+      <c r="U3" s="37"/>
+      <c r="V3" s="37"/>
+      <c r="W3" s="37"/>
+      <c r="X3" s="37"/>
+      <c r="Y3" s="37"/>
+      <c r="Z3" s="38"/>
     </row>
     <row r="4" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B4" s="15"/>
-      <c r="C4" s="16"/>
-      <c r="D4" s="16"/>
-      <c r="E4" s="16"/>
-      <c r="F4" s="16"/>
-      <c r="G4" s="16"/>
-      <c r="H4" s="16"/>
-      <c r="I4" s="16"/>
-      <c r="J4" s="16"/>
-      <c r="K4" s="16"/>
-      <c r="L4" s="16"/>
-      <c r="M4" s="16"/>
-      <c r="N4" s="16"/>
-      <c r="O4" s="16"/>
-      <c r="P4" s="16"/>
-      <c r="Q4" s="16"/>
-      <c r="R4" s="16"/>
-      <c r="S4" s="16"/>
-      <c r="T4" s="16"/>
-      <c r="U4" s="16"/>
-      <c r="V4" s="16"/>
-      <c r="W4" s="16"/>
-      <c r="X4" s="16"/>
-      <c r="Y4" s="16"/>
-      <c r="Z4" s="17"/>
+      <c r="B4" s="30"/>
+      <c r="C4" s="31"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
+      <c r="H4" s="31"/>
+      <c r="I4" s="31"/>
+      <c r="J4" s="31"/>
+      <c r="K4" s="31"/>
+      <c r="L4" s="31"/>
+      <c r="M4" s="31"/>
+      <c r="N4" s="31"/>
+      <c r="O4" s="31"/>
+      <c r="P4" s="31"/>
+      <c r="Q4" s="31"/>
+      <c r="R4" s="31"/>
+      <c r="S4" s="31"/>
+      <c r="T4" s="31"/>
+      <c r="U4" s="31"/>
+      <c r="V4" s="31"/>
+      <c r="W4" s="31"/>
+      <c r="X4" s="31"/>
+      <c r="Y4" s="31"/>
+      <c r="Z4" s="32"/>
     </row>
     <row r="6" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="V6" s="18" t="s">
+      <c r="V6" s="33" t="s">
         <v>202</v>
       </c>
-      <c r="W6" s="19"/>
-      <c r="X6" s="19"/>
-      <c r="Y6" s="19"/>
-      <c r="Z6" s="20"/>
+      <c r="W6" s="34"/>
+      <c r="X6" s="34"/>
+      <c r="Y6" s="34"/>
+      <c r="Z6" s="35"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -7061,4 +9133,2126 @@
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A2:AA197"/>
+  <sheetFormatPr defaultColWidth="2.875" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="27" width="2.875" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:26" x14ac:dyDescent="0.3">
+      <c r="B2" s="27" t="s">
+        <v>283</v>
+      </c>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
+      <c r="I2" s="28"/>
+      <c r="J2" s="28"/>
+      <c r="K2" s="28"/>
+      <c r="L2" s="28"/>
+      <c r="M2" s="28"/>
+      <c r="N2" s="28"/>
+      <c r="O2" s="28"/>
+      <c r="P2" s="28"/>
+      <c r="Q2" s="28"/>
+      <c r="R2" s="28"/>
+      <c r="S2" s="28"/>
+      <c r="T2" s="28"/>
+      <c r="U2" s="28"/>
+      <c r="V2" s="28"/>
+      <c r="W2" s="28"/>
+      <c r="X2" s="28"/>
+      <c r="Y2" s="28"/>
+      <c r="Z2" s="29"/>
+    </row>
+    <row r="3" spans="2:26" x14ac:dyDescent="0.3">
+      <c r="B3" s="36"/>
+      <c r="C3" s="37"/>
+      <c r="D3" s="37"/>
+      <c r="E3" s="37"/>
+      <c r="F3" s="37"/>
+      <c r="G3" s="37"/>
+      <c r="H3" s="37"/>
+      <c r="I3" s="37"/>
+      <c r="J3" s="37"/>
+      <c r="K3" s="37"/>
+      <c r="L3" s="37"/>
+      <c r="M3" s="37"/>
+      <c r="N3" s="37"/>
+      <c r="O3" s="37"/>
+      <c r="P3" s="37"/>
+      <c r="Q3" s="37"/>
+      <c r="R3" s="37"/>
+      <c r="S3" s="37"/>
+      <c r="T3" s="37"/>
+      <c r="U3" s="37"/>
+      <c r="V3" s="37"/>
+      <c r="W3" s="37"/>
+      <c r="X3" s="37"/>
+      <c r="Y3" s="37"/>
+      <c r="Z3" s="38"/>
+    </row>
+    <row r="4" spans="2:26" x14ac:dyDescent="0.3">
+      <c r="B4" s="30"/>
+      <c r="C4" s="31"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
+      <c r="H4" s="31"/>
+      <c r="I4" s="31"/>
+      <c r="J4" s="31"/>
+      <c r="K4" s="31"/>
+      <c r="L4" s="31"/>
+      <c r="M4" s="31"/>
+      <c r="N4" s="31"/>
+      <c r="O4" s="31"/>
+      <c r="P4" s="31"/>
+      <c r="Q4" s="31"/>
+      <c r="R4" s="31"/>
+      <c r="S4" s="31"/>
+      <c r="T4" s="31"/>
+      <c r="U4" s="31"/>
+      <c r="V4" s="31"/>
+      <c r="W4" s="31"/>
+      <c r="X4" s="31"/>
+      <c r="Y4" s="31"/>
+      <c r="Z4" s="32"/>
+    </row>
+    <row r="6" spans="2:26" x14ac:dyDescent="0.3">
+      <c r="V6" s="33" t="s">
+        <v>202</v>
+      </c>
+      <c r="W6" s="34"/>
+      <c r="X6" s="34"/>
+      <c r="Y6" s="34"/>
+      <c r="Z6" s="35"/>
+    </row>
+    <row r="8" spans="2:26" x14ac:dyDescent="0.3">
+      <c r="C8" s="2" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="10" spans="2:26" x14ac:dyDescent="0.3">
+      <c r="D10" s="2">
+        <v>1</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="11" spans="2:26" x14ac:dyDescent="0.3">
+      <c r="D11" s="2">
+        <v>2</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="12" spans="2:26" x14ac:dyDescent="0.3">
+      <c r="D12" s="2">
+        <v>3</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="13" spans="2:26" x14ac:dyDescent="0.3">
+      <c r="E13" s="23" t="s">
+        <v>335</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="14" spans="2:26" x14ac:dyDescent="0.3">
+      <c r="D14" s="2">
+        <v>4</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="16" spans="2:26" x14ac:dyDescent="0.3">
+      <c r="C16" s="27" t="s">
+        <v>206</v>
+      </c>
+      <c r="D16" s="28"/>
+      <c r="E16" s="28"/>
+      <c r="F16" s="28"/>
+      <c r="G16" s="28"/>
+      <c r="H16" s="28"/>
+      <c r="I16" s="28"/>
+      <c r="J16" s="28"/>
+      <c r="K16" s="28"/>
+      <c r="L16" s="28"/>
+      <c r="M16" s="28"/>
+      <c r="N16" s="28"/>
+      <c r="O16" s="28"/>
+      <c r="P16" s="28"/>
+      <c r="Q16" s="28"/>
+      <c r="R16" s="28"/>
+      <c r="S16" s="28"/>
+      <c r="T16" s="28"/>
+      <c r="U16" s="28"/>
+      <c r="V16" s="28"/>
+      <c r="W16" s="28"/>
+      <c r="X16" s="28"/>
+      <c r="Y16" s="28"/>
+      <c r="Z16" s="29"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="C17" s="30"/>
+      <c r="D17" s="31"/>
+      <c r="E17" s="31"/>
+      <c r="F17" s="31"/>
+      <c r="G17" s="31"/>
+      <c r="H17" s="31"/>
+      <c r="I17" s="31"/>
+      <c r="J17" s="31"/>
+      <c r="K17" s="31"/>
+      <c r="L17" s="31"/>
+      <c r="M17" s="31"/>
+      <c r="N17" s="31"/>
+      <c r="O17" s="31"/>
+      <c r="P17" s="31"/>
+      <c r="Q17" s="31"/>
+      <c r="R17" s="31"/>
+      <c r="S17" s="31"/>
+      <c r="T17" s="31"/>
+      <c r="U17" s="31"/>
+      <c r="V17" s="31"/>
+      <c r="W17" s="31"/>
+      <c r="X17" s="31"/>
+      <c r="Y17" s="31"/>
+      <c r="Z17" s="32"/>
+    </row>
+    <row r="19" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="C19" s="2">
+        <v>1</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="D20" s="2" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="21" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="C21" s="2">
+        <v>2</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="22" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="D22" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="C23" s="2">
+        <v>3</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="24" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="D24" s="2" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="25" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="C25" s="2">
+        <v>4</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="D26" s="2" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="28" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="C28" s="27" t="s">
+        <v>292</v>
+      </c>
+      <c r="D28" s="28"/>
+      <c r="E28" s="28"/>
+      <c r="F28" s="28"/>
+      <c r="G28" s="28"/>
+      <c r="H28" s="28"/>
+      <c r="I28" s="28"/>
+      <c r="J28" s="28"/>
+      <c r="K28" s="28"/>
+      <c r="L28" s="28"/>
+      <c r="M28" s="28"/>
+      <c r="N28" s="28"/>
+      <c r="O28" s="28"/>
+      <c r="P28" s="28"/>
+      <c r="Q28" s="28"/>
+      <c r="R28" s="28"/>
+      <c r="S28" s="28"/>
+      <c r="T28" s="28"/>
+      <c r="U28" s="28"/>
+      <c r="V28" s="28"/>
+      <c r="W28" s="28"/>
+      <c r="X28" s="28"/>
+      <c r="Y28" s="28"/>
+      <c r="Z28" s="29"/>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="C29" s="30"/>
+      <c r="D29" s="31"/>
+      <c r="E29" s="31"/>
+      <c r="F29" s="31"/>
+      <c r="G29" s="31"/>
+      <c r="H29" s="31"/>
+      <c r="I29" s="31"/>
+      <c r="J29" s="31"/>
+      <c r="K29" s="31"/>
+      <c r="L29" s="31"/>
+      <c r="M29" s="31"/>
+      <c r="N29" s="31"/>
+      <c r="O29" s="31"/>
+      <c r="P29" s="31"/>
+      <c r="Q29" s="31"/>
+      <c r="R29" s="31"/>
+      <c r="S29" s="31"/>
+      <c r="T29" s="31"/>
+      <c r="U29" s="31"/>
+      <c r="V29" s="31"/>
+      <c r="W29" s="31"/>
+      <c r="X29" s="31"/>
+      <c r="Y29" s="31"/>
+      <c r="Z29" s="32"/>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="C31" s="25">
+        <v>1</v>
+      </c>
+      <c r="D31" s="25" t="s">
+        <v>293</v>
+      </c>
+      <c r="E31" s="25"/>
+      <c r="F31" s="25"/>
+      <c r="G31" s="25"/>
+      <c r="H31" s="25"/>
+      <c r="I31" s="25"/>
+      <c r="J31" s="49" t="s">
+        <v>294</v>
+      </c>
+      <c r="K31" s="50"/>
+      <c r="L31" s="50"/>
+      <c r="M31" s="50"/>
+      <c r="N31" s="50"/>
+      <c r="O31" s="50"/>
+      <c r="P31" s="50"/>
+      <c r="Q31" s="50"/>
+      <c r="R31" s="50"/>
+      <c r="S31" s="50"/>
+      <c r="T31" s="50"/>
+      <c r="U31" s="50"/>
+      <c r="V31" s="50"/>
+      <c r="W31" s="50"/>
+      <c r="X31" s="50"/>
+      <c r="Y31" s="50"/>
+      <c r="Z31" s="51"/>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="C32" s="25"/>
+      <c r="D32" s="25"/>
+      <c r="E32" s="25"/>
+      <c r="F32" s="25"/>
+      <c r="G32" s="25"/>
+      <c r="H32" s="25"/>
+      <c r="I32" s="25"/>
+      <c r="J32" s="52" t="s">
+        <v>295</v>
+      </c>
+      <c r="K32" s="53"/>
+      <c r="L32" s="53"/>
+      <c r="M32" s="53"/>
+      <c r="N32" s="53"/>
+      <c r="O32" s="53"/>
+      <c r="P32" s="53"/>
+      <c r="Q32" s="53"/>
+      <c r="R32" s="53"/>
+      <c r="S32" s="53"/>
+      <c r="T32" s="53"/>
+      <c r="U32" s="53"/>
+      <c r="V32" s="53"/>
+      <c r="W32" s="53"/>
+      <c r="X32" s="53"/>
+      <c r="Y32" s="53"/>
+      <c r="Z32" s="54"/>
+    </row>
+    <row r="33" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="C33" s="25">
+        <v>2</v>
+      </c>
+      <c r="D33" s="25" t="s">
+        <v>296</v>
+      </c>
+      <c r="E33" s="25"/>
+      <c r="F33" s="25"/>
+      <c r="G33" s="25"/>
+      <c r="H33" s="25"/>
+      <c r="I33" s="25"/>
+      <c r="J33" s="49" t="s">
+        <v>298</v>
+      </c>
+      <c r="K33" s="50"/>
+      <c r="L33" s="50"/>
+      <c r="M33" s="50"/>
+      <c r="N33" s="50"/>
+      <c r="O33" s="50"/>
+      <c r="P33" s="50"/>
+      <c r="Q33" s="50"/>
+      <c r="R33" s="50"/>
+      <c r="S33" s="50"/>
+      <c r="T33" s="50"/>
+      <c r="U33" s="50"/>
+      <c r="V33" s="50"/>
+      <c r="W33" s="50"/>
+      <c r="X33" s="50"/>
+      <c r="Y33" s="50"/>
+      <c r="Z33" s="51"/>
+    </row>
+    <row r="34" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="C34" s="25"/>
+      <c r="D34" s="25"/>
+      <c r="E34" s="25"/>
+      <c r="F34" s="25"/>
+      <c r="G34" s="25"/>
+      <c r="H34" s="25"/>
+      <c r="I34" s="25"/>
+      <c r="J34" s="52" t="s">
+        <v>299</v>
+      </c>
+      <c r="K34" s="53"/>
+      <c r="L34" s="53"/>
+      <c r="M34" s="53"/>
+      <c r="N34" s="53"/>
+      <c r="O34" s="53"/>
+      <c r="P34" s="53"/>
+      <c r="Q34" s="53"/>
+      <c r="R34" s="53"/>
+      <c r="S34" s="53"/>
+      <c r="T34" s="53"/>
+      <c r="U34" s="53"/>
+      <c r="V34" s="53"/>
+      <c r="W34" s="53"/>
+      <c r="X34" s="53"/>
+      <c r="Y34" s="53"/>
+      <c r="Z34" s="54"/>
+    </row>
+    <row r="35" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="C35" s="25">
+        <v>3</v>
+      </c>
+      <c r="D35" s="25" t="s">
+        <v>297</v>
+      </c>
+      <c r="E35" s="25"/>
+      <c r="F35" s="25"/>
+      <c r="G35" s="25"/>
+      <c r="H35" s="25"/>
+      <c r="I35" s="25"/>
+      <c r="J35" s="49" t="s">
+        <v>300</v>
+      </c>
+      <c r="K35" s="50"/>
+      <c r="L35" s="50"/>
+      <c r="M35" s="50"/>
+      <c r="N35" s="50"/>
+      <c r="O35" s="50"/>
+      <c r="P35" s="50"/>
+      <c r="Q35" s="50"/>
+      <c r="R35" s="50"/>
+      <c r="S35" s="50"/>
+      <c r="T35" s="50"/>
+      <c r="U35" s="50"/>
+      <c r="V35" s="50"/>
+      <c r="W35" s="50"/>
+      <c r="X35" s="50"/>
+      <c r="Y35" s="50"/>
+      <c r="Z35" s="51"/>
+    </row>
+    <row r="36" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="C36" s="25"/>
+      <c r="D36" s="25"/>
+      <c r="E36" s="25"/>
+      <c r="F36" s="25"/>
+      <c r="G36" s="25"/>
+      <c r="H36" s="25"/>
+      <c r="I36" s="25"/>
+      <c r="J36" s="52" t="s">
+        <v>301</v>
+      </c>
+      <c r="K36" s="53"/>
+      <c r="L36" s="53"/>
+      <c r="M36" s="53"/>
+      <c r="N36" s="53"/>
+      <c r="O36" s="53"/>
+      <c r="P36" s="53"/>
+      <c r="Q36" s="53"/>
+      <c r="R36" s="53"/>
+      <c r="S36" s="53"/>
+      <c r="T36" s="53"/>
+      <c r="U36" s="53"/>
+      <c r="V36" s="53"/>
+      <c r="W36" s="53"/>
+      <c r="X36" s="53"/>
+      <c r="Y36" s="53"/>
+      <c r="Z36" s="54"/>
+    </row>
+    <row r="37" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="C37" s="8">
+        <v>4</v>
+      </c>
+      <c r="D37" s="25" t="s">
+        <v>302</v>
+      </c>
+      <c r="E37" s="25"/>
+      <c r="F37" s="25"/>
+      <c r="G37" s="25"/>
+      <c r="H37" s="25"/>
+      <c r="I37" s="25"/>
+      <c r="J37" s="64" t="s">
+        <v>303</v>
+      </c>
+      <c r="K37" s="65"/>
+      <c r="L37" s="65"/>
+      <c r="M37" s="65"/>
+      <c r="N37" s="65"/>
+      <c r="O37" s="65"/>
+      <c r="P37" s="65"/>
+      <c r="Q37" s="65"/>
+      <c r="R37" s="65"/>
+      <c r="S37" s="65"/>
+      <c r="T37" s="65"/>
+      <c r="U37" s="65"/>
+      <c r="V37" s="65"/>
+      <c r="W37" s="65"/>
+      <c r="X37" s="65"/>
+      <c r="Y37" s="65"/>
+      <c r="Z37" s="66"/>
+    </row>
+    <row r="38" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="C38" s="8">
+        <v>5</v>
+      </c>
+      <c r="D38" s="64" t="s">
+        <v>304</v>
+      </c>
+      <c r="E38" s="65"/>
+      <c r="F38" s="65"/>
+      <c r="G38" s="65"/>
+      <c r="H38" s="65"/>
+      <c r="I38" s="65"/>
+      <c r="J38" s="65"/>
+      <c r="K38" s="65"/>
+      <c r="L38" s="65"/>
+      <c r="M38" s="65"/>
+      <c r="N38" s="65"/>
+      <c r="O38" s="65"/>
+      <c r="P38" s="65"/>
+      <c r="Q38" s="65"/>
+      <c r="R38" s="65"/>
+      <c r="S38" s="65"/>
+      <c r="T38" s="65"/>
+      <c r="U38" s="65"/>
+      <c r="V38" s="65"/>
+      <c r="W38" s="65"/>
+      <c r="X38" s="65"/>
+      <c r="Y38" s="65"/>
+      <c r="Z38" s="66"/>
+    </row>
+    <row r="40" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="C40" s="27" t="s">
+        <v>305</v>
+      </c>
+      <c r="D40" s="28"/>
+      <c r="E40" s="28"/>
+      <c r="F40" s="28"/>
+      <c r="G40" s="28"/>
+      <c r="H40" s="28"/>
+      <c r="I40" s="28"/>
+      <c r="J40" s="28"/>
+      <c r="K40" s="28"/>
+      <c r="L40" s="28"/>
+      <c r="M40" s="28"/>
+      <c r="N40" s="28"/>
+      <c r="O40" s="28"/>
+      <c r="P40" s="28"/>
+      <c r="Q40" s="28"/>
+      <c r="R40" s="28"/>
+      <c r="S40" s="28"/>
+      <c r="T40" s="28"/>
+      <c r="U40" s="28"/>
+      <c r="V40" s="28"/>
+      <c r="W40" s="28"/>
+      <c r="X40" s="28"/>
+      <c r="Y40" s="28"/>
+      <c r="Z40" s="29"/>
+    </row>
+    <row r="41" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="C41" s="30"/>
+      <c r="D41" s="31"/>
+      <c r="E41" s="31"/>
+      <c r="F41" s="31"/>
+      <c r="G41" s="31"/>
+      <c r="H41" s="31"/>
+      <c r="I41" s="31"/>
+      <c r="J41" s="31"/>
+      <c r="K41" s="31"/>
+      <c r="L41" s="31"/>
+      <c r="M41" s="31"/>
+      <c r="N41" s="31"/>
+      <c r="O41" s="31"/>
+      <c r="P41" s="31"/>
+      <c r="Q41" s="31"/>
+      <c r="R41" s="31"/>
+      <c r="S41" s="31"/>
+      <c r="T41" s="31"/>
+      <c r="U41" s="31"/>
+      <c r="V41" s="31"/>
+      <c r="W41" s="31"/>
+      <c r="X41" s="31"/>
+      <c r="Y41" s="31"/>
+      <c r="Z41" s="32"/>
+    </row>
+    <row r="43" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="D43" s="33" t="s">
+        <v>306</v>
+      </c>
+      <c r="E43" s="34"/>
+      <c r="F43" s="34"/>
+      <c r="G43" s="34"/>
+      <c r="H43" s="34"/>
+      <c r="I43" s="34"/>
+      <c r="J43" s="34"/>
+      <c r="K43" s="34"/>
+      <c r="L43" s="34"/>
+      <c r="M43" s="34"/>
+      <c r="N43" s="34"/>
+      <c r="O43" s="34"/>
+      <c r="P43" s="34"/>
+      <c r="Q43" s="34"/>
+      <c r="R43" s="34"/>
+      <c r="S43" s="34"/>
+      <c r="T43" s="34"/>
+      <c r="U43" s="34"/>
+      <c r="V43" s="34"/>
+      <c r="W43" s="34"/>
+      <c r="X43" s="34"/>
+      <c r="Y43" s="34"/>
+      <c r="Z43" s="35"/>
+    </row>
+    <row r="57" spans="4:26" x14ac:dyDescent="0.3">
+      <c r="D57" s="39">
+        <v>1</v>
+      </c>
+      <c r="E57" s="49" t="s">
+        <v>307</v>
+      </c>
+      <c r="F57" s="50"/>
+      <c r="G57" s="50"/>
+      <c r="H57" s="50"/>
+      <c r="I57" s="50"/>
+      <c r="J57" s="50"/>
+      <c r="K57" s="50"/>
+      <c r="L57" s="50"/>
+      <c r="M57" s="50"/>
+      <c r="N57" s="50"/>
+      <c r="O57" s="50"/>
+      <c r="P57" s="50"/>
+      <c r="Q57" s="50"/>
+      <c r="R57" s="50"/>
+      <c r="S57" s="50"/>
+      <c r="T57" s="50"/>
+      <c r="U57" s="50"/>
+      <c r="V57" s="50"/>
+      <c r="W57" s="50"/>
+      <c r="X57" s="50"/>
+      <c r="Y57" s="50"/>
+      <c r="Z57" s="51"/>
+    </row>
+    <row r="58" spans="4:26" x14ac:dyDescent="0.3">
+      <c r="D58" s="40"/>
+      <c r="E58" s="52" t="s">
+        <v>308</v>
+      </c>
+      <c r="F58" s="53"/>
+      <c r="G58" s="53"/>
+      <c r="H58" s="53"/>
+      <c r="I58" s="53"/>
+      <c r="J58" s="53"/>
+      <c r="K58" s="53"/>
+      <c r="L58" s="53"/>
+      <c r="M58" s="53"/>
+      <c r="N58" s="53"/>
+      <c r="O58" s="53"/>
+      <c r="P58" s="53"/>
+      <c r="Q58" s="53"/>
+      <c r="R58" s="53"/>
+      <c r="S58" s="53"/>
+      <c r="T58" s="53"/>
+      <c r="U58" s="53"/>
+      <c r="V58" s="53"/>
+      <c r="W58" s="53"/>
+      <c r="X58" s="53"/>
+      <c r="Y58" s="53"/>
+      <c r="Z58" s="54"/>
+    </row>
+    <row r="60" spans="4:26" x14ac:dyDescent="0.3">
+      <c r="D60" s="33" t="s">
+        <v>309</v>
+      </c>
+      <c r="E60" s="34"/>
+      <c r="F60" s="34"/>
+      <c r="G60" s="34"/>
+      <c r="H60" s="34"/>
+      <c r="I60" s="34"/>
+      <c r="J60" s="34"/>
+      <c r="K60" s="34"/>
+      <c r="L60" s="34"/>
+      <c r="M60" s="34"/>
+      <c r="N60" s="34"/>
+      <c r="O60" s="34"/>
+      <c r="P60" s="34"/>
+      <c r="Q60" s="34"/>
+      <c r="R60" s="34"/>
+      <c r="S60" s="34"/>
+      <c r="T60" s="34"/>
+      <c r="U60" s="34"/>
+      <c r="V60" s="34"/>
+      <c r="W60" s="34"/>
+      <c r="X60" s="34"/>
+      <c r="Y60" s="34"/>
+      <c r="Z60" s="35"/>
+    </row>
+    <row r="74" spans="4:26" x14ac:dyDescent="0.3">
+      <c r="D74" s="39">
+        <v>1</v>
+      </c>
+      <c r="E74" s="49" t="s">
+        <v>310</v>
+      </c>
+      <c r="F74" s="50"/>
+      <c r="G74" s="50"/>
+      <c r="H74" s="50"/>
+      <c r="I74" s="50"/>
+      <c r="J74" s="50"/>
+      <c r="K74" s="50"/>
+      <c r="L74" s="50"/>
+      <c r="M74" s="50"/>
+      <c r="N74" s="50"/>
+      <c r="O74" s="50"/>
+      <c r="P74" s="50"/>
+      <c r="Q74" s="50"/>
+      <c r="R74" s="50"/>
+      <c r="S74" s="50"/>
+      <c r="T74" s="50"/>
+      <c r="U74" s="50"/>
+      <c r="V74" s="50"/>
+      <c r="W74" s="50"/>
+      <c r="X74" s="50"/>
+      <c r="Y74" s="50"/>
+      <c r="Z74" s="51"/>
+    </row>
+    <row r="75" spans="4:26" x14ac:dyDescent="0.3">
+      <c r="D75" s="67"/>
+      <c r="E75" s="68" t="s">
+        <v>311</v>
+      </c>
+      <c r="F75" s="69"/>
+      <c r="G75" s="69"/>
+      <c r="H75" s="69"/>
+      <c r="I75" s="69"/>
+      <c r="J75" s="69"/>
+      <c r="K75" s="69"/>
+      <c r="L75" s="69"/>
+      <c r="M75" s="69"/>
+      <c r="N75" s="69"/>
+      <c r="O75" s="69"/>
+      <c r="P75" s="69"/>
+      <c r="Q75" s="69"/>
+      <c r="R75" s="69"/>
+      <c r="S75" s="69"/>
+      <c r="T75" s="69"/>
+      <c r="U75" s="69"/>
+      <c r="V75" s="69"/>
+      <c r="W75" s="69"/>
+      <c r="X75" s="69"/>
+      <c r="Y75" s="69"/>
+      <c r="Z75" s="70"/>
+    </row>
+    <row r="76" spans="4:26" x14ac:dyDescent="0.3">
+      <c r="D76" s="40"/>
+      <c r="E76" s="52" t="s">
+        <v>312</v>
+      </c>
+      <c r="F76" s="53"/>
+      <c r="G76" s="53"/>
+      <c r="H76" s="53"/>
+      <c r="I76" s="53"/>
+      <c r="J76" s="53"/>
+      <c r="K76" s="53"/>
+      <c r="L76" s="53"/>
+      <c r="M76" s="53"/>
+      <c r="N76" s="53"/>
+      <c r="O76" s="53"/>
+      <c r="P76" s="53"/>
+      <c r="Q76" s="53"/>
+      <c r="R76" s="53"/>
+      <c r="S76" s="53"/>
+      <c r="T76" s="53"/>
+      <c r="U76" s="53"/>
+      <c r="V76" s="53"/>
+      <c r="W76" s="53"/>
+      <c r="X76" s="53"/>
+      <c r="Y76" s="53"/>
+      <c r="Z76" s="54"/>
+    </row>
+    <row r="77" spans="4:26" x14ac:dyDescent="0.3">
+      <c r="D77" s="39">
+        <v>2</v>
+      </c>
+      <c r="E77" s="49" t="s">
+        <v>313</v>
+      </c>
+      <c r="F77" s="50"/>
+      <c r="G77" s="50"/>
+      <c r="H77" s="50"/>
+      <c r="I77" s="50"/>
+      <c r="J77" s="50"/>
+      <c r="K77" s="50"/>
+      <c r="L77" s="50"/>
+      <c r="M77" s="50"/>
+      <c r="N77" s="50"/>
+      <c r="O77" s="50"/>
+      <c r="P77" s="50"/>
+      <c r="Q77" s="50"/>
+      <c r="R77" s="50"/>
+      <c r="S77" s="50"/>
+      <c r="T77" s="50"/>
+      <c r="U77" s="50"/>
+      <c r="V77" s="50"/>
+      <c r="W77" s="50"/>
+      <c r="X77" s="50"/>
+      <c r="Y77" s="50"/>
+      <c r="Z77" s="51"/>
+    </row>
+    <row r="78" spans="4:26" x14ac:dyDescent="0.3">
+      <c r="D78" s="67"/>
+      <c r="E78" s="68" t="s">
+        <v>314</v>
+      </c>
+      <c r="F78" s="69"/>
+      <c r="G78" s="69"/>
+      <c r="H78" s="69"/>
+      <c r="I78" s="69"/>
+      <c r="J78" s="69"/>
+      <c r="K78" s="69"/>
+      <c r="L78" s="69"/>
+      <c r="M78" s="69"/>
+      <c r="N78" s="69"/>
+      <c r="O78" s="69"/>
+      <c r="P78" s="69"/>
+      <c r="Q78" s="69"/>
+      <c r="R78" s="69"/>
+      <c r="S78" s="69"/>
+      <c r="T78" s="69"/>
+      <c r="U78" s="69"/>
+      <c r="V78" s="69"/>
+      <c r="W78" s="69"/>
+      <c r="X78" s="69"/>
+      <c r="Y78" s="69"/>
+      <c r="Z78" s="70"/>
+    </row>
+    <row r="79" spans="4:26" x14ac:dyDescent="0.3">
+      <c r="D79" s="67"/>
+      <c r="E79" s="68" t="s">
+        <v>315</v>
+      </c>
+      <c r="F79" s="69"/>
+      <c r="G79" s="69"/>
+      <c r="H79" s="69"/>
+      <c r="I79" s="69"/>
+      <c r="J79" s="69"/>
+      <c r="K79" s="69"/>
+      <c r="L79" s="69"/>
+      <c r="M79" s="69"/>
+      <c r="N79" s="69"/>
+      <c r="O79" s="69"/>
+      <c r="P79" s="69"/>
+      <c r="Q79" s="69"/>
+      <c r="R79" s="69"/>
+      <c r="S79" s="69"/>
+      <c r="T79" s="69"/>
+      <c r="U79" s="69"/>
+      <c r="V79" s="69"/>
+      <c r="W79" s="69"/>
+      <c r="X79" s="69"/>
+      <c r="Y79" s="69"/>
+      <c r="Z79" s="70"/>
+    </row>
+    <row r="80" spans="4:26" x14ac:dyDescent="0.3">
+      <c r="D80" s="40"/>
+      <c r="E80" s="52" t="s">
+        <v>316</v>
+      </c>
+      <c r="F80" s="53"/>
+      <c r="G80" s="53"/>
+      <c r="H80" s="53"/>
+      <c r="I80" s="53"/>
+      <c r="J80" s="53"/>
+      <c r="K80" s="53"/>
+      <c r="L80" s="53"/>
+      <c r="M80" s="53"/>
+      <c r="N80" s="53"/>
+      <c r="O80" s="53"/>
+      <c r="P80" s="53"/>
+      <c r="Q80" s="53"/>
+      <c r="R80" s="53"/>
+      <c r="S80" s="53"/>
+      <c r="T80" s="53"/>
+      <c r="U80" s="53"/>
+      <c r="V80" s="53"/>
+      <c r="W80" s="53"/>
+      <c r="X80" s="53"/>
+      <c r="Y80" s="53"/>
+      <c r="Z80" s="54"/>
+    </row>
+    <row r="93" spans="4:26" x14ac:dyDescent="0.3">
+      <c r="D93" s="71" t="s">
+        <v>317</v>
+      </c>
+      <c r="E93" s="71"/>
+      <c r="F93" s="71"/>
+      <c r="G93" s="71"/>
+      <c r="H93" s="25" t="s">
+        <v>318</v>
+      </c>
+      <c r="I93" s="25"/>
+      <c r="J93" s="25"/>
+      <c r="K93" s="25"/>
+      <c r="L93" s="25"/>
+      <c r="M93" s="25"/>
+      <c r="N93" s="25"/>
+      <c r="O93" s="25"/>
+      <c r="P93" s="25"/>
+      <c r="Q93" s="25"/>
+      <c r="R93" s="25"/>
+      <c r="S93" s="25"/>
+      <c r="T93" s="25"/>
+      <c r="U93" s="25"/>
+      <c r="V93" s="25"/>
+      <c r="W93" s="25"/>
+      <c r="X93" s="25"/>
+      <c r="Y93" s="25"/>
+      <c r="Z93" s="25"/>
+    </row>
+    <row r="94" spans="4:26" x14ac:dyDescent="0.3">
+      <c r="D94" s="72" t="s">
+        <v>319</v>
+      </c>
+      <c r="E94" s="72"/>
+      <c r="F94" s="72"/>
+      <c r="G94" s="72"/>
+      <c r="H94" s="25" t="s">
+        <v>322</v>
+      </c>
+      <c r="I94" s="25"/>
+      <c r="J94" s="25"/>
+      <c r="K94" s="25"/>
+      <c r="L94" s="25"/>
+      <c r="M94" s="25"/>
+      <c r="N94" s="25"/>
+      <c r="O94" s="25"/>
+      <c r="P94" s="25"/>
+      <c r="Q94" s="25"/>
+      <c r="R94" s="25"/>
+      <c r="S94" s="25"/>
+      <c r="T94" s="25"/>
+      <c r="U94" s="25"/>
+      <c r="V94" s="25"/>
+      <c r="W94" s="25"/>
+      <c r="X94" s="25"/>
+      <c r="Y94" s="25"/>
+      <c r="Z94" s="25"/>
+    </row>
+    <row r="95" spans="4:26" x14ac:dyDescent="0.3">
+      <c r="D95" s="73" t="s">
+        <v>320</v>
+      </c>
+      <c r="E95" s="74"/>
+      <c r="F95" s="74"/>
+      <c r="G95" s="74"/>
+      <c r="H95" s="25" t="s">
+        <v>321</v>
+      </c>
+      <c r="I95" s="25"/>
+      <c r="J95" s="25"/>
+      <c r="K95" s="25"/>
+      <c r="L95" s="25"/>
+      <c r="M95" s="25"/>
+      <c r="N95" s="25"/>
+      <c r="O95" s="25"/>
+      <c r="P95" s="25"/>
+      <c r="Q95" s="25"/>
+      <c r="R95" s="25"/>
+      <c r="S95" s="25"/>
+      <c r="T95" s="25"/>
+      <c r="U95" s="25"/>
+      <c r="V95" s="25"/>
+      <c r="W95" s="25"/>
+      <c r="X95" s="25"/>
+      <c r="Y95" s="25"/>
+      <c r="Z95" s="25"/>
+    </row>
+    <row r="97" spans="4:26" x14ac:dyDescent="0.3">
+      <c r="D97" s="33" t="s">
+        <v>323</v>
+      </c>
+      <c r="E97" s="34"/>
+      <c r="F97" s="34"/>
+      <c r="G97" s="34"/>
+      <c r="H97" s="34"/>
+      <c r="I97" s="34"/>
+      <c r="J97" s="34"/>
+      <c r="K97" s="34"/>
+      <c r="L97" s="34"/>
+      <c r="M97" s="34"/>
+      <c r="N97" s="34"/>
+      <c r="O97" s="34"/>
+      <c r="P97" s="34"/>
+      <c r="Q97" s="34"/>
+      <c r="R97" s="34"/>
+      <c r="S97" s="34"/>
+      <c r="T97" s="34"/>
+      <c r="U97" s="34"/>
+      <c r="V97" s="34"/>
+      <c r="W97" s="34"/>
+      <c r="X97" s="34"/>
+      <c r="Y97" s="34"/>
+      <c r="Z97" s="35"/>
+    </row>
+    <row r="111" spans="4:26" x14ac:dyDescent="0.3">
+      <c r="D111" s="39">
+        <v>1</v>
+      </c>
+      <c r="E111" s="49" t="s">
+        <v>324</v>
+      </c>
+      <c r="F111" s="50"/>
+      <c r="G111" s="50"/>
+      <c r="H111" s="50"/>
+      <c r="I111" s="50"/>
+      <c r="J111" s="50"/>
+      <c r="K111" s="50"/>
+      <c r="L111" s="50"/>
+      <c r="M111" s="50"/>
+      <c r="N111" s="50"/>
+      <c r="O111" s="50"/>
+      <c r="P111" s="50"/>
+      <c r="Q111" s="50"/>
+      <c r="R111" s="50"/>
+      <c r="S111" s="50"/>
+      <c r="T111" s="50"/>
+      <c r="U111" s="50"/>
+      <c r="V111" s="50"/>
+      <c r="W111" s="50"/>
+      <c r="X111" s="50"/>
+      <c r="Y111" s="50"/>
+      <c r="Z111" s="51"/>
+    </row>
+    <row r="112" spans="4:26" x14ac:dyDescent="0.3">
+      <c r="D112" s="40"/>
+      <c r="E112" s="52" t="s">
+        <v>325</v>
+      </c>
+      <c r="F112" s="53"/>
+      <c r="G112" s="53"/>
+      <c r="H112" s="53"/>
+      <c r="I112" s="53"/>
+      <c r="J112" s="53"/>
+      <c r="K112" s="53"/>
+      <c r="L112" s="53"/>
+      <c r="M112" s="53"/>
+      <c r="N112" s="53"/>
+      <c r="O112" s="53"/>
+      <c r="P112" s="53"/>
+      <c r="Q112" s="53"/>
+      <c r="R112" s="53"/>
+      <c r="S112" s="53"/>
+      <c r="T112" s="53"/>
+      <c r="U112" s="53"/>
+      <c r="V112" s="53"/>
+      <c r="W112" s="53"/>
+      <c r="X112" s="53"/>
+      <c r="Y112" s="53"/>
+      <c r="Z112" s="54"/>
+    </row>
+    <row r="114" spans="4:26" x14ac:dyDescent="0.3">
+      <c r="D114" s="33" t="s">
+        <v>326</v>
+      </c>
+      <c r="E114" s="34"/>
+      <c r="F114" s="34"/>
+      <c r="G114" s="34"/>
+      <c r="H114" s="34"/>
+      <c r="I114" s="34"/>
+      <c r="J114" s="34"/>
+      <c r="K114" s="34"/>
+      <c r="L114" s="34"/>
+      <c r="M114" s="34"/>
+      <c r="N114" s="34"/>
+      <c r="O114" s="34"/>
+      <c r="P114" s="34"/>
+      <c r="Q114" s="34"/>
+      <c r="R114" s="34"/>
+      <c r="S114" s="34"/>
+      <c r="T114" s="34"/>
+      <c r="U114" s="34"/>
+      <c r="V114" s="34"/>
+      <c r="W114" s="34"/>
+      <c r="X114" s="34"/>
+      <c r="Y114" s="34"/>
+      <c r="Z114" s="35"/>
+    </row>
+    <row r="128" spans="4:26" x14ac:dyDescent="0.3">
+      <c r="D128" s="10" t="s">
+        <v>327</v>
+      </c>
+      <c r="E128" s="11"/>
+      <c r="F128" s="11"/>
+      <c r="G128" s="11"/>
+      <c r="H128" s="11"/>
+      <c r="I128" s="11"/>
+      <c r="J128" s="11"/>
+      <c r="K128" s="11"/>
+      <c r="L128" s="11"/>
+      <c r="M128" s="11"/>
+      <c r="N128" s="11"/>
+      <c r="O128" s="11"/>
+      <c r="P128" s="11"/>
+      <c r="Q128" s="11"/>
+      <c r="R128" s="11"/>
+      <c r="S128" s="11"/>
+      <c r="T128" s="11"/>
+      <c r="U128" s="11"/>
+      <c r="V128" s="11"/>
+      <c r="W128" s="11"/>
+      <c r="X128" s="11"/>
+      <c r="Y128" s="11"/>
+      <c r="Z128" s="12"/>
+    </row>
+    <row r="129" spans="4:26" x14ac:dyDescent="0.3">
+      <c r="D129" s="13"/>
+      <c r="E129" s="9">
+        <v>1</v>
+      </c>
+      <c r="F129" s="69" t="s">
+        <v>328</v>
+      </c>
+      <c r="G129" s="69"/>
+      <c r="H129" s="69"/>
+      <c r="I129" s="69"/>
+      <c r="J129" s="69"/>
+      <c r="K129" s="69"/>
+      <c r="L129" s="69"/>
+      <c r="M129" s="69"/>
+      <c r="N129" s="69"/>
+      <c r="O129" s="69"/>
+      <c r="P129" s="69"/>
+      <c r="Q129" s="69"/>
+      <c r="R129" s="69"/>
+      <c r="S129" s="69"/>
+      <c r="T129" s="14"/>
+      <c r="U129" s="14"/>
+      <c r="V129" s="14"/>
+      <c r="W129" s="14"/>
+      <c r="X129" s="14"/>
+      <c r="Y129" s="14"/>
+      <c r="Z129" s="15"/>
+    </row>
+    <row r="130" spans="4:26" x14ac:dyDescent="0.3">
+      <c r="D130" s="13"/>
+      <c r="E130" s="9">
+        <v>2</v>
+      </c>
+      <c r="F130" s="69" t="s">
+        <v>329</v>
+      </c>
+      <c r="G130" s="69"/>
+      <c r="H130" s="69"/>
+      <c r="I130" s="69"/>
+      <c r="J130" s="69"/>
+      <c r="K130" s="69"/>
+      <c r="L130" s="69"/>
+      <c r="M130" s="69"/>
+      <c r="N130" s="69"/>
+      <c r="O130" s="69"/>
+      <c r="P130" s="69"/>
+      <c r="Q130" s="69"/>
+      <c r="R130" s="69"/>
+      <c r="S130" s="69"/>
+      <c r="T130" s="14"/>
+      <c r="U130" s="14"/>
+      <c r="V130" s="14"/>
+      <c r="W130" s="14"/>
+      <c r="X130" s="14"/>
+      <c r="Y130" s="14"/>
+      <c r="Z130" s="15"/>
+    </row>
+    <row r="131" spans="4:26" x14ac:dyDescent="0.3">
+      <c r="D131" s="16" t="s">
+        <v>330</v>
+      </c>
+      <c r="E131" s="17"/>
+      <c r="F131" s="17"/>
+      <c r="G131" s="17"/>
+      <c r="H131" s="17"/>
+      <c r="I131" s="17"/>
+      <c r="J131" s="17"/>
+      <c r="K131" s="17"/>
+      <c r="L131" s="17"/>
+      <c r="M131" s="17"/>
+      <c r="N131" s="17"/>
+      <c r="O131" s="17"/>
+      <c r="P131" s="17"/>
+      <c r="Q131" s="17"/>
+      <c r="R131" s="17"/>
+      <c r="S131" s="17"/>
+      <c r="T131" s="17"/>
+      <c r="U131" s="17"/>
+      <c r="V131" s="17"/>
+      <c r="W131" s="17"/>
+      <c r="X131" s="17"/>
+      <c r="Y131" s="17"/>
+      <c r="Z131" s="18"/>
+    </row>
+    <row r="132" spans="4:26" x14ac:dyDescent="0.3">
+      <c r="D132" s="14"/>
+      <c r="E132" s="14"/>
+      <c r="F132" s="14"/>
+      <c r="G132" s="14"/>
+      <c r="H132" s="14"/>
+      <c r="I132" s="14"/>
+      <c r="J132" s="14"/>
+      <c r="K132" s="14"/>
+      <c r="L132" s="14"/>
+      <c r="M132" s="14"/>
+      <c r="N132" s="14"/>
+      <c r="O132" s="14"/>
+      <c r="P132" s="14"/>
+      <c r="Q132" s="14"/>
+      <c r="R132" s="14"/>
+      <c r="S132" s="14"/>
+      <c r="T132" s="14"/>
+      <c r="U132" s="14"/>
+      <c r="V132" s="14"/>
+      <c r="W132" s="14"/>
+      <c r="X132" s="14"/>
+      <c r="Y132" s="14"/>
+      <c r="Z132" s="14"/>
+    </row>
+    <row r="156" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="D156" s="49" t="s">
+        <v>331</v>
+      </c>
+      <c r="E156" s="50"/>
+      <c r="F156" s="50"/>
+      <c r="G156" s="50"/>
+      <c r="H156" s="50"/>
+      <c r="I156" s="50"/>
+      <c r="J156" s="50"/>
+      <c r="K156" s="50"/>
+      <c r="L156" s="50"/>
+      <c r="M156" s="50"/>
+      <c r="N156" s="50"/>
+      <c r="O156" s="50"/>
+      <c r="P156" s="50"/>
+      <c r="Q156" s="50"/>
+      <c r="R156" s="50"/>
+      <c r="S156" s="50"/>
+      <c r="T156" s="50"/>
+      <c r="U156" s="50"/>
+      <c r="V156" s="50"/>
+      <c r="W156" s="50"/>
+      <c r="X156" s="50"/>
+      <c r="Y156" s="50"/>
+      <c r="Z156" s="51"/>
+    </row>
+    <row r="157" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="D157" s="68" t="s">
+        <v>332</v>
+      </c>
+      <c r="E157" s="69"/>
+      <c r="F157" s="69"/>
+      <c r="G157" s="69"/>
+      <c r="H157" s="69"/>
+      <c r="I157" s="69"/>
+      <c r="J157" s="69"/>
+      <c r="K157" s="69"/>
+      <c r="L157" s="69"/>
+      <c r="M157" s="69"/>
+      <c r="N157" s="69"/>
+      <c r="O157" s="69"/>
+      <c r="P157" s="69"/>
+      <c r="Q157" s="69"/>
+      <c r="R157" s="69"/>
+      <c r="S157" s="69"/>
+      <c r="T157" s="69"/>
+      <c r="U157" s="69"/>
+      <c r="V157" s="69"/>
+      <c r="W157" s="69"/>
+      <c r="X157" s="69"/>
+      <c r="Y157" s="69"/>
+      <c r="Z157" s="70"/>
+    </row>
+    <row r="158" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="D158" s="52" t="s">
+        <v>333</v>
+      </c>
+      <c r="E158" s="53"/>
+      <c r="F158" s="53"/>
+      <c r="G158" s="53"/>
+      <c r="H158" s="53"/>
+      <c r="I158" s="53"/>
+      <c r="J158" s="53"/>
+      <c r="K158" s="53"/>
+      <c r="L158" s="53"/>
+      <c r="M158" s="53"/>
+      <c r="N158" s="53"/>
+      <c r="O158" s="53"/>
+      <c r="P158" s="53"/>
+      <c r="Q158" s="53"/>
+      <c r="R158" s="53"/>
+      <c r="S158" s="53"/>
+      <c r="T158" s="53"/>
+      <c r="U158" s="53"/>
+      <c r="V158" s="53"/>
+      <c r="W158" s="53"/>
+      <c r="X158" s="53"/>
+      <c r="Y158" s="53"/>
+      <c r="Z158" s="54"/>
+    </row>
+    <row r="160" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="C160" s="27" t="s">
+        <v>337</v>
+      </c>
+      <c r="D160" s="28"/>
+      <c r="E160" s="28"/>
+      <c r="F160" s="28"/>
+      <c r="G160" s="28"/>
+      <c r="H160" s="28"/>
+      <c r="I160" s="28"/>
+      <c r="J160" s="28"/>
+      <c r="K160" s="28"/>
+      <c r="L160" s="28"/>
+      <c r="M160" s="28"/>
+      <c r="N160" s="28"/>
+      <c r="O160" s="28"/>
+      <c r="P160" s="28"/>
+      <c r="Q160" s="28"/>
+      <c r="R160" s="28"/>
+      <c r="S160" s="28"/>
+      <c r="T160" s="28"/>
+      <c r="U160" s="28"/>
+      <c r="V160" s="28"/>
+      <c r="W160" s="28"/>
+      <c r="X160" s="28"/>
+      <c r="Y160" s="28"/>
+      <c r="Z160" s="29"/>
+    </row>
+    <row r="161" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="C161" s="30"/>
+      <c r="D161" s="31"/>
+      <c r="E161" s="31"/>
+      <c r="F161" s="31"/>
+      <c r="G161" s="31"/>
+      <c r="H161" s="31"/>
+      <c r="I161" s="31"/>
+      <c r="J161" s="31"/>
+      <c r="K161" s="31"/>
+      <c r="L161" s="31"/>
+      <c r="M161" s="31"/>
+      <c r="N161" s="31"/>
+      <c r="O161" s="31"/>
+      <c r="P161" s="31"/>
+      <c r="Q161" s="31"/>
+      <c r="R161" s="31"/>
+      <c r="S161" s="31"/>
+      <c r="T161" s="31"/>
+      <c r="U161" s="31"/>
+      <c r="V161" s="31"/>
+      <c r="W161" s="31"/>
+      <c r="X161" s="31"/>
+      <c r="Y161" s="31"/>
+      <c r="Z161" s="32"/>
+    </row>
+    <row r="175" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="D175" s="49" t="s">
+        <v>334</v>
+      </c>
+      <c r="E175" s="50"/>
+      <c r="F175" s="50"/>
+      <c r="G175" s="50"/>
+      <c r="H175" s="50"/>
+      <c r="I175" s="50"/>
+      <c r="J175" s="50"/>
+      <c r="K175" s="50"/>
+      <c r="L175" s="50"/>
+      <c r="M175" s="50"/>
+      <c r="N175" s="50"/>
+      <c r="O175" s="50"/>
+      <c r="P175" s="50"/>
+      <c r="Q175" s="50"/>
+      <c r="R175" s="50"/>
+      <c r="S175" s="50"/>
+      <c r="T175" s="50"/>
+      <c r="U175" s="50"/>
+      <c r="V175" s="50"/>
+      <c r="W175" s="50"/>
+      <c r="X175" s="50"/>
+      <c r="Y175" s="50"/>
+      <c r="Z175" s="51"/>
+    </row>
+    <row r="176" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="D176" s="52" t="s">
+        <v>338</v>
+      </c>
+      <c r="E176" s="53"/>
+      <c r="F176" s="53"/>
+      <c r="G176" s="53"/>
+      <c r="H176" s="53"/>
+      <c r="I176" s="53"/>
+      <c r="J176" s="53"/>
+      <c r="K176" s="53"/>
+      <c r="L176" s="53"/>
+      <c r="M176" s="53"/>
+      <c r="N176" s="53"/>
+      <c r="O176" s="53"/>
+      <c r="P176" s="53"/>
+      <c r="Q176" s="53"/>
+      <c r="R176" s="53"/>
+      <c r="S176" s="53"/>
+      <c r="T176" s="53"/>
+      <c r="U176" s="53"/>
+      <c r="V176" s="53"/>
+      <c r="W176" s="53"/>
+      <c r="X176" s="53"/>
+      <c r="Y176" s="53"/>
+      <c r="Z176" s="54"/>
+    </row>
+    <row r="189" spans="4:26" x14ac:dyDescent="0.3">
+      <c r="D189" s="49" t="s">
+        <v>339</v>
+      </c>
+      <c r="E189" s="50"/>
+      <c r="F189" s="50"/>
+      <c r="G189" s="50"/>
+      <c r="H189" s="50"/>
+      <c r="I189" s="50"/>
+      <c r="J189" s="50"/>
+      <c r="K189" s="50"/>
+      <c r="L189" s="50"/>
+      <c r="M189" s="50"/>
+      <c r="N189" s="50"/>
+      <c r="O189" s="50"/>
+      <c r="P189" s="50"/>
+      <c r="Q189" s="50"/>
+      <c r="R189" s="50"/>
+      <c r="S189" s="50"/>
+      <c r="T189" s="50"/>
+      <c r="U189" s="50"/>
+      <c r="V189" s="50"/>
+      <c r="W189" s="50"/>
+      <c r="X189" s="50"/>
+      <c r="Y189" s="50"/>
+      <c r="Z189" s="51"/>
+    </row>
+    <row r="190" spans="4:26" x14ac:dyDescent="0.3">
+      <c r="D190" s="52" t="s">
+        <v>340</v>
+      </c>
+      <c r="E190" s="53"/>
+      <c r="F190" s="53"/>
+      <c r="G190" s="53"/>
+      <c r="H190" s="53"/>
+      <c r="I190" s="53"/>
+      <c r="J190" s="53"/>
+      <c r="K190" s="53"/>
+      <c r="L190" s="53"/>
+      <c r="M190" s="53"/>
+      <c r="N190" s="53"/>
+      <c r="O190" s="53"/>
+      <c r="P190" s="53"/>
+      <c r="Q190" s="53"/>
+      <c r="R190" s="53"/>
+      <c r="S190" s="53"/>
+      <c r="T190" s="53"/>
+      <c r="U190" s="53"/>
+      <c r="V190" s="53"/>
+      <c r="W190" s="53"/>
+      <c r="X190" s="53"/>
+      <c r="Y190" s="53"/>
+      <c r="Z190" s="54"/>
+    </row>
+    <row r="192" spans="4:26" x14ac:dyDescent="0.3">
+      <c r="D192" s="49" t="s">
+        <v>341</v>
+      </c>
+      <c r="E192" s="50"/>
+      <c r="F192" s="50"/>
+      <c r="G192" s="50"/>
+      <c r="H192" s="50"/>
+      <c r="I192" s="50"/>
+      <c r="J192" s="50"/>
+      <c r="K192" s="50"/>
+      <c r="L192" s="50"/>
+      <c r="M192" s="50"/>
+      <c r="N192" s="50"/>
+      <c r="O192" s="50"/>
+      <c r="P192" s="50"/>
+      <c r="Q192" s="50"/>
+      <c r="R192" s="50"/>
+      <c r="S192" s="50"/>
+      <c r="T192" s="50"/>
+      <c r="U192" s="50"/>
+      <c r="V192" s="50"/>
+      <c r="W192" s="50"/>
+      <c r="X192" s="50"/>
+      <c r="Y192" s="50"/>
+      <c r="Z192" s="51"/>
+    </row>
+    <row r="193" spans="2:26" x14ac:dyDescent="0.3">
+      <c r="D193" s="52" t="s">
+        <v>342</v>
+      </c>
+      <c r="E193" s="53"/>
+      <c r="F193" s="53"/>
+      <c r="G193" s="53"/>
+      <c r="H193" s="53"/>
+      <c r="I193" s="53"/>
+      <c r="J193" s="53"/>
+      <c r="K193" s="53"/>
+      <c r="L193" s="53"/>
+      <c r="M193" s="53"/>
+      <c r="N193" s="53"/>
+      <c r="O193" s="53"/>
+      <c r="P193" s="53"/>
+      <c r="Q193" s="53"/>
+      <c r="R193" s="53"/>
+      <c r="S193" s="53"/>
+      <c r="T193" s="53"/>
+      <c r="U193" s="53"/>
+      <c r="V193" s="53"/>
+      <c r="W193" s="53"/>
+      <c r="X193" s="53"/>
+      <c r="Y193" s="53"/>
+      <c r="Z193" s="54"/>
+    </row>
+    <row r="195" spans="2:26" x14ac:dyDescent="0.3">
+      <c r="B195" s="55" t="s">
+        <v>343</v>
+      </c>
+      <c r="C195" s="56"/>
+      <c r="D195" s="56"/>
+      <c r="E195" s="56"/>
+      <c r="F195" s="56"/>
+      <c r="G195" s="56"/>
+      <c r="H195" s="56"/>
+      <c r="I195" s="56"/>
+      <c r="J195" s="56"/>
+      <c r="K195" s="56"/>
+      <c r="L195" s="56"/>
+      <c r="M195" s="56"/>
+      <c r="N195" s="56"/>
+      <c r="O195" s="56"/>
+      <c r="P195" s="56"/>
+      <c r="Q195" s="56"/>
+      <c r="R195" s="56"/>
+      <c r="S195" s="56"/>
+      <c r="T195" s="56"/>
+      <c r="U195" s="56"/>
+      <c r="V195" s="56"/>
+      <c r="W195" s="56"/>
+      <c r="X195" s="56"/>
+      <c r="Y195" s="56"/>
+      <c r="Z195" s="57"/>
+    </row>
+    <row r="196" spans="2:26" x14ac:dyDescent="0.3">
+      <c r="B196" s="58"/>
+      <c r="C196" s="59"/>
+      <c r="D196" s="59"/>
+      <c r="E196" s="59"/>
+      <c r="F196" s="59"/>
+      <c r="G196" s="59"/>
+      <c r="H196" s="59"/>
+      <c r="I196" s="59"/>
+      <c r="J196" s="59"/>
+      <c r="K196" s="59"/>
+      <c r="L196" s="59"/>
+      <c r="M196" s="59"/>
+      <c r="N196" s="59"/>
+      <c r="O196" s="59"/>
+      <c r="P196" s="59"/>
+      <c r="Q196" s="59"/>
+      <c r="R196" s="59"/>
+      <c r="S196" s="59"/>
+      <c r="T196" s="59"/>
+      <c r="U196" s="59"/>
+      <c r="V196" s="59"/>
+      <c r="W196" s="59"/>
+      <c r="X196" s="59"/>
+      <c r="Y196" s="59"/>
+      <c r="Z196" s="60"/>
+    </row>
+    <row r="197" spans="2:26" x14ac:dyDescent="0.3">
+      <c r="B197" s="61"/>
+      <c r="C197" s="62"/>
+      <c r="D197" s="62"/>
+      <c r="E197" s="62"/>
+      <c r="F197" s="62"/>
+      <c r="G197" s="62"/>
+      <c r="H197" s="62"/>
+      <c r="I197" s="62"/>
+      <c r="J197" s="62"/>
+      <c r="K197" s="62"/>
+      <c r="L197" s="62"/>
+      <c r="M197" s="62"/>
+      <c r="N197" s="62"/>
+      <c r="O197" s="62"/>
+      <c r="P197" s="62"/>
+      <c r="Q197" s="62"/>
+      <c r="R197" s="62"/>
+      <c r="S197" s="62"/>
+      <c r="T197" s="62"/>
+      <c r="U197" s="62"/>
+      <c r="V197" s="62"/>
+      <c r="W197" s="62"/>
+      <c r="X197" s="62"/>
+      <c r="Y197" s="62"/>
+      <c r="Z197" s="63"/>
+    </row>
+  </sheetData>
+  <mergeCells count="58">
+    <mergeCell ref="F130:S130"/>
+    <mergeCell ref="D156:Z156"/>
+    <mergeCell ref="D157:Z157"/>
+    <mergeCell ref="D158:Z158"/>
+    <mergeCell ref="F129:S129"/>
+    <mergeCell ref="E79:Z79"/>
+    <mergeCell ref="E80:Z80"/>
+    <mergeCell ref="D77:D80"/>
+    <mergeCell ref="D93:G93"/>
+    <mergeCell ref="D94:G94"/>
+    <mergeCell ref="D95:G95"/>
+    <mergeCell ref="H93:Z93"/>
+    <mergeCell ref="H94:Z94"/>
+    <mergeCell ref="H95:Z95"/>
+    <mergeCell ref="E78:Z78"/>
+    <mergeCell ref="D97:Z97"/>
+    <mergeCell ref="E111:Z111"/>
+    <mergeCell ref="E112:Z112"/>
+    <mergeCell ref="D111:D112"/>
+    <mergeCell ref="D114:Z114"/>
+    <mergeCell ref="D74:D76"/>
+    <mergeCell ref="E74:Z74"/>
+    <mergeCell ref="E75:Z75"/>
+    <mergeCell ref="E76:Z76"/>
+    <mergeCell ref="E77:Z77"/>
+    <mergeCell ref="C40:Z41"/>
+    <mergeCell ref="D43:Z43"/>
+    <mergeCell ref="D60:Z60"/>
+    <mergeCell ref="D57:D58"/>
+    <mergeCell ref="E57:Z57"/>
+    <mergeCell ref="E58:Z58"/>
+    <mergeCell ref="C33:C34"/>
+    <mergeCell ref="C35:C36"/>
+    <mergeCell ref="J35:Z35"/>
+    <mergeCell ref="J36:Z36"/>
+    <mergeCell ref="D37:I37"/>
+    <mergeCell ref="J37:Z37"/>
+    <mergeCell ref="D38:Z38"/>
+    <mergeCell ref="D33:I34"/>
+    <mergeCell ref="D35:I36"/>
+    <mergeCell ref="J31:Z31"/>
+    <mergeCell ref="J32:Z32"/>
+    <mergeCell ref="J33:Z33"/>
+    <mergeCell ref="J34:Z34"/>
+    <mergeCell ref="B2:Z4"/>
+    <mergeCell ref="V6:Z6"/>
+    <mergeCell ref="C16:Z17"/>
+    <mergeCell ref="C28:Z29"/>
+    <mergeCell ref="D31:I32"/>
+    <mergeCell ref="C31:C32"/>
+    <mergeCell ref="D192:Z192"/>
+    <mergeCell ref="D193:Z193"/>
+    <mergeCell ref="B195:Z197"/>
+    <mergeCell ref="C160:Z161"/>
+    <mergeCell ref="D175:Z175"/>
+    <mergeCell ref="D176:Z176"/>
+    <mergeCell ref="D189:Z189"/>
+    <mergeCell ref="D190:Z190"/>
+  </mergeCells>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A49"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>345</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A2:AA29"/>
+  <sheetFormatPr defaultColWidth="2.875" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="27" width="2.875" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:26" x14ac:dyDescent="0.3">
+      <c r="B2" s="27" t="s">
+        <v>344</v>
+      </c>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
+      <c r="I2" s="28"/>
+      <c r="J2" s="28"/>
+      <c r="K2" s="28"/>
+      <c r="L2" s="28"/>
+      <c r="M2" s="28"/>
+      <c r="N2" s="28"/>
+      <c r="O2" s="28"/>
+      <c r="P2" s="28"/>
+      <c r="Q2" s="28"/>
+      <c r="R2" s="28"/>
+      <c r="S2" s="28"/>
+      <c r="T2" s="28"/>
+      <c r="U2" s="28"/>
+      <c r="V2" s="28"/>
+      <c r="W2" s="28"/>
+      <c r="X2" s="28"/>
+      <c r="Y2" s="28"/>
+      <c r="Z2" s="29"/>
+    </row>
+    <row r="3" spans="2:26" x14ac:dyDescent="0.3">
+      <c r="B3" s="36"/>
+      <c r="C3" s="37"/>
+      <c r="D3" s="37"/>
+      <c r="E3" s="37"/>
+      <c r="F3" s="37"/>
+      <c r="G3" s="37"/>
+      <c r="H3" s="37"/>
+      <c r="I3" s="37"/>
+      <c r="J3" s="37"/>
+      <c r="K3" s="37"/>
+      <c r="L3" s="37"/>
+      <c r="M3" s="37"/>
+      <c r="N3" s="37"/>
+      <c r="O3" s="37"/>
+      <c r="P3" s="37"/>
+      <c r="Q3" s="37"/>
+      <c r="R3" s="37"/>
+      <c r="S3" s="37"/>
+      <c r="T3" s="37"/>
+      <c r="U3" s="37"/>
+      <c r="V3" s="37"/>
+      <c r="W3" s="37"/>
+      <c r="X3" s="37"/>
+      <c r="Y3" s="37"/>
+      <c r="Z3" s="38"/>
+    </row>
+    <row r="4" spans="2:26" x14ac:dyDescent="0.3">
+      <c r="B4" s="30"/>
+      <c r="C4" s="31"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
+      <c r="H4" s="31"/>
+      <c r="I4" s="31"/>
+      <c r="J4" s="31"/>
+      <c r="K4" s="31"/>
+      <c r="L4" s="31"/>
+      <c r="M4" s="31"/>
+      <c r="N4" s="31"/>
+      <c r="O4" s="31"/>
+      <c r="P4" s="31"/>
+      <c r="Q4" s="31"/>
+      <c r="R4" s="31"/>
+      <c r="S4" s="31"/>
+      <c r="T4" s="31"/>
+      <c r="U4" s="31"/>
+      <c r="V4" s="31"/>
+      <c r="W4" s="31"/>
+      <c r="X4" s="31"/>
+      <c r="Y4" s="31"/>
+      <c r="Z4" s="32"/>
+    </row>
+    <row r="6" spans="2:26" x14ac:dyDescent="0.3">
+      <c r="V6" s="33" t="s">
+        <v>202</v>
+      </c>
+      <c r="W6" s="34"/>
+      <c r="X6" s="34"/>
+      <c r="Y6" s="34"/>
+      <c r="Z6" s="35"/>
+    </row>
+    <row r="8" spans="2:26" x14ac:dyDescent="0.3">
+      <c r="C8" s="2" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="10" spans="2:26" x14ac:dyDescent="0.3">
+      <c r="D10" s="2">
+        <v>1</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="11" spans="2:26" x14ac:dyDescent="0.3">
+      <c r="D11" s="2">
+        <v>2</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="12" spans="2:26" x14ac:dyDescent="0.3">
+      <c r="D12" s="2">
+        <v>3</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="13" spans="2:26" x14ac:dyDescent="0.3">
+      <c r="E13" s="23" t="s">
+        <v>335</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="14" spans="2:26" x14ac:dyDescent="0.3">
+      <c r="D14" s="2">
+        <v>4</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="16" spans="2:26" x14ac:dyDescent="0.3">
+      <c r="C16" s="27" t="s">
+        <v>346</v>
+      </c>
+      <c r="D16" s="28"/>
+      <c r="E16" s="28"/>
+      <c r="F16" s="28"/>
+      <c r="G16" s="28"/>
+      <c r="H16" s="28"/>
+      <c r="I16" s="28"/>
+      <c r="J16" s="28"/>
+      <c r="K16" s="28"/>
+      <c r="L16" s="28"/>
+      <c r="M16" s="28"/>
+      <c r="N16" s="28"/>
+      <c r="O16" s="28"/>
+      <c r="P16" s="28"/>
+      <c r="Q16" s="28"/>
+      <c r="R16" s="28"/>
+      <c r="S16" s="28"/>
+      <c r="T16" s="28"/>
+      <c r="U16" s="28"/>
+      <c r="V16" s="28"/>
+      <c r="W16" s="28"/>
+      <c r="X16" s="28"/>
+      <c r="Y16" s="28"/>
+      <c r="Z16" s="29"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="C17" s="30"/>
+      <c r="D17" s="31"/>
+      <c r="E17" s="31"/>
+      <c r="F17" s="31"/>
+      <c r="G17" s="31"/>
+      <c r="H17" s="31"/>
+      <c r="I17" s="31"/>
+      <c r="J17" s="31"/>
+      <c r="K17" s="31"/>
+      <c r="L17" s="31"/>
+      <c r="M17" s="31"/>
+      <c r="N17" s="31"/>
+      <c r="O17" s="31"/>
+      <c r="P17" s="31"/>
+      <c r="Q17" s="31"/>
+      <c r="R17" s="31"/>
+      <c r="S17" s="31"/>
+      <c r="T17" s="31"/>
+      <c r="U17" s="31"/>
+      <c r="V17" s="31"/>
+      <c r="W17" s="31"/>
+      <c r="X17" s="31"/>
+      <c r="Y17" s="31"/>
+      <c r="Z17" s="32"/>
+    </row>
+    <row r="19" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="D19" s="22">
+        <v>1</v>
+      </c>
+      <c r="E19" s="26" t="s">
+        <v>347</v>
+      </c>
+      <c r="F19" s="26"/>
+      <c r="G19" s="26"/>
+      <c r="H19" s="26"/>
+      <c r="I19" s="26"/>
+      <c r="J19" s="26"/>
+      <c r="K19" s="26"/>
+      <c r="L19" s="26"/>
+      <c r="M19" s="26"/>
+      <c r="N19" s="26"/>
+      <c r="O19" s="26"/>
+      <c r="P19" s="26"/>
+      <c r="Q19" s="26"/>
+      <c r="R19" s="26"/>
+      <c r="S19" s="26"/>
+      <c r="T19" s="26"/>
+      <c r="U19" s="26"/>
+      <c r="V19" s="26"/>
+      <c r="W19" s="26"/>
+      <c r="X19" s="26"/>
+      <c r="Y19" s="26"/>
+      <c r="Z19" s="26"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="D20" s="22">
+        <v>2</v>
+      </c>
+      <c r="E20" s="26" t="s">
+        <v>348</v>
+      </c>
+      <c r="F20" s="26"/>
+      <c r="G20" s="26"/>
+      <c r="H20" s="26"/>
+      <c r="I20" s="26"/>
+      <c r="J20" s="26"/>
+      <c r="K20" s="26"/>
+      <c r="L20" s="26"/>
+      <c r="M20" s="26"/>
+      <c r="N20" s="26"/>
+      <c r="O20" s="26"/>
+      <c r="P20" s="26"/>
+      <c r="Q20" s="26"/>
+      <c r="R20" s="26"/>
+      <c r="S20" s="26"/>
+      <c r="T20" s="26"/>
+      <c r="U20" s="26"/>
+      <c r="V20" s="26"/>
+      <c r="W20" s="26"/>
+      <c r="X20" s="26"/>
+      <c r="Y20" s="26"/>
+      <c r="Z20" s="26"/>
+    </row>
+    <row r="21" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="D21" s="22">
+        <v>3</v>
+      </c>
+      <c r="E21" s="26" t="s">
+        <v>349</v>
+      </c>
+      <c r="F21" s="26"/>
+      <c r="G21" s="26"/>
+      <c r="H21" s="26"/>
+      <c r="I21" s="26"/>
+      <c r="J21" s="26"/>
+      <c r="K21" s="26"/>
+      <c r="L21" s="26"/>
+      <c r="M21" s="26"/>
+      <c r="N21" s="26"/>
+      <c r="O21" s="26"/>
+      <c r="P21" s="26"/>
+      <c r="Q21" s="26"/>
+      <c r="R21" s="26"/>
+      <c r="S21" s="26"/>
+      <c r="T21" s="26"/>
+      <c r="U21" s="26"/>
+      <c r="V21" s="26"/>
+      <c r="W21" s="26"/>
+      <c r="X21" s="26"/>
+      <c r="Y21" s="26"/>
+      <c r="Z21" s="26"/>
+    </row>
+    <row r="22" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="D22" s="25">
+        <v>4</v>
+      </c>
+      <c r="E22" s="49" t="s">
+        <v>350</v>
+      </c>
+      <c r="F22" s="50"/>
+      <c r="G22" s="50"/>
+      <c r="H22" s="50"/>
+      <c r="I22" s="50"/>
+      <c r="J22" s="50"/>
+      <c r="K22" s="50"/>
+      <c r="L22" s="50"/>
+      <c r="M22" s="50"/>
+      <c r="N22" s="50"/>
+      <c r="O22" s="50"/>
+      <c r="P22" s="50"/>
+      <c r="Q22" s="50"/>
+      <c r="R22" s="50"/>
+      <c r="S22" s="50"/>
+      <c r="T22" s="50"/>
+      <c r="U22" s="50"/>
+      <c r="V22" s="50"/>
+      <c r="W22" s="50"/>
+      <c r="X22" s="50"/>
+      <c r="Y22" s="50"/>
+      <c r="Z22" s="51"/>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="D23" s="25"/>
+      <c r="E23" s="52" t="s">
+        <v>351</v>
+      </c>
+      <c r="F23" s="53"/>
+      <c r="G23" s="53"/>
+      <c r="H23" s="53"/>
+      <c r="I23" s="53"/>
+      <c r="J23" s="53"/>
+      <c r="K23" s="53"/>
+      <c r="L23" s="53"/>
+      <c r="M23" s="53"/>
+      <c r="N23" s="53"/>
+      <c r="O23" s="53"/>
+      <c r="P23" s="53"/>
+      <c r="Q23" s="53"/>
+      <c r="R23" s="53"/>
+      <c r="S23" s="53"/>
+      <c r="T23" s="53"/>
+      <c r="U23" s="53"/>
+      <c r="V23" s="53"/>
+      <c r="W23" s="53"/>
+      <c r="X23" s="53"/>
+      <c r="Y23" s="53"/>
+      <c r="Z23" s="54"/>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="C26" s="27" t="s">
+        <v>352</v>
+      </c>
+      <c r="D26" s="28"/>
+      <c r="E26" s="28"/>
+      <c r="F26" s="28"/>
+      <c r="G26" s="28"/>
+      <c r="H26" s="28"/>
+      <c r="I26" s="28"/>
+      <c r="J26" s="28"/>
+      <c r="K26" s="28"/>
+      <c r="L26" s="28"/>
+      <c r="M26" s="28"/>
+      <c r="N26" s="28"/>
+      <c r="O26" s="28"/>
+      <c r="P26" s="28"/>
+      <c r="Q26" s="28"/>
+      <c r="R26" s="28"/>
+      <c r="S26" s="28"/>
+      <c r="T26" s="28"/>
+      <c r="U26" s="28"/>
+      <c r="V26" s="28"/>
+      <c r="W26" s="28"/>
+      <c r="X26" s="28"/>
+      <c r="Y26" s="28"/>
+      <c r="Z26" s="29"/>
+    </row>
+    <row r="27" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="C27" s="30"/>
+      <c r="D27" s="31"/>
+      <c r="E27" s="31"/>
+      <c r="F27" s="31"/>
+      <c r="G27" s="31"/>
+      <c r="H27" s="31"/>
+      <c r="I27" s="31"/>
+      <c r="J27" s="31"/>
+      <c r="K27" s="31"/>
+      <c r="L27" s="31"/>
+      <c r="M27" s="31"/>
+      <c r="N27" s="31"/>
+      <c r="O27" s="31"/>
+      <c r="P27" s="31"/>
+      <c r="Q27" s="31"/>
+      <c r="R27" s="31"/>
+      <c r="S27" s="31"/>
+      <c r="T27" s="31"/>
+      <c r="U27" s="31"/>
+      <c r="V27" s="31"/>
+      <c r="W27" s="31"/>
+      <c r="X27" s="31"/>
+      <c r="Y27" s="31"/>
+      <c r="Z27" s="32"/>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="D29" s="2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="C26:Z27"/>
+    <mergeCell ref="B2:Z4"/>
+    <mergeCell ref="V6:Z6"/>
+    <mergeCell ref="C16:Z17"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="E19:Z19"/>
+    <mergeCell ref="E20:Z20"/>
+    <mergeCell ref="E21:Z21"/>
+    <mergeCell ref="E22:Z22"/>
+    <mergeCell ref="E23:Z23"/>
+  </mergeCells>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>